--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -72,8 +72,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:AH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -465,6 +465,18 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="73" customWidth="1" min="31" max="31"/>
+    <col width="66" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -578,6 +590,66 @@
           <t>最新日期</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>所属板块</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>板块当日涨跌幅%</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>板块5日涨跌幅%</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>趋势得分(0-25)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>量能得分(0-17)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>板块得分(0-12)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>风险扣分</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>综合评分(0-100)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>评分明细_趋势</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>评分明细_量能</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>评分明细_板块</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>评分明细_风险</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -585,32 +657,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>224.46</v>
+        <v>34.9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>19.22</v>
+        <v>5.76</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>4.67</v>
+        <v>17.31</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-10.19</v>
       </c>
       <c r="H2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.92</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -619,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>16.11</v>
+        <v>9.57</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -627,30 +699,30 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>超买区间</t>
+        <v>66.09999999999999</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>24.14</v>
+        <v>20.65</v>
       </c>
       <c r="P2" t="n">
-        <v>12.84</v>
+        <v>16.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>195.64</v>
+        <v>29.28</v>
       </c>
       <c r="R2" t="n">
-        <v>193.32</v>
+        <v>31.85</v>
       </c>
       <c r="S2" t="n">
-        <v>263.21</v>
+        <v>46.46</v>
       </c>
       <c r="T2" t="n">
-        <v>125.61</v>
+        <v>23.2</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>4</v>
@@ -658,6 +730,41 @@
       <c r="V2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -667,32 +774,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>128.25</v>
+        <v>224.46</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>15.02</v>
+        <v>19.22</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>-13.29</v>
+        <v>20.8</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>4.67</v>
       </c>
       <c r="H3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.26</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -701,7 +808,7 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>6.27</v>
+        <v>16.11</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -709,30 +816,30 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>71.5</v>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>超买区间</t>
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>9.1</v>
+        <v>24.14</v>
       </c>
       <c r="P3" t="n">
-        <v>10.03</v>
+        <v>12.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>115.39</v>
+        <v>195.64</v>
       </c>
       <c r="R3" t="n">
-        <v>120.68</v>
+        <v>193.32</v>
       </c>
       <c r="S3" t="n">
-        <v>158.2</v>
+        <v>263.21</v>
       </c>
       <c r="T3" t="n">
-        <v>94.73</v>
+        <v>125.61</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>4</v>
@@ -740,6 +847,41 @@
       <c r="V3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -749,32 +891,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>200.86</v>
+        <v>96.09</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11.59</v>
+        <v>7.59</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>24.37</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>-24.94</v>
+        <v>2.88</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-29.22</v>
       </c>
       <c r="H4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.14</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -783,15 +925,15 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>4.57</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>48.8</v>
+        <v>67.3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -799,22 +941,22 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>27.71</v>
+        <v>6.22</v>
       </c>
       <c r="P4" t="n">
-        <v>12.03</v>
+        <v>10.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>176.69</v>
+        <v>85.61</v>
       </c>
       <c r="R4" t="n">
-        <v>199.1</v>
+        <v>91.89</v>
       </c>
       <c r="S4" t="n">
-        <v>284.85</v>
+        <v>144.2</v>
       </c>
       <c r="T4" t="n">
-        <v>102.3</v>
+        <v>69.8</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>4</v>
@@ -822,6 +964,41 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -831,28 +1008,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>96.09</v>
+        <v>167.65</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7.59</v>
+        <v>1.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>-29.22</v>
+        <v>4.11</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-34.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -865,7 +1042,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4.57</v>
+        <v>0.4</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -873,7 +1050,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>67.3</v>
+        <v>58.8</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -881,22 +1058,22 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>6.22</v>
+        <v>7.45</v>
       </c>
       <c r="P5" t="n">
-        <v>10.91</v>
+        <v>12.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>85.61</v>
+        <v>146.5</v>
       </c>
       <c r="R5" t="n">
-        <v>91.89</v>
+        <v>166.98</v>
       </c>
       <c r="S5" t="n">
-        <v>144.2</v>
+        <v>325.74</v>
       </c>
       <c r="T5" t="n">
-        <v>69.8</v>
+        <v>133.61</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>4</v>
@@ -904,6 +1081,41 @@
       <c r="V5" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>37</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -913,28 +1125,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>34.9</v>
+        <v>128.25</v>
       </c>
       <c r="E6" s="2" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>5.76</v>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>17.31</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>-10.19</v>
+      <c r="G6" s="3" t="n">
+        <v>-13.29</v>
       </c>
       <c r="H6" t="n">
-        <v>1.92</v>
+        <v>1.21</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -947,7 +1159,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>9.57</v>
+        <v>6.27</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -955,7 +1167,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>66.09999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -963,22 +1175,22 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>20.65</v>
+        <v>9.1</v>
       </c>
       <c r="P6" t="n">
-        <v>16.09</v>
+        <v>10.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>29.28</v>
+        <v>115.39</v>
       </c>
       <c r="R6" t="n">
-        <v>31.85</v>
+        <v>120.68</v>
       </c>
       <c r="S6" t="n">
-        <v>46.46</v>
+        <v>158.2</v>
       </c>
       <c r="T6" t="n">
-        <v>23.2</v>
+        <v>94.73</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>4</v>
@@ -986,6 +1198,41 @@
       <c r="V6" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；OBV创20日新高</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -995,32 +1242,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>167.65</v>
+        <v>200.86</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.7</v>
+        <v>11.59</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>-34.2</v>
+        <v>24.37</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-24.94</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.93</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1029,15 +1276,15 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>0.88</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>58.8</v>
+        <v>48.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1045,22 +1292,22 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>7.45</v>
+        <v>27.71</v>
       </c>
       <c r="P7" t="n">
-        <v>12.62</v>
+        <v>12.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>146.5</v>
+        <v>176.69</v>
       </c>
       <c r="R7" t="n">
-        <v>166.98</v>
+        <v>199.1</v>
       </c>
       <c r="S7" t="n">
-        <v>325.74</v>
+        <v>284.85</v>
       </c>
       <c r="T7" t="n">
-        <v>133.61</v>
+        <v>102.3</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>4</v>
@@ -1068,6 +1315,41 @@
       <c r="V7" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1091,10 +1373,10 @@
       <c r="E8" s="2" t="n">
         <v>9.59</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="3" t="n">
         <v>-5.6</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="3" t="n">
         <v>-27.25</v>
       </c>
       <c r="H8" t="n">
@@ -1126,7 +1408,7 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="O8" s="3" t="n">
         <v>-2.26</v>
       </c>
       <c r="P8" t="n">
@@ -1150,6 +1432,41 @@
       <c r="V8" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1173,10 +1490,10 @@
       <c r="E9" s="2" t="n">
         <v>5.91</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="3" t="n">
         <v>-6.21</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="3" t="n">
         <v>-31.17</v>
       </c>
       <c r="H9" t="n">
@@ -1208,7 +1525,7 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="O9" s="3" t="n">
         <v>-2.87</v>
       </c>
       <c r="P9" t="n">
@@ -1232,6 +1549,41 @@
       <c r="V9" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1241,30 +1593,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>402.73</v>
+        <v>194.42</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>-43.44</v>
+        <v>8.82</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-28.78</v>
       </c>
       <c r="H10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
+        <v>1.09</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1274,8 +1626,8 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K10" s="4" t="n">
-        <v>-2.27</v>
+      <c r="K10" s="3" t="n">
+        <v>-0.08</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1283,37 +1635,72 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>2.49</v>
+      <c r="O10" s="3" t="n">
+        <v>-1.91</v>
       </c>
       <c r="P10" t="n">
-        <v>10.65</v>
+        <v>10.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>359.84</v>
+        <v>173.29</v>
       </c>
       <c r="R10" t="n">
-        <v>412.09</v>
+        <v>194.57</v>
       </c>
       <c r="S10" t="n">
-        <v>980</v>
+        <v>280.08</v>
       </c>
       <c r="T10" t="n">
-        <v>334</v>
+        <v>161.8</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1323,30 +1710,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55.39</v>
+        <v>402.73</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>-20.63</v>
+        <v>2.92</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-43.44</v>
       </c>
       <c r="H11" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
+        <v>0.83</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1356,8 +1743,8 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K11" s="4" t="n">
-        <v>-0.76</v>
+      <c r="K11" s="3" t="n">
+        <v>-2.27</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1365,7 +1752,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>55.8</v>
+        <v>50.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1373,22 +1760,22 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>1.24</v>
+        <v>2.49</v>
       </c>
       <c r="P11" t="n">
-        <v>7.95</v>
+        <v>10.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>50.99</v>
+        <v>359.84</v>
       </c>
       <c r="R11" t="n">
-        <v>55.82</v>
+        <v>412.09</v>
       </c>
       <c r="S11" t="n">
-        <v>76.16</v>
+        <v>980</v>
       </c>
       <c r="T11" t="n">
-        <v>51.88</v>
+        <v>334</v>
       </c>
       <c r="U11" t="n">
         <v>3</v>
@@ -1396,6 +1783,41 @@
       <c r="V11" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1405,28 +1827,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64.92</v>
+        <v>103.88</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>-36.91</v>
+        <v>8.66</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-41.49</v>
       </c>
       <c r="H12" t="n">
-        <v>0.67</v>
+        <v>1.46</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1438,8 +1860,8 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K12" s="4" t="n">
-        <v>-1.79</v>
+      <c r="K12" s="3" t="n">
+        <v>-0.13</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1447,37 +1869,72 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>55.3</v>
+        <v>50.7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>3.28</v>
+      <c r="O12" s="3" t="n">
+        <v>-2.04</v>
       </c>
       <c r="P12" t="n">
-        <v>10.06</v>
+        <v>10.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>58.39</v>
+        <v>92.73</v>
       </c>
       <c r="R12" t="n">
-        <v>66.09999999999999</v>
+        <v>104.01</v>
       </c>
       <c r="S12" t="n">
-        <v>108.05</v>
+        <v>187.66</v>
       </c>
       <c r="T12" t="n">
-        <v>47.3</v>
+        <v>90.23</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1944,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>194.42</v>
+        <v>177.36</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>-5.25</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>-28.78</v>
+        <v>5.76</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-7.39</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-33.37</v>
       </c>
       <c r="H13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.95</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1520,8 +1977,8 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K13" s="4" t="n">
-        <v>-0.08</v>
+      <c r="K13" s="3" t="n">
+        <v>-0.3</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -1529,30 +1986,30 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>50.6</v>
+        <v>58.8</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O13" s="4" t="n">
-        <v>-1.91</v>
+      <c r="O13" s="3" t="n">
+        <v>-4.05</v>
       </c>
       <c r="P13" t="n">
-        <v>10.87</v>
+        <v>11.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>173.29</v>
+        <v>156.95</v>
       </c>
       <c r="R13" t="n">
-        <v>194.57</v>
+        <v>177.89</v>
       </c>
       <c r="S13" t="n">
-        <v>280.08</v>
+        <v>279</v>
       </c>
       <c r="T13" t="n">
-        <v>161.8</v>
+        <v>152.33</v>
       </c>
       <c r="U13" t="n">
         <v>2</v>
@@ -1560,6 +2017,41 @@
       <c r="V13" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1569,28 +2061,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>103.88</v>
+        <v>261.96</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>-41.49</v>
+        <v>5.33</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-22.17</v>
       </c>
       <c r="H14" t="n">
-        <v>1.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1602,39 +2094,39 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K14" s="4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+      <c r="K14" s="3" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>50.7</v>
+        <v>57</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O14" s="4" t="n">
-        <v>-2.04</v>
+      <c r="O14" s="2" t="n">
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>10.73</v>
+        <v>12.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>92.73</v>
+        <v>228.52</v>
       </c>
       <c r="R14" t="n">
-        <v>104.01</v>
+        <v>263.62</v>
       </c>
       <c r="S14" t="n">
-        <v>187.66</v>
+        <v>346</v>
       </c>
       <c r="T14" t="n">
-        <v>90.23</v>
+        <v>155.55</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
@@ -1642,6 +2134,41 @@
       <c r="V14" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1651,32 +2178,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>177.36</v>
+        <v>55.39</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>-7.39</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>-33.37</v>
+        <v>2.01</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-20.63</v>
       </c>
       <c r="H15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.78</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1684,8 +2211,8 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K15" s="4" t="n">
-        <v>-0.3</v>
+      <c r="K15" s="3" t="n">
+        <v>-0.76</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -1693,37 +2220,72 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>58.8</v>
+        <v>55.8</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O15" s="4" t="n">
-        <v>-4.05</v>
+      <c r="O15" s="2" t="n">
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>11.51</v>
+        <v>7.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>156.95</v>
+        <v>50.99</v>
       </c>
       <c r="R15" t="n">
-        <v>177.89</v>
+        <v>55.82</v>
       </c>
       <c r="S15" t="n">
-        <v>279</v>
+        <v>76.16</v>
       </c>
       <c r="T15" t="n">
-        <v>152.33</v>
+        <v>51.88</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1733,28 +2295,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>261.96</v>
+        <v>64.92</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>-22.17</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-36.91</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1766,16 +2328,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K16" s="4" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+      <c r="K16" s="3" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>57</v>
+        <v>55.3</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1783,29 +2345,64 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1.19</v>
+        <v>3.28</v>
       </c>
       <c r="P16" t="n">
-        <v>12.77</v>
+        <v>10.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>228.52</v>
+        <v>58.39</v>
       </c>
       <c r="R16" t="n">
-        <v>263.62</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>346</v>
+        <v>108.05</v>
       </c>
       <c r="T16" t="n">
-        <v>155.55</v>
+        <v>47.3</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1815,30 +2412,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>58.02</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>-16.86</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>-46.31</v>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-27.69</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-42.58</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1848,46 +2445,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K17" s="4" t="n">
-        <v>-4.41</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+      <c r="K17" s="3" t="n">
+        <v>-14.71</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>-13.52</v>
+        <v>14.2</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>-24.35</v>
       </c>
       <c r="P17" t="n">
-        <v>15.34</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>49.12</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>60.7</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>115.44</v>
+        <v>167.15</v>
       </c>
       <c r="T17" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
+        <v>83.12</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1908,13 +2540,13 @@
       <c r="D18" t="n">
         <v>60.55</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="3" t="n">
         <v>-5.26</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>6.06</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="3" t="n">
         <v>-18.58</v>
       </c>
       <c r="H18" t="n">
@@ -1930,10 +2562,10 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="K18" s="3" t="n">
         <v>-1.36</v>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>死叉(转空)</t>
         </is>
@@ -1970,6 +2602,41 @@
       <c r="V18" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1979,30 +2646,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>230.46</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>-25.94</v>
+        <v>24.67</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-10.36</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-33.03</v>
       </c>
       <c r="H19" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
+        <v>0.68</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2012,46 +2679,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K19" s="4" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+      <c r="K19" s="3" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>40.2</v>
+        <v>46.7</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O19" s="4" t="n">
-        <v>-6.6</v>
+      <c r="O19" s="3" t="n">
+        <v>-7.02</v>
       </c>
       <c r="P19" t="n">
-        <v>11.37</v>
+        <v>8.31</v>
       </c>
       <c r="Q19" t="n">
-        <v>204.25</v>
+        <v>22.62</v>
       </c>
       <c r="R19" t="n">
-        <v>241.07</v>
+        <v>26.13</v>
       </c>
       <c r="S19" t="n">
-        <v>418.99</v>
+        <v>42.08</v>
       </c>
       <c r="T19" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U19" s="4" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2061,30 +2763,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>-7.88</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>-15.04</v>
+        <v>339.55</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-16.46</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-41.23</v>
       </c>
       <c r="H20" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
+        <v>0.68</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2094,46 +2796,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K20" s="4" t="n">
-        <v>-6.12</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+      <c r="K20" s="3" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>39.3</v>
+        <v>38.7</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O20" s="4" t="n">
-        <v>-4.54</v>
+      <c r="O20" s="3" t="n">
+        <v>-13.12</v>
       </c>
       <c r="P20" t="n">
-        <v>8.85</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>52.87</v>
+        <v>311.38</v>
       </c>
       <c r="R20" t="n">
-        <v>61.78</v>
+        <v>370.18</v>
       </c>
       <c r="S20" t="n">
-        <v>84.7</v>
+        <v>749.88</v>
       </c>
       <c r="T20" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="U20" s="4" t="n">
+        <v>308</v>
+      </c>
+      <c r="U20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2143,32 +2880,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67.73999999999999</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>-13.94</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>-18.32</v>
+        <v>36.77</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-14.09</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-25.75</v>
       </c>
       <c r="H21" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.98</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2176,46 +2913,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K21" s="4" t="n">
-        <v>-8.529999999999999</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="K21" s="3" t="n">
+        <v>-13.57</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>32.6</v>
+        <v>35.9</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O21" s="4" t="n">
-        <v>-10.6</v>
+      <c r="O21" s="3" t="n">
+        <v>-1.65</v>
       </c>
       <c r="P21" t="n">
-        <v>8.630000000000001</v>
+        <v>14.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>61.89</v>
+        <v>31.56</v>
       </c>
       <c r="R21" t="n">
-        <v>74.05</v>
+        <v>42.54</v>
       </c>
       <c r="S21" t="n">
-        <v>113.87</v>
+        <v>52.92</v>
       </c>
       <c r="T21" t="n">
-        <v>60.84</v>
-      </c>
-      <c r="U21" s="4" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="U21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2225,30 +2997,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>24.67</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>-10.36</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>-33.03</v>
+        <v>230.46</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>-9.94</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-25.94</v>
       </c>
       <c r="H22" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
+        <v>0.65</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2258,46 +3030,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K22" s="4" t="n">
-        <v>-5.57</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>死叉(转空)</t>
+      <c r="K22" s="3" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>46.7</v>
+        <v>40.2</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O22" s="4" t="n">
-        <v>-7.02</v>
+      <c r="O22" s="3" t="n">
+        <v>-6.6</v>
       </c>
       <c r="P22" t="n">
-        <v>8.31</v>
+        <v>11.37</v>
       </c>
       <c r="Q22" t="n">
-        <v>22.62</v>
+        <v>204.25</v>
       </c>
       <c r="R22" t="n">
-        <v>26.13</v>
+        <v>241.07</v>
       </c>
       <c r="S22" t="n">
-        <v>42.08</v>
+        <v>418.99</v>
       </c>
       <c r="T22" t="n">
-        <v>23.93</v>
-      </c>
-      <c r="U22" s="4" t="n">
+        <v>183.83</v>
+      </c>
+      <c r="U22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2307,30 +3114,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>82.25</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>-7.96</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>-7.25</v>
+        <v>58.02</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-16.86</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-46.31</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
+        <v>0.9</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2340,46 +3147,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K23" s="4" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+      <c r="K23" s="3" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>50.2</v>
+        <v>47.4</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O23" s="4" t="n">
-        <v>-4.62</v>
+      <c r="O23" s="3" t="n">
+        <v>-13.52</v>
       </c>
       <c r="P23" t="n">
-        <v>5.1</v>
+        <v>15.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>78.06</v>
+        <v>49.12</v>
       </c>
       <c r="R23" t="n">
-        <v>84.8</v>
+        <v>60.7</v>
       </c>
       <c r="S23" t="n">
-        <v>113</v>
+        <v>115.44</v>
       </c>
       <c r="T23" t="n">
-        <v>80.55</v>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>1</v>
+        <v>53.35</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2389,30 +3231,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>339.55</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>-16.46</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>-41.23</v>
+        <v>58</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-7.88</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-15.04</v>
       </c>
       <c r="H24" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
+        <v>0.58</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2422,46 +3264,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K24" s="4" t="n">
-        <v>-8.27</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>死叉(转空)</t>
+      <c r="K24" s="3" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>38.7</v>
+        <v>39.3</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O24" s="4" t="n">
-        <v>-13.12</v>
+      <c r="O24" s="3" t="n">
+        <v>-4.54</v>
       </c>
       <c r="P24" t="n">
-        <v>8.300000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>311.38</v>
+        <v>52.87</v>
       </c>
       <c r="R24" t="n">
-        <v>370.18</v>
+        <v>61.78</v>
       </c>
       <c r="S24" t="n">
-        <v>749.88</v>
+        <v>84.7</v>
       </c>
       <c r="T24" t="n">
-        <v>308</v>
-      </c>
-      <c r="U24" s="4" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="U24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2471,30 +3348,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>52.04</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>-3.06</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>-13.01</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>-37.24</v>
+        <v>67.73999999999999</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-13.94</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-18.32</v>
       </c>
       <c r="H25" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
+        <v>0.61</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2504,46 +3381,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K25" s="4" t="n">
-        <v>-9.390000000000001</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="K25" s="3" t="n">
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>30.6</v>
+        <v>32.6</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O25" s="4" t="n">
-        <v>-9.67</v>
+      <c r="O25" s="3" t="n">
+        <v>-10.6</v>
       </c>
       <c r="P25" t="n">
-        <v>10.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>46.33</v>
+        <v>61.89</v>
       </c>
       <c r="R25" t="n">
-        <v>57.44</v>
+        <v>74.05</v>
       </c>
       <c r="S25" t="n">
-        <v>107.55</v>
+        <v>113.87</v>
       </c>
       <c r="T25" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U25" s="4" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="U25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2553,30 +3465,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>180.3</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>-11.61</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0.47</v>
+        <v>82.25</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-7.96</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-7.25</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2586,46 +3498,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K26" s="4" t="n">
-        <v>-3.82</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>死叉(转空)</t>
+      <c r="K26" s="3" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>54.2</v>
+        <v>50.2</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O26" s="4" t="n">
-        <v>-8.27</v>
+      <c r="O26" s="3" t="n">
+        <v>-4.62</v>
       </c>
       <c r="P26" t="n">
-        <v>9.1</v>
+        <v>5.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>163.88</v>
+        <v>78.06</v>
       </c>
       <c r="R26" t="n">
-        <v>187.46</v>
+        <v>84.8</v>
       </c>
       <c r="S26" t="n">
-        <v>232.68</v>
+        <v>113</v>
       </c>
       <c r="T26" t="n">
-        <v>170.1</v>
-      </c>
-      <c r="U26" s="4" t="n">
+        <v>80.55</v>
+      </c>
+      <c r="U26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2635,32 +3582,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>36.77</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>-14.09</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>-4.99</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>-25.75</v>
+        <v>52.04</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-13.01</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-37.24</v>
       </c>
       <c r="H27" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.62</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2668,46 +3615,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K27" s="4" t="n">
-        <v>-13.57</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="K27" s="3" t="n">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>35.9</v>
+        <v>30.6</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O27" s="4" t="n">
-        <v>-1.65</v>
+      <c r="O27" s="3" t="n">
+        <v>-9.67</v>
       </c>
       <c r="P27" t="n">
-        <v>14.18</v>
+        <v>10.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>31.56</v>
+        <v>46.33</v>
       </c>
       <c r="R27" t="n">
-        <v>42.54</v>
+        <v>57.44</v>
       </c>
       <c r="S27" t="n">
-        <v>52.92</v>
+        <v>107.55</v>
       </c>
       <c r="T27" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="U27" s="4" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="U27" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2717,30 +3699,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32.31</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>-4.49</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>-17.93</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>-37.27</v>
+        <v>180.3</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>-11.61</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0.47</v>
       </c>
       <c r="H28" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
+        <v>0.6</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2750,46 +3732,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K28" s="4" t="n">
-        <v>-9.960000000000001</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+      <c r="K28" s="3" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v>-14.59</v>
+        <v>54.2</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>-8.27</v>
       </c>
       <c r="P28" t="n">
-        <v>6.77</v>
+        <v>9.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>30.12</v>
+        <v>163.88</v>
       </c>
       <c r="R28" t="n">
-        <v>35.89</v>
+        <v>187.46</v>
       </c>
       <c r="S28" t="n">
-        <v>56.81</v>
+        <v>232.68</v>
       </c>
       <c r="T28" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="U28" s="4" t="n">
-        <v>0</v>
+        <v>170.1</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>近5日上涨日成交量大于下跌日</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2799,30 +3816,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>-4.56</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>-27.69</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>-42.58</v>
+        <v>32.31</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-17.93</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-37.27</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
+        <v>0.62</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2832,46 +3849,81 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K29" s="4" t="n">
-        <v>-14.71</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="K29" s="3" t="n">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
+        <v>16.9</v>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O29" s="4" t="n">
-        <v>-24.35</v>
+      <c r="O29" s="3" t="n">
+        <v>-14.59</v>
       </c>
       <c r="P29" t="n">
-        <v>9.539999999999999</v>
+        <v>6.77</v>
       </c>
       <c r="Q29" t="n">
-        <v>76.34999999999999</v>
+        <v>30.12</v>
       </c>
       <c r="R29" t="n">
-        <v>98.95999999999999</v>
+        <v>35.89</v>
       </c>
       <c r="S29" t="n">
-        <v>167.15</v>
+        <v>56.81</v>
       </c>
       <c r="T29" t="n">
-        <v>83.12</v>
-      </c>
-      <c r="U29" s="4" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="U29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>无明显信号</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>量能温和(0.8-1.2倍)</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>无板块数据或无明显信号</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2886,7 +3938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2899,7 +3951,7 @@
           <t>重要说明</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>本报表所有指标基于公开技术分析公式计算，是历史价格的客观统计描述，不构成投资建议，不保证未来表现。是否建仓、仓位大小、止损位设置，最终需要你自己判断和承担风险。</t>
         </is>
@@ -3038,6 +4090,93 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>0-5分，统计多头排列/MACD偏多/RSI中性/站上20日线/跑赢大盘 这5项各是否成立，分数越高代表当前技术面信号偏多，仅供参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <f>= 量化打分引擎(0-100) ==</f>
+        <v/>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>参考常见的多因子选股框架，把趋势/量能/板块拆解成具体加分项。只实现了个股趋势、量能、板块相对表现三大模块和部分风险扣分项，不含大盘环境和集合竞价模块，分数换算到0-100仅为直观比较，不能和以后补全全部模块的分数直接对比。评分高不等于上涨概率高，两者是不同概念，仅供参考，不构成投资建议。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>趋势得分(0-25)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>均线多头排列/站上20日线/均线向上/突破20日或60日新高/跑赢大盘/合理乖离幅度 等信号加总</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>量能得分(0-17)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>成交量倍数/换手率合理分位/上涨放量/近5日量价关系/OBV创新高 等信号加总</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>板块得分(0-12)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>所属申万行业板块当日及5日涨跌幅、个股是否跑赢所属板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>风险扣分</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3日涨幅过大/严重偏离20日均线/换手率处于历史极端分位 等风险信号扣分</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>综合评分(0-100)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>(趋势得分+量能得分+板块得分-风险扣分)/54 换算成的0-100分，分数越高代表当前技术面信号越集中偏多，不是上涨概率，仅供参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>评分明细_XX</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>具体触发了哪些加分/扣分项，方便理解分数是怎么来的</t>
         </is>
       </c>
     </row>

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -465,7 +465,7 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
@@ -732,6 +732,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W2" t="n">
+        <v>640209</v>
+      </c>
       <c r="Z2" t="n">
         <v>17</v>
       </c>
@@ -849,6 +852,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W3" t="n">
+        <v>730206</v>
+      </c>
       <c r="Z3" t="n">
         <v>14</v>
       </c>
@@ -966,6 +972,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W4" t="n">
+        <v>650201</v>
+      </c>
       <c r="Z4" t="n">
         <v>15</v>
       </c>
@@ -1083,6 +1092,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W5" t="n">
+        <v>270401</v>
+      </c>
       <c r="Z5" t="n">
         <v>15</v>
       </c>
@@ -1200,6 +1212,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W6" t="n">
+        <v>270202</v>
+      </c>
       <c r="Z6" t="n">
         <v>14</v>
       </c>
@@ -1317,6 +1332,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W7" t="n">
+        <v>730204</v>
+      </c>
       <c r="Z7" t="n">
         <v>13</v>
       </c>
@@ -1434,6 +1452,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W8" t="n">
+        <v>730204</v>
+      </c>
       <c r="Z8" t="n">
         <v>7</v>
       </c>
@@ -1551,6 +1572,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W9" t="n">
+        <v>640703</v>
+      </c>
       <c r="Z9" t="n">
         <v>12</v>
       </c>
@@ -1668,6 +1692,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W10" t="n">
+        <v>270202</v>
+      </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
@@ -1785,6 +1812,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W11" t="n">
+        <v>270104</v>
+      </c>
       <c r="Z11" t="n">
         <v>3</v>
       </c>
@@ -1902,6 +1932,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W12" t="n">
+        <v>640703</v>
+      </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
@@ -2019,6 +2052,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W13" t="n">
+        <v>730204</v>
+      </c>
       <c r="Z13" t="n">
         <v>5</v>
       </c>
@@ -2136,6 +2172,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W14" t="n">
+        <v>730204</v>
+      </c>
       <c r="Z14" t="n">
         <v>3</v>
       </c>
@@ -2253,6 +2292,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W15" t="n">
+        <v>270504</v>
+      </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
@@ -2370,6 +2412,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W16" t="n">
+        <v>270303</v>
+      </c>
       <c r="Z16" t="n">
         <v>3</v>
       </c>
@@ -2487,6 +2532,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W17" t="n">
+        <v>630503</v>
+      </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
@@ -2604,6 +2652,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W18" t="n">
+        <v>640209</v>
+      </c>
       <c r="Z18" t="n">
         <v>3</v>
       </c>
@@ -2721,6 +2772,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W19" t="n">
+        <v>270303</v>
+      </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
@@ -2838,6 +2892,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W20" t="n">
+        <v>270104</v>
+      </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
@@ -2955,6 +3012,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W21" t="n">
+        <v>270504</v>
+      </c>
       <c r="Z21" t="n">
         <v>3</v>
       </c>
@@ -3072,6 +3132,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W22" t="n">
+        <v>270103</v>
+      </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
@@ -3189,6 +3252,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W23" t="n">
+        <v>270203</v>
+      </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
@@ -3306,6 +3372,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W24" t="n">
+        <v>270107</v>
+      </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
@@ -3423,6 +3492,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W25" t="n">
+        <v>270107</v>
+      </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
@@ -3540,6 +3612,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W26" t="n">
+        <v>710101</v>
+      </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
@@ -3657,6 +3732,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W27" t="n">
+        <v>640108</v>
+      </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
@@ -3774,6 +3852,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="W28" t="n">
+        <v>270104</v>
+      </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
@@ -3890,6 +3971,9 @@
         <is>
           <t>2026-09-11</t>
         </is>
+      </c>
+      <c r="W29" t="n">
+        <v>630702</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,8 +473,8 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="73" customWidth="1" min="31" max="31"/>
-    <col width="66" customWidth="1" min="32" max="32"/>
+    <col width="74" customWidth="1" min="31" max="31"/>
+    <col width="43" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34.9</v>
+        <v>36.7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5.76</v>
+        <v>2.2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>17.31</v>
+        <v>20.41</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-10.19</v>
+        <v>-5.24</v>
       </c>
       <c r="H2" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>9.57</v>
+        <v>14.11</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>66.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>20.65</v>
+        <v>25.92</v>
       </c>
       <c r="P2" t="n">
-        <v>16.09</v>
+        <v>15.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>29.28</v>
+        <v>31.06</v>
       </c>
       <c r="R2" t="n">
-        <v>31.85</v>
+        <v>32.16</v>
       </c>
       <c r="S2" t="n">
         <v>46.46</v>
@@ -729,17 +729,17 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>640209</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -748,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -786,19 +786,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.46</v>
+        <v>218.88</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.22</v>
+        <v>5.68</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>4.67</v>
+        <v>15.13</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>-7.21</v>
       </c>
       <c r="H3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>16.11</v>
+        <v>12.39</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -819,24 +819,24 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>超买区间</t>
+        <v>69</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>24.14</v>
+        <v>20.64</v>
       </c>
       <c r="P3" t="n">
-        <v>12.84</v>
+        <v>13.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>195.64</v>
+        <v>189.02</v>
       </c>
       <c r="R3" t="n">
-        <v>193.32</v>
+        <v>194.76</v>
       </c>
       <c r="S3" t="n">
         <v>263.21</v>
@@ -845,21 +845,21 @@
         <v>125.61</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>730206</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>44.4</v>
+        <v>33.3</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,28 +897,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>96.09</v>
+        <v>125.7</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7.59</v>
+        <v>2.49</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2.88</v>
+        <v>0.49</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-29.22</v>
+        <v>-13.47</v>
       </c>
       <c r="H4" t="n">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4.57</v>
+        <v>4.13</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>67.3</v>
+        <v>63</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,39 +947,39 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>10.91</v>
+        <v>10.27</v>
       </c>
       <c r="Q4" t="n">
-        <v>85.61</v>
+        <v>112.79</v>
       </c>
       <c r="R4" t="n">
-        <v>91.89</v>
+        <v>120.71</v>
       </c>
       <c r="S4" t="n">
-        <v>144.2</v>
+        <v>158.2</v>
       </c>
       <c r="T4" t="n">
-        <v>69.8</v>
+        <v>94.73</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>650201</v>
+        <v>270202</v>
       </c>
       <c r="Z4" t="n">
         <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>40.7</v>
+        <v>33.3</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,28 +1017,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>167.65</v>
+        <v>95</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4.11</v>
+        <v>1.77</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-0.26</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-34.2</v>
+        <v>-31.28</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>58.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1067,39 +1067,39 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>7.45</v>
+        <v>5.25</v>
       </c>
       <c r="P5" t="n">
-        <v>12.62</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>146.5</v>
+        <v>84.55</v>
       </c>
       <c r="R5" t="n">
-        <v>166.98</v>
+        <v>91.88</v>
       </c>
       <c r="S5" t="n">
-        <v>325.74</v>
+        <v>144.2</v>
       </c>
       <c r="T5" t="n">
-        <v>133.61</v>
+        <v>69.8</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>270401</v>
+        <v>650201</v>
       </c>
       <c r="Z5" t="n">
         <v>15</v>
       </c>
       <c r="AA5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>37</v>
+        <v>33.3</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,28 +1137,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>128.25</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>5.76</v>
+        <v>92.28</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-8.43</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-13.29</v>
+        <v>-30.05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6.27</v>
+        <v>0.72</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,47 +1179,47 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>64.8</v>
+        <v>60</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>9.1</v>
+      <c r="O6" s="3" t="n">
+        <v>-2.92</v>
       </c>
       <c r="P6" t="n">
-        <v>10.03</v>
+        <v>11.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>115.39</v>
+        <v>81.37</v>
       </c>
       <c r="R6" t="n">
-        <v>120.68</v>
+        <v>91.62</v>
       </c>
       <c r="S6" t="n">
-        <v>158.2</v>
+        <v>168.08</v>
       </c>
       <c r="T6" t="n">
-        <v>94.73</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>4</v>
+        <v>80.31999999999999</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>270202</v>
+        <v>640703</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1227,17 +1227,17 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" t="n">
-        <v>33.3</v>
+      <c r="AD6" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；OBV创20日新高</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,89 +1257,89 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>200.86</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>11.59</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>24.37</v>
+        <v>161.38</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-6.17</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-24.94</v>
+        <v>-43.91</v>
       </c>
       <c r="H7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.91</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>48.8</v>
+        <v>54.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>27.71</v>
+      <c r="O7" s="3" t="n">
+        <v>-0.66</v>
       </c>
       <c r="P7" t="n">
-        <v>12.03</v>
+        <v>13.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>176.69</v>
+        <v>140.07</v>
       </c>
       <c r="R7" t="n">
-        <v>199.1</v>
+        <v>166.45</v>
       </c>
       <c r="S7" t="n">
-        <v>284.85</v>
+        <v>325.74</v>
       </c>
       <c r="T7" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>4</v>
+        <v>133.61</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>730204</v>
+        <v>270401</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1347,17 +1347,17 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" t="n">
-        <v>33.3</v>
+      <c r="AD7" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,49 +1377,49 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>9.59</v>
+        <v>237.1</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-0.9</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-5.6</v>
+        <v>-12.13</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-27.25</v>
+        <v>-23.21</v>
       </c>
       <c r="H8" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.61</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>2.54</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>-0.97</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>55.2</v>
+        <v>50.9</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,39 +1427,39 @@
         </is>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-2.26</v>
+        <v>-6.62</v>
       </c>
       <c r="P8" t="n">
-        <v>10.07</v>
+        <v>10.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>380.41</v>
+        <v>212.22</v>
       </c>
       <c r="R8" t="n">
-        <v>412.53</v>
+        <v>239.43</v>
       </c>
       <c r="S8" t="n">
-        <v>618.87</v>
+        <v>418.99</v>
       </c>
       <c r="T8" t="n">
-        <v>347</v>
+        <v>183.83</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>730204</v>
+        <v>270103</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1467,17 +1467,17 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" t="n">
-        <v>33.3</v>
+      <c r="AD8" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,89 +1497,89 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92.84999999999999</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>5.91</v>
+        <v>33.04</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-2.82</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-6.21</v>
+        <v>-17.28</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-31.17</v>
+        <v>-40.81</v>
       </c>
       <c r="H9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.68</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>-7.04</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>27.7</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-2.87</v>
+        <v>-11.77</v>
       </c>
       <c r="P9" t="n">
-        <v>11.69</v>
+        <v>6.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>81.98999999999999</v>
+        <v>30.89</v>
       </c>
       <c r="R9" t="n">
-        <v>92.04000000000001</v>
+        <v>35.54</v>
       </c>
       <c r="S9" t="n">
-        <v>168.08</v>
+        <v>56.81</v>
       </c>
       <c r="T9" t="n">
-        <v>80.31999999999999</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
+        <v>31.68</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>640703</v>
+        <v>630702</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1587,17 +1587,17 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" t="n">
-        <v>31.5</v>
+      <c r="AD9" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,28 +1617,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>194.42</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>8.82</v>
+        <v>84.98</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-4.25</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-5.25</v>
+        <v>-28.47</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-28.78</v>
+        <v>-48.01</v>
       </c>
       <c r="H10" t="n">
-        <v>1.09</v>
+        <v>0.71</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1651,55 +1651,55 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-12.63</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>16.3</v>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-1.91</v>
+        <v>-22.96</v>
       </c>
       <c r="P10" t="n">
-        <v>10.87</v>
+        <v>9.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>173.29</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>194.57</v>
+        <v>97.27</v>
       </c>
       <c r="S10" t="n">
-        <v>280.08</v>
+        <v>162</v>
       </c>
       <c r="T10" t="n">
-        <v>161.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
+        <v>83.12</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270202</v>
+        <v>630503</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,32 +1737,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>402.73</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>2.92</v>
+        <v>171.81</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-6.86</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.85</v>
+        <v>-13.99</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-43.44</v>
+        <v>-37.77</v>
       </c>
       <c r="H11" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.88</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-2.27</v>
+        <v>-2.65</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1779,48 +1779,48 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>50.7</v>
+        <v>53.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O11" s="2" t="n">
-        <v>2.49</v>
+      <c r="O11" s="3" t="n">
+        <v>-8.48</v>
       </c>
       <c r="P11" t="n">
-        <v>10.65</v>
+        <v>11.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>359.84</v>
+        <v>151.59</v>
       </c>
       <c r="R11" t="n">
-        <v>412.09</v>
+        <v>176.49</v>
       </c>
       <c r="S11" t="n">
-        <v>980</v>
+        <v>278</v>
       </c>
       <c r="T11" t="n">
-        <v>334</v>
+        <v>152.33</v>
       </c>
       <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>730204</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
         <v>3</v>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="W11" t="n">
-        <v>270104</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>8</v>
-      </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
@@ -1828,16 +1828,16 @@
         <v>0</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>20.4</v>
+        <v>14.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,28 +1857,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>103.88</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>8.66</v>
+        <v>256.96</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-3.76</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-5.38</v>
+        <v>-10.33</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-41.49</v>
+        <v>-21.21</v>
       </c>
       <c r="H12" t="n">
-        <v>1.46</v>
+        <v>0.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1891,15 +1891,15 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-1.98</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>50.7</v>
+        <v>49.9</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>-2.04</v>
+        <v>-4.82</v>
       </c>
       <c r="P12" t="n">
-        <v>10.73</v>
+        <v>12.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>92.73</v>
+        <v>224.28</v>
       </c>
       <c r="R12" t="n">
-        <v>104.01</v>
+        <v>262.14</v>
       </c>
       <c r="S12" t="n">
-        <v>187.66</v>
+        <v>346</v>
       </c>
       <c r="T12" t="n">
-        <v>90.23</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
+        <v>155.55</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>640703</v>
+        <v>730204</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,16 +1948,16 @@
         <v>0</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>18.5</v>
+        <v>11.1</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>177.36</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-7.39</v>
+        <v>198.3</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2.32</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-33.37</v>
+        <v>-29.22</v>
       </c>
       <c r="H13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.82</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2011,55 +2011,55 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-0.52</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>58.8</v>
+        <v>47.4</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O13" s="3" t="n">
-        <v>-4.05</v>
+      <c r="O13" s="2" t="n">
+        <v>7.83</v>
       </c>
       <c r="P13" t="n">
-        <v>11.51</v>
+        <v>12.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>156.95</v>
+        <v>174.03</v>
       </c>
       <c r="R13" t="n">
-        <v>177.89</v>
+        <v>199.33</v>
       </c>
       <c r="S13" t="n">
-        <v>279</v>
+        <v>276.26</v>
       </c>
       <c r="T13" t="n">
-        <v>152.33</v>
+        <v>102.3</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W13" t="n">
         <v>730204</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2068,16 +2068,16 @@
         <v>0</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>18.5</v>
+        <v>11.1</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,28 +2097,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>261.96</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>5.33</v>
+        <v>100</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-1.87</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-2.15</v>
+        <v>-12.02</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-22.17</v>
+        <v>-42.75</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2131,52 +2131,52 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-3.22</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>57</v>
+        <v>43.5</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n">
-        <v>1.19</v>
+      <c r="O14" s="3" t="n">
+        <v>-6.51</v>
       </c>
       <c r="P14" t="n">
-        <v>12.77</v>
+        <v>10.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>228.52</v>
+        <v>89.16</v>
       </c>
       <c r="R14" t="n">
-        <v>263.62</v>
+        <v>103.33</v>
       </c>
       <c r="S14" t="n">
-        <v>346</v>
+        <v>187.66</v>
       </c>
       <c r="T14" t="n">
-        <v>155.55</v>
+        <v>90.23</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>730204</v>
+        <v>640703</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>5</v>
@@ -2188,11 +2188,11 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>14.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2217,28 +2217,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55.39</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>2.01</v>
+        <v>185.11</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-2.85</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-2.1</v>
+        <v>-14.95</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-20.63</v>
+        <v>-31.58</v>
       </c>
       <c r="H15" t="n">
-        <v>0.78</v>
+        <v>1.06</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-0.76</v>
+        <v>-4.06</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2259,47 +2259,47 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>55.8</v>
+        <v>46.1</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O15" s="2" t="n">
-        <v>1.24</v>
+      <c r="O15" s="3" t="n">
+        <v>-9.44</v>
       </c>
       <c r="P15" t="n">
-        <v>7.95</v>
+        <v>11.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>50.99</v>
+        <v>163.95</v>
       </c>
       <c r="R15" t="n">
-        <v>55.82</v>
+        <v>192.95</v>
       </c>
       <c r="S15" t="n">
-        <v>76.16</v>
+        <v>280.08</v>
       </c>
       <c r="T15" t="n">
-        <v>51.88</v>
+        <v>161.8</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270504</v>
+        <v>270202</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>14.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,28 +2337,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>64.92</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>401.9</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-3.67</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.06</v>
+        <v>-13.88</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-36.91</v>
+        <v>-30.7</v>
       </c>
       <c r="H16" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-1.79</v>
+        <v>-1.81</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -2379,44 +2379,44 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>55.3</v>
+        <v>50.4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O16" s="2" t="n">
-        <v>3.28</v>
+      <c r="O16" s="3" t="n">
+        <v>-8.369999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>10.06</v>
+        <v>10.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>58.39</v>
+        <v>358.31</v>
       </c>
       <c r="R16" t="n">
-        <v>66.09999999999999</v>
+        <v>409.29</v>
       </c>
       <c r="S16" t="n">
-        <v>108.05</v>
+        <v>618.87</v>
       </c>
       <c r="T16" t="n">
-        <v>47.3</v>
+        <v>347</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>270303</v>
+        <v>730204</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>5</v>
@@ -2428,11 +2428,11 @@
         <v>0</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>14.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>84.40000000000001</v>
+        <v>52.78</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-4.56</v>
+        <v>-5.63</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-27.69</v>
+        <v>-10.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-42.58</v>
+        <v>-22.68</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -2491,55 +2491,55 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-14.71</v>
+        <v>-4.92</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>43.4</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-24.35</v>
+        <v>-4.79</v>
       </c>
       <c r="P17" t="n">
-        <v>9.539999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="Q17" t="n">
-        <v>76.34999999999999</v>
+        <v>48.52</v>
       </c>
       <c r="R17" t="n">
-        <v>98.95999999999999</v>
+        <v>55.51</v>
       </c>
       <c r="S17" t="n">
-        <v>167.15</v>
+        <v>76.16</v>
       </c>
       <c r="T17" t="n">
-        <v>83.12</v>
+        <v>51.88</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>630503</v>
+        <v>270504</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>14.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,32 +2577,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60.55</v>
+        <v>66.33</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-5.26</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>6.06</v>
+        <v>-3.87</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-22.74</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-18.58</v>
+        <v>-27.29</v>
       </c>
       <c r="H18" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2611,52 +2611,52 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-1.36</v>
+        <v>-9.23</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>9.4</v>
+        <v>29.2</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>-17.23</v>
       </c>
       <c r="P18" t="n">
-        <v>12.41</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>53.03</v>
+        <v>60.78</v>
       </c>
       <c r="R18" t="n">
-        <v>61.38</v>
+        <v>73.08</v>
       </c>
       <c r="S18" t="n">
-        <v>89.69</v>
+        <v>113.87</v>
       </c>
       <c r="T18" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
+        <v>60.84</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>640209</v>
+        <v>270107</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>3</v>
@@ -2668,11 +2668,11 @@
         <v>0</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>24.67</v>
+        <v>387.9</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-0.48</v>
+        <v>-3.98</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-10.36</v>
+        <v>-10.91</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-33.03</v>
+        <v>-47.37</v>
       </c>
       <c r="H19" t="n">
-        <v>0.68</v>
+        <v>0.84</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -2731,15 +2731,15 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-5.57</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>死叉(转空)</t>
+        <v>-5.33</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>46.7</v>
+        <v>47.3</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2747,39 +2747,39 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>-7.02</v>
+        <v>-5.4</v>
       </c>
       <c r="P19" t="n">
-        <v>8.31</v>
+        <v>10.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.62</v>
+        <v>345.72</v>
       </c>
       <c r="R19" t="n">
-        <v>26.13</v>
+        <v>409.72</v>
       </c>
       <c r="S19" t="n">
-        <v>42.08</v>
+        <v>980</v>
       </c>
       <c r="T19" t="n">
-        <v>23.93</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>1</v>
+        <v>334</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270303</v>
+        <v>270104</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>339.55</v>
+        <v>24.46</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-2.15</v>
+        <v>-4.79</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-16.46</v>
+        <v>-15.66</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-41.23</v>
+        <v>-30.96</v>
       </c>
       <c r="H20" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -2851,15 +2851,15 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-8.27</v>
+        <v>-5.56</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>38.7</v>
+        <v>44.4</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2867,39 +2867,39 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-13.12</v>
+        <v>-10.15</v>
       </c>
       <c r="P20" t="n">
-        <v>8.300000000000001</v>
+        <v>7.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>311.38</v>
+        <v>22.54</v>
       </c>
       <c r="R20" t="n">
-        <v>370.18</v>
+        <v>25.9</v>
       </c>
       <c r="S20" t="n">
-        <v>749.88</v>
+        <v>42.08</v>
       </c>
       <c r="T20" t="n">
-        <v>308</v>
+        <v>23.93</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>270104</v>
+        <v>270303</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,32 +2937,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>36.77</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-14.09</v>
+        <v>-5.45</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-4.99</v>
+        <v>-4.55</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-25.75</v>
+        <v>-36.33</v>
       </c>
       <c r="H21" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.62</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2971,55 +2971,55 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-13.57</v>
+        <v>-2.09</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>35.9</v>
+        <v>51.9</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>-1.65</v>
+      <c r="O21" s="2" t="n">
+        <v>0.96</v>
       </c>
       <c r="P21" t="n">
-        <v>14.18</v>
+        <v>9.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>31.56</v>
+        <v>58.18</v>
       </c>
       <c r="R21" t="n">
-        <v>42.54</v>
+        <v>65.95</v>
       </c>
       <c r="S21" t="n">
-        <v>52.92</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>1</v>
+        <v>47.3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270504</v>
+        <v>270303</v>
       </c>
       <c r="Z21" t="n">
         <v>3</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,28 +3057,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>230.46</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>-9.94</v>
+        <v>60.01</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-6.92</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>2.25</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-25.94</v>
+        <v>-22.37</v>
       </c>
       <c r="H22" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>-4.4</v>
+        <v>-2.34</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -3099,47 +3099,47 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>40.2</v>
+        <v>49.6</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O22" s="3" t="n">
-        <v>-6.6</v>
+      <c r="O22" s="2" t="n">
+        <v>7.76</v>
       </c>
       <c r="P22" t="n">
-        <v>11.37</v>
+        <v>11.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>204.25</v>
+        <v>53.17</v>
       </c>
       <c r="R22" t="n">
-        <v>241.07</v>
+        <v>61.45</v>
       </c>
       <c r="S22" t="n">
-        <v>418.99</v>
+        <v>89.69</v>
       </c>
       <c r="T22" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>1</v>
+        <v>45.82</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>270103</v>
+        <v>640209</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3152,12 +3152,12 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
           <t>无明显信号</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>58.02</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>3.02</v>
+        <v>331.01</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-7.6</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-16.86</v>
+        <v>-21.05</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-46.31</v>
+        <v>-46.28</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9</v>
+        <v>0.66</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
@@ -3211,15 +3211,15 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-4.41</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-9.5</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>47.4</v>
+        <v>33.4</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -3227,33 +3227,33 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-13.52</v>
+        <v>-15.54</v>
       </c>
       <c r="P23" t="n">
-        <v>15.34</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>49.12</v>
+        <v>304.16</v>
       </c>
       <c r="R23" t="n">
-        <v>60.7</v>
+        <v>365.76</v>
       </c>
       <c r="S23" t="n">
-        <v>115.44</v>
+        <v>749.88</v>
       </c>
       <c r="T23" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
+        <v>308</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270203</v>
+        <v>270104</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1.99</v>
+        <v>81.97</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-1.69</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-7.88</v>
+        <v>-9.49</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-15.04</v>
+        <v>-7.92</v>
       </c>
       <c r="H24" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-6.12</v>
+        <v>-2.85</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>39.3</v>
+        <v>45.7</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -3347,39 +3347,39 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-4.54</v>
+        <v>-3.98</v>
       </c>
       <c r="P24" t="n">
-        <v>8.85</v>
+        <v>5.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>52.87</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="R24" t="n">
-        <v>61.78</v>
+        <v>84.37</v>
       </c>
       <c r="S24" t="n">
-        <v>84.7</v>
+        <v>113</v>
       </c>
       <c r="T24" t="n">
-        <v>51.23</v>
+        <v>80.55</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>270107</v>
+        <v>710101</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>67.73999999999999</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>53.55</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-3.57</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-13.94</v>
+        <v>-15.62</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-18.32</v>
+        <v>-34.82</v>
       </c>
       <c r="H25" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-8.529999999999999</v>
+        <v>-5.95</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>32.6</v>
+        <v>39</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3467,39 +3467,39 @@
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-10.6</v>
+        <v>-10.11</v>
       </c>
       <c r="P25" t="n">
-        <v>8.630000000000001</v>
+        <v>10.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>61.89</v>
+        <v>47.92</v>
       </c>
       <c r="R25" t="n">
-        <v>74.05</v>
+        <v>56.94</v>
       </c>
       <c r="S25" t="n">
-        <v>113.87</v>
+        <v>107.55</v>
       </c>
       <c r="T25" t="n">
-        <v>60.84</v>
+        <v>43.01</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>270107</v>
+        <v>640108</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,28 +3537,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>82.25</v>
+        <v>56.78</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.53</v>
+        <v>-4.01</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-7.96</v>
+        <v>-18.02</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-7.25</v>
+        <v>-20.31</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-3.01</v>
+        <v>-7.16</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>50.2</v>
+        <v>37.2</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3587,39 +3587,39 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-4.62</v>
+        <v>-12.51</v>
       </c>
       <c r="P26" t="n">
-        <v>5.1</v>
+        <v>8.77</v>
       </c>
       <c r="Q26" t="n">
-        <v>78.06</v>
+        <v>51.8</v>
       </c>
       <c r="R26" t="n">
-        <v>84.8</v>
+        <v>61.16</v>
       </c>
       <c r="S26" t="n">
-        <v>113</v>
+        <v>84.7</v>
       </c>
       <c r="T26" t="n">
-        <v>80.55</v>
+        <v>51.23</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>710101</v>
+        <v>270107</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,28 +3657,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>52.04</v>
+        <v>58.13</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.06</v>
+        <v>-6.17</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-13.01</v>
+        <v>-16.9</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-37.24</v>
+        <v>-44.64</v>
       </c>
       <c r="H27" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -3691,15 +3691,15 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-9.390000000000001</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-3.28</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>30.6</v>
+        <v>46.6</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3707,39 +3707,39 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-9.67</v>
+        <v>-11.39</v>
       </c>
       <c r="P27" t="n">
-        <v>10.98</v>
+        <v>15.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>46.33</v>
+        <v>49.32</v>
       </c>
       <c r="R27" t="n">
-        <v>57.44</v>
+        <v>60.1</v>
       </c>
       <c r="S27" t="n">
-        <v>107.55</v>
+        <v>115.44</v>
       </c>
       <c r="T27" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>1</v>
+        <v>53.35</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>640108</v>
+        <v>270203</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>180.3</v>
+        <v>178.75</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-4.6</v>
+        <v>-7.23</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-11.61</v>
+        <v>-15.49</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.47</v>
+        <v>0.02</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -3811,15 +3811,15 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-3.82</v>
+        <v>-3.81</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>54.2</v>
+        <v>52.6</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3827,16 +3827,16 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>-8.27</v>
+        <v>-9.98</v>
       </c>
       <c r="P28" t="n">
-        <v>9.1</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Q28" t="n">
-        <v>163.88</v>
+        <v>162.44</v>
       </c>
       <c r="R28" t="n">
-        <v>187.46</v>
+        <v>185.82</v>
       </c>
       <c r="S28" t="n">
         <v>232.68</v>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W28" t="n">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32.31</v>
+        <v>37.56</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.49</v>
+        <v>-11.04</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-17.93</v>
+        <v>-10.36</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-37.27</v>
+        <v>-23.47</v>
       </c>
       <c r="H29" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.84</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-9.960000000000001</v>
+        <v>-11.26</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>16.9</v>
+        <v>30</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
@@ -3947,39 +3947,39 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-14.59</v>
+        <v>-4.85</v>
       </c>
       <c r="P29" t="n">
-        <v>6.77</v>
+        <v>13.01</v>
       </c>
       <c r="Q29" t="n">
-        <v>30.12</v>
+        <v>32.67</v>
       </c>
       <c r="R29" t="n">
-        <v>35.89</v>
+        <v>42.33</v>
       </c>
       <c r="S29" t="n">
-        <v>56.81</v>
+        <v>52.92</v>
       </c>
       <c r="T29" t="n">
-        <v>31.68</v>
+        <v>30.54</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>630702</v>
+        <v>270504</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -474,7 +474,7 @@
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
     <col width="74" customWidth="1" min="31" max="31"/>
-    <col width="43" customWidth="1" min="32" max="32"/>
+    <col width="66" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
@@ -657,28 +657,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36.7</v>
+        <v>125.82</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.2</v>
+        <v>0.74</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>20.41</v>
+        <v>1.8</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-5.24</v>
+        <v>-9.16</v>
       </c>
       <c r="H2" t="n">
-        <v>1.65</v>
+        <v>0.84</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>14.11</v>
+        <v>4.14</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>66</v>
+        <v>58.4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,39 +707,39 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>25.92</v>
+        <v>7.64</v>
       </c>
       <c r="P2" t="n">
-        <v>15.36</v>
+        <v>10.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.06</v>
+        <v>113.22</v>
       </c>
       <c r="R2" t="n">
-        <v>32.16</v>
+        <v>120.82</v>
       </c>
       <c r="S2" t="n">
-        <v>46.46</v>
+        <v>158.2</v>
       </c>
       <c r="T2" t="n">
-        <v>23.2</v>
+        <v>94.73</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>640209</v>
+        <v>270202</v>
       </c>
       <c r="Z2" t="n">
         <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -748,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>37</v>
+        <v>46.3</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,32 +777,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>218.88</v>
+        <v>244.71</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>15.13</v>
+        <v>4.27</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>-12.06</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-7.21</v>
+        <v>-16.43</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.72</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>12.39</v>
+        <v>2.93</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -819,47 +819,47 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>69</v>
+        <v>54.4</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>20.64</v>
+      <c r="O3" s="3" t="n">
+        <v>-6.22</v>
       </c>
       <c r="P3" t="n">
-        <v>13.64</v>
+        <v>10.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>189.02</v>
+        <v>219.3</v>
       </c>
       <c r="R3" t="n">
-        <v>194.76</v>
+        <v>237.75</v>
       </c>
       <c r="S3" t="n">
-        <v>263.21</v>
+        <v>418.99</v>
       </c>
       <c r="T3" t="n">
-        <v>125.61</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>5</v>
+        <v>183.83</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>730206</v>
+        <v>270103</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>33.3</v>
+        <v>37</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,28 +897,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>125.7</v>
+        <v>96.48</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.49</v>
+        <v>1.25</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.49</v>
+        <v>3.02</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-13.47</v>
+        <v>-24.24</v>
       </c>
       <c r="H4" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4.13</v>
+        <v>4.85</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>63</v>
+        <v>62.4</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,39 +947,39 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>6</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>10.27</v>
+        <v>10.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>112.79</v>
+        <v>86.17</v>
       </c>
       <c r="R4" t="n">
-        <v>120.71</v>
+        <v>92.02</v>
       </c>
       <c r="S4" t="n">
-        <v>158.2</v>
+        <v>144.2</v>
       </c>
       <c r="T4" t="n">
-        <v>94.73</v>
+        <v>69.8</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270202</v>
+        <v>650201</v>
       </c>
       <c r="Z4" t="n">
         <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>33.3</v>
+        <v>37</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>95</v>
+        <v>37.86</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-0.26</v>
+        <v>11.48</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>27.91</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-31.28</v>
+        <v>-7.52</v>
       </c>
       <c r="H5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.55</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3.4</v>
+        <v>16.22</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -1059,47 +1059,47 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>71.5</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>超买区间</t>
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>5.25</v>
+        <v>33.75</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>14.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>84.55</v>
+        <v>32.19</v>
       </c>
       <c r="R5" t="n">
-        <v>91.88</v>
+        <v>32.58</v>
       </c>
       <c r="S5" t="n">
-        <v>144.2</v>
+        <v>45.19</v>
       </c>
       <c r="T5" t="n">
-        <v>69.8</v>
+        <v>23.2</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>650201</v>
+        <v>640209</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1108,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>33.3</v>
+        <v>35.2</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>92.28</v>
+        <v>216.4</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-8.43</v>
+        <v>-2.65</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>16.37</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-30.05</v>
+        <v>-9.18</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.98</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.72</v>
+        <v>10.25</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,44 +1179,44 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>60</v>
+        <v>62.2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O6" s="3" t="n">
-        <v>-2.92</v>
+      <c r="O6" s="2" t="n">
+        <v>22.21</v>
       </c>
       <c r="P6" t="n">
-        <v>11.83</v>
+        <v>13.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>81.37</v>
+        <v>187.68</v>
       </c>
       <c r="R6" t="n">
-        <v>91.62</v>
+        <v>196.28</v>
       </c>
       <c r="S6" t="n">
-        <v>168.08</v>
+        <v>263.21</v>
       </c>
       <c r="T6" t="n">
-        <v>80.31999999999999</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
+        <v>125.61</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>640703</v>
+        <v>730206</v>
       </c>
       <c r="Z6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
         <v>3</v>
@@ -1227,12 +1227,12 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="3" t="n">
-        <v>27.8</v>
+      <c r="AD6" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1257,28 +1257,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>161.38</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-8.75</v>
+        <v>-2.21</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-6.17</v>
+        <v>-4.49</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-43.91</v>
+        <v>-35.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1287,11 +1287,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>-3.05</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>2.41</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1299,48 +1299,48 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>54.3</v>
+        <v>60.7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.66</v>
+      <c r="O7" s="2" t="n">
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>13.2</v>
+        <v>11.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>140.07</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>166.45</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>325.74</v>
+        <v>168.08</v>
       </c>
       <c r="T7" t="n">
-        <v>133.61</v>
-      </c>
-      <c r="U7" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>640703</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2</v>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>270401</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3</v>
-      </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
@@ -1348,16 +1348,16 @@
         <v>0</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>20.4</v>
+        <v>25.9</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,28 +1377,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>237.1</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-0.9</v>
+        <v>55.67</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.96</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-12.13</v>
+        <v>-10.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-23.21</v>
+        <v>-29.34</v>
       </c>
       <c r="H8" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -1411,15 +1411,15 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>金叉(转多)</t>
+        <v>-1.66</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>50.9</v>
+        <v>41.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,39 +1427,39 @@
         </is>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-6.62</v>
+        <v>-4.76</v>
       </c>
       <c r="P8" t="n">
-        <v>10.49</v>
+        <v>10.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>212.22</v>
+        <v>49.99</v>
       </c>
       <c r="R8" t="n">
-        <v>239.43</v>
+        <v>56.61</v>
       </c>
       <c r="S8" t="n">
-        <v>418.99</v>
+        <v>107.55</v>
       </c>
       <c r="T8" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
+        <v>43.01</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270103</v>
+        <v>640108</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>14.8</v>
+        <v>20.4</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,28 +1497,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>33.04</v>
+        <v>58.89</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-2.82</v>
+        <v>-1.19</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-17.28</v>
+        <v>-12.64</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-40.81</v>
+        <v>-37.68</v>
       </c>
       <c r="H9" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -1531,49 +1531,49 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-7.04</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-1.32</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>48.8</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-11.77</v>
+        <v>-6.8</v>
       </c>
       <c r="P9" t="n">
-        <v>6.5</v>
+        <v>15.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>30.89</v>
+        <v>49.93</v>
       </c>
       <c r="R9" t="n">
-        <v>35.54</v>
+        <v>59.68</v>
       </c>
       <c r="S9" t="n">
-        <v>56.81</v>
+        <v>115.44</v>
       </c>
       <c r="T9" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="U9" s="3" t="n">
-        <v>0</v>
+        <v>53.35</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>630702</v>
+        <v>270203</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>84.98</v>
+        <v>168.37</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-4.25</v>
+        <v>-6.42</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-28.47</v>
+        <v>-14.81</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-48.01</v>
+        <v>-36.92</v>
       </c>
       <c r="H10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.83</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1651,55 +1651,55 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-12.63</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-3.8</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>50.3</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-22.96</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>9.44</v>
+        <v>11.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>76.95999999999999</v>
+        <v>148.44</v>
       </c>
       <c r="R10" t="n">
-        <v>97.27</v>
+        <v>175.03</v>
       </c>
       <c r="S10" t="n">
-        <v>162</v>
+        <v>272.44</v>
       </c>
       <c r="T10" t="n">
-        <v>83.12</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>0</v>
+        <v>152.33</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>630503</v>
+        <v>730204</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,32 +1737,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>171.81</v>
+        <v>194.39</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-6.86</v>
+        <v>-3.55</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-13.99</v>
+        <v>-2.45</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-37.77</v>
+        <v>-26.23</v>
       </c>
       <c r="H11" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.8</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1771,52 +1771,52 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-2.36</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>53.3</v>
+        <v>48.2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O11" s="3" t="n">
-        <v>-8.48</v>
+      <c r="O11" s="2" t="n">
+        <v>3.39</v>
       </c>
       <c r="P11" t="n">
-        <v>11.77</v>
+        <v>12.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>151.59</v>
+        <v>170.38</v>
       </c>
       <c r="R11" t="n">
-        <v>176.49</v>
+        <v>199.08</v>
       </c>
       <c r="S11" t="n">
-        <v>278</v>
+        <v>276.26</v>
       </c>
       <c r="T11" t="n">
-        <v>152.33</v>
+        <v>102.3</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W11" t="n">
         <v>730204</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
         <v>3</v>
@@ -1828,11 +1828,11 @@
         <v>0</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>14.8</v>
+        <v>11.1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1857,28 +1857,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>256.96</v>
+        <v>100.2</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-3.76</v>
+        <v>-0.33</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-10.33</v>
+        <v>-10.5</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-21.21</v>
+        <v>-38.78</v>
       </c>
       <c r="H12" t="n">
-        <v>0.85</v>
+        <v>1.48</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1891,15 +1891,15 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>-1.98</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-2.47</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>49.9</v>
+        <v>45.4</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>-4.82</v>
+        <v>-4.66</v>
       </c>
       <c r="P12" t="n">
-        <v>12.72</v>
+        <v>10.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>224.28</v>
+        <v>89.48</v>
       </c>
       <c r="R12" t="n">
-        <v>262.14</v>
+        <v>102.74</v>
       </c>
       <c r="S12" t="n">
-        <v>346</v>
+        <v>187.66</v>
       </c>
       <c r="T12" t="n">
-        <v>155.55</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>1</v>
+        <v>90.23</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>730204</v>
+        <v>640703</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,16 +1948,16 @@
         <v>0</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>11.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>198.3</v>
+        <v>182.82</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>2.32</v>
+        <v>-1.93</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-14.5</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-29.22</v>
+        <v>-28.31</v>
       </c>
       <c r="H13" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.05</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2011,55 +2011,55 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-4.48</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>47.4</v>
+        <v>42.1</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O13" s="2" t="n">
-        <v>7.83</v>
+      <c r="O13" s="3" t="n">
+        <v>-8.66</v>
       </c>
       <c r="P13" t="n">
-        <v>12.24</v>
+        <v>10.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>174.03</v>
+        <v>163.03</v>
       </c>
       <c r="R13" t="n">
-        <v>199.33</v>
+        <v>191.4</v>
       </c>
       <c r="S13" t="n">
-        <v>276.26</v>
+        <v>280.08</v>
       </c>
       <c r="T13" t="n">
-        <v>102.3</v>
+        <v>161.8</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>730204</v>
+        <v>270202</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2068,16 +2068,16 @@
         <v>0</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>11.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>23.91</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-1.87</v>
+        <v>-5.19</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-12.02</v>
+        <v>-17.27</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-42.75</v>
+        <v>-29.55</v>
       </c>
       <c r="H14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.65</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2131,15 +2131,15 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-6.78</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>43.5</v>
+        <v>35.7</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -2147,33 +2147,33 @@
         </is>
       </c>
       <c r="O14" s="3" t="n">
-        <v>-6.51</v>
+        <v>-11.43</v>
       </c>
       <c r="P14" t="n">
-        <v>10.84</v>
+        <v>7.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>89.16</v>
+        <v>22.07</v>
       </c>
       <c r="R14" t="n">
-        <v>103.33</v>
+        <v>25.65</v>
       </c>
       <c r="S14" t="n">
-        <v>187.66</v>
+        <v>42.08</v>
       </c>
       <c r="T14" t="n">
-        <v>90.23</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
+        <v>23.85</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>640703</v>
+        <v>270303</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2217,32 +2217,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>185.11</v>
+        <v>257.38</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-2.85</v>
+        <v>-0.43</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-14.95</v>
+        <v>-11.69</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-31.58</v>
+        <v>-17.26</v>
       </c>
       <c r="H15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2251,15 +2251,15 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-1.17</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>46.1</v>
+        <v>52.3</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2267,39 +2267,39 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-9.44</v>
+        <v>-5.85</v>
       </c>
       <c r="P15" t="n">
-        <v>11.43</v>
+        <v>12.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>163.95</v>
+        <v>224.23</v>
       </c>
       <c r="R15" t="n">
-        <v>192.95</v>
+        <v>260.44</v>
       </c>
       <c r="S15" t="n">
-        <v>280.08</v>
+        <v>346</v>
       </c>
       <c r="T15" t="n">
-        <v>161.8</v>
+        <v>155.55</v>
       </c>
       <c r="U15" t="n">
         <v>2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270202</v>
+        <v>730204</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>401.9</v>
+        <v>57.31</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-3.67</v>
+        <v>-1.73</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-13.88</v>
+        <v>-18.89</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-30.7</v>
+        <v>-16.24</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2371,15 +2371,15 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-1.81</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-5.26</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>50.4</v>
+        <v>37.9</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2387,39 +2387,39 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-8.369999999999999</v>
+        <v>-13.05</v>
       </c>
       <c r="P16" t="n">
-        <v>10.84</v>
+        <v>8.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>358.31</v>
+        <v>52.35</v>
       </c>
       <c r="R16" t="n">
-        <v>409.29</v>
+        <v>60.49</v>
       </c>
       <c r="S16" t="n">
-        <v>618.87</v>
+        <v>84.7</v>
       </c>
       <c r="T16" t="n">
-        <v>347</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
+        <v>51.23</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>730204</v>
+        <v>270107</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52.78</v>
+        <v>66.86</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-5.63</v>
+        <v>-2.54</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-10.3</v>
+        <v>-21.73</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-22.68</v>
+        <v>-22.34</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -2491,15 +2491,15 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-4.92</v>
+        <v>-7.33</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>43.4</v>
+        <v>31.9</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2507,39 +2507,39 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-4.79</v>
+        <v>-15.89</v>
       </c>
       <c r="P17" t="n">
-        <v>8.07</v>
+        <v>8.32</v>
       </c>
       <c r="Q17" t="n">
-        <v>48.52</v>
+        <v>61.3</v>
       </c>
       <c r="R17" t="n">
-        <v>55.51</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>76.16</v>
+        <v>113.87</v>
       </c>
       <c r="T17" t="n">
-        <v>51.88</v>
+        <v>60.84</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>270504</v>
+        <v>270107</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66.33</v>
+        <v>32.79</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-3.87</v>
+        <v>-2.61</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-22.74</v>
+        <v>-16.07</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-27.29</v>
+        <v>-39.21</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-9.23</v>
+        <v>-6.92</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>29.2</v>
+        <v>22.9</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
@@ -2627,33 +2627,33 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>-17.23</v>
+        <v>-10.23</v>
       </c>
       <c r="P18" t="n">
-        <v>8.369999999999999</v>
+        <v>6.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>60.78</v>
+        <v>30.68</v>
       </c>
       <c r="R18" t="n">
-        <v>73.08</v>
+        <v>35.23</v>
       </c>
       <c r="S18" t="n">
-        <v>113.87</v>
+        <v>56.81</v>
       </c>
       <c r="T18" t="n">
-        <v>60.84</v>
+        <v>31.68</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270107</v>
+        <v>630702</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>387.9</v>
+        <v>84.38</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-3.98</v>
+        <v>-3.95</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-10.91</v>
+        <v>-28.52</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-47.37</v>
+        <v>-44.49</v>
       </c>
       <c r="H19" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -2731,49 +2731,49 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-5.33</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-11.72</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>8.6</v>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>-5.4</v>
+        <v>-22.68</v>
       </c>
       <c r="P19" t="n">
-        <v>10.87</v>
+        <v>8.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>345.72</v>
+        <v>76.8</v>
       </c>
       <c r="R19" t="n">
-        <v>409.72</v>
+        <v>95.59</v>
       </c>
       <c r="S19" t="n">
-        <v>980</v>
+        <v>160.26</v>
       </c>
       <c r="T19" t="n">
-        <v>334</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
+        <v>83.12</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270104</v>
+        <v>630503</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -2817,32 +2817,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>24.46</v>
+        <v>397.01</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-4.79</v>
+        <v>-4.66</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-15.66</v>
+        <v>-12.21</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-30.96</v>
+        <v>-28.08</v>
       </c>
       <c r="H20" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.75</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2851,15 +2851,15 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-5.56</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-2.34</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>44.4</v>
+        <v>49.3</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2867,33 +2867,33 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-10.15</v>
+        <v>-6.37</v>
       </c>
       <c r="P20" t="n">
-        <v>7.83</v>
+        <v>10.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>22.54</v>
+        <v>354.86</v>
       </c>
       <c r="R20" t="n">
-        <v>25.9</v>
+        <v>406.53</v>
       </c>
       <c r="S20" t="n">
-        <v>42.08</v>
+        <v>618.87</v>
       </c>
       <c r="T20" t="n">
-        <v>23.93</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>1</v>
+        <v>347</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>270303</v>
+        <v>730204</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>64.56999999999999</v>
+        <v>59.84</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-5.45</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>-4.55</v>
+        <v>-5.02</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>3.94</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-36.33</v>
+        <v>-26.56</v>
       </c>
       <c r="H21" t="n">
-        <v>0.62</v>
+        <v>0.52</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -2971,15 +2971,15 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-2.09</v>
+        <v>-2.8</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>51.9</v>
+        <v>45.3</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2987,33 +2987,33 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.96</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>58.18</v>
+        <v>53.2</v>
       </c>
       <c r="R21" t="n">
-        <v>65.95</v>
+        <v>61.56</v>
       </c>
       <c r="S21" t="n">
-        <v>99.90000000000001</v>
+        <v>89.69</v>
       </c>
       <c r="T21" t="n">
-        <v>47.3</v>
+        <v>45.82</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270303</v>
+        <v>640209</v>
       </c>
       <c r="Z21" t="n">
         <v>3</v>
@@ -3057,28 +3057,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60.01</v>
+        <v>385.98</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-6.92</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>2.25</v>
+        <v>-7.4</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>-11.74</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-22.37</v>
+        <v>-48.88</v>
       </c>
       <c r="H22" t="n">
-        <v>0.61</v>
+        <v>0.74</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -3091,55 +3091,55 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-5.2</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>49.6</v>
+        <v>48.6</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O22" s="2" t="n">
-        <v>7.76</v>
+      <c r="O22" s="3" t="n">
+        <v>-5.9</v>
       </c>
       <c r="P22" t="n">
-        <v>11.4</v>
+        <v>10.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>53.17</v>
+        <v>343.78</v>
       </c>
       <c r="R22" t="n">
-        <v>61.45</v>
+        <v>407.15</v>
       </c>
       <c r="S22" t="n">
-        <v>89.69</v>
+        <v>980</v>
       </c>
       <c r="T22" t="n">
-        <v>45.82</v>
+        <v>334</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>640209</v>
+        <v>270104</v>
       </c>
       <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3152,12 +3152,12 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,32 +3177,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>331.01</v>
+        <v>161.67</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-7.6</v>
+        <v>-10.01</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-21.05</v>
+        <v>-6.86</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-46.28</v>
+        <v>-42.96</v>
       </c>
       <c r="H23" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.76</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3211,15 +3211,15 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-2.52</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>33.4</v>
+        <v>55.2</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -3227,39 +3227,39 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-15.54</v>
+        <v>-1.02</v>
       </c>
       <c r="P23" t="n">
-        <v>8.109999999999999</v>
+        <v>13.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>304.16</v>
+        <v>140.59</v>
       </c>
       <c r="R23" t="n">
-        <v>365.76</v>
+        <v>165.85</v>
       </c>
       <c r="S23" t="n">
-        <v>749.88</v>
+        <v>325.74</v>
       </c>
       <c r="T23" t="n">
-        <v>308</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>1</v>
+        <v>133.61</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270104</v>
+        <v>270401</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3272,12 +3272,12 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
           <t>无明显信号</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>81.97</v>
+        <v>51.63</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-1.69</v>
+        <v>-6.23</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-9.49</v>
+        <v>-10.58</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-7.92</v>
+        <v>-25.41</v>
       </c>
       <c r="H24" t="n">
-        <v>0.49</v>
+        <v>0.85</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-2.85</v>
+        <v>-6.48</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>45.7</v>
+        <v>31.4</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -3347,39 +3347,39 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-3.98</v>
+        <v>-4.74</v>
       </c>
       <c r="P24" t="n">
-        <v>5.02</v>
+        <v>7.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>77.84999999999999</v>
+        <v>47.73</v>
       </c>
       <c r="R24" t="n">
-        <v>84.37</v>
+        <v>55.21</v>
       </c>
       <c r="S24" t="n">
-        <v>113</v>
+        <v>76.16</v>
       </c>
       <c r="T24" t="n">
-        <v>80.55</v>
+        <v>51.55</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>710101</v>
+        <v>270504</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>53.55</v>
+        <v>82.06</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-3.57</v>
+        <v>-0.58</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-15.62</v>
+        <v>-8.69</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-34.82</v>
+        <v>-5.74</v>
       </c>
       <c r="H25" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-5.95</v>
+        <v>-2.29</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>39</v>
+        <v>41.7</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3467,33 +3467,33 @@
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-10.11</v>
+        <v>-2.85</v>
       </c>
       <c r="P25" t="n">
-        <v>10.52</v>
+        <v>4.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>47.92</v>
+        <v>78.06</v>
       </c>
       <c r="R25" t="n">
-        <v>56.94</v>
+        <v>83.98</v>
       </c>
       <c r="S25" t="n">
-        <v>107.55</v>
+        <v>113</v>
       </c>
       <c r="T25" t="n">
-        <v>43.01</v>
+        <v>80.55</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>640108</v>
+        <v>710101</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -3537,28 +3537,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>56.78</v>
+        <v>63.46</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-4.01</v>
+        <v>-4.56</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-18.02</v>
+        <v>-7.86</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-20.31</v>
+        <v>-31.69</v>
       </c>
       <c r="H26" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-7.16</v>
+        <v>-3.38</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>37.2</v>
+        <v>46.6</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3587,33 +3587,33 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-12.51</v>
+        <v>-2.02</v>
       </c>
       <c r="P26" t="n">
-        <v>8.77</v>
+        <v>10.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>51.8</v>
+        <v>57.07</v>
       </c>
       <c r="R26" t="n">
-        <v>61.16</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>84.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>51.23</v>
+        <v>47.3</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270107</v>
+        <v>270303</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -3657,28 +3657,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>58.13</v>
+        <v>177.2</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.17</v>
+        <v>-6.04</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-16.9</v>
+        <v>-10.53</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-44.64</v>
+        <v>-0.98</v>
       </c>
       <c r="H27" t="n">
-        <v>0.76</v>
+        <v>0.52</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -3691,15 +3691,15 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.28</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-4.1</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>46.6</v>
+        <v>50.7</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3707,33 +3707,33 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-11.39</v>
+        <v>-4.69</v>
       </c>
       <c r="P27" t="n">
-        <v>15.16</v>
+        <v>9.23</v>
       </c>
       <c r="Q27" t="n">
-        <v>49.32</v>
+        <v>160.84</v>
       </c>
       <c r="R27" t="n">
-        <v>60.1</v>
+        <v>184.78</v>
       </c>
       <c r="S27" t="n">
-        <v>115.44</v>
+        <v>232.68</v>
       </c>
       <c r="T27" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
+        <v>170.1</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>270203</v>
+        <v>270104</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>178.75</v>
+        <v>37.23</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-7.23</v>
+        <v>-6.32</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-15.49</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>0.02</v>
+        <v>-16.22</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-19.17</v>
       </c>
       <c r="H28" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.65</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-3.81</v>
+        <v>-11.29</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>52.6</v>
+        <v>33.7</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3827,33 +3827,33 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>-9.98</v>
+        <v>-10.38</v>
       </c>
       <c r="P28" t="n">
-        <v>9.119999999999999</v>
+        <v>12.31</v>
       </c>
       <c r="Q28" t="n">
-        <v>162.44</v>
+        <v>32.65</v>
       </c>
       <c r="R28" t="n">
-        <v>185.82</v>
+        <v>41.97</v>
       </c>
       <c r="S28" t="n">
-        <v>232.68</v>
+        <v>52.92</v>
       </c>
       <c r="T28" t="n">
-        <v>170.1</v>
+        <v>30.54</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>270104</v>
+        <v>270504</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>37.56</v>
+        <v>328.5</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-11.04</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-10.36</v>
+        <v>-20.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-23.47</v>
+        <v>-44.88</v>
       </c>
       <c r="H29" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.61</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-11.26</v>
+        <v>-9.15</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -3939,41 +3939,41 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>30</v>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>34.2</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.85</v>
+        <v>-14.46</v>
       </c>
       <c r="P29" t="n">
-        <v>13.01</v>
+        <v>8.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>32.67</v>
+        <v>301.71</v>
       </c>
       <c r="R29" t="n">
-        <v>42.33</v>
+        <v>361.58</v>
       </c>
       <c r="S29" t="n">
-        <v>52.92</v>
+        <v>749.88</v>
       </c>
       <c r="T29" t="n">
-        <v>30.54</v>
+        <v>308</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>270504</v>
+        <v>270104</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -474,7 +474,7 @@
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
     <col width="74" customWidth="1" min="31" max="31"/>
-    <col width="66" customWidth="1" min="32" max="32"/>
+    <col width="76" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>125.82</v>
+        <v>127.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.74</v>
+        <v>0.2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1.8</v>
+        <v>12.69</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-9.16</v>
+        <v>-10.85</v>
       </c>
       <c r="H2" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4.14</v>
+        <v>5.15</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>58.4</v>
+        <v>57.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>7.64</v>
+        <v>15.05</v>
       </c>
       <c r="P2" t="n">
-        <v>10.01</v>
+        <v>9.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>113.22</v>
+        <v>115.15</v>
       </c>
       <c r="R2" t="n">
-        <v>120.82</v>
+        <v>121.54</v>
       </c>
       <c r="S2" t="n">
         <v>158.2</v>
@@ -729,14 +729,14 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>270202</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
         <v>10</v>
@@ -748,11 +748,11 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>46.3</v>
+        <v>50</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -777,32 +777,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>244.71</v>
+        <v>223.63</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>-12.06</v>
+        <v>2.12</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>33.62</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-16.43</v>
+        <v>-14.68</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.96</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2.93</v>
+        <v>12.32</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -819,47 +819,47 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>54.4</v>
+        <v>62.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O3" s="3" t="n">
-        <v>-6.22</v>
+      <c r="O3" s="2" t="n">
+        <v>35.98</v>
       </c>
       <c r="P3" t="n">
-        <v>10.38</v>
+        <v>12.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>219.3</v>
+        <v>195.42</v>
       </c>
       <c r="R3" t="n">
-        <v>237.75</v>
+        <v>199.09</v>
       </c>
       <c r="S3" t="n">
-        <v>418.99</v>
+        <v>263.21</v>
       </c>
       <c r="T3" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
+        <v>125.61</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270103</v>
+        <v>730206</v>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>37</v>
+        <v>48.1</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,32 +897,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>96.48</v>
+        <v>68.59</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.25</v>
+        <v>3.13</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.02</v>
+        <v>10.66</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-24.24</v>
+        <v>-27.74</v>
       </c>
       <c r="H4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.85</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -931,15 +931,15 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>3.91</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>62.4</v>
+        <v>52</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,39 +947,39 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>13.02</v>
       </c>
       <c r="P4" t="n">
-        <v>10.68</v>
+        <v>9.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>86.17</v>
+        <v>61.78</v>
       </c>
       <c r="R4" t="n">
-        <v>92.02</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>144.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>4</v>
+        <v>47.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>650201</v>
+        <v>270303</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>37</v>
+        <v>46.3</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,28 +1017,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.86</v>
+        <v>206.39</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11.48</v>
+        <v>2.4</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>27.91</v>
+        <v>14.49</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-7.52</v>
+        <v>-23.65</v>
       </c>
       <c r="H5" t="n">
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -1051,55 +1051,55 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>2.99</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>超买区间</t>
+        <v>48.2</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>33.75</v>
+        <v>16.85</v>
       </c>
       <c r="P5" t="n">
-        <v>14.96</v>
+        <v>11.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>32.19</v>
+        <v>182.26</v>
       </c>
       <c r="R5" t="n">
-        <v>32.58</v>
+        <v>200.39</v>
       </c>
       <c r="S5" t="n">
-        <v>45.19</v>
+        <v>276.26</v>
       </c>
       <c r="T5" t="n">
-        <v>23.2</v>
+        <v>102.3</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>640209</v>
+        <v>730204</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1108,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>35.2</v>
+        <v>44.4</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>216.4</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-2.65</v>
+        <v>423.69</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2.14</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>16.37</v>
+        <v>2.96</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-9.18</v>
+        <v>-23.7</v>
       </c>
       <c r="H6" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>10.25</v>
+        <v>4.06</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>62.2</v>
+        <v>55.4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1187,39 +1187,39 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>22.21</v>
+        <v>5.32</v>
       </c>
       <c r="P6" t="n">
-        <v>13.27</v>
+        <v>10.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>187.68</v>
+        <v>378.74</v>
       </c>
       <c r="R6" t="n">
-        <v>196.28</v>
+        <v>407.14</v>
       </c>
       <c r="S6" t="n">
-        <v>263.21</v>
+        <v>618.87</v>
       </c>
       <c r="T6" t="n">
-        <v>125.61</v>
+        <v>347</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>730206</v>
+        <v>730204</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>33.3</v>
+        <v>42.6</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1266,19 +1266,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>-4.49</v>
+        <v>95.54000000000001</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>8.32</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-35.5</v>
+        <v>-37.24</v>
       </c>
       <c r="H7" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2.41</v>
+        <v>4.11</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>60.7</v>
+        <v>58</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.35</v>
+        <v>10.68</v>
       </c>
       <c r="P7" t="n">
-        <v>11.79</v>
+        <v>11.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>82.56999999999999</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>91.40000000000001</v>
+        <v>91.77</v>
       </c>
       <c r="S7" t="n">
         <v>168.08</v>
@@ -1329,17 +1329,17 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>640703</v>
       </c>
       <c r="Z7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1347,17 +1347,17 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="3" t="n">
-        <v>25.9</v>
+      <c r="AD7" t="n">
+        <v>42.6</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,89 +1377,89 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55.67</v>
+        <v>252.83</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>-10.6</v>
+        <v>9.449999999999999</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-29.34</v>
+        <v>-16.84</v>
       </c>
       <c r="H8" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.86</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>-1.66</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>41.4</v>
+        <v>52.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O8" s="3" t="n">
-        <v>-4.76</v>
+      <c r="O8" s="2" t="n">
+        <v>2.46</v>
       </c>
       <c r="P8" t="n">
-        <v>10.2</v>
+        <v>10.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>49.99</v>
+        <v>227.52</v>
       </c>
       <c r="R8" t="n">
-        <v>56.61</v>
+        <v>237.76</v>
       </c>
       <c r="S8" t="n">
-        <v>107.55</v>
+        <v>418.99</v>
       </c>
       <c r="T8" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>1</v>
+        <v>183.83</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>640108</v>
+        <v>270103</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1467,17 +1467,17 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="3" t="n">
-        <v>20.4</v>
+      <c r="AD8" t="n">
+        <v>38.9</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,41 +1497,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>58.89</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-12.64</v>
+        <v>98.51000000000001</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>12.93</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-37.68</v>
+        <v>-26.2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.09</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>-1.32</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>6.4</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -1539,65 +1539,65 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>48.8</v>
+        <v>63.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O9" s="3" t="n">
-        <v>-6.8</v>
+      <c r="O9" s="2" t="n">
+        <v>15.29</v>
       </c>
       <c r="P9" t="n">
-        <v>15.21</v>
+        <v>10.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>49.93</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>59.68</v>
+        <v>92.58</v>
       </c>
       <c r="S9" t="n">
-        <v>115.44</v>
+        <v>144.2</v>
       </c>
       <c r="T9" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="U9" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>650201</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA9" t="n">
         <v>2</v>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>270203</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>8</v>
-      </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="3" t="n">
-        <v>14.8</v>
+      <c r="AD9" t="n">
+        <v>35.2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,89 +1617,89 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>168.37</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>-6.42</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>-14.81</v>
+        <v>59.68</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>2.97</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-36.92</v>
+        <v>-28.78</v>
       </c>
       <c r="H10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.8</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>-3.8</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>5.26</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>50.3</v>
+        <v>47.1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O10" s="3" t="n">
-        <v>-8.970000000000001</v>
+      <c r="O10" s="2" t="n">
+        <v>5.33</v>
       </c>
       <c r="P10" t="n">
-        <v>11.84</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>148.44</v>
+        <v>53.73</v>
       </c>
       <c r="R10" t="n">
-        <v>175.03</v>
+        <v>56.7</v>
       </c>
       <c r="S10" t="n">
-        <v>272.44</v>
+        <v>107.55</v>
       </c>
       <c r="T10" t="n">
-        <v>152.33</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
+        <v>43.01</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>730204</v>
+        <v>640108</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1707,17 +1707,17 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" s="3" t="n">
-        <v>14.8</v>
+      <c r="AD10" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
+          <t>股价站上20日均线；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>194.39</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>-3.55</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>-2.45</v>
+        <v>38.18</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>40.47</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-26.23</v>
+        <v>-10.1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8</v>
+        <v>1.36</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1767,19 +1767,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>-2.36</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>48.2</v>
+        <v>69.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1787,39 +1787,39 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>3.39</v>
+        <v>42.83</v>
       </c>
       <c r="P11" t="n">
-        <v>12.35</v>
+        <v>14.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>170.38</v>
+        <v>32.59</v>
       </c>
       <c r="R11" t="n">
-        <v>199.08</v>
+        <v>33.12</v>
       </c>
       <c r="S11" t="n">
-        <v>276.26</v>
+        <v>45.19</v>
       </c>
       <c r="T11" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
+        <v>23.2</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>730204</v>
+        <v>640209</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1827,17 +1827,17 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="3" t="n">
-        <v>11.1</v>
+      <c r="AD11" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,41 +1857,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>100.2</v>
+        <v>192</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.33</v>
+        <v>-2.07</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-10.5</v>
+        <v>-2.59</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-38.78</v>
+        <v>-25.33</v>
       </c>
       <c r="H12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.98</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>-2.47</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.45</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>45.4</v>
+        <v>44.4</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>-4.66</v>
+        <v>-0.23</v>
       </c>
       <c r="P12" t="n">
-        <v>10.7</v>
+        <v>10.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>89.48</v>
+        <v>171.67</v>
       </c>
       <c r="R12" t="n">
-        <v>102.74</v>
+        <v>191.14</v>
       </c>
       <c r="S12" t="n">
-        <v>187.66</v>
+        <v>280.08</v>
       </c>
       <c r="T12" t="n">
-        <v>90.23</v>
+        <v>161.8</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>640703</v>
+        <v>270202</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1947,17 +1947,17 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AD12" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD12" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,41 +1977,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>182.82</v>
+        <v>105.98</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-1.93</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-14.5</v>
+        <v>-2.58</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>3.55</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-28.31</v>
+        <v>-36.88</v>
       </c>
       <c r="H13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.22</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>-4.48</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>2.97</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -2019,47 +2019,47 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>42.1</v>
+        <v>51.2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O13" s="3" t="n">
-        <v>-8.66</v>
+      <c r="O13" s="2" t="n">
+        <v>5.91</v>
       </c>
       <c r="P13" t="n">
-        <v>10.82</v>
+        <v>10.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>163.03</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>191.4</v>
+        <v>102.92</v>
       </c>
       <c r="S13" t="n">
-        <v>280.08</v>
+        <v>187.66</v>
       </c>
       <c r="T13" t="n">
-        <v>161.8</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
+        <v>90.23</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270202</v>
+        <v>640703</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2067,17 +2067,17 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD13" t="n">
+        <v>31.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,89 +2097,89 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23.91</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-17.27</v>
+        <v>185.21</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>4.12</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-29.55</v>
+        <v>-30.47</v>
       </c>
       <c r="H14" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.85</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>-6.78</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>35.7</v>
+        <v>55.6</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O14" s="3" t="n">
-        <v>-11.43</v>
+      <c r="O14" s="2" t="n">
+        <v>6.48</v>
       </c>
       <c r="P14" t="n">
-        <v>7.71</v>
+        <v>11.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>22.07</v>
+        <v>164.34</v>
       </c>
       <c r="R14" t="n">
-        <v>25.65</v>
+        <v>175.39</v>
       </c>
       <c r="S14" t="n">
-        <v>42.08</v>
+        <v>271.12</v>
       </c>
       <c r="T14" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>1</v>
+        <v>152.33</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>270303</v>
+        <v>730204</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2188,16 +2188,16 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>29.6</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2226,19 +2226,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>257.38</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>-0.43</v>
+        <v>268.49</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>4.26</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-11.69</v>
+        <v>-3.04</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-17.26</v>
+        <v>-17.33</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -2247,11 +2247,11 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>-1.17</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>3.46</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>52.3</v>
+        <v>51.1</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2267,39 +2267,39 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-5.85</v>
+        <v>-0.68</v>
       </c>
       <c r="P15" t="n">
-        <v>12.88</v>
+        <v>12.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>224.23</v>
+        <v>236.21</v>
       </c>
       <c r="R15" t="n">
-        <v>260.44</v>
+        <v>259.52</v>
       </c>
       <c r="S15" t="n">
-        <v>346</v>
+        <v>345.5</v>
       </c>
       <c r="T15" t="n">
-        <v>155.55</v>
+        <v>155.05</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W15" t="n">
         <v>730204</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2308,16 +2308,16 @@
         <v>0</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>5.6</v>
+        <v>27.8</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,28 +2337,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>57.31</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>-1.73</v>
+        <v>60.28</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2.22</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-18.89</v>
+        <v>-0.64</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-16.24</v>
+        <v>-40.28</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -2367,59 +2367,59 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>-5.26</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>37.9</v>
+        <v>46.6</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O16" s="3" t="n">
-        <v>-13.05</v>
+      <c r="O16" s="2" t="n">
+        <v>1.72</v>
       </c>
       <c r="P16" t="n">
-        <v>8.65</v>
+        <v>14.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.35</v>
+        <v>51.38</v>
       </c>
       <c r="R16" t="n">
-        <v>60.49</v>
+        <v>59.66</v>
       </c>
       <c r="S16" t="n">
-        <v>84.7</v>
+        <v>115.44</v>
       </c>
       <c r="T16" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>1</v>
+        <v>53.35</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>270107</v>
+        <v>270203</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         <v>0</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>5.6</v>
+        <v>27.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>66.86</v>
+        <v>62.03</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-2.54</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>-21.73</v>
+        <v>-0.64</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>17.95</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-22.34</v>
+        <v>-25.14</v>
       </c>
       <c r="H17" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-7.33</v>
+        <v>-0.01</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2499,47 +2499,47 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>31.9</v>
+        <v>41.1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O17" s="3" t="n">
-        <v>-15.89</v>
+      <c r="O17" s="2" t="n">
+        <v>20.31</v>
       </c>
       <c r="P17" t="n">
-        <v>8.32</v>
+        <v>10.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>61.3</v>
+        <v>55.59</v>
       </c>
       <c r="R17" t="n">
-        <v>72.15000000000001</v>
+        <v>62.04</v>
       </c>
       <c r="S17" t="n">
-        <v>113.87</v>
+        <v>89.69</v>
       </c>
       <c r="T17" t="n">
-        <v>60.84</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>1</v>
+        <v>45.82</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>270107</v>
+        <v>640209</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,16 +2548,16 @@
         <v>0</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>5.6</v>
+        <v>22.2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32.79</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-2.61</v>
+        <v>69.55</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1.33</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-16.07</v>
+        <v>-10.54</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-39.21</v>
+        <v>-26.56</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-6.92</v>
+        <v>-3.05</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2619,47 +2619,47 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>31</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>-10.23</v>
+        <v>-8.18</v>
       </c>
       <c r="P18" t="n">
-        <v>6.43</v>
+        <v>7.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>30.68</v>
+        <v>63.99</v>
       </c>
       <c r="R18" t="n">
-        <v>35.23</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>56.81</v>
+        <v>113.87</v>
       </c>
       <c r="T18" t="n">
-        <v>31.68</v>
+        <v>60.84</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>630702</v>
+        <v>270107</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>5.6</v>
+        <v>20.4</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>84.38</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-3.95</v>
+        <v>59.21</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1.47</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-28.52</v>
+        <v>-6.89</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-44.49</v>
+        <v>-20.67</v>
       </c>
       <c r="H19" t="n">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-11.72</v>
+        <v>-1.76</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2739,47 +2739,47 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>35.6</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>-22.68</v>
+        <v>-4.53</v>
       </c>
       <c r="P19" t="n">
-        <v>8.98</v>
+        <v>8.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>76.8</v>
+        <v>54.24</v>
       </c>
       <c r="R19" t="n">
-        <v>95.59</v>
+        <v>60.27</v>
       </c>
       <c r="S19" t="n">
-        <v>160.26</v>
+        <v>84.7</v>
       </c>
       <c r="T19" t="n">
-        <v>83.12</v>
+        <v>51.23</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>630503</v>
+        <v>270107</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>5.6</v>
+        <v>14.8</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,32 +2817,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>397.01</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-4.66</v>
+        <v>83.3</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1.06</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-12.21</v>
+        <v>-2</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-28.08</v>
+        <v>-6.33</v>
       </c>
       <c r="H20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.52</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2851,55 +2851,55 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-2.34</v>
+        <v>-0.71</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>49.3</v>
+        <v>36.7</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O20" s="3" t="n">
-        <v>-6.37</v>
+      <c r="O20" s="2" t="n">
+        <v>0.36</v>
       </c>
       <c r="P20" t="n">
-        <v>10.62</v>
+        <v>4.59</v>
       </c>
       <c r="Q20" t="n">
-        <v>354.86</v>
+        <v>79.48</v>
       </c>
       <c r="R20" t="n">
-        <v>406.53</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>618.87</v>
+        <v>113</v>
       </c>
       <c r="T20" t="n">
-        <v>347</v>
+        <v>80.55</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>730204</v>
+        <v>710101</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>5.6</v>
+        <v>14.8</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>59.84</v>
+        <v>33.1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-5.02</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>3.94</v>
+        <v>-1.66</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-12.6</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-26.56</v>
+        <v>-41.15</v>
       </c>
       <c r="H21" t="n">
-        <v>0.52</v>
+        <v>0.74</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-2.8</v>
+        <v>-5.4</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -2979,47 +2979,47 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>21</v>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>-10.24</v>
       </c>
       <c r="P21" t="n">
-        <v>11.1</v>
+        <v>6.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>53.2</v>
+        <v>31.02</v>
       </c>
       <c r="R21" t="n">
-        <v>61.56</v>
+        <v>34.99</v>
       </c>
       <c r="S21" t="n">
-        <v>89.69</v>
+        <v>56.7</v>
       </c>
       <c r="T21" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
+        <v>31.68</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>640209</v>
+        <v>630702</v>
       </c>
       <c r="Z21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3028,16 +3028,16 @@
         <v>0</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>5.6</v>
+        <v>14.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,28 +3057,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>385.98</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-7.4</v>
+        <v>-2.09</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-11.74</v>
+        <v>-23.6</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-48.88</v>
+        <v>-44.97</v>
       </c>
       <c r="H22" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -3091,55 +3091,55 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>17.7</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>-5.9</v>
+        <v>-21.24</v>
       </c>
       <c r="P22" t="n">
-        <v>10.93</v>
+        <v>6.59</v>
       </c>
       <c r="Q22" t="n">
-        <v>343.78</v>
+        <v>79.56</v>
       </c>
       <c r="R22" t="n">
-        <v>407.15</v>
+        <v>94.27</v>
       </c>
       <c r="S22" t="n">
-        <v>980</v>
+        <v>160.26</v>
       </c>
       <c r="T22" t="n">
-        <v>334</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
+        <v>83.12</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>270104</v>
+        <v>630503</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>5.6</v>
+        <v>14.8</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,32 +3177,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>161.67</v>
+        <v>401</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-10.01</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>-6.86</v>
+        <v>-2.11</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>1.83</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-42.96</v>
+        <v>-50.49</v>
       </c>
       <c r="H23" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.79</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-2.52</v>
+        <v>-1.6</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -3219,47 +3219,47 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>55.2</v>
+        <v>39.9</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O23" s="3" t="n">
-        <v>-1.02</v>
+      <c r="O23" s="2" t="n">
+        <v>4.19</v>
       </c>
       <c r="P23" t="n">
-        <v>13.04</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>140.59</v>
+        <v>361.48</v>
       </c>
       <c r="R23" t="n">
-        <v>165.85</v>
+        <v>407.51</v>
       </c>
       <c r="S23" t="n">
-        <v>325.74</v>
+        <v>980</v>
       </c>
       <c r="T23" t="n">
-        <v>133.61</v>
+        <v>334</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270401</v>
+        <v>270104</v>
       </c>
       <c r="Z23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3268,16 +3268,16 @@
         <v>0</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>5.6</v>
+        <v>14.8</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>51.63</v>
+        <v>338.96</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-6.23</v>
+        <v>-2.61</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-10.58</v>
+        <v>-10.56</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-25.41</v>
+        <v>-45.33</v>
       </c>
       <c r="H24" t="n">
-        <v>0.85</v>
+        <v>0.61</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-6.48</v>
+        <v>-5.73</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3339,47 +3339,47 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>26.7</v>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-4.74</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>7.56</v>
+        <v>7.49</v>
       </c>
       <c r="Q24" t="n">
-        <v>47.73</v>
+        <v>313.57</v>
       </c>
       <c r="R24" t="n">
-        <v>55.21</v>
+        <v>359.58</v>
       </c>
       <c r="S24" t="n">
-        <v>76.16</v>
+        <v>749.88</v>
       </c>
       <c r="T24" t="n">
-        <v>51.55</v>
+        <v>308</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>270504</v>
+        <v>270104</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>3.7</v>
+        <v>14.8</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>82.06</v>
+        <v>24.68</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-0.58</v>
+        <v>-3.18</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-8.69</v>
+        <v>-6.97</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-5.74</v>
+        <v>-31.27</v>
       </c>
       <c r="H25" t="n">
-        <v>0.47</v>
+        <v>0.68</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-2.29</v>
+        <v>-3.43</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>41.7</v>
+        <v>35.7</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3467,39 +3467,39 @@
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-2.85</v>
+        <v>-4.61</v>
       </c>
       <c r="P25" t="n">
-        <v>4.88</v>
+        <v>7.43</v>
       </c>
       <c r="Q25" t="n">
-        <v>78.06</v>
+        <v>22.85</v>
       </c>
       <c r="R25" t="n">
-        <v>83.98</v>
+        <v>25.56</v>
       </c>
       <c r="S25" t="n">
-        <v>113</v>
+        <v>42.08</v>
       </c>
       <c r="T25" t="n">
-        <v>80.55</v>
+        <v>23.8</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>710101</v>
+        <v>270303</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,28 +3537,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>63.46</v>
+        <v>180.33</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-4.56</v>
+        <v>-3.75</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-7.86</v>
+        <v>-0.97</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-31.69</v>
+        <v>-2.1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-3.38</v>
+        <v>-2.36</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -3579,47 +3579,47 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>46.6</v>
+        <v>49.2</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O26" s="3" t="n">
-        <v>-2.02</v>
+      <c r="O26" s="2" t="n">
+        <v>1.39</v>
       </c>
       <c r="P26" t="n">
-        <v>10.06</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>57.07</v>
+        <v>164.03</v>
       </c>
       <c r="R26" t="n">
-        <v>65.68000000000001</v>
+        <v>184.69</v>
       </c>
       <c r="S26" t="n">
-        <v>99.40000000000001</v>
+        <v>232.68</v>
       </c>
       <c r="T26" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>1</v>
+        <v>170.1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270303</v>
+        <v>270104</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>177.2</v>
+        <v>38.75</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.04</v>
+        <v>-2.39</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-10.53</v>
+        <v>-3.2</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.98</v>
+        <v>-21.24</v>
       </c>
       <c r="H27" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.61</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-4.1</v>
+        <v>-7.52</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>50.7</v>
+        <v>34.4</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3707,39 +3707,39 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.69</v>
+        <v>-0.84</v>
       </c>
       <c r="P27" t="n">
-        <v>9.23</v>
+        <v>11.78</v>
       </c>
       <c r="Q27" t="n">
-        <v>160.84</v>
+        <v>34.19</v>
       </c>
       <c r="R27" t="n">
-        <v>184.78</v>
+        <v>41.9</v>
       </c>
       <c r="S27" t="n">
-        <v>232.68</v>
+        <v>52.92</v>
       </c>
       <c r="T27" t="n">
-        <v>170.1</v>
+        <v>30.54</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>270104</v>
+        <v>270504</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>今日上涨且放量</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>37.23</v>
+        <v>166.07</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-6.32</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>-16.22</v>
+        <v>-4.84</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>7.56</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-19.17</v>
+        <v>-42.64</v>
       </c>
       <c r="H28" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.7</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3811,52 +3811,52 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-11.29</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-0.22</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>33.7</v>
+        <v>50.5</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O28" s="3" t="n">
-        <v>-10.38</v>
+      <c r="O28" s="2" t="n">
+        <v>9.92</v>
       </c>
       <c r="P28" t="n">
-        <v>12.31</v>
+        <v>12.19</v>
       </c>
       <c r="Q28" t="n">
-        <v>32.65</v>
+        <v>145.82</v>
       </c>
       <c r="R28" t="n">
-        <v>41.97</v>
+        <v>166.44</v>
       </c>
       <c r="S28" t="n">
-        <v>52.92</v>
+        <v>325.74</v>
       </c>
       <c r="T28" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>1</v>
+        <v>133.61</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>270504</v>
+        <v>270401</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -3868,11 +3868,11 @@
         <v>0</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3897,28 +3897,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>328.5</v>
+        <v>52.89</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.460000000000001</v>
+        <v>-5.32</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-20.3</v>
+        <v>-1.14</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-44.88</v>
+        <v>-29.4</v>
       </c>
       <c r="H29" t="n">
-        <v>0.61</v>
+        <v>0.88</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-9.15</v>
+        <v>-4.14</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -3939,47 +3939,47 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>34.2</v>
+        <v>36.5</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O29" s="3" t="n">
-        <v>-14.46</v>
+      <c r="O29" s="2" t="n">
+        <v>1.22</v>
       </c>
       <c r="P29" t="n">
-        <v>8.16</v>
+        <v>7.52</v>
       </c>
       <c r="Q29" t="n">
-        <v>301.71</v>
+        <v>48.91</v>
       </c>
       <c r="R29" t="n">
-        <v>361.58</v>
+        <v>55.18</v>
       </c>
       <c r="S29" t="n">
-        <v>749.88</v>
+        <v>75.66</v>
       </c>
       <c r="T29" t="n">
-        <v>308</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>270104</v>
+        <v>270504</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,8 +473,8 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="74" customWidth="1" min="31" max="31"/>
-    <col width="76" customWidth="1" min="32" max="32"/>
+    <col width="79" customWidth="1" min="31" max="31"/>
+    <col width="66" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
@@ -657,32 +657,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>127.8</v>
+        <v>215.98</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2</v>
+        <v>6.25</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>12.69</v>
+        <v>1.21</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-10.85</v>
+        <v>-16.06</v>
       </c>
       <c r="H2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.85</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -691,15 +691,15 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>5.15</v>
+        <v>7.71</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>57.5</v>
+        <v>56.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,39 +707,39 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>15.05</v>
+        <v>4.1</v>
       </c>
       <c r="P2" t="n">
-        <v>9.9</v>
+        <v>11.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>115.15</v>
+        <v>191.08</v>
       </c>
       <c r="R2" t="n">
-        <v>121.54</v>
+        <v>200.52</v>
       </c>
       <c r="S2" t="n">
-        <v>158.2</v>
+        <v>251</v>
       </c>
       <c r="T2" t="n">
-        <v>94.73</v>
+        <v>102.3</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>270202</v>
+        <v>730204</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,32 +777,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.63</v>
+        <v>68.7</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.12</v>
+        <v>2.77</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>33.62</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-14.68</v>
+        <v>-30.05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.03</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -811,15 +811,15 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>12.32</v>
+        <v>3.68</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>62.2</v>
+        <v>51.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -827,39 +827,39 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>35.98</v>
+        <v>10.93</v>
       </c>
       <c r="P3" t="n">
-        <v>12.62</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>195.42</v>
+        <v>62.03</v>
       </c>
       <c r="R3" t="n">
-        <v>199.09</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>263.21</v>
+        <v>96.09</v>
       </c>
       <c r="T3" t="n">
-        <v>125.61</v>
+        <v>47.3</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>730206</v>
+        <v>270303</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>48.1</v>
+        <v>42.6</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,32 +897,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>68.59</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>3.13</v>
+        <v>123.48</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-3.47</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10.66</v>
+        <v>8.01</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-27.74</v>
+        <v>-20.33</v>
       </c>
       <c r="H4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.87</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -931,15 +931,15 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>1.21</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,39 +947,39 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>13.02</v>
+        <v>10.9</v>
       </c>
       <c r="P4" t="n">
-        <v>9.92</v>
+        <v>10.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>61.78</v>
+        <v>110.97</v>
       </c>
       <c r="R4" t="n">
-        <v>66.01000000000001</v>
+        <v>122</v>
       </c>
       <c r="S4" t="n">
-        <v>99.40000000000001</v>
+        <v>158.2</v>
       </c>
       <c r="T4" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3</v>
+        <v>94.73</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270303</v>
+        <v>270202</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>46.3</v>
+        <v>42.6</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,28 +1017,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>206.39</v>
+        <v>277.65</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2.4</v>
+        <v>3.41</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>14.49</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-23.65</v>
+        <v>-18.69</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -1051,15 +1051,15 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>6.95</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>48.2</v>
+        <v>58.4</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1067,36 +1067,36 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>16.85</v>
+        <v>3.58</v>
       </c>
       <c r="P5" t="n">
-        <v>11.69</v>
+        <v>11.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>182.26</v>
+        <v>245.22</v>
       </c>
       <c r="R5" t="n">
-        <v>200.39</v>
+        <v>259.61</v>
       </c>
       <c r="S5" t="n">
-        <v>276.26</v>
+        <v>334.18</v>
       </c>
       <c r="T5" t="n">
-        <v>102.3</v>
+        <v>155.05</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>730204</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
         <v>11</v>
@@ -1108,11 +1108,11 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>44.4</v>
+        <v>40.7</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>423.69</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>2.14</v>
+        <v>219.03</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-6.57</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.96</v>
+        <v>22.36</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-23.7</v>
+        <v>-15.86</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.9</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4.06</v>
+        <v>8.92</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1187,39 +1187,39 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>5.32</v>
+        <v>25.25</v>
       </c>
       <c r="P6" t="n">
-        <v>10.61</v>
+        <v>12.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>378.74</v>
+        <v>191.09</v>
       </c>
       <c r="R6" t="n">
-        <v>407.14</v>
+        <v>201.09</v>
       </c>
       <c r="S6" t="n">
-        <v>618.87</v>
+        <v>259.79</v>
       </c>
       <c r="T6" t="n">
-        <v>347</v>
+        <v>125.61</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>730204</v>
+        <v>730206</v>
       </c>
       <c r="Z6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>42.6</v>
+        <v>40.7</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,28 +1257,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>95.54000000000001</v>
+        <v>191.22</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.73</v>
+        <v>6.59</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>8.32</v>
+        <v>10.44</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-37.24</v>
+        <v>-26.86</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>4.11</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>58</v>
+        <v>60.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,39 +1307,39 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>10.68</v>
+        <v>13.33</v>
       </c>
       <c r="P7" t="n">
-        <v>11.48</v>
+        <v>11.21</v>
       </c>
       <c r="Q7" t="n">
-        <v>84.56999999999999</v>
+        <v>169.78</v>
       </c>
       <c r="R7" t="n">
-        <v>91.77</v>
+        <v>176.3</v>
       </c>
       <c r="S7" t="n">
-        <v>168.08</v>
+        <v>264.88</v>
       </c>
       <c r="T7" t="n">
-        <v>80.31999999999999</v>
+        <v>152.33</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>640703</v>
+        <v>730204</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1348,16 +1348,16 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>42.6</v>
+        <v>38.9</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,28 +1377,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>252.83</v>
+        <v>424.34</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9.449999999999999</v>
+        <v>3.27</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1</v>
+        <v>2.49</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-16.84</v>
+        <v>-30.49</v>
       </c>
       <c r="H8" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>6.34</v>
+        <v>4.09</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>52.4</v>
+        <v>60.1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,39 +1427,39 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>2.46</v>
+        <v>5.38</v>
       </c>
       <c r="P8" t="n">
-        <v>10.01</v>
+        <v>10.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>227.52</v>
+        <v>380.85</v>
       </c>
       <c r="R8" t="n">
-        <v>237.76</v>
+        <v>407.66</v>
       </c>
       <c r="S8" t="n">
-        <v>418.99</v>
+        <v>618.87</v>
       </c>
       <c r="T8" t="n">
-        <v>183.83</v>
+        <v>347</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270103</v>
+        <v>730204</v>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1468,16 +1468,16 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>38.9</v>
+        <v>37</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>98.51000000000001</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.12</v>
+        <v>95.95</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-4.52</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>12.93</v>
+        <v>7.78</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-26.2</v>
+        <v>-28.15</v>
       </c>
       <c r="H9" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>63.8</v>
+        <v>58.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1547,16 +1547,16 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>15.29</v>
+        <v>10.67</v>
       </c>
       <c r="P9" t="n">
-        <v>10.65</v>
+        <v>11.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>88.01000000000001</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>92.58</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="S9" t="n">
         <v>144.2</v>
@@ -1569,14 +1569,14 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>650201</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
         <v>2</v>
@@ -1588,11 +1588,11 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>35.2</v>
+        <v>37</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1626,19 +1626,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59.68</v>
+        <v>60.3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9.609999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2.97</v>
+        <v>3.91</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-28.78</v>
+        <v>-25.61</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1651,15 +1651,15 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>5.26</v>
+        <v>6.15</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>47.1</v>
+        <v>52.6</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1667,16 +1667,16 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>5.33</v>
+        <v>6.8</v>
       </c>
       <c r="P10" t="n">
-        <v>9.960000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>53.73</v>
+        <v>54.26</v>
       </c>
       <c r="R10" t="n">
-        <v>56.7</v>
+        <v>56.81</v>
       </c>
       <c r="S10" t="n">
         <v>107.55</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W10" t="n">
@@ -1699,7 +1699,7 @@
         <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>33.3</v>
+        <v>35.2</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1746,19 +1746,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38.18</v>
+        <v>38.26</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.69</v>
+        <v>4.74</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>40.47</v>
+        <v>40.51</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-10.1</v>
+        <v>-10.73</v>
       </c>
       <c r="H11" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>15.26</v>
+        <v>13.61</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1779,44 +1779,44 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>71.90000000000001</v>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>超买区间</t>
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>42.83</v>
+        <v>43.4</v>
       </c>
       <c r="P11" t="n">
-        <v>14.65</v>
+        <v>14.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>32.59</v>
+        <v>32.67</v>
       </c>
       <c r="R11" t="n">
-        <v>33.12</v>
+        <v>33.68</v>
       </c>
       <c r="S11" t="n">
-        <v>45.19</v>
+        <v>43.43</v>
       </c>
       <c r="T11" t="n">
         <v>23.2</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W11" t="n">
         <v>640209</v>
       </c>
       <c r="Z11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="n">
         <v>4</v>
@@ -1828,11 +1828,11 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>33.3</v>
+        <v>35.2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1857,32 +1857,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>192</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>-2.59</v>
+        <v>94.81</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>3.55</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-25.33</v>
+        <v>-37.95</v>
       </c>
       <c r="H12" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.79</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.45</v>
+        <v>3.13</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1899,47 +1899,47 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>44.4</v>
+        <v>60.9</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O12" s="3" t="n">
-        <v>-0.23</v>
+      <c r="O12" s="2" t="n">
+        <v>6.44</v>
       </c>
       <c r="P12" t="n">
-        <v>10.59</v>
+        <v>11.68</v>
       </c>
       <c r="Q12" t="n">
-        <v>171.67</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>191.14</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>280.08</v>
+        <v>168.08</v>
       </c>
       <c r="T12" t="n">
-        <v>161.8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
+        <v>80.31999999999999</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>270202</v>
+        <v>640703</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AA12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,16 +1948,16 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>33.3</v>
+        <v>31.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>105.98</v>
+        <v>193.53</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>3.55</v>
+        <v>-0.11</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-2.09</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-36.88</v>
+        <v>-29.83</v>
       </c>
       <c r="H13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.01</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2.97</v>
+        <v>1.36</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>51.2</v>
+        <v>48.6</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -2027,39 +2027,39 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>5.91</v>
+        <v>0.8</v>
       </c>
       <c r="P13" t="n">
-        <v>10.09</v>
+        <v>10.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>95.29000000000001</v>
+        <v>173.5</v>
       </c>
       <c r="R13" t="n">
-        <v>102.92</v>
+        <v>190.94</v>
       </c>
       <c r="S13" t="n">
-        <v>187.66</v>
+        <v>280.08</v>
       </c>
       <c r="T13" t="n">
-        <v>90.23</v>
+        <v>161.8</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>640703</v>
+        <v>270202</v>
       </c>
       <c r="Z13" t="n">
         <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2067,8 +2067,8 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" t="n">
-        <v>31.5</v>
+      <c r="AD13" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,28 +2097,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>185.21</v>
+        <v>249.39</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.32</v>
+        <v>6.71</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>4.12</v>
+        <v>0.14</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-30.47</v>
+        <v>-24.43</v>
       </c>
       <c r="H14" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>5.6</v>
+        <v>4.88</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>55.6</v>
+        <v>55.2</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -2147,39 +2147,39 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>6.48</v>
+        <v>3.03</v>
       </c>
       <c r="P14" t="n">
-        <v>11.27</v>
+        <v>10.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>164.34</v>
+        <v>224.26</v>
       </c>
       <c r="R14" t="n">
-        <v>175.39</v>
+        <v>237.78</v>
       </c>
       <c r="S14" t="n">
-        <v>271.12</v>
+        <v>418.99</v>
       </c>
       <c r="T14" t="n">
-        <v>152.33</v>
+        <v>183.83</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>730204</v>
+        <v>270103</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2188,16 +2188,16 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>29.6</v>
+        <v>22.2</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线5-10%</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,32 +2217,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>268.49</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>-3.04</v>
+        <v>105.78</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>1.54</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-17.33</v>
+        <v>-39.06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.05</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2251,55 +2251,55 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>2.7</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>51.1</v>
+        <v>53.4</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O15" s="3" t="n">
-        <v>-0.68</v>
+      <c r="O15" s="2" t="n">
+        <v>4.43</v>
       </c>
       <c r="P15" t="n">
-        <v>12.02</v>
+        <v>9.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>236.21</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>259.52</v>
+        <v>103</v>
       </c>
       <c r="S15" t="n">
-        <v>345.5</v>
+        <v>187.66</v>
       </c>
       <c r="T15" t="n">
-        <v>155.05</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
+        <v>90.23</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>730204</v>
+        <v>640703</v>
       </c>
       <c r="Z15" t="n">
         <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>27.8</v>
+        <v>22.2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2346,40 +2346,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60.28</v>
+        <v>60.06</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>-0.64</v>
+        <v>3.53</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.15</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-40.28</v>
+        <v>-45.9</v>
       </c>
       <c r="H16" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
         <v>0.67</v>
       </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>1.04</v>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>46.6</v>
+        <v>48.6</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1.72</v>
+        <v>3.04</v>
       </c>
       <c r="P16" t="n">
-        <v>14.76</v>
+        <v>14.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>51.38</v>
+        <v>51.39</v>
       </c>
       <c r="R16" t="n">
         <v>59.66</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -2419,7 +2419,7 @@
         <v>7</v>
       </c>
       <c r="AA16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>27.8</v>
+        <v>16.7</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2466,23 +2466,23 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>62.03</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-0.64</v>
+        <v>61.75</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1.1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>17.95</v>
+        <v>16.66</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-25.14</v>
+        <v>-29.01</v>
       </c>
       <c r="H17" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.53</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0.01</v>
+        <v>-1.16</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>41.1</v>
+        <v>43.5</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>20.31</v>
+        <v>19.55</v>
       </c>
       <c r="P17" t="n">
-        <v>10.39</v>
+        <v>10.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>55.59</v>
+        <v>55.4</v>
       </c>
       <c r="R17" t="n">
-        <v>62.04</v>
+        <v>62.48</v>
       </c>
       <c r="S17" t="n">
-        <v>89.69</v>
+        <v>85.58</v>
       </c>
       <c r="T17" t="n">
         <v>45.82</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W17" t="n">
@@ -2539,7 +2539,7 @@
         <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>1.33</v>
+        <v>181.21</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-0.79</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-10.54</v>
+        <v>-0.79</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-26.56</v>
+        <v>-3.25</v>
       </c>
       <c r="H18" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-3.05</v>
+        <v>-1.85</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2619,47 +2619,47 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>31</v>
+        <v>53.3</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O18" s="3" t="n">
-        <v>-8.18</v>
+      <c r="O18" s="2" t="n">
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>7.99</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>63.99</v>
+        <v>164.95</v>
       </c>
       <c r="R18" t="n">
-        <v>71.73999999999999</v>
+        <v>184.62</v>
       </c>
       <c r="S18" t="n">
-        <v>113.87</v>
+        <v>232.68</v>
       </c>
       <c r="T18" t="n">
-        <v>60.84</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>1</v>
+        <v>170.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270107</v>
+        <v>270104</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>20.4</v>
+        <v>11.1</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2706,19 +2706,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>59.21</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>1.47</v>
+        <v>58.31</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.05</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-6.89</v>
+        <v>-7.66</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-20.67</v>
+        <v>-25.06</v>
       </c>
       <c r="H19" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -2731,15 +2731,15 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-2.86</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>35.6</v>
+        <v>33.6</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2747,16 +2747,16 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>-4.53</v>
+        <v>-4.77</v>
       </c>
       <c r="P19" t="n">
-        <v>8.4</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>54.24</v>
+        <v>53.52</v>
       </c>
       <c r="R19" t="n">
-        <v>60.27</v>
+        <v>60.03</v>
       </c>
       <c r="S19" t="n">
         <v>84.7</v>
@@ -2764,12 +2764,12 @@
       <c r="T19" t="n">
         <v>51.23</v>
       </c>
-      <c r="U19" s="3" t="n">
-        <v>1</v>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W19" t="n">
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>14.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>1.06</v>
+        <v>67.75</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.54</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-2</v>
+        <v>-14.76</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-6.33</v>
+        <v>-34.96</v>
       </c>
       <c r="H20" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -2851,55 +2851,55 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>金叉(转多)</t>
+        <v>-4.78</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>36.7</v>
+        <v>30.7</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O20" s="2" t="n">
-        <v>0.36</v>
+      <c r="O20" s="3" t="n">
+        <v>-11.87</v>
       </c>
       <c r="P20" t="n">
-        <v>4.59</v>
+        <v>8.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>79.48</v>
+        <v>62.26</v>
       </c>
       <c r="R20" t="n">
-        <v>83.90000000000001</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>113</v>
+        <v>113.87</v>
       </c>
       <c r="T20" t="n">
-        <v>80.55</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
+        <v>60.84</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>710101</v>
+        <v>270107</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>14.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,32 +2937,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-1.66</v>
+        <v>38.45</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0.21</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-12.6</v>
+        <v>-5.11</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-41.15</v>
+        <v>-22.45</v>
       </c>
       <c r="H21" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.6</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-5.4</v>
+        <v>-8.01</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -2979,47 +2979,47 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>21</v>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>38</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-10.24</v>
+        <v>-2.22</v>
       </c>
       <c r="P21" t="n">
-        <v>6.28</v>
+        <v>11.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>31.02</v>
+        <v>34.01</v>
       </c>
       <c r="R21" t="n">
-        <v>34.99</v>
+        <v>41.8</v>
       </c>
       <c r="S21" t="n">
-        <v>56.7</v>
+        <v>52.92</v>
       </c>
       <c r="T21" t="n">
-        <v>31.68</v>
+        <v>30.54</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>630702</v>
+        <v>270504</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,28 +3057,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.18000000000001</v>
+        <v>32.88</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-2.09</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-23.6</v>
+        <v>-11.09</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-44.97</v>
+        <v>-40.33</v>
       </c>
       <c r="H22" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>-9.640000000000001</v>
+        <v>-5.47</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>17.7</v>
+        <v>20.7</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
@@ -3107,39 +3107,39 @@
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>-21.24</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>6.59</v>
+        <v>6.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>79.56</v>
+        <v>30.81</v>
       </c>
       <c r="R22" t="n">
-        <v>94.27</v>
+        <v>34.78</v>
       </c>
       <c r="S22" t="n">
-        <v>160.26</v>
+        <v>56.7</v>
       </c>
       <c r="T22" t="n">
-        <v>83.12</v>
+        <v>31.68</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>630503</v>
+        <v>630702</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>401</v>
+        <v>84.67</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-2.11</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>1.83</v>
+        <v>-1.47</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-23.65</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-50.49</v>
+        <v>-44.54</v>
       </c>
       <c r="H23" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
@@ -3211,56 +3211,56 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-1.6</v>
+        <v>-8.92</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="n">
-        <v>4.19</v>
+        <v>18.2</v>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>-20.76</v>
       </c>
       <c r="P23" t="n">
-        <v>9.859999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>361.48</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>407.51</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>980</v>
+        <v>160.26</v>
       </c>
       <c r="T23" t="n">
-        <v>334</v>
-      </c>
-      <c r="U23" t="n">
+        <v>83.12</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>630503</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
         <v>3</v>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="W23" t="n">
-        <v>270104</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>8</v>
-      </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>338.96</v>
+        <v>24.57</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-2.61</v>
+        <v>-2.19</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-10.56</v>
+        <v>-9.1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-45.33</v>
+        <v>-32.33</v>
       </c>
       <c r="H24" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-5.73</v>
+        <v>-3.4</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3339,47 +3339,47 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>38.9</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-8.199999999999999</v>
+        <v>-6.21</v>
       </c>
       <c r="P24" t="n">
-        <v>7.49</v>
+        <v>7.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>313.57</v>
+        <v>22.8</v>
       </c>
       <c r="R24" t="n">
-        <v>359.58</v>
+        <v>25.43</v>
       </c>
       <c r="S24" t="n">
-        <v>749.88</v>
+        <v>42.08</v>
       </c>
       <c r="T24" t="n">
-        <v>308</v>
+        <v>23.8</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>270104</v>
+        <v>270303</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>24.68</v>
+        <v>335.09</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-3.18</v>
+        <v>-3.43</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-6.97</v>
+        <v>-11.59</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-31.27</v>
+        <v>-50.53</v>
       </c>
       <c r="H25" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-3.43</v>
+        <v>-6.24</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3459,47 +3459,47 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>28.3</v>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-4.61</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>22.85</v>
+        <v>309.97</v>
       </c>
       <c r="R25" t="n">
-        <v>25.56</v>
+        <v>357.38</v>
       </c>
       <c r="S25" t="n">
-        <v>42.08</v>
+        <v>749.88</v>
       </c>
       <c r="T25" t="n">
-        <v>23.8</v>
+        <v>308</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>270303</v>
+        <v>270104</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,28 +3537,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>180.33</v>
+        <v>396.93</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-3.75</v>
+        <v>-5.09</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.29</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-2.1</v>
+        <v>-55.45</v>
       </c>
       <c r="H26" t="n">
-        <v>0.52</v>
+        <v>0.76</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -3571,15 +3571,15 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-2.36</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-2.58</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>49.2</v>
+        <v>38.9</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3587,29 +3587,29 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1.39</v>
+        <v>2.6</v>
       </c>
       <c r="P26" t="n">
-        <v>9.039999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>164.03</v>
+        <v>358.09</v>
       </c>
       <c r="R26" t="n">
-        <v>184.69</v>
+        <v>407.45</v>
       </c>
       <c r="S26" t="n">
-        <v>232.68</v>
+        <v>980</v>
       </c>
       <c r="T26" t="n">
-        <v>170.1</v>
+        <v>334</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>38.75</v>
+        <v>164.03</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>-3.2</v>
+        <v>-5.28</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>4.38</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-21.24</v>
+        <v>-46.43</v>
       </c>
       <c r="H27" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.7</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3691,55 +3691,55 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-7.52</v>
+        <v>-1.65</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>34.4</v>
+        <v>44.6</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O27" s="3" t="n">
-        <v>-0.84</v>
+      <c r="O27" s="2" t="n">
+        <v>7.27</v>
       </c>
       <c r="P27" t="n">
-        <v>11.78</v>
+        <v>11.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>34.19</v>
+        <v>144.76</v>
       </c>
       <c r="R27" t="n">
-        <v>41.9</v>
+        <v>166.78</v>
       </c>
       <c r="S27" t="n">
-        <v>52.92</v>
+        <v>325.74</v>
       </c>
       <c r="T27" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>1</v>
+        <v>133.61</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>270504</v>
+        <v>270401</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
           <t>无明显信号</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>今日上涨且放量</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,28 +3777,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>166.07</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>-4.84</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>7.56</v>
+        <v>82.68000000000001</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>-1.97</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-42.64</v>
+        <v>-15.48</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-0.22</v>
+        <v>-1.36</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>50.5</v>
+        <v>37</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3827,36 +3827,36 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>9.92</v>
+        <v>0.92</v>
       </c>
       <c r="P28" t="n">
-        <v>12.19</v>
+        <v>4.54</v>
       </c>
       <c r="Q28" t="n">
-        <v>145.82</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="R28" t="n">
-        <v>166.44</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>325.74</v>
+        <v>113</v>
       </c>
       <c r="T28" t="n">
-        <v>133.61</v>
+        <v>80.55</v>
       </c>
       <c r="U28" t="n">
         <v>3</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>270401</v>
+        <v>710101</v>
       </c>
       <c r="Z28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -3868,11 +3868,11 @@
         <v>0</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3906,19 +3906,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52.89</v>
+        <v>52.13</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.32</v>
+        <v>-4.26</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.14</v>
+        <v>-2.27</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-29.4</v>
+        <v>-29.82</v>
       </c>
       <c r="H29" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.14</v>
+        <v>-5.42</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>36.5</v>
+        <v>36.1</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3947,19 +3947,19 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>1.22</v>
+        <v>0.62</v>
       </c>
       <c r="P29" t="n">
-        <v>7.52</v>
+        <v>7.39</v>
       </c>
       <c r="Q29" t="n">
-        <v>48.91</v>
+        <v>48.28</v>
       </c>
       <c r="R29" t="n">
-        <v>55.18</v>
+        <v>55.12</v>
       </c>
       <c r="S29" t="n">
-        <v>75.66</v>
+        <v>71.36</v>
       </c>
       <c r="T29" t="n">
         <v>51</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,8 +473,8 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="79" customWidth="1" min="31" max="31"/>
-    <col width="66" customWidth="1" min="32" max="32"/>
+    <col width="81" customWidth="1" min="31" max="31"/>
+    <col width="76" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
@@ -657,32 +657,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>215.98</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6.25</v>
+        <v>7.27</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1.21</v>
+        <v>9.57</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-16.06</v>
+        <v>-34.16</v>
       </c>
       <c r="H2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.89</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -691,15 +691,15 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>7.71</v>
+        <v>7.83</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>56.7</v>
+        <v>55.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,36 +707,36 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>4.1</v>
+        <v>11.98</v>
       </c>
       <c r="P2" t="n">
-        <v>11.53</v>
+        <v>10.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>191.08</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>200.52</v>
+        <v>92.36</v>
       </c>
       <c r="S2" t="n">
-        <v>251</v>
+        <v>157.42</v>
       </c>
       <c r="T2" t="n">
-        <v>102.3</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>730204</v>
+        <v>640703</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
         <v>13</v>
@@ -748,11 +748,11 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；突破20日新高；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -786,23 +786,23 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>68.7</v>
+        <v>69.7</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.77</v>
+        <v>7.36</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-30.05</v>
+        <v>-22.62</v>
       </c>
       <c r="H3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -811,15 +811,15 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3.68</v>
+        <v>4.78</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>51.2</v>
+        <v>48.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -827,39 +827,39 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>10.93</v>
+        <v>10.29</v>
       </c>
       <c r="P3" t="n">
-        <v>9.710000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>62.03</v>
+        <v>63.37</v>
       </c>
       <c r="R3" t="n">
-        <v>66.26000000000001</v>
+        <v>66.52</v>
       </c>
       <c r="S3" t="n">
-        <v>96.09</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>47.3</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>270303</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>42.6</v>
+        <v>61.1</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,28 +897,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>123.48</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-3.47</v>
+        <v>260.44</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>13.01</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>8.01</v>
+        <v>5.57</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-20.33</v>
+        <v>-26.59</v>
       </c>
       <c r="H4" t="n">
-        <v>0.87</v>
+        <v>1.05</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1.21</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>52.1</v>
+        <v>58.3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,39 +947,39 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>10.9</v>
+        <v>7.98</v>
       </c>
       <c r="P4" t="n">
-        <v>10.13</v>
+        <v>9.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>110.97</v>
+        <v>235.44</v>
       </c>
       <c r="R4" t="n">
-        <v>122</v>
+        <v>238.47</v>
       </c>
       <c r="S4" t="n">
-        <v>158.2</v>
+        <v>418.99</v>
       </c>
       <c r="T4" t="n">
-        <v>94.73</v>
+        <v>183.83</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270202</v>
+        <v>270103</v>
       </c>
       <c r="Z4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>42.6</v>
+        <v>55.6</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；突破20日新高；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>277.65</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>3.41</v>
+        <v>123.5</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-3.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.89</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-18.69</v>
+        <v>-16.15</v>
       </c>
       <c r="H5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.93</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1051,15 +1051,15 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>6.95</v>
+        <v>1.13</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>58.4</v>
+        <v>48.2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1067,39 +1067,39 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>11.68</v>
+        <v>10.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>245.22</v>
+        <v>110.94</v>
       </c>
       <c r="R5" t="n">
-        <v>259.61</v>
+        <v>122.12</v>
       </c>
       <c r="S5" t="n">
-        <v>334.18</v>
+        <v>158.2</v>
       </c>
       <c r="T5" t="n">
-        <v>155.05</v>
+        <v>94.73</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>730204</v>
+        <v>270202</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1108,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>40.7</v>
+        <v>46.3</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线5-10%</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,28 +1137,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>219.03</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-6.57</v>
+        <v>229.35</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>14.18</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>22.36</v>
+        <v>6.94</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-15.86</v>
+        <v>-1.61</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>8.92</v>
+        <v>13.96</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>63</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1187,39 +1187,39 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>25.25</v>
+        <v>9.35</v>
       </c>
       <c r="P6" t="n">
-        <v>12.76</v>
+        <v>11.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>191.09</v>
+        <v>201.98</v>
       </c>
       <c r="R6" t="n">
-        <v>201.09</v>
+        <v>201.26</v>
       </c>
       <c r="S6" t="n">
-        <v>259.79</v>
+        <v>251</v>
       </c>
       <c r="T6" t="n">
-        <v>125.61</v>
+        <v>102.3</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>730206</v>
+        <v>730204</v>
       </c>
       <c r="Z6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>40.7</v>
+        <v>44.4</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1266,19 +1266,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>191.22</v>
+        <v>195.4</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6.59</v>
+        <v>10.17</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>10.44</v>
+        <v>9.42</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-26.86</v>
+        <v>-18.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>10.31</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>60.8</v>
+        <v>59.7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>13.33</v>
+        <v>11.83</v>
       </c>
       <c r="P7" t="n">
-        <v>11.21</v>
+        <v>10.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>169.78</v>
+        <v>174.3</v>
       </c>
       <c r="R7" t="n">
-        <v>176.3</v>
+        <v>177.14</v>
       </c>
       <c r="S7" t="n">
         <v>264.88</v>
@@ -1329,14 +1329,14 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>730204</v>
       </c>
       <c r="Z7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="n">
         <v>12</v>
@@ -1348,16 +1348,16 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>38.9</v>
+        <v>44.4</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1386,16 +1386,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>424.34</v>
+        <v>445</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.27</v>
+        <v>5.2</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2.49</v>
+        <v>0.68</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-30.49</v>
+        <v>-21.38</v>
       </c>
       <c r="H8" t="n">
         <v>0.9</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4.09</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>60.1</v>
+        <v>65</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,16 +1427,16 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>5.38</v>
+        <v>3.09</v>
       </c>
       <c r="P8" t="n">
-        <v>10.25</v>
+        <v>10.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>380.85</v>
+        <v>400.31</v>
       </c>
       <c r="R8" t="n">
-        <v>407.66</v>
+        <v>407.81</v>
       </c>
       <c r="S8" t="n">
         <v>618.87</v>
@@ -1449,17 +1449,17 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>730204</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1468,16 +1468,16 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>37</v>
+        <v>44.4</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>95.95</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-4.52</v>
+        <v>174.32</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>3.98</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>7.78</v>
+        <v>10.26</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-28.15</v>
+        <v>-42.07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.76</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,15 +1531,15 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3.25</v>
+        <v>4.01</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>58.8</v>
+        <v>47.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1547,39 +1547,39 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>10.67</v>
+        <v>12.67</v>
       </c>
       <c r="P9" t="n">
-        <v>11.16</v>
+        <v>11.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>85.23999999999999</v>
+        <v>154.91</v>
       </c>
       <c r="R9" t="n">
-        <v>92.93000000000001</v>
+        <v>167.59</v>
       </c>
       <c r="S9" t="n">
-        <v>144.2</v>
+        <v>325.74</v>
       </c>
       <c r="T9" t="n">
-        <v>69.8</v>
+        <v>133.61</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>650201</v>
+        <v>270401</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1588,16 +1588,16 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>37</v>
+        <v>44.4</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1626,23 +1626,23 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>60.3</v>
+        <v>64.27</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12.5</v>
+        <v>23.5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3.91</v>
+        <v>10.62</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-25.61</v>
+        <v>-30.78</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.25</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>6.15</v>
+        <v>12.52</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>52.6</v>
+        <v>60.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1667,16 +1667,16 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>6.8</v>
+        <v>13.03</v>
       </c>
       <c r="P10" t="n">
-        <v>10.02</v>
+        <v>9.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>54.26</v>
+        <v>57.91</v>
       </c>
       <c r="R10" t="n">
-        <v>56.81</v>
+        <v>57.12</v>
       </c>
       <c r="S10" t="n">
         <v>107.55</v>
@@ -1689,17 +1689,17 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W10" t="n">
         <v>640108</v>
       </c>
       <c r="Z10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1708,16 +1708,16 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>35.2</v>
+        <v>40.7</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线5-10%</t>
+          <t>股价站上20日均线；突破20日新高；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38.26</v>
+        <v>284.66</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4.74</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>40.51</v>
+        <v>4.43</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-10.73</v>
+        <v>-10.34</v>
       </c>
       <c r="H11" t="n">
-        <v>1.19</v>
+        <v>0.88</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>13.61</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1779,47 +1779,47 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>超买区间</t>
+        <v>61.9</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>43.4</v>
+        <v>6.84</v>
       </c>
       <c r="P11" t="n">
-        <v>14.61</v>
+        <v>11.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>32.67</v>
+        <v>251.73</v>
       </c>
       <c r="R11" t="n">
-        <v>33.68</v>
+        <v>260.22</v>
       </c>
       <c r="S11" t="n">
-        <v>43.43</v>
+        <v>313.49</v>
       </c>
       <c r="T11" t="n">
-        <v>23.2</v>
+        <v>155.05</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>640209</v>
+        <v>730204</v>
       </c>
       <c r="Z11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,16 +1828,16 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>35.2</v>
+        <v>40.7</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,32 +1857,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>94.81</v>
+        <v>227.98</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.03</v>
+        <v>1.57</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3.55</v>
+        <v>26.04</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-37.95</v>
+        <v>-7.26</v>
       </c>
       <c r="H12" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.85</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>3.13</v>
+        <v>12.06</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>60.9</v>
+        <v>68.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>6.44</v>
+        <v>28.45</v>
       </c>
       <c r="P12" t="n">
-        <v>11.68</v>
+        <v>12.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>83.73999999999999</v>
+        <v>198.89</v>
       </c>
       <c r="R12" t="n">
-        <v>91.93000000000001</v>
+        <v>203.45</v>
       </c>
       <c r="S12" t="n">
-        <v>168.08</v>
+        <v>258.39</v>
       </c>
       <c r="T12" t="n">
-        <v>80.31999999999999</v>
+        <v>125.61</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>640703</v>
+        <v>730206</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,16 +1948,16 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>31.5</v>
+        <v>38.9</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>193.53</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-2.09</v>
+        <v>37.72</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>33.47</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-29.83</v>
+        <v>-6.08</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.1</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.36</v>
+        <v>10.46</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>48.6</v>
+        <v>66.8</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -2027,39 +2027,39 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>0.8</v>
+        <v>35.88</v>
       </c>
       <c r="P13" t="n">
-        <v>10.35</v>
+        <v>14.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>173.5</v>
+        <v>32.21</v>
       </c>
       <c r="R13" t="n">
-        <v>190.94</v>
+        <v>34.15</v>
       </c>
       <c r="S13" t="n">
-        <v>280.08</v>
+        <v>43.43</v>
       </c>
       <c r="T13" t="n">
-        <v>161.8</v>
+        <v>23.2</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270202</v>
+        <v>640209</v>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2067,17 +2067,17 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" s="3" t="n">
-        <v>27.8</v>
+      <c r="AD13" t="n">
+        <v>37</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,28 +2097,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>249.39</v>
+        <v>61.48</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.14</v>
+        <v>5.96</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-4.43</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-24.43</v>
+        <v>-43.6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>4.88</v>
+        <v>3.29</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -2139,47 +2139,47 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>55.2</v>
+        <v>46.1</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n">
-        <v>3.03</v>
+      <c r="O14" s="3" t="n">
+        <v>-2.02</v>
       </c>
       <c r="P14" t="n">
-        <v>10.08</v>
+        <v>13.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>224.26</v>
+        <v>53.27</v>
       </c>
       <c r="R14" t="n">
-        <v>237.78</v>
+        <v>59.52</v>
       </c>
       <c r="S14" t="n">
-        <v>418.99</v>
+        <v>114.5</v>
       </c>
       <c r="T14" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U14" s="2" t="n">
-        <v>4</v>
+        <v>53.35</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>270103</v>
+        <v>270203</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2187,17 +2187,17 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="n">
-        <v>22.2</v>
+      <c r="AD14" t="n">
+        <v>37</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,32 +2217,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>105.78</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>-0.02</v>
+        <v>84.3</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2.49</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.54</v>
+        <v>0.23</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-39.06</v>
+        <v>-14.64</v>
       </c>
       <c r="H15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2.7</v>
+        <v>0.57</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>53.4</v>
+        <v>32.4</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2267,39 +2267,39 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>4.43</v>
+        <v>2.64</v>
       </c>
       <c r="P15" t="n">
-        <v>9.92</v>
+        <v>3.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>95.29000000000001</v>
+        <v>80.94</v>
       </c>
       <c r="R15" t="n">
-        <v>103</v>
+        <v>83.83</v>
       </c>
       <c r="S15" t="n">
-        <v>187.66</v>
+        <v>113</v>
       </c>
       <c r="T15" t="n">
-        <v>90.23</v>
+        <v>80.55</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>640703</v>
+        <v>710101</v>
       </c>
       <c r="Z15" t="n">
         <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2307,8 +2307,8 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="n">
-        <v>22.2</v>
+      <c r="AD15" t="n">
+        <v>37</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,28 +2337,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60.06</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.15</v>
+        <v>7.76</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-7.09</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-45.9</v>
+        <v>-27.64</v>
       </c>
       <c r="H16" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -2371,55 +2371,55 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.67</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>48.6</v>
+        <v>44</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O16" s="2" t="n">
-        <v>3.04</v>
+      <c r="O16" s="3" t="n">
+        <v>-4.68</v>
       </c>
       <c r="P16" t="n">
-        <v>14.43</v>
+        <v>7.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>51.39</v>
+        <v>67.16</v>
       </c>
       <c r="R16" t="n">
-        <v>59.66</v>
+        <v>70.88</v>
       </c>
       <c r="S16" t="n">
-        <v>115.44</v>
+        <v>113.87</v>
       </c>
       <c r="T16" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="U16" s="2" t="n">
-        <v>4</v>
+        <v>60.84</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>270203</v>
+        <v>270107</v>
       </c>
       <c r="Z16" t="n">
         <v>7</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2427,8 +2427,8 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" s="3" t="n">
-        <v>16.7</v>
+      <c r="AD16" t="n">
+        <v>35.2</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,89 +2457,89 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>61.75</v>
+        <v>61.38</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>16.66</v>
+        <v>5.83</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-3.91</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-29.01</v>
+        <v>-14.27</v>
       </c>
       <c r="H17" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.75</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>43.5</v>
+        <v>41.5</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O17" s="2" t="n">
-        <v>19.55</v>
+      <c r="O17" s="3" t="n">
+        <v>-1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>10.29</v>
+        <v>7.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>55.4</v>
+        <v>56.49</v>
       </c>
       <c r="R17" t="n">
-        <v>62.48</v>
+        <v>59.9</v>
       </c>
       <c r="S17" t="n">
-        <v>85.58</v>
+        <v>84.7</v>
       </c>
       <c r="T17" t="n">
-        <v>45.82</v>
+        <v>51.23</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>640209</v>
+        <v>270107</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2547,17 +2547,17 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" s="3" t="n">
-        <v>16.7</v>
+      <c r="AD17" t="n">
+        <v>35.2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,41 +2577,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>181.21</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>-0.79</v>
+        <v>63.28</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>16.93</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-3.25</v>
+        <v>-23.36</v>
       </c>
       <c r="H18" t="n">
         <v>0.55</v>
       </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>-1.85</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.55</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>53.3</v>
+        <v>36.8</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2627,36 +2627,36 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>2.1</v>
+        <v>19.34</v>
       </c>
       <c r="P18" t="n">
-        <v>8.970000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>164.95</v>
+        <v>57.41</v>
       </c>
       <c r="R18" t="n">
-        <v>184.62</v>
+        <v>62.93</v>
       </c>
       <c r="S18" t="n">
-        <v>232.68</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>170.1</v>
+        <v>45.82</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270104</v>
+        <v>640209</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="n">
         <v>6</v>
@@ -2667,12 +2667,12 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" s="3" t="n">
-        <v>11.1</v>
+      <c r="AD18" t="n">
+        <v>35.2</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58.31</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>-7.66</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>-25.06</v>
+        <v>190.04</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>5.11</v>
       </c>
       <c r="H19" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -2727,11 +2727,11 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>-2.86</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>2.67</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -2739,47 +2739,47 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>33.6</v>
+        <v>45.9</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O19" s="3" t="n">
-        <v>-4.77</v>
+      <c r="O19" s="2" t="n">
+        <v>7.63</v>
       </c>
       <c r="P19" t="n">
-        <v>8.210000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>53.52</v>
+        <v>174.74</v>
       </c>
       <c r="R19" t="n">
-        <v>60.03</v>
+        <v>185.09</v>
       </c>
       <c r="S19" t="n">
-        <v>84.7</v>
+        <v>232.68</v>
       </c>
       <c r="T19" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
+        <v>170.1</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270107</v>
+        <v>270104</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2787,17 +2787,17 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD19" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,89 +2817,89 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>67.75</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-14.76</v>
+        <v>107.8</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.96</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-34.96</v>
+        <v>-33.02</v>
       </c>
       <c r="H20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.02</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>-4.78</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>30.7</v>
+        <v>53.6</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O20" s="3" t="n">
-        <v>-11.87</v>
+      <c r="O20" s="2" t="n">
+        <v>3.37</v>
       </c>
       <c r="P20" t="n">
-        <v>8.1</v>
+        <v>9.77</v>
       </c>
       <c r="Q20" t="n">
-        <v>62.26</v>
+        <v>97.27</v>
       </c>
       <c r="R20" t="n">
-        <v>71.15000000000001</v>
+        <v>103.05</v>
       </c>
       <c r="S20" t="n">
-        <v>113.87</v>
+        <v>187.66</v>
       </c>
       <c r="T20" t="n">
-        <v>60.84</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>1</v>
+        <v>90.23</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>270107</v>
+        <v>640703</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2907,17 +2907,17 @@
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD20" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,49 +2937,49 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38.45</v>
+        <v>25.47</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.21</v>
+        <v>3.24</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-5.11</v>
+        <v>-6.98</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-22.45</v>
+        <v>-28.72</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.77</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>-8.01</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>38</v>
+        <v>41.6</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2987,39 +2987,39 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-2.22</v>
+        <v>-4.57</v>
       </c>
       <c r="P21" t="n">
-        <v>11.55</v>
+        <v>6.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>34.01</v>
+        <v>23.72</v>
       </c>
       <c r="R21" t="n">
-        <v>41.8</v>
+        <v>25.34</v>
       </c>
       <c r="S21" t="n">
-        <v>52.92</v>
+        <v>42.08</v>
       </c>
       <c r="T21" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>1</v>
+        <v>23.8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270504</v>
+        <v>270303</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3027,17 +3027,17 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" s="3" t="n">
-        <v>5.6</v>
+      <c r="AD21" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,28 +3057,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>32.88</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>413.09</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>2.57</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-11.09</v>
+        <v>-0.49</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-40.33</v>
+        <v>-56.56</v>
       </c>
       <c r="H22" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -3087,59 +3087,59 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>-5.47</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>-8.199999999999999</v>
+        <v>42.4</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>1.92</v>
       </c>
       <c r="P22" t="n">
-        <v>6.3</v>
+        <v>9.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>30.81</v>
+        <v>374.52</v>
       </c>
       <c r="R22" t="n">
-        <v>34.78</v>
+        <v>407.35</v>
       </c>
       <c r="S22" t="n">
-        <v>56.7</v>
+        <v>978</v>
       </c>
       <c r="T22" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>0</v>
+        <v>334</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>630702</v>
+        <v>270104</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3147,17 +3147,17 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="n">
-        <v>5.6</v>
+      <c r="AD22" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>84.67</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>-1.47</v>
+        <v>196.15</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0.89</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-23.65</v>
+        <v>-2.45</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-44.54</v>
+        <v>-24.65</v>
       </c>
       <c r="H23" t="n">
-        <v>0.78</v>
+        <v>0.98</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
@@ -3207,59 +3207,59 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>-8.92</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>2.86</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>48.7</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-20.76</v>
+        <v>-0.04</v>
       </c>
       <c r="P23" t="n">
-        <v>6.49</v>
+        <v>10.22</v>
       </c>
       <c r="Q23" t="n">
-        <v>79.18000000000001</v>
+        <v>176.1</v>
       </c>
       <c r="R23" t="n">
-        <v>92.95999999999999</v>
+        <v>190.69</v>
       </c>
       <c r="S23" t="n">
-        <v>160.26</v>
+        <v>280.08</v>
       </c>
       <c r="T23" t="n">
-        <v>83.12</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>1</v>
+        <v>161.8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>630503</v>
+        <v>270202</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA23" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3267,17 +3267,17 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" s="3" t="n">
-        <v>5.6</v>
+      <c r="AD23" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,89 +3297,89 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.57</v>
+        <v>93.38</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>-9.1</v>
+        <v>-2.82</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>6.13</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-32.33</v>
+        <v>-33.28</v>
       </c>
       <c r="H24" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.95</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>38.9</v>
+        <v>46.7</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O24" s="3" t="n">
-        <v>-6.21</v>
+      <c r="O24" s="2" t="n">
+        <v>8.539999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>7.2</v>
+        <v>11.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>22.8</v>
+        <v>82.87</v>
       </c>
       <c r="R24" t="n">
-        <v>25.43</v>
+        <v>93.2</v>
       </c>
       <c r="S24" t="n">
-        <v>42.08</v>
+        <v>141.8</v>
       </c>
       <c r="T24" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>1</v>
+        <v>69.8</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>270303</v>
+        <v>650201</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,16 +3388,16 @@
         <v>0</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>5.6</v>
+        <v>27.8</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>335.09</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-3.43</v>
+        <v>346.96</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>2.18</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-11.59</v>
+        <v>-8.85</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-50.53</v>
+        <v>-48.95</v>
       </c>
       <c r="H25" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -3451,32 +3451,32 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-6.24</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-2.46</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>33.1</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-8.699999999999999</v>
+        <v>-6.44</v>
       </c>
       <c r="P25" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>309.97</v>
+        <v>322.31</v>
       </c>
       <c r="R25" t="n">
-        <v>357.38</v>
+        <v>355.7</v>
       </c>
       <c r="S25" t="n">
         <v>749.88</v>
@@ -3484,12 +3484,12 @@
       <c r="T25" t="n">
         <v>308</v>
       </c>
-      <c r="U25" s="3" t="n">
-        <v>0</v>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>5.6</v>
+        <v>24.1</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,28 +3537,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>396.93</v>
+        <v>54.1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-5.09</v>
+        <v>-2.33</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.29</v>
+        <v>-1.01</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-55.45</v>
+        <v>-20.28</v>
       </c>
       <c r="H26" t="n">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -3571,15 +3571,15 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-1.8</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>38.9</v>
+        <v>39.7</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3587,39 +3587,39 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="P26" t="n">
-        <v>9.789999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>358.09</v>
+        <v>50.21</v>
       </c>
       <c r="R26" t="n">
-        <v>407.45</v>
+        <v>55.09</v>
       </c>
       <c r="S26" t="n">
-        <v>980</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>334</v>
+        <v>51</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270104</v>
+        <v>270504</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>5.6</v>
+        <v>24.1</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,28 +3657,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>164.03</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>4.38</v>
+        <v>87.25</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-22.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-46.43</v>
+        <v>-41.99</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -3691,55 +3691,55 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.65</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>死叉(转空)</t>
+        <v>-4.18</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>44.6</v>
+        <v>39.7</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O27" s="2" t="n">
-        <v>7.27</v>
+      <c r="O27" s="3" t="n">
+        <v>-19.99</v>
       </c>
       <c r="P27" t="n">
-        <v>11.75</v>
+        <v>5.53</v>
       </c>
       <c r="Q27" t="n">
-        <v>144.76</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="R27" t="n">
-        <v>166.78</v>
+        <v>91.06</v>
       </c>
       <c r="S27" t="n">
-        <v>325.74</v>
+        <v>159.62</v>
       </c>
       <c r="T27" t="n">
-        <v>133.61</v>
+        <v>82.48</v>
       </c>
       <c r="U27" t="n">
         <v>2</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>270401</v>
+        <v>630503</v>
       </c>
       <c r="Z27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3748,16 +3748,16 @@
         <v>0</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>5.6</v>
+        <v>20.4</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,28 +3777,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>82.68000000000001</v>
+        <v>33.36</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.4</v>
+        <v>3.25</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-1.97</v>
+        <v>-11.89</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-15.48</v>
+        <v>-33.16</v>
       </c>
       <c r="H28" t="n">
-        <v>0.61</v>
+        <v>0.76</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -3811,55 +3811,55 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-1.36</v>
+        <v>-3.47</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>37</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="n">
-        <v>0.92</v>
+        <v>28.3</v>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>-9.48</v>
       </c>
       <c r="P28" t="n">
-        <v>4.54</v>
+        <v>5.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>78.93000000000001</v>
+        <v>31.41</v>
       </c>
       <c r="R28" t="n">
-        <v>83.81999999999999</v>
+        <v>34.56</v>
       </c>
       <c r="S28" t="n">
-        <v>113</v>
+        <v>56.7</v>
       </c>
       <c r="T28" t="n">
-        <v>80.55</v>
-      </c>
-      <c r="U28" t="n">
-        <v>3</v>
+        <v>31.68</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>710101</v>
+        <v>630702</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52.13</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-4.26</v>
+        <v>39.08</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>6.28</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.27</v>
+        <v>-5.99</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-29.82</v>
+        <v>-21.79</v>
       </c>
       <c r="H29" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.55</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.42</v>
+        <v>-6.23</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -3939,37 +3939,37 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="n">
-        <v>0.62</v>
+        <v>24.1</v>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>-3.58</v>
       </c>
       <c r="P29" t="n">
-        <v>7.39</v>
+        <v>10.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>48.28</v>
+        <v>35.13</v>
       </c>
       <c r="R29" t="n">
-        <v>55.12</v>
+        <v>41.68</v>
       </c>
       <c r="S29" t="n">
-        <v>71.36</v>
+        <v>51.83</v>
       </c>
       <c r="T29" t="n">
-        <v>51</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2</v>
+        <v>30.54</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,8 +473,8 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="81" customWidth="1" min="31" max="31"/>
-    <col width="76" customWidth="1" min="32" max="32"/>
+    <col width="82" customWidth="1" min="31" max="31"/>
+    <col width="68" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
@@ -657,28 +657,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>99.59999999999999</v>
+        <v>456.73</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.27</v>
+        <v>13.64</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>9.57</v>
+        <v>10.86</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-34.16</v>
+        <v>-18</v>
       </c>
       <c r="H2" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>7.83</v>
+        <v>11.39</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>55.6</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,39 +707,39 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>11.98</v>
+        <v>11.38</v>
       </c>
       <c r="P2" t="n">
-        <v>10.63</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>89.01000000000001</v>
+        <v>412.38</v>
       </c>
       <c r="R2" t="n">
-        <v>92.36</v>
+        <v>410.04</v>
       </c>
       <c r="S2" t="n">
-        <v>157.42</v>
+        <v>618.87</v>
       </c>
       <c r="T2" t="n">
-        <v>80.31999999999999</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>640703</v>
+        <v>730204</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -748,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>63</v>
+        <v>53.7</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；突破20日新高；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；突破20日新高；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -786,19 +786,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69.7</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7.36</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>7.88</v>
+        <v>11.44</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-22.62</v>
+        <v>-17.54</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4.78</v>
+        <v>4.31</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>48.2</v>
+        <v>55.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -827,16 +827,16 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>10.29</v>
+        <v>11.96</v>
       </c>
       <c r="P3" t="n">
-        <v>9.09</v>
+        <v>8.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>63.37</v>
+        <v>63.66</v>
       </c>
       <c r="R3" t="n">
-        <v>66.52</v>
+        <v>66.88</v>
       </c>
       <c r="S3" t="n">
         <v>92.90000000000001</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -859,7 +859,7 @@
         <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>61.1</v>
+        <v>51.9</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,28 +897,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>260.44</v>
+        <v>96.55</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13.01</v>
+        <v>4.63</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5.57</v>
+        <v>12.14</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-26.59</v>
+        <v>-31.62</v>
       </c>
       <c r="H4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>9.210000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>58.3</v>
+        <v>53.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,39 +947,39 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>7.98</v>
+        <v>12.66</v>
       </c>
       <c r="P4" t="n">
-        <v>9.6</v>
+        <v>10.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>235.44</v>
+        <v>86.02</v>
       </c>
       <c r="R4" t="n">
-        <v>238.47</v>
+        <v>92.89</v>
       </c>
       <c r="S4" t="n">
-        <v>418.99</v>
+        <v>155.32</v>
       </c>
       <c r="T4" t="n">
-        <v>183.83</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270103</v>
+        <v>640703</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>55.6</v>
+        <v>48.1</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；突破20日新高；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,28 +1017,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-3.7</v>
+        <v>183.2</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>13.52</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1.89</v>
+        <v>19.74</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-16.15</v>
+        <v>-38.09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1.13</v>
+        <v>8.34</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>48.2</v>
+        <v>58.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1067,39 +1067,39 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>4.3</v>
+        <v>20.26</v>
       </c>
       <c r="P5" t="n">
-        <v>10.17</v>
+        <v>10.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>110.94</v>
+        <v>163.15</v>
       </c>
       <c r="R5" t="n">
-        <v>122.12</v>
+        <v>169.1</v>
       </c>
       <c r="S5" t="n">
-        <v>158.2</v>
+        <v>325.74</v>
       </c>
       <c r="T5" t="n">
-        <v>94.73</v>
+        <v>133.61</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>270202</v>
+        <v>270401</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>229.35</v>
+        <v>109.51</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14.18</v>
+        <v>9.51</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6.94</v>
+        <v>5.96</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-1.61</v>
+        <v>-38.14</v>
       </c>
       <c r="H6" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.08</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>13.96</v>
+        <v>5.95</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>65.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1187,39 +1187,39 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>9.35</v>
+        <v>6.48</v>
       </c>
       <c r="P6" t="n">
-        <v>11.93</v>
+        <v>9.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>201.98</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>201.26</v>
+        <v>103.36</v>
       </c>
       <c r="S6" t="n">
-        <v>251</v>
+        <v>187.66</v>
       </c>
       <c r="T6" t="n">
-        <v>102.3</v>
+        <v>90.23</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>730204</v>
+        <v>640703</v>
       </c>
       <c r="Z6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>44.4</v>
+        <v>46.3</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线10-15%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>195.4</v>
+        <v>223.7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>10.17</v>
+        <v>12.81</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>9.42</v>
+        <v>10.25</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-18.7</v>
+        <v>-0.42</v>
       </c>
       <c r="H7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.06</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>10.31</v>
+        <v>10.58</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>59.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,39 +1307,39 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>11.83</v>
+        <v>10.77</v>
       </c>
       <c r="P7" t="n">
-        <v>10.8</v>
+        <v>12.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>174.3</v>
+        <v>196.21</v>
       </c>
       <c r="R7" t="n">
-        <v>177.14</v>
+        <v>202.3</v>
       </c>
       <c r="S7" t="n">
-        <v>264.88</v>
+        <v>251</v>
       </c>
       <c r="T7" t="n">
-        <v>152.33</v>
+        <v>102.3</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>730204</v>
       </c>
       <c r="Z7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1348,16 +1348,16 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>44.4</v>
+        <v>42.6</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,32 +1377,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>198</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5.2</v>
+        <v>10.77</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>-21.38</v>
+        <v>13.4</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>10.24</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.77</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>65</v>
+        <v>44.9</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,40 +1427,40 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>3.09</v>
+        <v>13.92</v>
       </c>
       <c r="P8" t="n">
-        <v>10.04</v>
+        <v>7.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>400.31</v>
+        <v>183.85</v>
       </c>
       <c r="R8" t="n">
-        <v>407.81</v>
+        <v>186.26</v>
       </c>
       <c r="S8" t="n">
-        <v>618.87</v>
+        <v>232.68</v>
       </c>
       <c r="T8" t="n">
-        <v>347</v>
+        <v>170.1</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>730204</v>
+        <v>270104</v>
       </c>
       <c r="Z8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA8" t="n">
         <v>11</v>
       </c>
-      <c r="AA8" t="n">
-        <v>13</v>
-      </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
@@ -1468,16 +1468,16 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>44.4</v>
+        <v>42.6</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线5-10%</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>174.32</v>
+        <v>193.76</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.98</v>
+        <v>12.78</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>10.26</v>
+        <v>16.45</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-42.07</v>
+        <v>-17.88</v>
       </c>
       <c r="H9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.26</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,15 +1531,15 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4.01</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>47.7</v>
+        <v>58.1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1547,39 +1547,39 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>12.67</v>
+        <v>16.97</v>
       </c>
       <c r="P9" t="n">
-        <v>11.13</v>
+        <v>10.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>154.91</v>
+        <v>172.9</v>
       </c>
       <c r="R9" t="n">
-        <v>167.59</v>
+        <v>178.51</v>
       </c>
       <c r="S9" t="n">
-        <v>325.74</v>
+        <v>264.88</v>
       </c>
       <c r="T9" t="n">
-        <v>133.61</v>
+        <v>152.33</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>270401</v>
+        <v>730204</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AA9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1588,16 +1588,16 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>44.4</v>
+        <v>40.7</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>64.27</v>
+        <v>279.26</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>23.5</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.62</v>
+        <v>12.15</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-30.78</v>
+        <v>-5.22</v>
       </c>
       <c r="H10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.92</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>12.52</v>
+        <v>6.7</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>60.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1667,39 +1667,39 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>13.03</v>
+        <v>12.67</v>
       </c>
       <c r="P10" t="n">
-        <v>9.9</v>
+        <v>11.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>57.91</v>
+        <v>246.57</v>
       </c>
       <c r="R10" t="n">
-        <v>57.12</v>
+        <v>261.73</v>
       </c>
       <c r="S10" t="n">
-        <v>107.55</v>
+        <v>309.39</v>
       </c>
       <c r="T10" t="n">
-        <v>43.01</v>
+        <v>155.05</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>640108</v>
+        <v>730204</v>
       </c>
       <c r="Z10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AA10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>股价站上20日均线；突破20日新高；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>284.66</v>
+        <v>37.04</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8.869999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>4.43</v>
+        <v>27.94</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-10.34</v>
+        <v>-0.19</v>
       </c>
       <c r="H11" t="n">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>61.9</v>
+        <v>64</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1787,39 +1787,39 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>6.84</v>
+        <v>28.46</v>
       </c>
       <c r="P11" t="n">
-        <v>11.57</v>
+        <v>14.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>251.73</v>
+        <v>31.56</v>
       </c>
       <c r="R11" t="n">
-        <v>260.22</v>
+        <v>34.55</v>
       </c>
       <c r="S11" t="n">
-        <v>313.49</v>
+        <v>43.43</v>
       </c>
       <c r="T11" t="n">
-        <v>155.05</v>
+        <v>23.2</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>5</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>730204</v>
+        <v>640209</v>
       </c>
       <c r="Z11" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,16 +1828,16 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>40.7</v>
+        <v>37</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,32 +1857,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>227.98</v>
+        <v>64.52</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.57</v>
+        <v>20.49</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>26.04</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-7.26</v>
+        <v>-37.69</v>
       </c>
       <c r="H12" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.55</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>12.06</v>
+        <v>12.43</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>68.8</v>
+        <v>67.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1907,36 +1907,36 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>28.45</v>
+        <v>9.65</v>
       </c>
       <c r="P12" t="n">
-        <v>12.76</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>198.89</v>
+        <v>58.1</v>
       </c>
       <c r="R12" t="n">
-        <v>203.45</v>
+        <v>57.39</v>
       </c>
       <c r="S12" t="n">
-        <v>258.39</v>
+        <v>107.55</v>
       </c>
       <c r="T12" t="n">
-        <v>125.61</v>
+        <v>43.01</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>730206</v>
+        <v>640108</v>
       </c>
       <c r="Z12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="n">
         <v>11</v>
@@ -1948,16 +1948,16 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>38.9</v>
+        <v>33.3</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>37.72</v>
+        <v>72.22</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>33.47</v>
+        <v>8.880000000000001</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-2.14</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-6.08</v>
+        <v>-30.05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.13</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>10.46</v>
+        <v>2.01</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -2019,47 +2019,47 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>66.8</v>
+        <v>47.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O13" s="2" t="n">
-        <v>35.88</v>
+      <c r="O13" s="3" t="n">
+        <v>-1.62</v>
       </c>
       <c r="P13" t="n">
-        <v>14.62</v>
+        <v>7.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>32.21</v>
+        <v>66.58</v>
       </c>
       <c r="R13" t="n">
-        <v>34.15</v>
+        <v>70.8</v>
       </c>
       <c r="S13" t="n">
-        <v>43.43</v>
+        <v>113.87</v>
       </c>
       <c r="T13" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="U13" s="2" t="n">
-        <v>5</v>
+        <v>60.84</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>640209</v>
+        <v>270107</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2068,16 +2068,16 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>37</v>
+        <v>31.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,28 +2097,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61.48</v>
+        <v>195.02</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-4.43</v>
+        <v>5.35</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.73</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-43.6</v>
+        <v>-21.86</v>
       </c>
       <c r="H14" t="n">
-        <v>0.78</v>
+        <v>0.98</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3.29</v>
+        <v>2.23</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -2139,47 +2139,47 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>46.1</v>
+        <v>54.9</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O14" s="3" t="n">
-        <v>-2.02</v>
+      <c r="O14" s="2" t="n">
+        <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>13.35</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>53.27</v>
+        <v>175.76</v>
       </c>
       <c r="R14" t="n">
-        <v>59.52</v>
+        <v>190.76</v>
       </c>
       <c r="S14" t="n">
-        <v>114.5</v>
+        <v>280.08</v>
       </c>
       <c r="T14" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
+        <v>161.8</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>270203</v>
+        <v>270202</v>
       </c>
       <c r="Z14" t="n">
         <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>37</v>
+        <v>31.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,32 +2217,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.3</v>
+        <v>126</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2.49</v>
+        <v>0.24</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.23</v>
+        <v>9.02</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-14.64</v>
+        <v>-10.68</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.98</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.57</v>
+        <v>2.74</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>32.4</v>
+        <v>57</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2267,40 +2267,40 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>2.64</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>3.99</v>
+        <v>9.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>80.94</v>
+        <v>113.72</v>
       </c>
       <c r="R15" t="n">
-        <v>83.83</v>
+        <v>122.64</v>
       </c>
       <c r="S15" t="n">
-        <v>113</v>
+        <v>158.2</v>
       </c>
       <c r="T15" t="n">
-        <v>80.55</v>
+        <v>94.73</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>710101</v>
+        <v>270202</v>
       </c>
       <c r="Z15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA15" t="n">
         <v>7</v>
       </c>
-      <c r="AA15" t="n">
-        <v>13</v>
-      </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
@@ -2308,16 +2308,16 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>37</v>
+        <v>31.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>257.06</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>-7.09</v>
+        <v>8.42</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2.66</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-27.64</v>
+        <v>-32.79</v>
       </c>
       <c r="H16" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.07</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2371,55 +2371,55 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3</v>
+        <v>7.65</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>44</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O16" s="3" t="n">
-        <v>-4.68</v>
+      <c r="O16" s="2" t="n">
+        <v>3.18</v>
       </c>
       <c r="P16" t="n">
-        <v>7.99</v>
+        <v>9.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>67.16</v>
+        <v>233.33</v>
       </c>
       <c r="R16" t="n">
-        <v>70.88</v>
+        <v>238.8</v>
       </c>
       <c r="S16" t="n">
-        <v>113.87</v>
+        <v>418.99</v>
       </c>
       <c r="T16" t="n">
-        <v>60.84</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
+        <v>183.83</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>270107</v>
+        <v>270103</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2427,17 +2427,17 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" t="n">
-        <v>35.2</v>
+      <c r="AD16" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2466,19 +2466,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>61.38</v>
+        <v>61.18</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>5.83</v>
+        <v>7.75</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-3.91</v>
+        <v>-0.1</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-14.27</v>
+        <v>-15.71</v>
       </c>
       <c r="H17" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -2499,21 +2499,21 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>41.5</v>
+        <v>49.4</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O17" s="3" t="n">
-        <v>-1.5</v>
+      <c r="O17" s="2" t="n">
+        <v>0.42</v>
       </c>
       <c r="P17" t="n">
-        <v>7.96</v>
+        <v>7.52</v>
       </c>
       <c r="Q17" t="n">
-        <v>56.49</v>
+        <v>56.58</v>
       </c>
       <c r="R17" t="n">
         <v>59.9</v>
@@ -2524,12 +2524,12 @@
       <c r="T17" t="n">
         <v>51.23</v>
       </c>
-      <c r="U17" t="n">
-        <v>3</v>
+      <c r="U17" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W17" t="n">
@@ -2539,7 +2539,7 @@
         <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2547,8 +2547,8 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" t="n">
-        <v>35.2</v>
+      <c r="AD17" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63.28</v>
+        <v>60.68</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4.51</v>
+        <v>4.39</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>16.93</v>
+        <v>1.98</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-23.36</v>
+        <v>-42.75</v>
       </c>
       <c r="H18" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2611,15 +2611,15 @@
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>1.85</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>36.8</v>
+        <v>52.8</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2627,39 +2627,39 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>19.34</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>9.27</v>
+        <v>11.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>57.41</v>
+        <v>53.57</v>
       </c>
       <c r="R18" t="n">
-        <v>62.93</v>
+        <v>59.58</v>
       </c>
       <c r="S18" t="n">
-        <v>82.81999999999999</v>
+        <v>113.18</v>
       </c>
       <c r="T18" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
+        <v>53.35</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>640209</v>
+        <v>270203</v>
       </c>
       <c r="Z18" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2667,17 +2667,17 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" t="n">
-        <v>35.2</v>
+      <c r="AD18" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>190.04</v>
+        <v>223.32</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>5.4</v>
+        <v>2.03</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>5.11</v>
+        <v>27.68</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-9.84</v>
       </c>
       <c r="H19" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.88</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2731,15 +2731,15 @@
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2.67</v>
+        <v>8.48</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>45.9</v>
+        <v>67.8</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2747,39 +2747,39 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>7.63</v>
+        <v>28.2</v>
       </c>
       <c r="P19" t="n">
-        <v>8.050000000000001</v>
+        <v>12.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>174.74</v>
+        <v>194.44</v>
       </c>
       <c r="R19" t="n">
-        <v>185.09</v>
+        <v>205.87</v>
       </c>
       <c r="S19" t="n">
-        <v>232.68</v>
+        <v>257.41</v>
       </c>
       <c r="T19" t="n">
-        <v>170.1</v>
+        <v>125.61</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270104</v>
+        <v>730206</v>
       </c>
       <c r="Z19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2787,17 +2787,17 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" t="n">
-        <v>33.3</v>
+      <c r="AD19" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,41 +2817,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>107.8</v>
+        <v>347.79</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>0.96</v>
+        <v>5.07</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-4.69</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-33.02</v>
+        <v>-51.9</v>
       </c>
       <c r="H20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.83</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>4.61</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>-1.99</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -2859,47 +2859,47 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>53.6</v>
+        <v>38.3</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O20" s="2" t="n">
-        <v>3.37</v>
+      <c r="O20" s="3" t="n">
+        <v>-4.17</v>
       </c>
       <c r="P20" t="n">
-        <v>9.77</v>
+        <v>7.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>97.27</v>
+        <v>323.31</v>
       </c>
       <c r="R20" t="n">
-        <v>103.05</v>
+        <v>354.84</v>
       </c>
       <c r="S20" t="n">
-        <v>187.66</v>
+        <v>749.88</v>
       </c>
       <c r="T20" t="n">
-        <v>90.23</v>
-      </c>
-      <c r="U20" s="2" t="n">
-        <v>4</v>
+        <v>308</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>640703</v>
+        <v>270104</v>
       </c>
       <c r="Z20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2907,17 +2907,17 @@
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" t="n">
-        <v>33.3</v>
+      <c r="AD20" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,32 +2937,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.47</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>-6.98</v>
+        <v>94.23</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>12.42</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-28.72</v>
+        <v>-27.98</v>
       </c>
       <c r="H21" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.95</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2971,55 +2971,55 @@
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>金叉(转多)</t>
+        <v>0.73</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>41.6</v>
+        <v>50.4</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>-4.57</v>
+      <c r="O21" s="2" t="n">
+        <v>12.94</v>
       </c>
       <c r="P21" t="n">
-        <v>6.89</v>
+        <v>10.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.72</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>25.34</v>
+        <v>93.55</v>
       </c>
       <c r="S21" t="n">
-        <v>42.08</v>
+        <v>136.42</v>
       </c>
       <c r="T21" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
+        <v>69.63</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270303</v>
+        <v>650201</v>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AA21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3027,17 +3027,17 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" t="n">
-        <v>33.3</v>
+      <c r="AD21" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3066,19 +3066,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>413.09</v>
+        <v>415</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>-0.49</v>
+        <v>6.99</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>3.66</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-56.56</v>
+        <v>-57.22</v>
       </c>
       <c r="H22" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>42.4</v>
+        <v>48.9</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -3107,19 +3107,19 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1.92</v>
+        <v>4.18</v>
       </c>
       <c r="P22" t="n">
-        <v>9.34</v>
+        <v>8.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>374.52</v>
+        <v>377.68</v>
       </c>
       <c r="R22" t="n">
-        <v>407.35</v>
+        <v>408.08</v>
       </c>
       <c r="S22" t="n">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="T22" t="n">
         <v>334</v>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -3139,7 +3139,7 @@
         <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3147,8 +3147,8 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" t="n">
-        <v>33.3</v>
+      <c r="AD22" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,89 +3177,89 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>196.15</v>
+        <v>25.61</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>-2.45</v>
+        <v>4.7</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>1.87</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-24.65</v>
+        <v>-20.34</v>
       </c>
       <c r="H23" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>2.86</v>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>48.7</v>
+        <v>47.7</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O23" s="3" t="n">
-        <v>-0.04</v>
+      <c r="O23" s="2" t="n">
+        <v>2.39</v>
       </c>
       <c r="P23" t="n">
-        <v>10.22</v>
+        <v>6.68</v>
       </c>
       <c r="Q23" t="n">
-        <v>176.1</v>
+        <v>23.9</v>
       </c>
       <c r="R23" t="n">
-        <v>190.69</v>
+        <v>25.36</v>
       </c>
       <c r="S23" t="n">
-        <v>280.08</v>
+        <v>42.08</v>
       </c>
       <c r="T23" t="n">
-        <v>161.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3</v>
+        <v>23.8</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270202</v>
+        <v>270303</v>
       </c>
       <c r="Z23" t="n">
         <v>7</v>
       </c>
       <c r="AA23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3267,8 +3267,8 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" t="n">
-        <v>33.3</v>
+      <c r="AD23" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>93.38</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-2.82</v>
+        <v>83.94</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>6.13</v>
+        <v>2.14</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-33.28</v>
+        <v>-13.89</v>
       </c>
       <c r="H24" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.76</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>46.7</v>
+        <v>36.4</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -3347,36 +3347,36 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>8.539999999999999</v>
+        <v>2.66</v>
       </c>
       <c r="P24" t="n">
-        <v>11.25</v>
+        <v>3.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>82.87</v>
+        <v>80.62</v>
       </c>
       <c r="R24" t="n">
-        <v>93.2</v>
+        <v>83.91</v>
       </c>
       <c r="S24" t="n">
-        <v>141.8</v>
+        <v>113</v>
       </c>
       <c r="T24" t="n">
-        <v>69.8</v>
+        <v>80.55</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>650201</v>
+        <v>710101</v>
       </c>
       <c r="Z24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA24" t="n">
         <v>5</v>
@@ -3388,16 +3388,16 @@
         <v>0</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>27.8</v>
+        <v>22.2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>346.96</v>
+        <v>88.47</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2.18</v>
+        <v>4.9</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-8.85</v>
+        <v>-20.2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-48.95</v>
+        <v>-42.92</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -3451,15 +3451,15 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-2.46</v>
+        <v>-1.64</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>33.1</v>
+        <v>49.3</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3467,39 +3467,39 @@
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-6.44</v>
+        <v>-19.68</v>
       </c>
       <c r="P25" t="n">
-        <v>7.1</v>
+        <v>5.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>322.31</v>
+        <v>83.62</v>
       </c>
       <c r="R25" t="n">
-        <v>355.7</v>
+        <v>89.94</v>
       </c>
       <c r="S25" t="n">
-        <v>749.88</v>
+        <v>159.62</v>
       </c>
       <c r="T25" t="n">
-        <v>308</v>
+        <v>82.48</v>
       </c>
       <c r="U25" t="n">
         <v>2</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>270104</v>
+        <v>630503</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>24.1</v>
+        <v>20.4</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,32 +3537,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-2.33</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-1.01</v>
+        <v>62.23</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>13.66</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-20.28</v>
+        <v>-18.87</v>
       </c>
       <c r="H26" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.57</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>39.7</v>
+        <v>39.5</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3587,39 +3587,39 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1.4</v>
+        <v>14.18</v>
       </c>
       <c r="P26" t="n">
-        <v>7.2</v>
+        <v>9.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>50.21</v>
+        <v>56.47</v>
       </c>
       <c r="R26" t="n">
-        <v>55.09</v>
+        <v>63.31</v>
       </c>
       <c r="S26" t="n">
-        <v>70.73999999999999</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>51</v>
+        <v>45.82</v>
       </c>
       <c r="U26" t="n">
         <v>2</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270504</v>
+        <v>640209</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,16 +3628,16 @@
         <v>0</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>24.1</v>
+        <v>16.7</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,28 +3657,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>87.25</v>
+        <v>33.53</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>4.17</v>
+        <v>1.48</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-22.4</v>
+        <v>-10.3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-41.99</v>
+        <v>-34.01</v>
       </c>
       <c r="H27" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-4.18</v>
+        <v>-2.43</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>39.7</v>
+        <v>34.1</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3707,39 +3707,39 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-19.99</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="Q27" t="n">
-        <v>82.43000000000001</v>
+        <v>31.71</v>
       </c>
       <c r="R27" t="n">
-        <v>91.06</v>
+        <v>34.37</v>
       </c>
       <c r="S27" t="n">
-        <v>159.62</v>
+        <v>56.7</v>
       </c>
       <c r="T27" t="n">
-        <v>82.48</v>
+        <v>31.68</v>
       </c>
       <c r="U27" t="n">
         <v>2</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>630503</v>
+        <v>630702</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>20.4</v>
+        <v>14.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,28 +3777,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>33.36</v>
+        <v>54.44</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>-11.89</v>
+        <v>3.15</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>1.34</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-33.16</v>
+        <v>-16.45</v>
       </c>
       <c r="H28" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -3811,55 +3811,55 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-3.47</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>金叉(转多)</t>
+        <v>-1.24</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>-9.48</v>
+        <v>42.6</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>1.86</v>
       </c>
       <c r="P28" t="n">
-        <v>5.85</v>
+        <v>7.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>31.41</v>
+        <v>50.61</v>
       </c>
       <c r="R28" t="n">
-        <v>34.56</v>
+        <v>55.12</v>
       </c>
       <c r="S28" t="n">
-        <v>56.7</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>630702</v>
+        <v>270504</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3906,19 +3906,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.08</v>
+        <v>38.74</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>6.28</v>
+        <v>3.14</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.99</v>
+        <v>-10.16</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-21.79</v>
+        <v>-18.97</v>
       </c>
       <c r="H29" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.23</v>
+        <v>-6.55</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
@@ -3947,19 +3947,19 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.58</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>10.12</v>
+        <v>10.29</v>
       </c>
       <c r="Q29" t="n">
-        <v>35.13</v>
+        <v>34.75</v>
       </c>
       <c r="R29" t="n">
-        <v>41.68</v>
+        <v>41.46</v>
       </c>
       <c r="S29" t="n">
-        <v>51.83</v>
+        <v>51.68</v>
       </c>
       <c r="T29" t="n">
         <v>30.54</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,8 +473,8 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="82" customWidth="1" min="31" max="31"/>
-    <col width="68" customWidth="1" min="32" max="32"/>
+    <col width="81" customWidth="1" min="31" max="31"/>
+    <col width="66" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
@@ -657,32 +657,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>456.73</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13.64</v>
+        <v>12.12</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>10.86</v>
+        <v>11.61</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-18</v>
+        <v>-22.81</v>
       </c>
       <c r="H2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.45</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>11.39</v>
+        <v>5.8</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>67.40000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,39 +707,39 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>11.38</v>
+        <v>11.77</v>
       </c>
       <c r="P2" t="n">
-        <v>9.710000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>412.38</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>410.04</v>
+        <v>67.25</v>
       </c>
       <c r="S2" t="n">
-        <v>618.87</v>
+        <v>92.06</v>
       </c>
       <c r="T2" t="n">
-        <v>347</v>
+        <v>47.3</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>730204</v>
+        <v>270303</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -748,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>53.7</v>
+        <v>59.3</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；突破20日新高；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；突破20日新高；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,32 +777,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69.76000000000001</v>
+        <v>63.34</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>13.78</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>11.44</v>
+        <v>10.08</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-17.54</v>
+        <v>-36.92</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.69</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4.31</v>
+        <v>9.82</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>55.8</v>
+        <v>66.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -827,36 +827,36 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>11.96</v>
+        <v>10.24</v>
       </c>
       <c r="P3" t="n">
-        <v>8.74</v>
+        <v>10.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>63.66</v>
+        <v>56.72</v>
       </c>
       <c r="R3" t="n">
-        <v>66.88</v>
+        <v>57.68</v>
       </c>
       <c r="S3" t="n">
-        <v>92.90000000000001</v>
+        <v>107.55</v>
       </c>
       <c r="T3" t="n">
-        <v>47.3</v>
+        <v>43.01</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270303</v>
+        <v>640108</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
         <v>10</v>
@@ -868,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>51.9</v>
+        <v>50</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,28 +897,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>96.55</v>
+        <v>198.12</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.63</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>12.14</v>
+        <v>3.81</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-31.62</v>
+        <v>-24.48</v>
       </c>
       <c r="H4" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>53.2</v>
+        <v>61.7</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,39 +947,39 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>12.66</v>
+        <v>3.97</v>
       </c>
       <c r="P4" t="n">
-        <v>10.91</v>
+        <v>10.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>86.02</v>
+        <v>178</v>
       </c>
       <c r="R4" t="n">
-        <v>92.89</v>
+        <v>191.12</v>
       </c>
       <c r="S4" t="n">
-        <v>155.32</v>
+        <v>280.08</v>
       </c>
       <c r="T4" t="n">
-        <v>80.31999999999999</v>
+        <v>161.8</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>640703</v>
+        <v>270202</v>
       </c>
       <c r="Z4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>48.1</v>
+        <v>44.4</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>183.2</v>
+        <v>227.46</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13.52</v>
+        <v>17.01</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>19.74</v>
+        <v>12.22</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-38.09</v>
+        <v>-7.43</v>
       </c>
       <c r="H5" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.17</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>8.34</v>
+        <v>11.75</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -1059,47 +1059,47 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>70.3</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>超买区间</t>
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>20.26</v>
+        <v>12.38</v>
       </c>
       <c r="P5" t="n">
-        <v>10.94</v>
+        <v>12.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>163.15</v>
+        <v>199.66</v>
       </c>
       <c r="R5" t="n">
-        <v>169.1</v>
+        <v>203.54</v>
       </c>
       <c r="S5" t="n">
-        <v>325.74</v>
+        <v>250.82</v>
       </c>
       <c r="T5" t="n">
-        <v>133.61</v>
+        <v>102.3</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>270401</v>
+        <v>730204</v>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1108,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>46.3</v>
+        <v>42.6</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>109.51</v>
+        <v>107.09</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>9.51</v>
+        <v>6.88</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5.96</v>
+        <v>1.73</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-38.14</v>
+        <v>-41.99</v>
       </c>
       <c r="H6" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>5.95</v>
+        <v>3.52</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1187,16 +1187,16 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>6.48</v>
+        <v>1.89</v>
       </c>
       <c r="P6" t="n">
-        <v>9.43</v>
+        <v>9.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>99.18000000000001</v>
+        <v>96.48</v>
       </c>
       <c r="R6" t="n">
-        <v>103.36</v>
+        <v>103.45</v>
       </c>
       <c r="S6" t="n">
         <v>187.66</v>
@@ -1209,17 +1209,17 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>640703</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>46.3</v>
+        <v>42.6</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>223.7</v>
+        <v>84.67</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12.81</v>
+        <v>3.18</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>10.25</v>
+        <v>1.78</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-0.42</v>
+        <v>-21.04</v>
       </c>
       <c r="H7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.96</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>10.58</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>65.59999999999999</v>
+        <v>46.7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,39 +1307,39 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>10.77</v>
+        <v>1.94</v>
       </c>
       <c r="P7" t="n">
-        <v>12.29</v>
+        <v>4.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>196.21</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>202.3</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>251</v>
+        <v>113</v>
       </c>
       <c r="T7" t="n">
-        <v>102.3</v>
+        <v>80.55</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>730204</v>
+        <v>710101</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,32 +1377,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>198</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10.77</v>
+        <v>0.71</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>10.24</v>
+        <v>10.83</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>-37.21</v>
       </c>
       <c r="H8" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.06</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>6.3</v>
+        <v>0.98</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>44.9</v>
+        <v>51.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,39 +1427,39 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>13.92</v>
+        <v>10.99</v>
       </c>
       <c r="P8" t="n">
-        <v>7.15</v>
+        <v>11.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>183.85</v>
+        <v>83.69</v>
       </c>
       <c r="R8" t="n">
-        <v>186.26</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>232.68</v>
+        <v>150.49</v>
       </c>
       <c r="T8" t="n">
-        <v>170.1</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270104</v>
+        <v>640703</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AA8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,28 +1497,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>193.76</v>
+        <v>217.8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12.78</v>
+        <v>22.91</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>16.45</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>-17.88</v>
+        <v>24.41</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>16.37</v>
       </c>
       <c r="H9" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>8.550000000000001</v>
+        <v>15.61</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>58.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1547,39 +1547,39 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>16.97</v>
+        <v>24.57</v>
       </c>
       <c r="P9" t="n">
-        <v>10.76</v>
+        <v>7.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>172.9</v>
+        <v>202.32</v>
       </c>
       <c r="R9" t="n">
-        <v>178.51</v>
+        <v>188.4</v>
       </c>
       <c r="S9" t="n">
-        <v>264.88</v>
+        <v>232.68</v>
       </c>
       <c r="T9" t="n">
-        <v>152.33</v>
+        <v>170.1</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>730204</v>
+        <v>270104</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>股价站上20日均线；20日均线自身向上；突破20日新高；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>279.26</v>
+        <v>190.37</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>13.07</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>12.15</v>
+        <v>13.78</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-5.22</v>
+        <v>-25.91</v>
       </c>
       <c r="H10" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.32</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>6.7</v>
+        <v>5.96</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>66.09999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1667,29 +1667,29 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>12.67</v>
+        <v>13.94</v>
       </c>
       <c r="P10" t="n">
-        <v>11.7</v>
+        <v>10.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>246.57</v>
+        <v>169.94</v>
       </c>
       <c r="R10" t="n">
-        <v>261.73</v>
+        <v>179.66</v>
       </c>
       <c r="S10" t="n">
-        <v>309.39</v>
+        <v>264.88</v>
       </c>
       <c r="T10" t="n">
-        <v>155.05</v>
+        <v>152.33</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W10" t="n">
@@ -1737,32 +1737,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>37.04</v>
+        <v>181.2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.93</v>
+        <v>12.08</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>27.94</v>
+        <v>17.89</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.19</v>
+        <v>-39.58</v>
       </c>
       <c r="H11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>7.19</v>
+        <v>6.29</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>64</v>
+        <v>58.4</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1787,39 +1787,39 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>28.46</v>
+        <v>18.05</v>
       </c>
       <c r="P11" t="n">
-        <v>14.79</v>
+        <v>10.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.56</v>
+        <v>161.33</v>
       </c>
       <c r="R11" t="n">
-        <v>34.55</v>
+        <v>170.48</v>
       </c>
       <c r="S11" t="n">
-        <v>43.43</v>
+        <v>325.74</v>
       </c>
       <c r="T11" t="n">
-        <v>23.2</v>
+        <v>133.61</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>640209</v>
+        <v>270401</v>
       </c>
       <c r="Z11" t="n">
         <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>37</v>
+        <v>40.7</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,32 +1857,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64.52</v>
+        <v>97.08</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>20.49</v>
+        <v>0.8</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>16.81</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-37.69</v>
+        <v>-27.31</v>
       </c>
       <c r="H12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1891,15 +1891,15 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>12.43</v>
+        <v>3.01</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>67.8</v>
+        <v>54.3</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>9.65</v>
+        <v>16.97</v>
       </c>
       <c r="P12" t="n">
-        <v>9.949999999999999</v>
+        <v>10.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>58.1</v>
+        <v>86.8</v>
       </c>
       <c r="R12" t="n">
-        <v>57.39</v>
+        <v>94.25</v>
       </c>
       <c r="S12" t="n">
-        <v>107.55</v>
+        <v>136.42</v>
       </c>
       <c r="T12" t="n">
-        <v>43.01</v>
+        <v>69.63</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>640108</v>
+        <v>650201</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,16 +1948,16 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>33.3</v>
+        <v>38.9</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线10-15%</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>72.22</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-2.14</v>
+        <v>36.3</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>17.86</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-30.05</v>
+        <v>-6.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.93</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2.01</v>
+        <v>4.22</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -2019,48 +2019,48 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>47.5</v>
+        <v>61.2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O13" s="3" t="n">
-        <v>-1.62</v>
+      <c r="O13" s="2" t="n">
+        <v>18.02</v>
       </c>
       <c r="P13" t="n">
-        <v>7.81</v>
+        <v>15.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>66.58</v>
+        <v>30.82</v>
       </c>
       <c r="R13" t="n">
-        <v>70.8</v>
+        <v>34.83</v>
       </c>
       <c r="S13" t="n">
-        <v>113.87</v>
+        <v>43.43</v>
       </c>
       <c r="T13" t="n">
-        <v>60.84</v>
-      </c>
-      <c r="U13" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>640209</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA13" t="n">
         <v>3</v>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="W13" t="n">
-        <v>270107</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>10</v>
-      </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
@@ -2068,16 +2068,16 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>31.5</v>
+        <v>38.9</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,28 +2097,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>195.02</v>
+        <v>455</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5.35</v>
+        <v>14.61</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.73</v>
+        <v>13.5</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-21.86</v>
+        <v>-25.04</v>
       </c>
       <c r="H14" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2.23</v>
+        <v>10.24</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -2139,44 +2139,44 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>超买区间</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1.25</v>
+        <v>13.66</v>
       </c>
       <c r="P14" t="n">
-        <v>9.880000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>175.76</v>
+        <v>410.82</v>
       </c>
       <c r="R14" t="n">
-        <v>190.76</v>
+        <v>412.75</v>
       </c>
       <c r="S14" t="n">
-        <v>280.08</v>
+        <v>618.87</v>
       </c>
       <c r="T14" t="n">
-        <v>161.8</v>
-      </c>
-      <c r="U14" s="2" t="n">
-        <v>4</v>
+        <v>347</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>270202</v>
+        <v>730204</v>
       </c>
       <c r="Z14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
         <v>5</v>
@@ -2188,11 +2188,11 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>31.5</v>
+        <v>37</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2217,32 +2217,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>126</v>
+        <v>25.85</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.24</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>9.02</v>
+        <v>2.3</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-10.68</v>
+        <v>-26.94</v>
       </c>
       <c r="H15" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.9</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2.74</v>
+        <v>1.81</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>57</v>
+        <v>52.1</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2267,39 +2267,39 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>9.539999999999999</v>
+        <v>2.46</v>
       </c>
       <c r="P15" t="n">
-        <v>9.75</v>
+        <v>6.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>113.72</v>
+        <v>24.07</v>
       </c>
       <c r="R15" t="n">
-        <v>122.64</v>
+        <v>25.39</v>
       </c>
       <c r="S15" t="n">
-        <v>158.2</v>
+        <v>42.08</v>
       </c>
       <c r="T15" t="n">
-        <v>94.73</v>
+        <v>23.8</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270202</v>
+        <v>270303</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2308,16 +2308,16 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>31.5</v>
+        <v>37</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2346,19 +2346,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>257.06</v>
+        <v>249.61</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>8.42</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2.66</v>
+        <v>5.99</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-32.79</v>
+        <v>-32.28</v>
       </c>
       <c r="H16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>7.65</v>
+        <v>4.22</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>66.40000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2387,16 +2387,16 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>3.18</v>
+        <v>6.15</v>
       </c>
       <c r="P16" t="n">
-        <v>9.23</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>233.33</v>
+        <v>225</v>
       </c>
       <c r="R16" t="n">
-        <v>238.8</v>
+        <v>239.51</v>
       </c>
       <c r="S16" t="n">
         <v>418.99</v>
@@ -2409,14 +2409,14 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W16" t="n">
         <v>270103</v>
       </c>
       <c r="Z16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
         <v>5</v>
@@ -2427,12 +2427,12 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" s="3" t="n">
-        <v>29.6</v>
+      <c r="AD16" t="n">
+        <v>37</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2466,23 +2466,23 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>61.18</v>
+        <v>63.52</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>-0.1</v>
+        <v>10.84</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>4.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-15.71</v>
+        <v>-16.28</v>
       </c>
       <c r="H17" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.25</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2.14</v>
+        <v>5.81</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>49.4</v>
+        <v>61.6</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2507,16 +2507,16 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>0.42</v>
+        <v>4.46</v>
       </c>
       <c r="P17" t="n">
-        <v>7.52</v>
+        <v>7.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>56.58</v>
+        <v>58.49</v>
       </c>
       <c r="R17" t="n">
-        <v>59.9</v>
+        <v>60.03</v>
       </c>
       <c r="S17" t="n">
         <v>84.7</v>
@@ -2529,17 +2529,17 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W17" t="n">
         <v>270107</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2547,17 +2547,17 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" s="3" t="n">
-        <v>27.8</v>
+      <c r="AD17" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,32 +2577,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60.68</v>
+        <v>411.57</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4.39</v>
+        <v>6.63</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.98</v>
+        <v>3.66</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-42.75</v>
+        <v>-56.35</v>
       </c>
       <c r="H18" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.9</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.85</v>
+        <v>0.68</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>52.8</v>
+        <v>49.5</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2627,36 +2627,36 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>2.5</v>
+        <v>3.82</v>
       </c>
       <c r="P18" t="n">
-        <v>11.72</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>53.57</v>
+        <v>373.62</v>
       </c>
       <c r="R18" t="n">
-        <v>59.58</v>
+        <v>408.81</v>
       </c>
       <c r="S18" t="n">
-        <v>113.18</v>
+        <v>976</v>
       </c>
       <c r="T18" t="n">
-        <v>53.35</v>
+        <v>334</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270203</v>
+        <v>270104</v>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
         <v>8</v>
@@ -2667,12 +2667,12 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" s="3" t="n">
-        <v>27.8</v>
+      <c r="AD18" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>223.32</v>
+        <v>60.98</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2.03</v>
+        <v>3.55</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>27.68</v>
+        <v>1.58</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-9.84</v>
+        <v>-41.92</v>
       </c>
       <c r="H19" t="n">
         <v>0.88</v>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>8.48</v>
+        <v>2.27</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>67.8</v>
+        <v>64</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2747,39 +2747,39 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>28.2</v>
+        <v>1.74</v>
       </c>
       <c r="P19" t="n">
-        <v>12.93</v>
+        <v>11.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>194.44</v>
+        <v>54.21</v>
       </c>
       <c r="R19" t="n">
-        <v>205.87</v>
+        <v>59.63</v>
       </c>
       <c r="S19" t="n">
-        <v>257.41</v>
+        <v>113.18</v>
       </c>
       <c r="T19" t="n">
-        <v>125.61</v>
+        <v>53.35</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>730206</v>
+        <v>270203</v>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AA19" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2787,17 +2787,17 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" s="3" t="n">
-        <v>27.8</v>
+      <c r="AD19" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,41 +2817,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>347.79</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>5.07</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-4.69</v>
+        <v>-2.44</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-51.9</v>
+        <v>-30.24</v>
       </c>
       <c r="H20" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.33</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>-1.99</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>2.17</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>38.3</v>
+        <v>52.4</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2867,39 +2867,39 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-4.17</v>
+        <v>-2.28</v>
       </c>
       <c r="P20" t="n">
-        <v>7.04</v>
+        <v>7.93</v>
       </c>
       <c r="Q20" t="n">
-        <v>323.31</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>354.84</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>749.88</v>
+        <v>113.87</v>
       </c>
       <c r="T20" t="n">
-        <v>308</v>
+        <v>60.84</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>270104</v>
+        <v>270107</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2907,17 +2907,17 @@
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="n">
-        <v>24.1</v>
+      <c r="AD20" t="n">
+        <v>31.5</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>94.23</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-0.63</v>
+        <v>275.84</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>7.38</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>12.42</v>
+        <v>7.5</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-27.98</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -2971,15 +2971,15 @@
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>死叉(转空)</t>
+        <v>5.01</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>50.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2987,39 +2987,39 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>12.94</v>
+        <v>7.66</v>
       </c>
       <c r="P21" t="n">
-        <v>10.7</v>
+        <v>11.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>84.15000000000001</v>
+        <v>244.29</v>
       </c>
       <c r="R21" t="n">
-        <v>93.55</v>
+        <v>262.69</v>
       </c>
       <c r="S21" t="n">
-        <v>136.42</v>
+        <v>303.5</v>
       </c>
       <c r="T21" t="n">
-        <v>69.63</v>
+        <v>155.05</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>650201</v>
+        <v>730204</v>
       </c>
       <c r="Z21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3027,17 +3027,17 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" s="3" t="n">
-        <v>24.1</v>
+      <c r="AD21" t="n">
+        <v>31.5</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,32 +3057,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>415</v>
+        <v>219</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6.99</v>
+        <v>1.2</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>3.66</v>
+        <v>26.29</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-57.22</v>
+        <v>-14.04</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.92</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1.7</v>
+        <v>5.21</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>48.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -3107,36 +3107,36 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>4.18</v>
+        <v>26.45</v>
       </c>
       <c r="P22" t="n">
-        <v>8.99</v>
+        <v>13.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>377.68</v>
+        <v>189.44</v>
       </c>
       <c r="R22" t="n">
-        <v>408.08</v>
+        <v>208.15</v>
       </c>
       <c r="S22" t="n">
-        <v>976</v>
+        <v>257.41</v>
       </c>
       <c r="T22" t="n">
-        <v>334</v>
+        <v>125.61</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>270104</v>
+        <v>730206</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AA22" t="n">
         <v>5</v>
@@ -3147,12 +3147,12 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="n">
-        <v>22.2</v>
+      <c r="AD22" t="n">
+        <v>31.5</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3177,32 +3177,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25.61</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>4.7</v>
+        <v>125.14</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.54</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1.87</v>
+        <v>9.49</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-20.34</v>
+        <v>-18.1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.98</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.98</v>
+        <v>1.59</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>47.7</v>
+        <v>59.4</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -3227,36 +3227,36 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>2.39</v>
+        <v>9.65</v>
       </c>
       <c r="P23" t="n">
-        <v>6.68</v>
+        <v>10.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.9</v>
+        <v>112.48</v>
       </c>
       <c r="R23" t="n">
-        <v>25.36</v>
+        <v>123.18</v>
       </c>
       <c r="S23" t="n">
-        <v>42.08</v>
+        <v>158.2</v>
       </c>
       <c r="T23" t="n">
-        <v>23.8</v>
+        <v>94.73</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270303</v>
+        <v>270202</v>
       </c>
       <c r="Z23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA23" t="n">
         <v>5</v>
@@ -3268,11 +3268,11 @@
         <v>0</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>22.2</v>
+        <v>27.8</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>83.94</v>
+        <v>54.84</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>2.14</v>
+        <v>6.22</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-13.89</v>
+        <v>-21.95</v>
       </c>
       <c r="H24" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -3327,19 +3327,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>0.03</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>-0.52</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>36.4</v>
+        <v>43.4</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -3347,39 +3347,39 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>2.66</v>
+        <v>0.12</v>
       </c>
       <c r="P24" t="n">
-        <v>3.95</v>
+        <v>6.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>80.62</v>
+        <v>51.02</v>
       </c>
       <c r="R24" t="n">
-        <v>83.91</v>
+        <v>55.12</v>
       </c>
       <c r="S24" t="n">
-        <v>113</v>
+        <v>70.63</v>
       </c>
       <c r="T24" t="n">
-        <v>80.55</v>
-      </c>
-      <c r="U24" s="2" t="n">
-        <v>4</v>
+        <v>51</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>710101</v>
+        <v>270504</v>
       </c>
       <c r="Z24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,16 +3388,16 @@
         <v>0</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>22.2</v>
+        <v>18.5</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>88.47</v>
+        <v>348.27</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>4.9</v>
+        <v>6.02</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-20.2</v>
+        <v>-5.79</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-42.92</v>
+        <v>-50.52</v>
       </c>
       <c r="H25" t="n">
-        <v>0.87</v>
+        <v>1.02</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.56</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>49.3</v>
+        <v>41.7</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3467,39 +3467,39 @@
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-19.68</v>
+        <v>-5.63</v>
       </c>
       <c r="P25" t="n">
-        <v>5.48</v>
+        <v>7.13</v>
       </c>
       <c r="Q25" t="n">
-        <v>83.62</v>
+        <v>323.45</v>
       </c>
       <c r="R25" t="n">
-        <v>89.94</v>
+        <v>353.77</v>
       </c>
       <c r="S25" t="n">
-        <v>159.62</v>
+        <v>749.88</v>
       </c>
       <c r="T25" t="n">
-        <v>82.48</v>
+        <v>308</v>
       </c>
       <c r="U25" t="n">
         <v>2</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>630503</v>
+        <v>270104</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>20.4</v>
+        <v>18.5</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,32 +3537,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>62.23</v>
+        <v>88.2</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>13.66</v>
+        <v>5.33</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-19.05</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-18.87</v>
+        <v>-44.31</v>
       </c>
       <c r="H26" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.96</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3571,55 +3571,55 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-0.79</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>39.5</v>
+        <v>58.8</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O26" s="2" t="n">
-        <v>14.18</v>
+      <c r="O26" s="3" t="n">
+        <v>-18.89</v>
       </c>
       <c r="P26" t="n">
-        <v>9.25</v>
+        <v>5.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>56.47</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>63.31</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>80.68000000000001</v>
+        <v>150.45</v>
       </c>
       <c r="T26" t="n">
-        <v>45.82</v>
+        <v>82.48</v>
       </c>
       <c r="U26" t="n">
         <v>2</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>640209</v>
+        <v>630503</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,16 +3628,16 @@
         <v>0</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>16.7</v>
+        <v>14.8</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>33.53</v>
+        <v>38.88</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1.48</v>
+        <v>4.43</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-10.3</v>
+        <v>-15.11</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-34.01</v>
+        <v>-24.06</v>
       </c>
       <c r="H27" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.61</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3691,55 +3691,55 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-5.42</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>25.6</v>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-9.779999999999999</v>
+        <v>-14.95</v>
       </c>
       <c r="P27" t="n">
-        <v>5.44</v>
+        <v>10.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>31.71</v>
+        <v>34.91</v>
       </c>
       <c r="R27" t="n">
-        <v>34.37</v>
+        <v>41.11</v>
       </c>
       <c r="S27" t="n">
-        <v>56.7</v>
+        <v>51.68</v>
       </c>
       <c r="T27" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
+        <v>30.54</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>630702</v>
+        <v>270504</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>14.8</v>
+        <v>11.1</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>54.44</v>
+        <v>61.52</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1.34</v>
+        <v>2.14</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-16.45</v>
+        <v>-22.67</v>
       </c>
       <c r="H28" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.59</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-1.24</v>
+        <v>-2.92</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>42.6</v>
+        <v>36.8</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3827,36 +3827,36 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>7.04</v>
+        <v>9.09</v>
       </c>
       <c r="Q28" t="n">
-        <v>50.61</v>
+        <v>55.93</v>
       </c>
       <c r="R28" t="n">
-        <v>55.12</v>
+        <v>63.37</v>
       </c>
       <c r="S28" t="n">
-        <v>70.73999999999999</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>51</v>
+        <v>45.82</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>270504</v>
+        <v>640209</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA28" t="n">
         <v>3</v>
@@ -3868,11 +3868,11 @@
         <v>0</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>5.6</v>
+        <v>11.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>38.74</v>
+        <v>33.31</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>3.14</v>
+        <v>1.59</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-10.16</v>
+        <v>-8.24</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-18.97</v>
+        <v>-35.11</v>
       </c>
       <c r="H29" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.78</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3931,55 +3931,55 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.55</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-2.65</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>40.2</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-9.640000000000001</v>
+        <v>-8.08</v>
       </c>
       <c r="P29" t="n">
-        <v>10.29</v>
+        <v>5.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>34.75</v>
+        <v>31.63</v>
       </c>
       <c r="R29" t="n">
-        <v>41.46</v>
+        <v>34.22</v>
       </c>
       <c r="S29" t="n">
-        <v>51.68</v>
+        <v>56.7</v>
       </c>
       <c r="T29" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>0</v>
+        <v>31.68</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>270504</v>
+        <v>630702</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -72,8 +72,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -473,8 +473,8 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="81" customWidth="1" min="31" max="31"/>
-    <col width="66" customWidth="1" min="32" max="32"/>
+    <col width="79" customWidth="1" min="31" max="31"/>
+    <col width="76" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
@@ -657,32 +657,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>71.15000000000001</v>
+        <v>223.01</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.12</v>
+        <v>23.67</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>-22.81</v>
+        <v>26.58</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>22.47</v>
       </c>
       <c r="H2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.63</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>5.8</v>
+        <v>16.92</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,44 +699,44 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>70.8</v>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>超买区间</t>
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>11.77</v>
+        <v>28.18</v>
       </c>
       <c r="P2" t="n">
-        <v>8.779999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>64.90000000000001</v>
+        <v>207.13</v>
       </c>
       <c r="R2" t="n">
-        <v>67.25</v>
+        <v>190.74</v>
       </c>
       <c r="S2" t="n">
-        <v>92.06</v>
+        <v>232.68</v>
       </c>
       <c r="T2" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>5</v>
+        <v>170.1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>270303</v>
+        <v>270104</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
         <v>11</v>
@@ -748,11 +748,11 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>59.3</v>
+        <v>53.7</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；突破20日新高；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；突破20日新高；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -777,32 +777,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63.34</v>
+        <v>128.1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13.78</v>
+        <v>0.23</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>-36.92</v>
+        <v>7.45</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-11.66</v>
       </c>
       <c r="H3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.07</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>9.82</v>
+        <v>3.62</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>66.3</v>
+        <v>65.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -827,39 +827,39 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>10.24</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>10.44</v>
+        <v>9.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>56.72</v>
+        <v>115.4</v>
       </c>
       <c r="R3" t="n">
-        <v>57.68</v>
+        <v>123.62</v>
       </c>
       <c r="S3" t="n">
-        <v>107.55</v>
+        <v>142.99</v>
       </c>
       <c r="T3" t="n">
-        <v>43.01</v>
+        <v>94.73</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>640108</v>
+        <v>270202</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>50</v>
+        <v>46.3</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,32 +897,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>198.12</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>-24.48</v>
+        <v>7.75</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>-19.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.33</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>61.7</v>
+        <v>59.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,39 +947,39 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>3.97</v>
+        <v>9.35</v>
       </c>
       <c r="P4" t="n">
-        <v>10.15</v>
+        <v>9.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>178</v>
+        <v>63.59</v>
       </c>
       <c r="R4" t="n">
-        <v>191.12</v>
+        <v>67.5</v>
       </c>
       <c r="S4" t="n">
-        <v>280.08</v>
+        <v>88.66</v>
       </c>
       <c r="T4" t="n">
-        <v>161.8</v>
+        <v>47.3</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270202</v>
+        <v>270303</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>44.4</v>
+        <v>42.6</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,28 +1017,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>227.46</v>
+        <v>275.4</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17.01</v>
+        <v>2.57</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>-7.43</v>
+        <v>8.82</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.17</v>
+        <v>0.86</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>11.75</v>
+        <v>4.39</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -1059,47 +1059,47 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>超买区间</t>
+        <v>65.40000000000001</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>12.38</v>
+        <v>10.42</v>
       </c>
       <c r="P5" t="n">
-        <v>12.22</v>
+        <v>11.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>199.66</v>
+        <v>243.9</v>
       </c>
       <c r="R5" t="n">
-        <v>203.54</v>
+        <v>263.81</v>
       </c>
       <c r="S5" t="n">
-        <v>250.82</v>
+        <v>294.5</v>
       </c>
       <c r="T5" t="n">
-        <v>102.3</v>
+        <v>155.05</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>730204</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1108,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>42.6</v>
+        <v>38.9</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>107.09</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6.88</v>
+        <v>36.02</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>-5.66</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>-41.99</v>
+        <v>20.67</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-3.3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.82</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,15 +1171,15 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>2.51</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>59.6</v>
+        <v>56.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1187,39 +1187,39 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.89</v>
+        <v>22.27</v>
       </c>
       <c r="P6" t="n">
-        <v>9.9</v>
+        <v>14.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>96.48</v>
+        <v>30.64</v>
       </c>
       <c r="R6" t="n">
-        <v>103.45</v>
+        <v>35.14</v>
       </c>
       <c r="S6" t="n">
-        <v>187.66</v>
+        <v>43.43</v>
       </c>
       <c r="T6" t="n">
-        <v>90.23</v>
+        <v>23.2</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>640703</v>
+        <v>640209</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>42.6</v>
+        <v>38.9</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>84.67</v>
+        <v>451.2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3.18</v>
+        <v>6.49</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>-21.04</v>
+        <v>13.15</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-21.61</v>
       </c>
       <c r="H7" t="n">
         <v>0.96</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1299,47 +1299,47 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>73.40000000000001</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>超买区间</t>
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.94</v>
+        <v>14.75</v>
       </c>
       <c r="P7" t="n">
-        <v>4.16</v>
+        <v>9.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>81.15000000000001</v>
+        <v>407.64</v>
       </c>
       <c r="R7" t="n">
-        <v>83.98999999999999</v>
+        <v>415.37</v>
       </c>
       <c r="S7" t="n">
-        <v>113</v>
+        <v>579.42</v>
       </c>
       <c r="T7" t="n">
-        <v>80.55</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>4</v>
+        <v>347</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>710101</v>
+        <v>730204</v>
       </c>
       <c r="Z7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1348,16 +1348,16 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>42.6</v>
+        <v>37</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,28 +1377,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>94.26000000000001</v>
+        <v>190</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.71</v>
+        <v>2.59</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>-37.21</v>
+        <v>13.18</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-21.63</v>
       </c>
       <c r="H8" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.98</v>
+        <v>5.11</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>51.4</v>
+        <v>60.8</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,39 +1427,39 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>10.99</v>
+        <v>14.78</v>
       </c>
       <c r="P8" t="n">
-        <v>11.22</v>
+        <v>10.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>83.69</v>
+        <v>169.72</v>
       </c>
       <c r="R8" t="n">
-        <v>93.34999999999999</v>
+        <v>180.76</v>
       </c>
       <c r="S8" t="n">
-        <v>150.49</v>
+        <v>258.66</v>
       </c>
       <c r="T8" t="n">
-        <v>80.31999999999999</v>
+        <v>152.33</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>640703</v>
+        <v>730204</v>
       </c>
       <c r="Z8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1468,16 +1468,16 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>42.6</v>
+        <v>37</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>217.8</v>
+        <v>226.18</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>22.91</v>
+        <v>9.59</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>16.37</v>
+        <v>14.63</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>-4.71</v>
       </c>
       <c r="H9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.11</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>15.61</v>
+        <v>10.34</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>64.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1547,39 +1547,39 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>24.57</v>
+        <v>16.23</v>
       </c>
       <c r="P9" t="n">
-        <v>7.11</v>
+        <v>12.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>202.32</v>
+        <v>198.73</v>
       </c>
       <c r="R9" t="n">
-        <v>188.4</v>
+        <v>204.98</v>
       </c>
       <c r="S9" t="n">
-        <v>232.68</v>
+        <v>250.82</v>
       </c>
       <c r="T9" t="n">
-        <v>170.1</v>
+        <v>102.3</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>270104</v>
+        <v>730204</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1588,16 +1588,16 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>40.7</v>
+        <v>33.3</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；突破20日新高；20日跑赢沪深300超过10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,28 +1617,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>190.37</v>
+        <v>26.19</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13.07</v>
+        <v>6.12</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>-25.91</v>
+        <v>0.96</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-32.73</v>
       </c>
       <c r="H10" t="n">
-        <v>1.32</v>
+        <v>0.95</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>5.96</v>
+        <v>3.09</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>61.1</v>
+        <v>55.1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1667,39 +1667,39 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>13.94</v>
+        <v>2.56</v>
       </c>
       <c r="P10" t="n">
-        <v>10.73</v>
+        <v>6.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>169.94</v>
+        <v>24.44</v>
       </c>
       <c r="R10" t="n">
-        <v>179.66</v>
+        <v>25.4</v>
       </c>
       <c r="S10" t="n">
-        <v>264.88</v>
+        <v>42.08</v>
       </c>
       <c r="T10" t="n">
-        <v>152.33</v>
+        <v>23.8</v>
       </c>
       <c r="U10" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>730204</v>
+        <v>270303</v>
       </c>
       <c r="Z10" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1708,16 +1708,16 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>40.7</v>
+        <v>33.3</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>181.2</v>
+        <v>106.06</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>12.08</v>
+        <v>0.08</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>-39.58</v>
+        <v>2.18</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-38.89</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>6.29</v>
+        <v>2.41</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1787,39 +1787,39 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>18.05</v>
+        <v>3.78</v>
       </c>
       <c r="P11" t="n">
-        <v>10.96</v>
+        <v>9.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>161.33</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>170.48</v>
+        <v>103.57</v>
       </c>
       <c r="S11" t="n">
-        <v>325.74</v>
+        <v>168.98</v>
       </c>
       <c r="T11" t="n">
-        <v>133.61</v>
+        <v>90.23</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>270401</v>
+        <v>640703</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,16 +1828,16 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>40.7</v>
+        <v>33.3</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,32 +1857,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>97.08</v>
+        <v>64.05</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.8</v>
+        <v>7.32</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>-27.31</v>
+        <v>8.710000000000001</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-38.31</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.58</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1891,15 +1891,15 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>3.01</v>
+        <v>10.56</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>54.3</v>
+        <v>66.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>16.97</v>
+        <v>10.31</v>
       </c>
       <c r="P12" t="n">
-        <v>10.59</v>
+        <v>10.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>86.8</v>
+        <v>57.42</v>
       </c>
       <c r="R12" t="n">
-        <v>94.25</v>
+        <v>57.93</v>
       </c>
       <c r="S12" t="n">
-        <v>136.42</v>
+        <v>100.99</v>
       </c>
       <c r="T12" t="n">
-        <v>69.63</v>
+        <v>43.01</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>650201</v>
+        <v>640108</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,16 +1948,16 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>38.9</v>
+        <v>31.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>17.86</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>-6.2</v>
+        <v>193</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>-21.64</v>
       </c>
       <c r="H13" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.06</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>4.22</v>
+        <v>1.02</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>61.2</v>
+        <v>60.9</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -2027,40 +2027,40 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>18.02</v>
+        <v>0.9</v>
       </c>
       <c r="P13" t="n">
-        <v>15.11</v>
+        <v>10.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>30.82</v>
+        <v>173.03</v>
       </c>
       <c r="R13" t="n">
-        <v>34.83</v>
+        <v>191.06</v>
       </c>
       <c r="S13" t="n">
-        <v>43.43</v>
+        <v>280.08</v>
       </c>
       <c r="T13" t="n">
-        <v>23.2</v>
+        <v>161.8</v>
       </c>
       <c r="U13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>270202</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA13" t="n">
         <v>5</v>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="W13" t="n">
-        <v>640209</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3</v>
-      </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
@@ -2068,16 +2068,16 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>38.9</v>
+        <v>31.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>455</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>14.61</v>
+        <v>0.12</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>-25.04</v>
+        <v>11.25</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-21.86</v>
       </c>
       <c r="H14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.03</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>10.24</v>
+        <v>3.92</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -2139,47 +2139,47 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>超买区间</t>
+        <v>59.1</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>13.66</v>
+        <v>12.85</v>
       </c>
       <c r="P14" t="n">
-        <v>9.710000000000001</v>
+        <v>10.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>410.82</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>412.75</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>618.87</v>
+        <v>123.08</v>
       </c>
       <c r="T14" t="n">
-        <v>347</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
+        <v>69.63</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>730204</v>
+        <v>650201</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2188,16 +2188,16 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>37</v>
+        <v>31.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,32 +2217,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.85</v>
+        <v>179.03</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>-26.94</v>
+        <v>17.42</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-40.8</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.02</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1.81</v>
+        <v>4.21</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2267,39 +2267,39 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>2.46</v>
+        <v>19.02</v>
       </c>
       <c r="P15" t="n">
-        <v>6.89</v>
+        <v>10.57</v>
       </c>
       <c r="Q15" t="n">
-        <v>24.07</v>
+        <v>160.1</v>
       </c>
       <c r="R15" t="n">
-        <v>25.39</v>
+        <v>171.8</v>
       </c>
       <c r="S15" t="n">
-        <v>42.08</v>
+        <v>284.37</v>
       </c>
       <c r="T15" t="n">
-        <v>23.8</v>
+        <v>133.61</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270303</v>
+        <v>270401</v>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2307,17 +2307,17 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" t="n">
-        <v>37</v>
+      <c r="AD15" s="4" t="n">
+        <v>29.6</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>249.61</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>2</v>
+        <v>218.17</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-2.44</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>-32.28</v>
+        <v>14.37</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-10.07</v>
       </c>
       <c r="H16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.84</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2371,15 +2371,15 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>4.13</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>63.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2387,39 +2387,39 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>6.15</v>
+        <v>15.97</v>
       </c>
       <c r="P16" t="n">
-        <v>9.859999999999999</v>
+        <v>13.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>225</v>
+        <v>189.32</v>
       </c>
       <c r="R16" t="n">
-        <v>239.51</v>
+        <v>209.52</v>
       </c>
       <c r="S16" t="n">
-        <v>418.99</v>
+        <v>237.87</v>
       </c>
       <c r="T16" t="n">
-        <v>183.83</v>
+        <v>125.61</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>270103</v>
+        <v>730206</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2427,17 +2427,17 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" t="n">
-        <v>37</v>
+      <c r="AD16" s="4" t="n">
+        <v>29.6</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2466,19 +2466,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63.52</v>
+        <v>62.8</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>10.84</v>
+        <v>6.06</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>-16.28</v>
+        <v>2.53</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-15.03</v>
       </c>
       <c r="H17" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>5.81</v>
+        <v>4.48</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>61.6</v>
+        <v>59.6</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2507,16 +2507,16 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>4.46</v>
+        <v>4.13</v>
       </c>
       <c r="P17" t="n">
-        <v>7.93</v>
+        <v>8.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>58.49</v>
+        <v>57.72</v>
       </c>
       <c r="R17" t="n">
-        <v>60.03</v>
+        <v>60.11</v>
       </c>
       <c r="S17" t="n">
         <v>84.7</v>
@@ -2529,17 +2529,17 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W17" t="n">
         <v>270107</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2547,17 +2547,17 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" t="n">
-        <v>33.3</v>
+      <c r="AD17" s="4" t="n">
+        <v>27.8</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线5-10%</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,32 +2577,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>411.57</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>6.63</v>
+        <v>251.99</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-0.33</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>-56.35</v>
+        <v>6.84</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-36.1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.85</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.68</v>
+        <v>4.86</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>49.5</v>
+        <v>63.5</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2627,39 +2627,39 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>3.82</v>
+        <v>8.44</v>
       </c>
       <c r="P18" t="n">
-        <v>9.220000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="Q18" t="n">
-        <v>373.62</v>
+        <v>227.46</v>
       </c>
       <c r="R18" t="n">
-        <v>408.81</v>
+        <v>240.31</v>
       </c>
       <c r="S18" t="n">
-        <v>976</v>
+        <v>385</v>
       </c>
       <c r="T18" t="n">
-        <v>334</v>
+        <v>183.83</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270104</v>
+        <v>270103</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2667,17 +2667,17 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" t="n">
-        <v>33.3</v>
+      <c r="AD18" s="4" t="n">
+        <v>27.8</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60.98</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>3.55</v>
+        <v>92.98</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>-2.68</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>-41.92</v>
+        <v>8.52</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-32.61</v>
       </c>
       <c r="H19" t="n">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2727,11 +2727,11 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>2.27</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>-0.78</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2747,39 +2747,39 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>1.74</v>
+        <v>10.12</v>
       </c>
       <c r="P19" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>54.21</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>59.63</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>113.18</v>
+        <v>140.68</v>
       </c>
       <c r="T19" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>4</v>
+        <v>80.31999999999999</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270203</v>
+        <v>640703</v>
       </c>
       <c r="Z19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA19" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2787,17 +2787,17 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" t="n">
-        <v>33.3</v>
+      <c r="AD19" s="4" t="n">
+        <v>25.9</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,32 +2817,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>72.23999999999999</v>
+        <v>410.32</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>-30.24</v>
+        <v>2.32</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-54.06</v>
       </c>
       <c r="H20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.87</v>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2.17</v>
+        <v>0.13</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -2859,65 +2859,65 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>52.4</v>
+        <v>52</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O20" s="3" t="n">
-        <v>-2.28</v>
+      <c r="O20" s="2" t="n">
+        <v>6.62</v>
       </c>
       <c r="P20" t="n">
-        <v>7.93</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>66.51000000000001</v>
+        <v>373.17</v>
       </c>
       <c r="R20" t="n">
-        <v>70.70999999999999</v>
+        <v>409.79</v>
       </c>
       <c r="S20" t="n">
-        <v>113.87</v>
+        <v>954.1900000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>60.84</v>
-      </c>
-      <c r="U20" t="n">
+        <v>334</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>270104</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA20" t="n">
         <v>3</v>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="W20" t="n">
-        <v>270107</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>10</v>
-      </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" t="n">
-        <v>31.5</v>
+      <c r="AD20" s="4" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,32 +2937,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>275.84</v>
+        <v>71.77</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>-8.720000000000001</v>
+        <v>3.27</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-32.67</v>
       </c>
       <c r="H21" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.33</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>5.01</v>
+        <v>1.71</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -2979,44 +2979,44 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>64.90000000000001</v>
+        <v>51.4</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>7.66</v>
+      <c r="O21" s="4" t="n">
+        <v>-0.85</v>
       </c>
       <c r="P21" t="n">
-        <v>11.44</v>
+        <v>7.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>244.29</v>
+        <v>66.13</v>
       </c>
       <c r="R21" t="n">
-        <v>262.69</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>303.5</v>
+        <v>113.82</v>
       </c>
       <c r="T21" t="n">
-        <v>155.05</v>
-      </c>
-      <c r="U21" s="2" t="n">
-        <v>5</v>
+        <v>60.79</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>730204</v>
+        <v>270107</v>
       </c>
       <c r="Z21" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
         <v>3</v>
@@ -3027,12 +3027,12 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" t="n">
-        <v>31.5</v>
+      <c r="AD21" s="4" t="n">
+        <v>18.5</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3057,32 +3057,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>219</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>1.2</v>
+        <v>59.85</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-0.71</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>26.29</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>-14.04</v>
+        <v>0.44</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-43.89</v>
       </c>
       <c r="H22" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.85</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5.21</v>
+        <v>0.35</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>67.90000000000001</v>
+        <v>55.5</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -3107,39 +3107,39 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>26.45</v>
+        <v>2.04</v>
       </c>
       <c r="P22" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Q22" t="n">
-        <v>189.44</v>
+        <v>53.27</v>
       </c>
       <c r="R22" t="n">
-        <v>208.15</v>
+        <v>59.64</v>
       </c>
       <c r="S22" t="n">
-        <v>257.41</v>
+        <v>105</v>
       </c>
       <c r="T22" t="n">
-        <v>125.61</v>
+        <v>53.35</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>730206</v>
+        <v>270203</v>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3147,17 +3147,17 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" t="n">
-        <v>31.5</v>
+      <c r="AD22" s="4" t="n">
+        <v>18.5</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,49 +3177,49 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>125.14</v>
-      </c>
-      <c r="E23" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>空头排列</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="n">
         <v>-0.54</v>
       </c>
-      <c r="F23" s="2" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>-18.1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>1.59</v>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>59.4</v>
+        <v>45.6</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -3227,39 +3227,39 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>9.65</v>
+        <v>0.71</v>
       </c>
       <c r="P23" t="n">
-        <v>10.12</v>
+        <v>4.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>112.48</v>
+        <v>80.09</v>
       </c>
       <c r="R23" t="n">
-        <v>123.18</v>
+        <v>83.95</v>
       </c>
       <c r="S23" t="n">
-        <v>158.2</v>
+        <v>113</v>
       </c>
       <c r="T23" t="n">
-        <v>94.73</v>
-      </c>
-      <c r="U23" s="2" t="n">
-        <v>5</v>
+        <v>80.55</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270202</v>
+        <v>710101</v>
       </c>
       <c r="Z23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AA23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3267,17 +3267,17 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" s="3" t="n">
-        <v>27.8</v>
+      <c r="AD23" s="4" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>54.84</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>-21.95</v>
+        <v>61.25</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>-18.04</v>
       </c>
       <c r="H24" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.54</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3330,56 +3330,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>金叉(转多)</t>
+      <c r="K24" s="4" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>27.1</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>0.12</v>
+        <v>0.28</v>
       </c>
       <c r="P24" t="n">
-        <v>6.96</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>51.02</v>
+        <v>56.21</v>
       </c>
       <c r="R24" t="n">
-        <v>55.12</v>
+        <v>63.33</v>
       </c>
       <c r="S24" t="n">
-        <v>70.63</v>
+        <v>78.5</v>
       </c>
       <c r="T24" t="n">
-        <v>51</v>
-      </c>
-      <c r="U24" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>640209</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3</v>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="W24" t="n">
-        <v>270504</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
       <c r="AA24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3387,17 +3387,17 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" s="3" t="n">
-        <v>18.5</v>
+      <c r="AD24" s="4" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3426,21 +3426,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>348.27</v>
+        <v>346</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>-5.79</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>-50.52</v>
+        <v>2.08</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>-48.19</v>
       </c>
       <c r="H25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
+        <v>1.09</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3450,8 +3450,8 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>-1.56</v>
+      <c r="K25" s="4" t="n">
+        <v>-1.94</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -3459,27 +3459,27 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O25" s="3" t="n">
-        <v>-5.63</v>
+      <c r="O25" s="4" t="n">
+        <v>-3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>7.13</v>
+        <v>7.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>323.45</v>
+        <v>321.3</v>
       </c>
       <c r="R25" t="n">
-        <v>353.77</v>
+        <v>352.86</v>
       </c>
       <c r="S25" t="n">
-        <v>749.88</v>
+        <v>710</v>
       </c>
       <c r="T25" t="n">
         <v>308</v>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3507,8 +3507,8 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" s="3" t="n">
-        <v>18.5</v>
+      <c r="AD25" s="4" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,30 +3537,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-19.05</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>-44.31</v>
+        <v>32.84</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>-10.47</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>-39.6</v>
       </c>
       <c r="H26" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
+        <v>0.76</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3570,8 +3570,8 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>-0.79</v>
+      <c r="K26" s="4" t="n">
+        <v>-3.48</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -3579,47 +3579,47 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>58.8</v>
+        <v>33.9</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O26" s="3" t="n">
-        <v>-18.89</v>
+      <c r="O26" s="4" t="n">
+        <v>-8.869999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>5.44</v>
+        <v>5.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>83.40000000000001</v>
+        <v>31.17</v>
       </c>
       <c r="R26" t="n">
-        <v>88.90000000000001</v>
+        <v>34.02</v>
       </c>
       <c r="S26" t="n">
-        <v>150.45</v>
+        <v>56.7</v>
       </c>
       <c r="T26" t="n">
-        <v>82.48</v>
+        <v>31.68</v>
       </c>
       <c r="U26" t="n">
         <v>2</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>630503</v>
+        <v>630702</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3627,8 +3627,8 @@
       <c r="AC26" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="3" t="n">
-        <v>14.8</v>
+      <c r="AD26" s="4" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>38.88</v>
+        <v>54.37</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>-15.11</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>-24.06</v>
+        <v>2.8</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>-17.75</v>
       </c>
       <c r="H27" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.77</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3690,46 +3690,46 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K27" s="3" t="n">
-        <v>-5.42</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+      <c r="K27" s="4" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>-14.95</v>
+        <v>44.5</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>-3.2</v>
       </c>
       <c r="P27" t="n">
-        <v>10.22</v>
+        <v>6.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>34.91</v>
+        <v>50.72</v>
       </c>
       <c r="R27" t="n">
-        <v>41.11</v>
+        <v>54.99</v>
       </c>
       <c r="S27" t="n">
-        <v>51.68</v>
+        <v>65.83</v>
       </c>
       <c r="T27" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W27" t="n">
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3747,8 +3747,8 @@
       <c r="AC27" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="3" t="n">
-        <v>11.1</v>
+      <c r="AD27" s="4" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>61.52</v>
+        <v>86.83</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>-22.67</v>
+        <v>2.71</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>-22.46</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>-36.29</v>
       </c>
       <c r="H28" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3810,53 +3810,53 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K28" s="3" t="n">
-        <v>-2.92</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+      <c r="K28" s="4" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>36.8</v>
+        <v>51.3</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O28" s="2" t="n">
-        <v>2.3</v>
+      <c r="O28" s="4" t="n">
+        <v>-20.86</v>
       </c>
       <c r="P28" t="n">
-        <v>9.09</v>
+        <v>5.58</v>
       </c>
       <c r="Q28" t="n">
-        <v>55.93</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="R28" t="n">
-        <v>63.37</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>80.48999999999999</v>
+        <v>134.6</v>
       </c>
       <c r="T28" t="n">
-        <v>45.82</v>
+        <v>82.48</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>640209</v>
+        <v>630503</v>
       </c>
       <c r="Z28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>3</v>
@@ -3867,12 +3867,12 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" s="3" t="n">
-        <v>11.1</v>
+      <c r="AD28" s="4" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>33.31</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-8.24</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>-35.11</v>
+        <v>0.65</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>-19.22</v>
       </c>
       <c r="H29" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.59</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3930,56 +3930,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+      <c r="K29" s="4" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>-8.08</v>
+        <v>24.1</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>-8.18</v>
       </c>
       <c r="P29" t="n">
-        <v>5.05</v>
+        <v>9.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>31.63</v>
+        <v>35.12</v>
       </c>
       <c r="R29" t="n">
-        <v>34.22</v>
+        <v>40.9</v>
       </c>
       <c r="S29" t="n">
-        <v>56.7</v>
+        <v>51.14</v>
       </c>
       <c r="T29" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2</v>
+        <v>30.54</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>630702</v>
+        <v>270504</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3987,8 +3987,8 @@
       <c r="AC29" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD29" s="4" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -4035,7 +4035,7 @@
           <t>重要说明</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>本报表所有指标基于公开技术分析公式计算，是历史价格的客观统计描述，不构成投资建议，不保证未来表现。是否建仓、仓位大小、止损位设置，最终需要你自己判断和承担风险。</t>
         </is>

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -474,7 +474,7 @@
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
     <col width="79" customWidth="1" min="31" max="31"/>
-    <col width="76" customWidth="1" min="32" max="32"/>
+    <col width="58" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>223.01</v>
+        <v>219.05</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>23.67</v>
+        <v>20.88</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>26.58</v>
+        <v>20.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>22.47</v>
+        <v>24.35</v>
       </c>
       <c r="H2" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>16.92</v>
+        <v>13.72</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>70.8</v>
+        <v>71.8</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>28.18</v>
+        <v>24.9</v>
       </c>
       <c r="P2" t="n">
-        <v>7.12</v>
+        <v>7.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>207.13</v>
+        <v>203.14</v>
       </c>
       <c r="R2" t="n">
-        <v>190.74</v>
+        <v>192.62</v>
       </c>
       <c r="S2" t="n">
         <v>232.68</v>
@@ -729,17 +729,17 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>270104</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -748,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>53.7</v>
+        <v>42.6</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；突破20日新高；20日跑赢沪深300超过10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,32 +777,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>128.1</v>
+        <v>435</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.23</v>
+        <v>2.51</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>7.45</v>
+        <v>6.33</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-11.66</v>
+        <v>-14.54</v>
       </c>
       <c r="H3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.89</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>65.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -827,39 +827,39 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>10.46</v>
       </c>
       <c r="P3" t="n">
-        <v>9.92</v>
+        <v>10.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>115.4</v>
+        <v>391.15</v>
       </c>
       <c r="R3" t="n">
-        <v>123.62</v>
+        <v>416.67</v>
       </c>
       <c r="S3" t="n">
-        <v>142.99</v>
+        <v>579.42</v>
       </c>
       <c r="T3" t="n">
-        <v>94.73</v>
+        <v>347</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270202</v>
+        <v>730204</v>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>46.3</v>
+        <v>38.9</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>69.93000000000001</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1.95</v>
+        <v>68.06999999999999</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>-0.92</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>7.75</v>
+        <v>0.65</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-19.7</v>
+        <v>-19.96</v>
       </c>
       <c r="H4" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3.6</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,19 +947,19 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>9.35</v>
+        <v>4.78</v>
       </c>
       <c r="P4" t="n">
-        <v>9.07</v>
+        <v>9.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>63.59</v>
+        <v>61.87</v>
       </c>
       <c r="R4" t="n">
-        <v>67.5</v>
+        <v>67.52</v>
       </c>
       <c r="S4" t="n">
-        <v>88.66</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>47.3</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -979,7 +979,7 @@
         <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>42.6</v>
+        <v>37</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>275.4</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>8.82</v>
+        <v>1.82</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-3.2</v>
+        <v>-34.01</v>
       </c>
       <c r="H5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.44</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4.39</v>
+        <v>6.92</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1067,40 +1067,40 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>10.42</v>
+        <v>5.95</v>
       </c>
       <c r="P5" t="n">
-        <v>11.44</v>
+        <v>10.23</v>
       </c>
       <c r="Q5" t="n">
-        <v>243.9</v>
+        <v>55.66</v>
       </c>
       <c r="R5" t="n">
-        <v>263.81</v>
+        <v>57.99</v>
       </c>
       <c r="S5" t="n">
-        <v>294.5</v>
+        <v>95.95</v>
       </c>
       <c r="T5" t="n">
-        <v>155.05</v>
+        <v>43.01</v>
       </c>
       <c r="U5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>640108</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA5" t="n">
         <v>5</v>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>730204</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3</v>
-      </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
@@ -1108,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>38.9</v>
+        <v>35.2</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>36.02</v>
+        <v>243.62</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-5.66</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>20.67</v>
+        <v>-2.31</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>-1.84</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.3</v>
+        <v>-28.86</v>
       </c>
       <c r="H6" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.77</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,15 +1171,15 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>死叉(转空)</t>
+        <v>1.47</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>56.8</v>
+        <v>62.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1187,36 +1187,36 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>22.27</v>
+        <v>2.29</v>
       </c>
       <c r="P6" t="n">
-        <v>14.92</v>
+        <v>9.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>30.64</v>
+        <v>219.81</v>
       </c>
       <c r="R6" t="n">
-        <v>35.14</v>
+        <v>240.09</v>
       </c>
       <c r="S6" t="n">
-        <v>43.43</v>
+        <v>385</v>
       </c>
       <c r="T6" t="n">
-        <v>23.2</v>
+        <v>183.83</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>640209</v>
+        <v>270103</v>
       </c>
       <c r="Z6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
         <v>3</v>
@@ -1228,11 +1228,11 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>38.9</v>
+        <v>33.3</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>451.2</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>6.49</v>
+        <v>267.93</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>-3.5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>-21.61</v>
+        <v>0.48</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>7.06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.75</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>8.630000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1299,44 +1299,44 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>超买区间</t>
+        <v>60.4</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>14.75</v>
+        <v>4.61</v>
       </c>
       <c r="P7" t="n">
-        <v>9.65</v>
+        <v>11.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>407.64</v>
+        <v>237.35</v>
       </c>
       <c r="R7" t="n">
-        <v>415.37</v>
+        <v>263.87</v>
       </c>
       <c r="S7" t="n">
-        <v>579.42</v>
+        <v>294.5</v>
       </c>
       <c r="T7" t="n">
-        <v>347</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
+        <v>155.05</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>730204</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
         <v>3</v>
@@ -1348,11 +1348,11 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>37</v>
+        <v>33.3</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1386,19 +1386,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>190</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>2.59</v>
+        <v>181.99</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-4.83</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>13.18</v>
+        <v>3.18</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-21.63</v>
+        <v>-16.59</v>
       </c>
       <c r="H8" t="n">
-        <v>1.18</v>
+        <v>0.89</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>5.11</v>
+        <v>0.52</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>60.8</v>
+        <v>59</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,16 +1427,16 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>14.78</v>
+        <v>7.31</v>
       </c>
       <c r="P8" t="n">
-        <v>10.67</v>
+        <v>10.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>169.72</v>
+        <v>161.99</v>
       </c>
       <c r="R8" t="n">
-        <v>180.76</v>
+        <v>181.05</v>
       </c>
       <c r="S8" t="n">
         <v>258.66</v>
@@ -1449,14 +1449,14 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>730204</v>
       </c>
       <c r="Z8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
         <v>3</v>
@@ -1468,11 +1468,11 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>37</v>
+        <v>33.3</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>226.18</v>
+        <v>219.11</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>9.59</v>
+        <v>1.45</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>14.63</v>
+        <v>4.65</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.71</v>
+        <v>-6.64</v>
       </c>
       <c r="H9" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>10.34</v>
+        <v>6.64</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -1539,44 +1539,44 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>70.8</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>超买区间</t>
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>16.23</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>12.13</v>
+        <v>12.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>198.73</v>
+        <v>192.06</v>
       </c>
       <c r="R9" t="n">
-        <v>204.98</v>
+        <v>205.47</v>
       </c>
       <c r="S9" t="n">
-        <v>250.82</v>
+        <v>248</v>
       </c>
       <c r="T9" t="n">
         <v>102.3</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>730204</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
         <v>3</v>
@@ -1588,11 +1588,11 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>33.3</v>
+        <v>31.5</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1617,28 +1617,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>26.19</v>
+        <v>172.87</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6.12</v>
+        <v>5.39</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.96</v>
+        <v>4.56</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-32.73</v>
+        <v>-34.01</v>
       </c>
       <c r="H10" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3.09</v>
+        <v>0.4</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>55.1</v>
+        <v>55.8</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1667,39 +1667,39 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>2.56</v>
+        <v>8.69</v>
       </c>
       <c r="P10" t="n">
-        <v>6.67</v>
+        <v>10.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>24.44</v>
+        <v>154.9</v>
       </c>
       <c r="R10" t="n">
-        <v>25.4</v>
+        <v>172.18</v>
       </c>
       <c r="S10" t="n">
-        <v>42.08</v>
+        <v>283.37</v>
       </c>
       <c r="T10" t="n">
-        <v>23.8</v>
+        <v>133.61</v>
       </c>
       <c r="U10" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270303</v>
+        <v>270401</v>
       </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA10" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1707,17 +1707,17 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" t="n">
-        <v>33.3</v>
+      <c r="AD10" s="4" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,32 +1737,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>106.06</v>
+        <v>124.05</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.08</v>
+        <v>0.46</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.18</v>
+        <v>1.66</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-38.89</v>
+        <v>-4.95</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.03</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2.41</v>
+        <v>0.26</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>58.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1787,36 +1787,36 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>3.78</v>
+        <v>5.79</v>
       </c>
       <c r="P11" t="n">
-        <v>9.76</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>95.70999999999999</v>
+        <v>111.89</v>
       </c>
       <c r="R11" t="n">
-        <v>103.57</v>
+        <v>123.72</v>
       </c>
       <c r="S11" t="n">
-        <v>168.98</v>
+        <v>142.99</v>
       </c>
       <c r="T11" t="n">
-        <v>90.23</v>
+        <v>94.73</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>640703</v>
+        <v>270202</v>
       </c>
       <c r="Z11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AA11" t="n">
         <v>3</v>
@@ -1827,12 +1827,12 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" t="n">
-        <v>33.3</v>
+      <c r="AD11" s="4" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1857,32 +1857,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64.05</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>7.32</v>
+        <v>95.56</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>-0.23</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>6.96</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-38.31</v>
+        <v>-18.35</v>
       </c>
       <c r="H12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.95</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>10.56</v>
+        <v>0.53</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>66.8</v>
+        <v>59.6</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>10.31</v>
+        <v>11.09</v>
       </c>
       <c r="P12" t="n">
-        <v>10.36</v>
+        <v>10.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>57.42</v>
+        <v>85.39</v>
       </c>
       <c r="R12" t="n">
-        <v>57.93</v>
+        <v>95.06</v>
       </c>
       <c r="S12" t="n">
-        <v>100.99</v>
+        <v>119.71</v>
       </c>
       <c r="T12" t="n">
-        <v>43.01</v>
+        <v>69.63</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>640108</v>
+        <v>650201</v>
       </c>
       <c r="Z12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1947,17 +1947,17 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AD12" t="n">
-        <v>31.5</v>
+      <c r="AD12" s="4" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>193</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>-0.7</v>
+        <v>35.92</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>14.03</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-21.64</v>
+        <v>-0.64</v>
       </c>
       <c r="H13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.7</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2011,15 +2011,15 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>1.59</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>60.9</v>
+        <v>59.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -2027,39 +2027,39 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>0.9</v>
+        <v>18.16</v>
       </c>
       <c r="P13" t="n">
-        <v>10.35</v>
+        <v>13.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>173.03</v>
+        <v>30.99</v>
       </c>
       <c r="R13" t="n">
-        <v>191.06</v>
+        <v>35.36</v>
       </c>
       <c r="S13" t="n">
-        <v>280.08</v>
+        <v>43.43</v>
       </c>
       <c r="T13" t="n">
-        <v>161.8</v>
+        <v>23.2</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270202</v>
+        <v>640209</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2067,17 +2067,17 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" t="n">
-        <v>31.5</v>
+      <c r="AD13" s="4" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,41 +2097,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>98.45999999999999</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>11.25</v>
+        <v>102.9</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>-1.91</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-21.86</v>
+        <v>-34.12</v>
       </c>
       <c r="H14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.91</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>3.92</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>-0.55</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>59.1</v>
+        <v>58.8</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -2147,39 +2147,39 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>12.85</v>
+        <v>2.22</v>
       </c>
       <c r="P14" t="n">
-        <v>10.36</v>
+        <v>9.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>88.26000000000001</v>
+        <v>92.97</v>
       </c>
       <c r="R14" t="n">
-        <v>94.73999999999999</v>
+        <v>103.47</v>
       </c>
       <c r="S14" t="n">
-        <v>123.08</v>
+        <v>168.98</v>
       </c>
       <c r="T14" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="U14" s="2" t="n">
-        <v>5</v>
+        <v>90.23</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>650201</v>
+        <v>640703</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AA14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2187,17 +2187,17 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" t="n">
-        <v>31.5</v>
+      <c r="AD14" s="4" t="n">
+        <v>20.4</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；OBV创20日新高</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,28 +2217,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>179.03</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>17.42</v>
+        <v>89.09</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-6.03</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>-1.01</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-40.8</v>
+        <v>-28.73</v>
       </c>
       <c r="H15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2247,11 +2247,11 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>4.21</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>-4.89</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2267,36 +2267,36 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>19.02</v>
+        <v>3.12</v>
       </c>
       <c r="P15" t="n">
-        <v>10.57</v>
+        <v>11.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>160.1</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>171.8</v>
+        <v>93.67</v>
       </c>
       <c r="S15" t="n">
-        <v>284.37</v>
+        <v>140.68</v>
       </c>
       <c r="T15" t="n">
-        <v>133.61</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>4</v>
+        <v>80.31999999999999</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270401</v>
+        <v>640703</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AA15" t="n">
         <v>3</v>
@@ -2308,11 +2308,11 @@
         <v>0</v>
       </c>
       <c r="AD15" s="4" t="n">
-        <v>29.6</v>
+        <v>20.4</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>218.17</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>14.37</v>
+        <v>61.02</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>-4.25</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-10.07</v>
+        <v>-9.43</v>
       </c>
       <c r="H16" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.4</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2371,52 +2371,52 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>死叉(转空)</t>
+        <v>1.75</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>65.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O16" s="2" t="n">
-        <v>15.97</v>
+      <c r="O16" s="4" t="n">
+        <v>-0.12</v>
       </c>
       <c r="P16" t="n">
-        <v>13.23</v>
+        <v>7.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>189.32</v>
+        <v>56.29</v>
       </c>
       <c r="R16" t="n">
-        <v>209.52</v>
+        <v>59.97</v>
       </c>
       <c r="S16" t="n">
-        <v>237.87</v>
+        <v>84.7</v>
       </c>
       <c r="T16" t="n">
-        <v>125.61</v>
-      </c>
-      <c r="U16" s="2" t="n">
-        <v>4</v>
+        <v>51.23</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>730206</v>
+        <v>270107</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
         <v>3</v>
@@ -2428,11 +2428,11 @@
         <v>0</v>
       </c>
       <c r="AD16" s="4" t="n">
-        <v>29.6</v>
+        <v>18.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>62.8</v>
+        <v>25.17</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>-5.77</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-15.03</v>
+        <v>-35.33</v>
       </c>
       <c r="H17" t="n">
-        <v>1.35</v>
+        <v>0.99</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2487,11 +2487,11 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>4.48</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>-0.62</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -2499,44 +2499,44 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>59.6</v>
+        <v>52.8</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O17" s="2" t="n">
-        <v>4.13</v>
+      <c r="O17" s="4" t="n">
+        <v>-1.64</v>
       </c>
       <c r="P17" t="n">
-        <v>8.1</v>
+        <v>6.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>57.72</v>
+        <v>23.48</v>
       </c>
       <c r="R17" t="n">
-        <v>60.11</v>
+        <v>25.33</v>
       </c>
       <c r="S17" t="n">
-        <v>84.7</v>
+        <v>39.76</v>
       </c>
       <c r="T17" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="U17" s="2" t="n">
-        <v>4</v>
+        <v>23.8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>270107</v>
+        <v>270303</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>8</v>
@@ -2548,11 +2548,11 @@
         <v>0</v>
       </c>
       <c r="AD17" s="4" t="n">
-        <v>27.8</v>
+        <v>14.8</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>251.99</v>
+        <v>57.96</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>6.84</v>
+        <v>-3.5</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-6.67</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-36.1</v>
+        <v>-41.25</v>
       </c>
       <c r="H18" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2607,11 +2607,11 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>4.86</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>-2.48</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -2619,47 +2619,47 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>63.5</v>
+        <v>54.7</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>8.44</v>
+      <c r="O18" s="4" t="n">
+        <v>-2.54</v>
       </c>
       <c r="P18" t="n">
-        <v>9.73</v>
+        <v>10.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>227.46</v>
+        <v>51.75</v>
       </c>
       <c r="R18" t="n">
-        <v>240.31</v>
+        <v>59.43</v>
       </c>
       <c r="S18" t="n">
-        <v>385</v>
+        <v>105</v>
       </c>
       <c r="T18" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U18" s="2" t="n">
-        <v>4</v>
+        <v>53.35</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270103</v>
+        <v>270203</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,16 +2668,16 @@
         <v>0</v>
       </c>
       <c r="AD18" s="4" t="n">
-        <v>27.8</v>
+        <v>14.8</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>92.98</v>
+        <v>185.99</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>8.52</v>
+        <v>-3.9</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>-7.28</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-32.61</v>
+        <v>-16.1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.78</v>
+        <v>-2.28</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -2739,44 +2739,44 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>50</v>
+        <v>55.2</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O19" s="2" t="n">
-        <v>10.12</v>
+      <c r="O19" s="4" t="n">
+        <v>-3.15</v>
       </c>
       <c r="P19" t="n">
-        <v>11.2</v>
+        <v>10.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>82.56999999999999</v>
+        <v>166.26</v>
       </c>
       <c r="R19" t="n">
-        <v>93.70999999999999</v>
+        <v>190.32</v>
       </c>
       <c r="S19" t="n">
-        <v>140.68</v>
+        <v>280.08</v>
       </c>
       <c r="T19" t="n">
-        <v>80.31999999999999</v>
+        <v>161.8</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>640703</v>
+        <v>270202</v>
       </c>
       <c r="Z19" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
         <v>3</v>
@@ -2788,11 +2788,11 @@
         <v>0</v>
       </c>
       <c r="AD19" s="4" t="n">
-        <v>25.9</v>
+        <v>14.8</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2817,89 +2817,89 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>410.32</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>5.02</v>
+        <v>57.22</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-7.34</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>-13.26</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-54.06</v>
+        <v>-19.86</v>
       </c>
       <c r="H20" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.6</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>-9.02</v>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>52</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>6.62</v>
+        <v>28.1</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>-9.130000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>9.050000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>373.17</v>
+        <v>52.43</v>
       </c>
       <c r="R20" t="n">
-        <v>409.79</v>
+        <v>62.89</v>
       </c>
       <c r="S20" t="n">
-        <v>954.1900000000001</v>
+        <v>78.5</v>
       </c>
       <c r="T20" t="n">
-        <v>334</v>
-      </c>
-      <c r="U20" s="2" t="n">
-        <v>4</v>
+        <v>45.82</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>270104</v>
+        <v>640209</v>
       </c>
       <c r="Z20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,16 +2908,16 @@
         <v>0</v>
       </c>
       <c r="AD20" s="4" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>71.77</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>3.27</v>
+        <v>394.43</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-0.63</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.45</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-32.67</v>
+        <v>-51.36</v>
       </c>
       <c r="H21" t="n">
-        <v>1.33</v>
+        <v>0.85</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2967,11 +2967,11 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>1.71</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>-3.33</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2987,36 +2987,36 @@
         </is>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.85</v>
+        <v>-4.09</v>
       </c>
       <c r="P21" t="n">
-        <v>7.85</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>66.13</v>
+        <v>358.48</v>
       </c>
       <c r="R21" t="n">
-        <v>70.56999999999999</v>
+        <v>408.02</v>
       </c>
       <c r="S21" t="n">
-        <v>113.82</v>
+        <v>954.1900000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>60.79</v>
+        <v>334</v>
       </c>
       <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>270104</v>
+      </c>
+      <c r="Z21" t="n">
         <v>3</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="W21" t="n">
-        <v>270107</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7</v>
       </c>
       <c r="AA21" t="n">
         <v>3</v>
@@ -3028,11 +3028,11 @@
         <v>0</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>18.5</v>
+        <v>11.1</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3057,49 +3057,49 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>59.85</v>
+        <v>209.63</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.71</v>
+        <v>-4.29</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.44</v>
+        <v>5.81</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-43.89</v>
+        <v>-3.99</v>
       </c>
       <c r="H22" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.77</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>55.5</v>
+        <v>59.7</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -3107,36 +3107,36 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>2.04</v>
+        <v>9.94</v>
       </c>
       <c r="P22" t="n">
-        <v>11</v>
+        <v>13.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>53.27</v>
+        <v>180.92</v>
       </c>
       <c r="R22" t="n">
-        <v>59.64</v>
+        <v>210.1</v>
       </c>
       <c r="S22" t="n">
-        <v>105</v>
+        <v>237.87</v>
       </c>
       <c r="T22" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="U22" s="2" t="n">
-        <v>4</v>
+        <v>125.61</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>270203</v>
+        <v>730206</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA22" t="n">
         <v>3</v>
@@ -3148,11 +3148,11 @@
         <v>0</v>
       </c>
       <c r="AD22" s="4" t="n">
-        <v>18.5</v>
+        <v>11.1</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>0.24</v>
+        <v>52</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>-0.25</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.89</v>
+        <v>-9.06</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-18.5</v>
+        <v>-14.42</v>
       </c>
       <c r="H23" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.54</v>
+        <v>-4.98</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -3219,47 +3219,47 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>45.6</v>
+        <v>43.2</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O23" s="2" t="n">
-        <v>0.71</v>
+      <c r="O23" s="4" t="n">
+        <v>-4.93</v>
       </c>
       <c r="P23" t="n">
-        <v>4.08</v>
+        <v>6.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>80.09</v>
+        <v>48.41</v>
       </c>
       <c r="R23" t="n">
-        <v>83.95</v>
+        <v>54.73</v>
       </c>
       <c r="S23" t="n">
-        <v>113</v>
+        <v>65.83</v>
       </c>
       <c r="T23" t="n">
-        <v>80.55</v>
+        <v>51</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>710101</v>
+        <v>270504</v>
       </c>
       <c r="Z23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3268,16 +3268,16 @@
         <v>0</v>
       </c>
       <c r="AD23" s="4" t="n">
-        <v>11.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.25</v>
+        <v>331.77</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.26</v>
+        <v>-0.99</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.32</v>
+        <v>-14.1</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-18.04</v>
+        <v>-44.63</v>
       </c>
       <c r="H24" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.14</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3331,55 +3331,55 @@
         </is>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-5.25</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="n">
-        <v>0.28</v>
+        <v>41.2</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>-9.970000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>8.220000000000001</v>
+        <v>7.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>56.21</v>
+        <v>308.09</v>
       </c>
       <c r="R24" t="n">
-        <v>63.33</v>
+        <v>350.14</v>
       </c>
       <c r="S24" t="n">
-        <v>78.5</v>
+        <v>710</v>
       </c>
       <c r="T24" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="U24" s="4" t="n">
-        <v>1</v>
+        <v>308</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>640209</v>
+        <v>270104</v>
       </c>
       <c r="Z24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,16 +3388,16 @@
         <v>0</v>
       </c>
       <c r="AD24" s="4" t="n">
-        <v>11.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>346</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>2.08</v>
+        <v>31.76</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>-3.41</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5</v>
+        <v>-14.55</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-48.19</v>
+        <v>-41.98</v>
       </c>
       <c r="H25" t="n">
-        <v>1.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.94</v>
+        <v>-5.91</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>41.9</v>
+        <v>32.1</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3467,33 +3467,33 @@
         </is>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.4</v>
+        <v>-10.42</v>
       </c>
       <c r="P25" t="n">
-        <v>7.14</v>
+        <v>5.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>321.3</v>
+        <v>30.1</v>
       </c>
       <c r="R25" t="n">
-        <v>352.86</v>
+        <v>33.75</v>
       </c>
       <c r="S25" t="n">
-        <v>710</v>
+        <v>55.28</v>
       </c>
       <c r="T25" t="n">
-        <v>308</v>
+        <v>31.68</v>
       </c>
       <c r="U25" t="n">
         <v>2</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>270104</v>
+        <v>630702</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -3537,32 +3537,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>-0.79</v>
+        <v>68.78</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1.6</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-10.47</v>
+        <v>-10.08</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-39.6</v>
+        <v>-28.3</v>
       </c>
       <c r="H26" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.33</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.48</v>
+        <v>-2</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>33.9</v>
+        <v>53.9</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3587,39 +3587,39 @@
         </is>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-8.869999999999999</v>
+        <v>-5.95</v>
       </c>
       <c r="P26" t="n">
-        <v>5.1</v>
+        <v>7.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>31.17</v>
+        <v>63.47</v>
       </c>
       <c r="R26" t="n">
-        <v>34.02</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>56.7</v>
+        <v>113.82</v>
       </c>
       <c r="T26" t="n">
-        <v>31.68</v>
+        <v>60.79</v>
       </c>
       <c r="U26" t="n">
         <v>2</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>630702</v>
+        <v>270107</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>54.37</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2.8</v>
+        <v>0.21</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.8</v>
+        <v>-14.25</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-17.75</v>
+        <v>-33.8</v>
       </c>
       <c r="H27" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.95</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.12</v>
+        <v>-3.15</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>44.5</v>
+        <v>38.7</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3707,33 +3707,33 @@
         </is>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.2</v>
+        <v>-10.12</v>
       </c>
       <c r="P27" t="n">
-        <v>6.71</v>
+        <v>5.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>50.72</v>
+        <v>79.37</v>
       </c>
       <c r="R27" t="n">
-        <v>54.99</v>
+        <v>86.95</v>
       </c>
       <c r="S27" t="n">
-        <v>65.83</v>
+        <v>131.26</v>
       </c>
       <c r="T27" t="n">
-        <v>51</v>
+        <v>82.48</v>
       </c>
       <c r="U27" t="n">
         <v>2</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>270504</v>
+        <v>630503</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3777,28 +3777,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>86.83</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>2.71</v>
+        <v>82.17</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>-0.62</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-22.46</v>
+        <v>-5.05</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-36.29</v>
+        <v>-13.1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.93</v>
+        <v>-1.86</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>51.3</v>
+        <v>47.2</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3827,33 +3827,33 @@
         </is>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-20.86</v>
+        <v>-0.92</v>
       </c>
       <c r="P28" t="n">
-        <v>5.58</v>
+        <v>3.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>81.98999999999999</v>
+        <v>79.02</v>
       </c>
       <c r="R28" t="n">
-        <v>87.65000000000001</v>
+        <v>83.73</v>
       </c>
       <c r="S28" t="n">
-        <v>134.6</v>
+        <v>113</v>
       </c>
       <c r="T28" t="n">
-        <v>82.48</v>
+        <v>80.55</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>630503</v>
+        <v>710101</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3906,19 +3906,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>0.65</v>
+        <v>37.47</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>-2.55</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-9.779999999999999</v>
+        <v>-15.89</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-19.22</v>
+        <v>-19.56</v>
       </c>
       <c r="H29" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4.64</v>
+        <v>-7.58</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>24.1</v>
+        <v>27.3</v>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
@@ -3947,16 +3947,16 @@
         </is>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-8.18</v>
+        <v>-11.76</v>
       </c>
       <c r="P29" t="n">
-        <v>9.94</v>
+        <v>9.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>35.12</v>
+        <v>33.87</v>
       </c>
       <c r="R29" t="n">
-        <v>40.9</v>
+        <v>40.54</v>
       </c>
       <c r="S29" t="n">
         <v>51.14</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="W29" t="n">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>24.9</v>
+        <v>26.59</v>
       </c>
       <c r="P2" t="n">
         <v>7.26</v>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>10.46</v>
+        <v>12.15</v>
       </c>
       <c r="P3" t="n">
         <v>10.08</v>
@@ -897,28 +897,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>68.06999999999999</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>-0.92</v>
+        <v>219.11</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1.45</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.65</v>
+        <v>4.65</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-19.96</v>
+        <v>-6.64</v>
       </c>
       <c r="H4" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>6.64</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,33 +939,33 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>70.8</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>超买区间</t>
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>4.78</v>
+        <v>10.47</v>
       </c>
       <c r="P4" t="n">
-        <v>9.1</v>
+        <v>12.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>61.87</v>
+        <v>192.06</v>
       </c>
       <c r="R4" t="n">
-        <v>67.52</v>
+        <v>205.47</v>
       </c>
       <c r="S4" t="n">
-        <v>85.76000000000001</v>
+        <v>248</v>
       </c>
       <c r="T4" t="n">
-        <v>47.3</v>
+        <v>102.3</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270303</v>
+        <v>730204</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -992,12 +992,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>2.82</v>
+        <v>68.06999999999999</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>-0.92</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1.82</v>
+        <v>0.65</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-34.01</v>
+        <v>-19.96</v>
       </c>
       <c r="H5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.22</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>6.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>69.09999999999999</v>
+        <v>59.1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1067,25 +1067,25 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>5.95</v>
+        <v>6.47</v>
       </c>
       <c r="P5" t="n">
-        <v>10.23</v>
+        <v>9.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>55.66</v>
+        <v>61.87</v>
       </c>
       <c r="R5" t="n">
-        <v>57.99</v>
+        <v>67.52</v>
       </c>
       <c r="S5" t="n">
-        <v>95.95</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>43.01</v>
+        <v>47.3</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>640108</v>
+        <v>270303</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA5" t="n">
         <v>5</v>
@@ -1108,11 +1108,11 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>35.2</v>
+        <v>37</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1137,28 +1137,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>243.62</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-1.84</v>
+        <v>62</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1.82</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-28.86</v>
+        <v>-34.01</v>
       </c>
       <c r="H6" t="n">
-        <v>0.77</v>
+        <v>1.44</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1.47</v>
+        <v>6.92</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>62.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1187,22 +1187,22 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>2.29</v>
+        <v>7.64</v>
       </c>
       <c r="P6" t="n">
-        <v>9.77</v>
+        <v>10.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>219.81</v>
+        <v>55.66</v>
       </c>
       <c r="R6" t="n">
-        <v>240.09</v>
+        <v>57.99</v>
       </c>
       <c r="S6" t="n">
-        <v>385</v>
+        <v>95.95</v>
       </c>
       <c r="T6" t="n">
-        <v>183.83</v>
+        <v>43.01</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>4</v>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>270103</v>
+        <v>640108</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>33.3</v>
+        <v>35.2</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>267.93</v>
+        <v>243.62</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>7.06</v>
+        <v>-2.31</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-28.86</v>
       </c>
       <c r="H7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.77</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>60.4</v>
+        <v>62.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,25 +1307,25 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>4.61</v>
+        <v>3.98</v>
       </c>
       <c r="P7" t="n">
-        <v>11.41</v>
+        <v>9.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>237.35</v>
+        <v>219.81</v>
       </c>
       <c r="R7" t="n">
-        <v>263.87</v>
+        <v>240.09</v>
       </c>
       <c r="S7" t="n">
-        <v>294.5</v>
+        <v>385</v>
       </c>
       <c r="T7" t="n">
-        <v>155.05</v>
+        <v>183.83</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>730204</v>
+        <v>270103</v>
       </c>
       <c r="Z7" t="n">
         <v>15</v>
@@ -1377,32 +1377,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>181.99</v>
+        <v>267.93</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.83</v>
+        <v>-3.5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>-16.59</v>
+        <v>0.48</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>7.06</v>
       </c>
       <c r="H8" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.75</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.52</v>
+        <v>1.54</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>59</v>
+        <v>60.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,25 +1427,25 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>7.31</v>
+        <v>6.3</v>
       </c>
       <c r="P8" t="n">
-        <v>10.99</v>
+        <v>11.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>161.99</v>
+        <v>237.35</v>
       </c>
       <c r="R8" t="n">
-        <v>181.05</v>
+        <v>263.87</v>
       </c>
       <c r="S8" t="n">
-        <v>258.66</v>
+        <v>294.5</v>
       </c>
       <c r="T8" t="n">
-        <v>152.33</v>
+        <v>155.05</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>219.11</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1.45</v>
+        <v>181.99</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>-4.83</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.65</v>
+        <v>3.18</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-6.64</v>
+        <v>-16.59</v>
       </c>
       <c r="H9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.89</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>6.64</v>
+        <v>0.52</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -1539,30 +1539,30 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>超买区间</t>
+        <v>59</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>9</v>
       </c>
       <c r="P9" t="n">
-        <v>12.35</v>
+        <v>10.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>192.06</v>
+        <v>161.99</v>
       </c>
       <c r="R9" t="n">
-        <v>205.47</v>
+        <v>181.05</v>
       </c>
       <c r="S9" t="n">
-        <v>248</v>
+        <v>258.66</v>
       </c>
       <c r="T9" t="n">
-        <v>102.3</v>
+        <v>152.33</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>4</v>
@@ -1576,7 +1576,7 @@
         <v>730204</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
         <v>3</v>
@@ -1588,11 +1588,11 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>31.5</v>
+        <v>33.3</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>8.69</v>
+        <v>10.38</v>
       </c>
       <c r="P10" t="n">
         <v>10.4</v>
@@ -1696,7 +1696,7 @@
         <v>270401</v>
       </c>
       <c r="Z10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
         <v>3</v>
@@ -1708,11 +1708,11 @@
         <v>0</v>
       </c>
       <c r="AD10" s="4" t="n">
-        <v>24.1</v>
+        <v>29.6</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>5.79</v>
+        <v>7.48</v>
       </c>
       <c r="P11" t="n">
         <v>9.800000000000001</v>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>11.09</v>
+        <v>12.78</v>
       </c>
       <c r="P12" t="n">
         <v>10.64</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>18.16</v>
+        <v>19.85</v>
       </c>
       <c r="P13" t="n">
         <v>13.74</v>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>2.22</v>
+        <v>3.91</v>
       </c>
       <c r="P14" t="n">
         <v>9.65</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>3.12</v>
+        <v>4.81</v>
       </c>
       <c r="P15" t="n">
         <v>11.09</v>
@@ -2386,8 +2386,8 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="O16" s="4" t="n">
-        <v>-0.12</v>
+      <c r="O16" s="2" t="n">
+        <v>1.57</v>
       </c>
       <c r="P16" t="n">
         <v>7.75</v>
@@ -2404,8 +2404,8 @@
       <c r="T16" t="n">
         <v>51.23</v>
       </c>
-      <c r="U16" t="n">
-        <v>3</v>
+      <c r="U16" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2457,32 +2457,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25.17</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>-5.77</v>
+        <v>209.63</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>5.81</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-35.33</v>
+        <v>-3.99</v>
       </c>
       <c r="H17" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.77</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,41 +2491,41 @@
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-0.22</v>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>52.8</v>
+        <v>59.7</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O17" s="4" t="n">
-        <v>-1.64</v>
+      <c r="O17" s="2" t="n">
+        <v>11.63</v>
       </c>
       <c r="P17" t="n">
-        <v>6.71</v>
+        <v>13.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.48</v>
+        <v>180.92</v>
       </c>
       <c r="R17" t="n">
-        <v>25.33</v>
+        <v>210.1</v>
       </c>
       <c r="S17" t="n">
-        <v>39.76</v>
+        <v>237.87</v>
       </c>
       <c r="T17" t="n">
-        <v>23.8</v>
+        <v>125.61</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="W17" t="n">
-        <v>270303</v>
+        <v>730206</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,16 +2548,16 @@
         <v>0</v>
       </c>
       <c r="AD17" s="4" t="n">
-        <v>14.8</v>
+        <v>16.7</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>57.96</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-3.5</v>
+        <v>25.17</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2.44</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-6.67</v>
+        <v>-5.77</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-41.25</v>
+        <v>-35.33</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.48</v>
+        <v>-0.62</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -2619,33 +2619,33 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>54.7</v>
+        <v>52.8</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O18" s="4" t="n">
-        <v>-2.54</v>
+      <c r="O18" s="2" t="n">
+        <v>0.05</v>
       </c>
       <c r="P18" t="n">
-        <v>10.71</v>
+        <v>6.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>51.75</v>
+        <v>23.48</v>
       </c>
       <c r="R18" t="n">
-        <v>59.43</v>
+        <v>25.33</v>
       </c>
       <c r="S18" t="n">
-        <v>105</v>
+        <v>39.76</v>
       </c>
       <c r="T18" t="n">
-        <v>53.35</v>
+        <v>23.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270203</v>
+        <v>270303</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2672,12 +2672,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>185.99</v>
+        <v>57.96</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.9</v>
+        <v>-3.5</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-7.28</v>
+        <v>-6.67</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-16.1</v>
+        <v>-41.25</v>
       </c>
       <c r="H19" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.28</v>
+        <v>-2.48</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>55.2</v>
+        <v>54.7</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2747,22 +2747,22 @@
         </is>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.15</v>
+        <v>-0.85</v>
       </c>
       <c r="P19" t="n">
-        <v>10.61</v>
+        <v>10.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>166.26</v>
+        <v>51.75</v>
       </c>
       <c r="R19" t="n">
-        <v>190.32</v>
+        <v>59.43</v>
       </c>
       <c r="S19" t="n">
-        <v>280.08</v>
+        <v>105</v>
       </c>
       <c r="T19" t="n">
-        <v>161.8</v>
+        <v>53.35</v>
       </c>
       <c r="U19" t="n">
         <v>2</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270202</v>
+        <v>270203</v>
       </c>
       <c r="Z19" t="n">
         <v>5</v>
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>57.22</v>
+        <v>185.99</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-7.34</v>
+        <v>-3.9</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-13.26</v>
+        <v>-7.28</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-19.86</v>
+        <v>-16.1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6</v>
+        <v>0.98</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2851,41 +2851,41 @@
         </is>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-9.02</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-2.28</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>55.2</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-9.130000000000001</v>
+        <v>-1.46</v>
       </c>
       <c r="P20" t="n">
-        <v>8.359999999999999</v>
+        <v>10.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>52.43</v>
+        <v>166.26</v>
       </c>
       <c r="R20" t="n">
-        <v>62.89</v>
+        <v>190.32</v>
       </c>
       <c r="S20" t="n">
-        <v>78.5</v>
+        <v>280.08</v>
       </c>
       <c r="T20" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="U20" s="4" t="n">
-        <v>0</v>
+        <v>161.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2893,13 +2893,13 @@
         </is>
       </c>
       <c r="W20" t="n">
-        <v>640209</v>
+        <v>270202</v>
       </c>
       <c r="Z20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA20" t="n">
         <v>3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>5</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>394.43</v>
+        <v>57.22</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.63</v>
+        <v>-7.34</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-8.220000000000001</v>
+        <v>-13.26</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-51.36</v>
+        <v>-19.86</v>
       </c>
       <c r="H21" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2971,41 +2971,41 @@
         </is>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-9.02</v>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>28.1</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.09</v>
+        <v>-7.44</v>
       </c>
       <c r="P21" t="n">
-        <v>9.109999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>358.48</v>
+        <v>52.43</v>
       </c>
       <c r="R21" t="n">
-        <v>408.02</v>
+        <v>62.89</v>
       </c>
       <c r="S21" t="n">
-        <v>954.1900000000001</v>
+        <v>78.5</v>
       </c>
       <c r="T21" t="n">
-        <v>334</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
+        <v>45.82</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270104</v>
+        <v>640209</v>
       </c>
       <c r="Z21" t="n">
         <v>3</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,32 +3057,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>209.63</v>
+        <v>394.43</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.29</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>5.81</v>
+        <v>-0.63</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>-8.220000000000001</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.99</v>
+        <v>-51.36</v>
       </c>
       <c r="H22" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.85</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3091,41 +3091,41 @@
         </is>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-3.33</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>59.7</v>
+        <v>51.2</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O22" s="2" t="n">
-        <v>9.94</v>
+      <c r="O22" s="4" t="n">
+        <v>-2.4</v>
       </c>
       <c r="P22" t="n">
-        <v>13.69</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>180.92</v>
+        <v>358.48</v>
       </c>
       <c r="R22" t="n">
-        <v>210.1</v>
+        <v>408.02</v>
       </c>
       <c r="S22" t="n">
-        <v>237.87</v>
+        <v>954.1900000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>125.61</v>
+        <v>334</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="W22" t="n">
-        <v>730206</v>
+        <v>270104</v>
       </c>
       <c r="Z22" t="n">
         <v>3</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.93</v>
+        <v>-3.24</v>
       </c>
       <c r="P23" t="n">
         <v>6.9</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-9.970000000000001</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="P24" t="n">
         <v>7.14</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-10.42</v>
+        <v>-8.73</v>
       </c>
       <c r="P25" t="n">
         <v>5.22</v>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-5.95</v>
+        <v>-4.26</v>
       </c>
       <c r="P26" t="n">
         <v>7.72</v>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-10.12</v>
+        <v>-8.43</v>
       </c>
       <c r="P27" t="n">
         <v>5.75</v>
@@ -3826,8 +3826,8 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="O28" s="4" t="n">
-        <v>-0.92</v>
+      <c r="O28" s="2" t="n">
+        <v>0.77</v>
       </c>
       <c r="P28" t="n">
         <v>3.84</v>
@@ -3845,7 +3845,7 @@
         <v>80.55</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-11.76</v>
+        <v>-10.07</v>
       </c>
       <c r="P29" t="n">
         <v>9.6</v>

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -39,14 +39,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -72,8 +72,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -473,7 +473,7 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="79" customWidth="1" min="31" max="31"/>
+    <col width="73" customWidth="1" min="31" max="31"/>
     <col width="58" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
@@ -657,28 +657,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>219.05</v>
+        <v>58.6</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>20.88</v>
+        <v>-8.82</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>20.77</v>
+        <v>-1.15</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>24.35</v>
+        <v>-35.96</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82</v>
+        <v>1.23</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -690,50 +690,50 @@
           <t>是</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>超买区间</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>26.59</v>
+        <v>56.6</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>4.67</v>
       </c>
       <c r="P2" t="n">
-        <v>7.26</v>
+        <v>11.39</v>
       </c>
       <c r="Q2" t="n">
-        <v>203.14</v>
+        <v>51.92</v>
       </c>
       <c r="R2" t="n">
-        <v>192.62</v>
+        <v>57.96</v>
       </c>
       <c r="S2" t="n">
-        <v>232.68</v>
+        <v>95.95</v>
       </c>
       <c r="T2" t="n">
-        <v>170.1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3</v>
+        <v>43.01</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>270104</v>
+        <v>640108</v>
       </c>
       <c r="Z2" t="n">
         <v>15</v>
@@ -752,7 +752,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -777,28 +777,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>435</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>-14.54</v>
+        <v>211.28</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>18.15</v>
       </c>
       <c r="H3" t="n">
-        <v>0.89</v>
+        <v>1.77</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -810,56 +810,56 @@
           <t>是</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>65.59999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>12.15</v>
+      <c r="O3" s="3" t="n">
+        <v>25.25</v>
       </c>
       <c r="P3" t="n">
-        <v>10.08</v>
+        <v>7.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>391.15</v>
+        <v>194.41</v>
       </c>
       <c r="R3" t="n">
-        <v>416.67</v>
+        <v>194.34</v>
       </c>
       <c r="S3" t="n">
-        <v>579.42</v>
+        <v>232.68</v>
       </c>
       <c r="T3" t="n">
-        <v>347</v>
-      </c>
-      <c r="U3" s="2" t="n">
+        <v>170.1</v>
+      </c>
+      <c r="U3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>730204</v>
+        <v>270104</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>38.9</v>
+        <v>40.7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,89 +897,89 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>219.11</v>
+        <v>399.7</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>-6.64</v>
+        <v>-10.18</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>-24.01</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.88</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+        <v>-4.08</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>超买区间</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>10.47</v>
+        <v>44.6</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>12.35</v>
+        <v>11.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>192.06</v>
+        <v>355.25</v>
       </c>
       <c r="R4" t="n">
-        <v>205.47</v>
+        <v>416.7</v>
       </c>
       <c r="S4" t="n">
-        <v>248</v>
+        <v>579.42</v>
       </c>
       <c r="T4" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>4</v>
+        <v>347</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>730204</v>
       </c>
       <c r="Z4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -987,17 +987,17 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="n">
-        <v>37</v>
+      <c r="AD4" s="2" t="n">
+        <v>29.6</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1026,40 +1026,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>68.06999999999999</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-0.92</v>
+        <v>61.72</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>-11.45</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>-19.96</v>
+        <v>-9.44</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>-24.91</v>
       </c>
       <c r="H5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+        <v>1.21</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>多头排列</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>-8.15</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>59.1</v>
+        <v>35.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1067,39 +1067,39 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>6.47</v>
+        <v>-3.62</v>
       </c>
       <c r="P5" t="n">
-        <v>9.1</v>
+        <v>10.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>61.87</v>
+        <v>55.16</v>
       </c>
       <c r="R5" t="n">
-        <v>67.52</v>
+        <v>67.2</v>
       </c>
       <c r="S5" t="n">
-        <v>85.76000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="T5" t="n">
         <v>47.3</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>5</v>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>270303</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1107,17 +1107,17 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" t="n">
-        <v>37</v>
+      <c r="AD5" s="2" t="n">
+        <v>29.6</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,28 +1137,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>163.8</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.82</v>
+        <v>-16.17</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>-34.01</v>
+        <v>-5.65</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>-24.63</v>
       </c>
       <c r="H6" t="n">
-        <v>1.44</v>
+        <v>0.84</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1167,56 +1167,56 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6.92</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>69.09999999999999</v>
+        <v>37.2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>7.64</v>
+      <c r="O6" s="3" t="n">
+        <v>0.17</v>
       </c>
       <c r="P6" t="n">
-        <v>10.23</v>
+        <v>12.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>55.66</v>
+        <v>143.6</v>
       </c>
       <c r="R6" t="n">
-        <v>57.99</v>
+        <v>180.56</v>
       </c>
       <c r="S6" t="n">
-        <v>95.95</v>
+        <v>258.66</v>
       </c>
       <c r="T6" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>4</v>
+        <v>152.33</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>640108</v>
+        <v>730204</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
         <v>5</v>
@@ -1227,17 +1227,17 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" t="n">
-        <v>35.2</v>
+      <c r="AD6" s="2" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,86 +1257,86 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>243.62</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>-28.86</v>
+        <v>202.37</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>-11.76</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>-14.29</v>
       </c>
       <c r="H7" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.86</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1.47</v>
+        <v>-1.46</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>62.8</v>
+        <v>47.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>3.98</v>
+      <c r="O7" s="3" t="n">
+        <v>4.88</v>
       </c>
       <c r="P7" t="n">
-        <v>9.77</v>
+        <v>12.76</v>
       </c>
       <c r="Q7" t="n">
-        <v>219.81</v>
+        <v>176.54</v>
       </c>
       <c r="R7" t="n">
-        <v>240.09</v>
+        <v>205.37</v>
       </c>
       <c r="S7" t="n">
-        <v>385</v>
+        <v>242.99</v>
       </c>
       <c r="T7" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>4</v>
+        <v>102.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>270103</v>
+        <v>730204</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
         <v>3</v>
@@ -1347,12 +1347,12 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" t="n">
-        <v>33.3</v>
+      <c r="AD7" s="2" t="n">
+        <v>20.4</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1377,49 +1377,49 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>267.93</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-3.5</v>
+        <v>58.9</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>-4.04</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.48</v>
+        <v>-7.61</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>7.06</v>
+        <v>-9.1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1.18</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+        <v>-1.39</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>60.4</v>
+        <v>49.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,39 +1427,39 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>6.3</v>
+        <v>-1.79</v>
       </c>
       <c r="P8" t="n">
-        <v>11.41</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>237.35</v>
+        <v>54.12</v>
       </c>
       <c r="R8" t="n">
-        <v>263.87</v>
+        <v>59.73</v>
       </c>
       <c r="S8" t="n">
-        <v>294.5</v>
+        <v>84.7</v>
       </c>
       <c r="T8" t="n">
-        <v>155.05</v>
-      </c>
-      <c r="U8" s="2" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>270107</v>
+      </c>
+      <c r="Z8" t="n">
         <v>5</v>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>730204</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>15</v>
-      </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1467,17 +1467,17 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" t="n">
-        <v>33.3</v>
+      <c r="AD8" s="2" t="n">
+        <v>18.5</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,28 +1497,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>181.99</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>-4.83</v>
+        <v>92.61</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>-14.09</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>-16.59</v>
+        <v>-10.03</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>-39.84</v>
       </c>
       <c r="H9" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1527,19 +1527,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.52</v>
+        <v>-10.04</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>59</v>
+        <v>39.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1547,39 +1547,39 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>9</v>
+        <v>-4.21</v>
       </c>
       <c r="P9" t="n">
-        <v>10.99</v>
+        <v>11.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>161.99</v>
+        <v>82.13</v>
       </c>
       <c r="R9" t="n">
-        <v>181.05</v>
+        <v>102.95</v>
       </c>
       <c r="S9" t="n">
-        <v>258.66</v>
+        <v>168.98</v>
       </c>
       <c r="T9" t="n">
-        <v>152.33</v>
+        <v>90.23</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>730204</v>
+        <v>640703</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1587,17 +1587,17 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" t="n">
-        <v>33.3</v>
+      <c r="AD9" s="2" t="n">
+        <v>18.5</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,49 +1617,49 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>172.87</v>
+        <v>80.02</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>5.39</v>
+        <v>-5.08</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>-34.01</v>
+        <v>-6.76</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>-13.66</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.91</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+        <v>-4.1</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>55.8</v>
+        <v>34.3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1667,39 +1667,39 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>10.38</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>10.4</v>
+        <v>4.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>154.9</v>
+        <v>76.75</v>
       </c>
       <c r="R10" t="n">
-        <v>172.18</v>
+        <v>83.44</v>
       </c>
       <c r="S10" t="n">
-        <v>283.37</v>
+        <v>113</v>
       </c>
       <c r="T10" t="n">
-        <v>133.61</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>4</v>
+        <v>80</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270401</v>
+        <v>710101</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1707,17 +1707,17 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" s="4" t="n">
-        <v>29.6</v>
+      <c r="AD10" s="2" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1746,57 +1746,57 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>124.05</v>
+        <v>117.2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.46</v>
+        <v>-5.1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>-4.95</v>
+        <v>-3.7</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>-13.41</v>
       </c>
       <c r="H11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+        <v>0.95</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>多头排列</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.26</v>
+        <v>-5.1</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>67.40000000000001</v>
+        <v>41.4</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O11" s="2" t="n">
-        <v>7.48</v>
+      <c r="O11" s="3" t="n">
+        <v>2.12</v>
       </c>
       <c r="P11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>111.89</v>
+        <v>105.52</v>
       </c>
       <c r="R11" t="n">
-        <v>123.72</v>
+        <v>123.5</v>
       </c>
       <c r="S11" t="n">
         <v>142.99</v>
@@ -1804,22 +1804,22 @@
       <c r="T11" t="n">
         <v>94.73</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>5</v>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W11" t="n">
         <v>270202</v>
       </c>
       <c r="Z11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1827,17 +1827,17 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="4" t="n">
-        <v>24.1</v>
+      <c r="AD11" s="2" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,49 +1857,49 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>95.56</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-0.23</v>
+        <v>49.92</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>-7.73</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>-18.35</v>
+        <v>-11.8</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>-22.36</v>
       </c>
       <c r="H12" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>多头排列</t>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.53</v>
+        <v>-8.23</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>59.6</v>
+        <v>32.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>12.78</v>
+        <v>-5.98</v>
       </c>
       <c r="P12" t="n">
-        <v>10.64</v>
+        <v>7.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>85.39</v>
+        <v>46.22</v>
       </c>
       <c r="R12" t="n">
-        <v>95.06</v>
+        <v>54.39</v>
       </c>
       <c r="S12" t="n">
-        <v>119.71</v>
+        <v>65.52</v>
       </c>
       <c r="T12" t="n">
-        <v>69.63</v>
+        <v>49.3</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>650201</v>
+        <v>270504</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1947,17 +1947,17 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AD12" s="4" t="n">
-        <v>24.1</v>
+      <c r="AD12" s="2" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,89 +1977,89 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35.92</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-6.12</v>
+        <v>52.16</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>-15.16</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>-0.64</v>
+        <v>-14.21</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>-46.75</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>多头排列</t>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-11.59</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>22.5</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>19.85</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>13.74</v>
+        <v>11.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>30.99</v>
+        <v>45.93</v>
       </c>
       <c r="R13" t="n">
-        <v>35.36</v>
+        <v>59</v>
       </c>
       <c r="S13" t="n">
-        <v>43.43</v>
+        <v>105</v>
       </c>
       <c r="T13" t="n">
-        <v>23.2</v>
+        <v>52.16</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>640209</v>
+        <v>270203</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2067,17 +2067,17 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" s="4" t="n">
-        <v>24.1</v>
+      <c r="AD13" s="2" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,28 +2097,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>102.9</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-2.72</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>-34.12</v>
+        <v>88.48999999999999</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>-22.27</v>
       </c>
       <c r="H14" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2130,53 +2130,53 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K14" s="4" t="n">
-        <v>-0.55</v>
+      <c r="K14" s="2" t="n">
+        <v>-6.85</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>58.8</v>
+        <v>43.6</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n">
-        <v>3.91</v>
+      <c r="O14" s="3" t="n">
+        <v>4.56</v>
       </c>
       <c r="P14" t="n">
-        <v>9.65</v>
+        <v>12.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>92.97</v>
+        <v>77.84</v>
       </c>
       <c r="R14" t="n">
-        <v>103.47</v>
+        <v>95</v>
       </c>
       <c r="S14" t="n">
-        <v>168.98</v>
+        <v>116.03</v>
       </c>
       <c r="T14" t="n">
-        <v>90.23</v>
+        <v>69.63</v>
       </c>
       <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>650201</v>
+      </c>
+      <c r="Z14" t="n">
         <v>3</v>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="W14" t="n">
-        <v>640703</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>8</v>
       </c>
       <c r="AA14" t="n">
         <v>3</v>
@@ -2187,12 +2187,12 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" s="4" t="n">
-        <v>20.4</v>
+      <c r="AD14" s="2" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2217,28 +2217,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>89.09</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-6.03</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>-28.73</v>
+        <v>159.7</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-7.21</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>-39.55</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2250,16 +2250,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K15" s="4" t="n">
-        <v>-4.89</v>
+      <c r="K15" s="2" t="n">
+        <v>-6.91</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>52.3</v>
+        <v>37.8</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2267,36 +2267,36 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>4.81</v>
+        <v>-1.39</v>
       </c>
       <c r="P15" t="n">
-        <v>11.09</v>
+        <v>11.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>79.20999999999999</v>
+        <v>141.53</v>
       </c>
       <c r="R15" t="n">
-        <v>93.67</v>
+        <v>171.56</v>
       </c>
       <c r="S15" t="n">
-        <v>140.68</v>
+        <v>283.37</v>
       </c>
       <c r="T15" t="n">
-        <v>80.31999999999999</v>
-      </c>
-      <c r="U15" t="n">
+        <v>133.61</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>270401</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3</v>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="W15" t="n">
-        <v>640703</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>8</v>
       </c>
       <c r="AA15" t="n">
         <v>3</v>
@@ -2307,12 +2307,12 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" s="4" t="n">
-        <v>20.4</v>
+      <c r="AD15" s="2" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2337,89 +2337,89 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>61.02</v>
+        <v>33.5</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>-9.43</v>
+        <v>-11.19</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>-8.470000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.61</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.75</v>
+        <v>-5.6</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>62.8</v>
+        <v>41.9</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O16" s="2" t="n">
-        <v>1.57</v>
+      <c r="O16" s="3" t="n">
+        <v>14.16</v>
       </c>
       <c r="P16" t="n">
-        <v>7.75</v>
+        <v>13.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>56.29</v>
+        <v>29.01</v>
       </c>
       <c r="R16" t="n">
-        <v>59.97</v>
+        <v>35.49</v>
       </c>
       <c r="S16" t="n">
-        <v>84.7</v>
+        <v>43.43</v>
       </c>
       <c r="T16" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="U16" s="2" t="n">
-        <v>4</v>
+        <v>23.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>270107</v>
+        <v>640209</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2427,17 +2427,17 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" s="4" t="n">
-        <v>18.5</v>
+      <c r="AD16" s="2" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,32 +2457,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>209.63</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>-4.29</v>
+        <v>23.85</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>-6.36</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>-3.99</v>
+        <v>-8.34</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>-35.33</v>
       </c>
       <c r="H17" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.98</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2490,16 +2490,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K17" s="4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+      <c r="K17" s="2" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>59.7</v>
+        <v>37.2</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2507,39 +2507,39 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>11.63</v>
+        <v>-2.52</v>
       </c>
       <c r="P17" t="n">
-        <v>13.69</v>
+        <v>7.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>180.92</v>
+        <v>22.09</v>
       </c>
       <c r="R17" t="n">
-        <v>210.1</v>
+        <v>25.22</v>
       </c>
       <c r="S17" t="n">
-        <v>237.87</v>
+        <v>37.99</v>
       </c>
       <c r="T17" t="n">
-        <v>125.61</v>
+        <v>23.62</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>730206</v>
+        <v>270303</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2547,17 +2547,17 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" s="4" t="n">
-        <v>16.7</v>
+      <c r="AD17" s="2" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,32 +2577,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>25.17</v>
+        <v>81.06</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>-5.77</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>-35.33</v>
+        <v>-7.09</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-16.48</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>-35.42</v>
       </c>
       <c r="H18" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.85</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2610,16 +2610,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K18" s="4" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>52.8</v>
+        <v>31.1</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2627,39 +2627,39 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.05</v>
+        <v>-10.66</v>
       </c>
       <c r="P18" t="n">
-        <v>6.71</v>
+        <v>6.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>23.48</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>25.33</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>39.76</v>
+        <v>131.26</v>
       </c>
       <c r="T18" t="n">
-        <v>23.8</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270303</v>
+        <v>630503</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2667,8 +2667,8 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" s="4" t="n">
-        <v>14.8</v>
+      <c r="AD18" s="2" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>57.96</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>-6.67</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>-41.25</v>
+        <v>30.47</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>-8.66</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-17.76</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>-43.51</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.83</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2730,74 +2730,74 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K19" s="4" t="n">
-        <v>-2.48</v>
+      <c r="K19" s="2" t="n">
+        <v>-8.84</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>-0.85</v>
+        <v>24.5</v>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>-11.94</v>
       </c>
       <c r="P19" t="n">
-        <v>10.71</v>
+        <v>5.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>51.75</v>
+        <v>28.7</v>
       </c>
       <c r="R19" t="n">
-        <v>59.43</v>
+        <v>33.42</v>
       </c>
       <c r="S19" t="n">
-        <v>105</v>
+        <v>52.69</v>
       </c>
       <c r="T19" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
+        <v>30.34</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270203</v>
+        <v>630702</v>
       </c>
       <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>5</v>
       </c>
-      <c r="AA19" t="n">
-        <v>3</v>
-      </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" s="4" t="n">
-        <v>14.8</v>
+      <c r="AD19" s="2" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,32 +2817,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>185.99</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>-7.28</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>-16.1</v>
+        <v>312</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>-10.08</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-17.22</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>-49.52</v>
       </c>
       <c r="H20" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.07</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2850,74 +2850,74 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K20" s="4" t="n">
-        <v>-2.28</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="n">
+        <v>-10.06</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v>-1.46</v>
+        <v>25.6</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>-11.4</v>
       </c>
       <c r="P20" t="n">
-        <v>10.61</v>
+        <v>7.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>166.26</v>
+        <v>287.22</v>
       </c>
       <c r="R20" t="n">
-        <v>190.32</v>
+        <v>346.89</v>
       </c>
       <c r="S20" t="n">
-        <v>280.08</v>
+        <v>710</v>
       </c>
       <c r="T20" t="n">
-        <v>161.8</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
+        <v>308</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>270202</v>
+        <v>270104</v>
       </c>
       <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>5</v>
       </c>
-      <c r="AA20" t="n">
-        <v>3</v>
-      </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" s="4" t="n">
-        <v>14.8</v>
+      <c r="AD20" s="2" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,32 +2937,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>57.22</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>-7.34</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>-13.26</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>-19.86</v>
+        <v>371.28</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>-10.12</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-13.46</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>-57.9</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2970,53 +2970,53 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K21" s="4" t="n">
-        <v>-9.02</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+      <c r="K21" s="2" t="n">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>-7.44</v>
+        <v>38.5</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>-7.64</v>
       </c>
       <c r="P21" t="n">
-        <v>8.359999999999999</v>
+        <v>10.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.43</v>
+        <v>333.5</v>
       </c>
       <c r="R21" t="n">
-        <v>62.89</v>
+        <v>405.14</v>
       </c>
       <c r="S21" t="n">
-        <v>78.5</v>
+        <v>954.1900000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>0</v>
+        <v>334</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>640209</v>
+        <v>270104</v>
       </c>
       <c r="Z21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>5</v>
@@ -3027,12 +3027,12 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" s="4" t="n">
-        <v>14.8</v>
+      <c r="AD21" s="2" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3057,28 +3057,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>394.43</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>-51.36</v>
+        <v>65.43000000000001</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>-10.31</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-12.62</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>-27.96</v>
       </c>
       <c r="H22" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3090,56 +3090,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K22" s="4" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="n">
+        <v>-6.14</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>51.2</v>
+        <v>41.4</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O22" s="4" t="n">
-        <v>-2.4</v>
+      <c r="O22" s="2" t="n">
+        <v>-6.8</v>
       </c>
       <c r="P22" t="n">
-        <v>9.109999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>358.48</v>
+        <v>59.9</v>
       </c>
       <c r="R22" t="n">
-        <v>408.02</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>954.1900000000001</v>
+        <v>113.82</v>
       </c>
       <c r="T22" t="n">
-        <v>334</v>
+        <v>60.79</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>270104</v>
+        <v>270107</v>
       </c>
       <c r="Z22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3147,17 +3147,17 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" s="4" t="n">
-        <v>11.1</v>
+      <c r="AD22" s="2" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,32 +3177,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>52</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>-9.06</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>-14.42</v>
+        <v>197.37</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>-13.43</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>-5.69</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.7</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3210,74 +3210,74 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K23" s="4" t="n">
-        <v>-4.98</v>
+      <c r="K23" s="2" t="n">
+        <v>-6.17</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>43.2</v>
+        <v>45.3</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O23" s="4" t="n">
-        <v>-3.24</v>
+      <c r="O23" s="3" t="n">
+        <v>8.5</v>
       </c>
       <c r="P23" t="n">
-        <v>6.9</v>
+        <v>14.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>48.41</v>
+        <v>168.28</v>
       </c>
       <c r="R23" t="n">
-        <v>54.73</v>
+        <v>210.35</v>
       </c>
       <c r="S23" t="n">
-        <v>65.83</v>
+        <v>237.87</v>
       </c>
       <c r="T23" t="n">
-        <v>51</v>
+        <v>125.61</v>
       </c>
       <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>730206</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2</v>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="W23" t="n">
-        <v>270504</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>5</v>
-      </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" s="4" t="n">
+      <c r="AD23" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>331.77</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>-44.63</v>
+        <v>244.8</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-6.95</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>-1.92</v>
       </c>
       <c r="H24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.7</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3330,56 +3330,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K24" s="4" t="n">
-        <v>-5.25</v>
+      <c r="K24" s="2" t="n">
+        <v>-6.9</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>41.2</v>
+        <v>39.2</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O24" s="4" t="n">
-        <v>-8.279999999999999</v>
+      <c r="O24" s="2" t="n">
+        <v>-1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>7.14</v>
+        <v>12.77</v>
       </c>
       <c r="Q24" t="n">
-        <v>308.09</v>
+        <v>213.54</v>
       </c>
       <c r="R24" t="n">
-        <v>350.14</v>
+        <v>262.96</v>
       </c>
       <c r="S24" t="n">
-        <v>710</v>
+        <v>294.5</v>
       </c>
       <c r="T24" t="n">
-        <v>308</v>
+        <v>155.05</v>
       </c>
       <c r="U24" t="n">
         <v>2</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>270104</v>
+        <v>730204</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3387,17 +3387,17 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" s="4" t="n">
+      <c r="AD24" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,30 +3417,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>-3.41</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>-14.55</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>-41.98</v>
+        <v>168.28</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>-14.21</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-13.98</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>-27.69</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
+        <v>0.92</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3450,50 +3450,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K25" s="4" t="n">
-        <v>-5.91</v>
+      <c r="K25" s="2" t="n">
+        <v>-10.94</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>32.1</v>
+        <v>35.3</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O25" s="4" t="n">
-        <v>-8.73</v>
+      <c r="O25" s="2" t="n">
+        <v>-8.16</v>
       </c>
       <c r="P25" t="n">
-        <v>5.22</v>
+        <v>12.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>30.1</v>
+        <v>147.75</v>
       </c>
       <c r="R25" t="n">
-        <v>33.75</v>
+        <v>188.96</v>
       </c>
       <c r="S25" t="n">
-        <v>55.28</v>
+        <v>280.08</v>
       </c>
       <c r="T25" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
+        <v>161.8</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>630702</v>
+        <v>270202</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" s="4" t="n">
+      <c r="AD25" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE25" t="inlineStr">
@@ -3537,32 +3537,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>68.78</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>-10.08</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>-28.3</v>
+        <v>-17.67</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-6.41</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>-36.75</v>
       </c>
       <c r="H26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.91</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3570,74 +3570,74 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K26" s="4" t="n">
-        <v>-2</v>
+      <c r="K26" s="2" t="n">
+        <v>-12.19</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>53.9</v>
+        <v>31.5</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O26" s="4" t="n">
-        <v>-4.26</v>
+      <c r="O26" s="2" t="n">
+        <v>-0.59</v>
       </c>
       <c r="P26" t="n">
-        <v>7.72</v>
+        <v>11.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>63.47</v>
+        <v>72.3</v>
       </c>
       <c r="R26" t="n">
-        <v>70.18000000000001</v>
+        <v>93.39</v>
       </c>
       <c r="S26" t="n">
-        <v>113.82</v>
+        <v>140.68</v>
       </c>
       <c r="T26" t="n">
-        <v>60.79</v>
-      </c>
-      <c r="U26" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>640703</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2</v>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="W26" t="n">
-        <v>270107</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3</v>
-      </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="4" t="n">
-        <v>5.6</v>
+      <c r="AD26" s="2" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,28 +3657,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>84.20999999999999</v>
+        <v>35.17</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>-14.25</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>-33.8</v>
+        <v>-10.01</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-17.25</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>-24.28</v>
       </c>
       <c r="H27" t="n">
-        <v>0.95</v>
+        <v>0.54</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3690,50 +3690,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K27" s="4" t="n">
-        <v>-3.15</v>
+      <c r="K27" s="2" t="n">
+        <v>-12.46</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v>-8.43</v>
+        <v>23.8</v>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>-11.43</v>
       </c>
       <c r="P27" t="n">
-        <v>5.75</v>
+        <v>10.47</v>
       </c>
       <c r="Q27" t="n">
-        <v>79.37</v>
+        <v>31.49</v>
       </c>
       <c r="R27" t="n">
-        <v>86.95</v>
+        <v>40.18</v>
       </c>
       <c r="S27" t="n">
-        <v>131.26</v>
+        <v>51.14</v>
       </c>
       <c r="T27" t="n">
-        <v>82.48</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
+        <v>30.54</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>630503</v>
+        <v>270504</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
       <c r="AC27" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="4" t="n">
+      <c r="AD27" s="2" t="n">
         <v>5.6</v>
       </c>
       <c r="AE27" t="inlineStr">
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>82.17</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>-5.05</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>-13.1</v>
+        <v>232.64</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>-10.67</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>-29.97</v>
       </c>
       <c r="H28" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.64</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3810,56 +3810,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K28" s="4" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>47.2</v>
+        <v>46</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O28" s="2" t="n">
-        <v>0.77</v>
+      <c r="O28" s="3" t="n">
+        <v>2.83</v>
       </c>
       <c r="P28" t="n">
-        <v>3.84</v>
+        <v>9.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>79.02</v>
+        <v>209.56</v>
       </c>
       <c r="R28" t="n">
-        <v>83.73</v>
+        <v>239.73</v>
       </c>
       <c r="S28" t="n">
-        <v>113</v>
+        <v>385</v>
       </c>
       <c r="T28" t="n">
-        <v>80.55</v>
+        <v>183.83</v>
       </c>
       <c r="U28" t="n">
         <v>3</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>710101</v>
+        <v>270103</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3867,17 +3867,17 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" s="4" t="n">
+      <c r="AD28" s="2" t="n">
         <v>5.6</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
           <t>无明显信号</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3897,28 +3897,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>37.47</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>-15.89</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>-19.56</v>
+        <v>54.36</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-15.69</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>-23.9</v>
       </c>
       <c r="H29" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3930,56 +3930,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K29" s="4" t="n">
-        <v>-7.58</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="K29" s="2" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
+        <v>21.2</v>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O29" s="4" t="n">
-        <v>-10.07</v>
+      <c r="O29" s="2" t="n">
+        <v>-9.869999999999999</v>
       </c>
       <c r="P29" t="n">
-        <v>9.6</v>
+        <v>8.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>33.87</v>
+        <v>49.56</v>
       </c>
       <c r="R29" t="n">
-        <v>40.54</v>
+        <v>62.39</v>
       </c>
       <c r="S29" t="n">
-        <v>51.14</v>
+        <v>78.5</v>
       </c>
       <c r="T29" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="U29" s="4" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="U29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>270504</v>
+        <v>640209</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3987,8 +3987,8 @@
       <c r="AC29" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" s="4" t="n">
-        <v>5.6</v>
+      <c r="AD29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -4035,7 +4035,7 @@
           <t>重要说明</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>本报表所有指标基于公开技术分析公式计算，是历史价格的客观统计描述，不构成投资建议，不保证未来表现。是否建仓、仓位大小、止损位设置，最终需要你自己判断和承担风险。</t>
         </is>

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,8 +473,8 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="73" customWidth="1" min="31" max="31"/>
-    <col width="58" customWidth="1" min="32" max="32"/>
+    <col width="79" customWidth="1" min="31" max="31"/>
+    <col width="41" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
@@ -657,32 +657,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>58.6</v>
+        <v>216.2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-8.82</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>-1.15</v>
+        <v>-3.35</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>8.380000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-35.96</v>
+        <v>-0.17</v>
       </c>
       <c r="H2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.83</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -691,15 +691,15 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>4.84</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>56.6</v>
+        <v>57.8</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,36 +707,36 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>4.67</v>
+        <v>14.43</v>
       </c>
       <c r="P2" t="n">
-        <v>11.39</v>
+        <v>12.79</v>
       </c>
       <c r="Q2" t="n">
-        <v>51.92</v>
+        <v>188.54</v>
       </c>
       <c r="R2" t="n">
-        <v>57.96</v>
+        <v>206.21</v>
       </c>
       <c r="S2" t="n">
-        <v>95.95</v>
+        <v>242.99</v>
       </c>
       <c r="T2" t="n">
-        <v>43.01</v>
+        <v>102.3</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>640108</v>
+        <v>730204</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
         <v>8</v>
@@ -748,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>42.6</v>
+        <v>48.1</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -786,19 +786,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>211.28</v>
+        <v>212.94</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>11.18</v>
+        <v>7.55</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>19.43</v>
+        <v>9.43</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>18.15</v>
+        <v>21.74</v>
       </c>
       <c r="H3" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>8.720000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>62.7</v>
+        <v>67.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -827,29 +827,29 @@
         </is>
       </c>
       <c r="O3" s="3" t="n">
-        <v>25.25</v>
+        <v>15.48</v>
       </c>
       <c r="P3" t="n">
-        <v>7.98</v>
+        <v>7.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>194.41</v>
+        <v>196.36</v>
       </c>
       <c r="R3" t="n">
-        <v>194.34</v>
+        <v>195.26</v>
       </c>
       <c r="S3" t="n">
         <v>232.68</v>
       </c>
       <c r="T3" t="n">
-        <v>170.1</v>
+        <v>170.88</v>
       </c>
       <c r="U3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -859,7 +859,7 @@
         <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>40.7</v>
+        <v>37</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,28 +897,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>399.7</v>
+        <v>60.36</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-10.18</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.18</v>
+        <v>-1.34</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-6.51</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-24.01</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.88</v>
+        <v>1.17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>-4.08</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1.41</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -939,47 +939,47 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>44.6</v>
+        <v>56.1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>6</v>
+      <c r="O4" s="2" t="n">
+        <v>-0.46</v>
       </c>
       <c r="P4" t="n">
-        <v>11.12</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>355.25</v>
+        <v>55.47</v>
       </c>
       <c r="R4" t="n">
-        <v>416.7</v>
+        <v>59.52</v>
       </c>
       <c r="S4" t="n">
-        <v>579.42</v>
+        <v>84.7</v>
       </c>
       <c r="T4" t="n">
-        <v>347</v>
+        <v>51.23</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>730204</v>
+        <v>270107</v>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -987,17 +987,17 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="2" t="n">
-        <v>29.6</v>
+      <c r="AD4" t="n">
+        <v>31.5</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,28 +1017,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61.72</v>
+        <v>255.99</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-11.45</v>
+        <v>-8.33</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-9.44</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>-24.91</v>
+        <v>-2.48</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>8.24</v>
       </c>
       <c r="H5" t="n">
-        <v>1.21</v>
+        <v>0.7</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -1051,52 +1051,52 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-8.15</v>
+        <v>-2.53</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>35.5</v>
+        <v>49</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>-3.62</v>
+      <c r="O5" s="3" t="n">
+        <v>3.57</v>
       </c>
       <c r="P5" t="n">
-        <v>10.62</v>
+        <v>12.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>55.16</v>
+        <v>224.83</v>
       </c>
       <c r="R5" t="n">
-        <v>67.2</v>
+        <v>262.63</v>
       </c>
       <c r="S5" t="n">
-        <v>84.5</v>
+        <v>294.5</v>
       </c>
       <c r="T5" t="n">
-        <v>47.3</v>
+        <v>155.05</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>270303</v>
+        <v>730204</v>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
         <v>8</v>
@@ -1108,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>29.6</v>
+        <v>20.4</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>163.8</v>
+        <v>31.08</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-16.17</v>
+        <v>-7.31</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5.65</v>
+        <v>-14.47</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-24.63</v>
+        <v>-36.44</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.87</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,56 +1171,56 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-9.279999999999999</v>
+        <v>-6.28</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>37.2</v>
+        <v>32</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O6" s="3" t="n">
-        <v>0.17</v>
+      <c r="O6" s="2" t="n">
+        <v>-8.42</v>
       </c>
       <c r="P6" t="n">
-        <v>12.33</v>
+        <v>5.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>143.6</v>
+        <v>29.25</v>
       </c>
       <c r="R6" t="n">
-        <v>180.56</v>
+        <v>33.16</v>
       </c>
       <c r="S6" t="n">
-        <v>258.66</v>
+        <v>50.15</v>
       </c>
       <c r="T6" t="n">
-        <v>152.33</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
+        <v>30.34</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>730204</v>
+        <v>630702</v>
       </c>
       <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>8</v>
       </c>
-      <c r="AA6" t="n">
-        <v>5</v>
-      </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>202.37</v>
+        <v>57.3</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-11.76</v>
+        <v>-11.19</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-3.32</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-14.29</v>
+        <v>-34.09</v>
       </c>
       <c r="H7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1291,15 +1291,15 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>死叉(转空)</t>
+        <v>-0.96</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>47.8</v>
+        <v>54.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,39 +1307,39 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>4.88</v>
+        <v>2.73</v>
       </c>
       <c r="P7" t="n">
-        <v>12.76</v>
+        <v>11.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>176.54</v>
+        <v>50.71</v>
       </c>
       <c r="R7" t="n">
-        <v>205.37</v>
+        <v>57.86</v>
       </c>
       <c r="S7" t="n">
-        <v>242.99</v>
+        <v>95.95</v>
       </c>
       <c r="T7" t="n">
-        <v>102.3</v>
+        <v>43.01</v>
       </c>
       <c r="U7" t="n">
         <v>3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>730204</v>
+        <v>640108</v>
       </c>
       <c r="Z7" t="n">
         <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>20.4</v>
+        <v>14.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,32 +1377,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>58.9</v>
+        <v>52.84</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-4.04</v>
+        <v>-12.92</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-7.61</v>
+        <v>-16.66</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-9.1</v>
+        <v>-45.19</v>
       </c>
       <c r="H8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1411,55 +1411,55 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>29</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-1.79</v>
+        <v>-10.61</v>
       </c>
       <c r="P8" t="n">
-        <v>8.109999999999999</v>
+        <v>11.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>54.12</v>
+        <v>46.94</v>
       </c>
       <c r="R8" t="n">
-        <v>59.73</v>
+        <v>58.47</v>
       </c>
       <c r="S8" t="n">
-        <v>84.7</v>
+        <v>96.3</v>
       </c>
       <c r="T8" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
+        <v>50.5</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270107</v>
+        <v>270203</v>
       </c>
       <c r="Z8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1468,16 +1468,16 @@
         <v>0</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>18.5</v>
+        <v>14.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,28 +1497,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92.61</v>
+        <v>92.7</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-14.09</v>
+        <v>-1.62</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-10.03</v>
+        <v>-2.76</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-39.84</v>
+        <v>-14.66</v>
       </c>
       <c r="H9" t="n">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1531,55 +1531,55 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-10.04</v>
+        <v>-2.28</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>39.7</v>
+        <v>46.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>-4.21</v>
+      <c r="O9" s="3" t="n">
+        <v>3.29</v>
       </c>
       <c r="P9" t="n">
-        <v>11.31</v>
+        <v>11.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>82.13</v>
+        <v>81.97</v>
       </c>
       <c r="R9" t="n">
-        <v>102.95</v>
+        <v>94.87</v>
       </c>
       <c r="S9" t="n">
-        <v>168.98</v>
+        <v>111.63</v>
       </c>
       <c r="T9" t="n">
-        <v>90.23</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>1</v>
+        <v>69.63</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>640703</v>
+        <v>650201</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1588,16 +1588,16 @@
         <v>0</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>18.5</v>
+        <v>11.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>80.02</v>
+        <v>119.07</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-5.08</v>
+        <v>-5.5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-6.76</v>
+        <v>-4.68</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-13.66</v>
+        <v>-7.58</v>
       </c>
       <c r="H10" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.87</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1651,55 +1651,55 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-3.36</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.3</v>
+        <v>40.7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>-0.9399999999999999</v>
+      <c r="O10" s="3" t="n">
+        <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>4.08</v>
+        <v>9.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>76.75</v>
+        <v>107.69</v>
       </c>
       <c r="R10" t="n">
-        <v>83.44</v>
+        <v>123.21</v>
       </c>
       <c r="S10" t="n">
-        <v>113</v>
+        <v>142.99</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>94.73</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>710101</v>
+        <v>270202</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1708,16 +1708,16 @@
         <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>14.8</v>
+        <v>11.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,32 +1737,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>117.2</v>
+        <v>201.1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>-13.41</v>
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>2.36</v>
       </c>
       <c r="H11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.67</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1771,15 +1771,15 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-5.1</v>
+        <v>-4.71</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>41.4</v>
+        <v>38.5</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1787,39 +1787,39 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>2.12</v>
+        <v>13.3</v>
       </c>
       <c r="P11" t="n">
-        <v>9.970000000000001</v>
+        <v>13.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>105.52</v>
+        <v>173.44</v>
       </c>
       <c r="R11" t="n">
-        <v>123.5</v>
+        <v>211.03</v>
       </c>
       <c r="S11" t="n">
-        <v>142.99</v>
+        <v>237.87</v>
       </c>
       <c r="T11" t="n">
-        <v>94.73</v>
+        <v>125.61</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>270202</v>
+        <v>730206</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,16 +1828,16 @@
         <v>0</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>14.8</v>
+        <v>11.1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,28 +1857,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49.92</v>
+        <v>23.51</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-7.73</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-11.8</v>
+        <v>-11.65</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-22.36</v>
+        <v>-33.68</v>
       </c>
       <c r="H12" t="n">
-        <v>0.73</v>
+        <v>1.08</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-8.23</v>
+        <v>-6.2</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>32.8</v>
+        <v>37.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>-5.98</v>
+        <v>-5.6</v>
       </c>
       <c r="P12" t="n">
-        <v>7.41</v>
+        <v>7.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>46.22</v>
+        <v>21.75</v>
       </c>
       <c r="R12" t="n">
-        <v>54.39</v>
+        <v>25.06</v>
       </c>
       <c r="S12" t="n">
-        <v>65.52</v>
+        <v>35.78</v>
       </c>
       <c r="T12" t="n">
-        <v>49.3</v>
+        <v>23.33</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>270504</v>
+        <v>270303</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>14.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,28 +1977,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>52.16</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-15.16</v>
+        <v>-4.22</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-14.21</v>
+        <v>-8.92</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-46.75</v>
+        <v>-14.97</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>-11.59</v>
+        <v>-3.19</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -2019,47 +2019,47 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>39.6</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-8.390000000000001</v>
+        <v>-2.87</v>
       </c>
       <c r="P13" t="n">
-        <v>11.95</v>
+        <v>3.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>45.93</v>
+        <v>77.22</v>
       </c>
       <c r="R13" t="n">
-        <v>59</v>
+        <v>83.05</v>
       </c>
       <c r="S13" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="T13" t="n">
-        <v>52.16</v>
+        <v>79.88</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270203</v>
+        <v>710101</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="2" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>88.48999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-5.06</v>
+        <v>-7.42</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1.26</v>
+        <v>-12.53</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-22.27</v>
+        <v>-19.67</v>
       </c>
       <c r="H14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.72</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2131,52 +2131,52 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-6.85</v>
+        <v>-6.72</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>43.6</v>
+        <v>36.3</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O14" s="3" t="n">
-        <v>4.56</v>
+      <c r="O14" s="2" t="n">
+        <v>-6.48</v>
       </c>
       <c r="P14" t="n">
-        <v>12.04</v>
+        <v>7.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>77.84</v>
+        <v>46.76</v>
       </c>
       <c r="R14" t="n">
-        <v>95</v>
+        <v>54.03</v>
       </c>
       <c r="S14" t="n">
-        <v>116.03</v>
+        <v>65.52</v>
       </c>
       <c r="T14" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
+        <v>49.3</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>650201</v>
+        <v>270504</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>3</v>
@@ -2188,11 +2188,11 @@
         <v>0</v>
       </c>
       <c r="AD14" s="2" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2217,28 +2217,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>159.7</v>
+        <v>35.77</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-8.390000000000001</v>
+        <v>-7.67</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-7.21</v>
+        <v>-22.58</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-39.55</v>
+        <v>-27.69</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2251,15 +2251,15 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>-6.91</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>37.8</v>
+        <v>32.8</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2267,36 +2267,36 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>-1.39</v>
+        <v>-16.53</v>
       </c>
       <c r="P15" t="n">
-        <v>11.37</v>
+        <v>9.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>141.53</v>
+        <v>32.32</v>
       </c>
       <c r="R15" t="n">
-        <v>171.56</v>
+        <v>39.66</v>
       </c>
       <c r="S15" t="n">
-        <v>283.37</v>
+        <v>49.85</v>
       </c>
       <c r="T15" t="n">
-        <v>133.61</v>
+        <v>30.54</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270401</v>
+        <v>270504</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>3</v>
@@ -2308,11 +2308,11 @@
         <v>0</v>
       </c>
       <c r="AD15" s="2" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>33.5</v>
+        <v>65.7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-11.19</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>8.34</v>
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-13.21</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-8.470000000000001</v>
+        <v>-30.87</v>
       </c>
       <c r="H16" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.83</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2371,56 +2371,56 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-5.07</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>41.9</v>
+        <v>43</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O16" s="3" t="n">
-        <v>14.16</v>
+      <c r="O16" s="2" t="n">
+        <v>-7.16</v>
       </c>
       <c r="P16" t="n">
-        <v>13.39</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>29.01</v>
+        <v>60.24</v>
       </c>
       <c r="R16" t="n">
-        <v>35.49</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>43.43</v>
+        <v>113.82</v>
       </c>
       <c r="T16" t="n">
-        <v>23.2</v>
+        <v>60.79</v>
       </c>
       <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>270107</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>3</v>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="W16" t="n">
-        <v>640209</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
@@ -2428,16 +2428,16 @@
         <v>0</v>
       </c>
       <c r="AD16" s="2" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23.85</v>
+        <v>33.48</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-6.36</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-8.34</v>
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>3.27</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-35.33</v>
+        <v>-16.92</v>
       </c>
       <c r="H17" t="n">
-        <v>0.98</v>
+        <v>0.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2491,55 +2491,55 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-5.43</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-5.8</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>37.2</v>
+        <v>48.1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O17" s="2" t="n">
-        <v>-2.52</v>
+      <c r="O17" s="3" t="n">
+        <v>9.32</v>
       </c>
       <c r="P17" t="n">
-        <v>7.36</v>
+        <v>12.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.09</v>
+        <v>29.18</v>
       </c>
       <c r="R17" t="n">
-        <v>25.22</v>
+        <v>35.54</v>
       </c>
       <c r="S17" t="n">
-        <v>37.99</v>
+        <v>41.05</v>
       </c>
       <c r="T17" t="n">
-        <v>23.62</v>
+        <v>23.2</v>
       </c>
       <c r="U17" t="n">
         <v>2</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>270303</v>
+        <v>640209</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,16 +2548,16 @@
         <v>0</v>
       </c>
       <c r="AD17" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
           <t>无明显信号</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>81.06</v>
+        <v>311.66</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-7.09</v>
+        <v>-10.39</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-16.48</v>
+        <v>-18.36</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-35.42</v>
+        <v>-54.29</v>
       </c>
       <c r="H18" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -2611,55 +2611,55 @@
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-5.91</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-9.24</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>25</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>-10.66</v>
+        <v>-12.31</v>
       </c>
       <c r="P18" t="n">
-        <v>6.19</v>
+        <v>7.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>76.04000000000001</v>
+        <v>288.16</v>
       </c>
       <c r="R18" t="n">
-        <v>86.15000000000001</v>
+        <v>343.39</v>
       </c>
       <c r="S18" t="n">
-        <v>131.26</v>
+        <v>647.78</v>
       </c>
       <c r="T18" t="n">
-        <v>80.76000000000001</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
+        <v>308</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>630503</v>
+        <v>270104</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>30.47</v>
+        <v>230.33</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-8.66</v>
+        <v>-10.4</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-17.76</v>
+        <v>-5.63</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-43.51</v>
+        <v>-29.53</v>
       </c>
       <c r="H19" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.61</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>-8.84</v>
+        <v>-3.64</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -2739,47 +2739,47 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="n">
-        <v>-11.94</v>
+        <v>47.3</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>0.42</v>
       </c>
       <c r="P19" t="n">
-        <v>5.81</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>28.7</v>
+        <v>207.61</v>
       </c>
       <c r="R19" t="n">
-        <v>33.42</v>
+        <v>239.04</v>
       </c>
       <c r="S19" t="n">
-        <v>52.69</v>
+        <v>385</v>
       </c>
       <c r="T19" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>0</v>
+        <v>183.83</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>630702</v>
+        <v>270103</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2788,16 +2788,16 @@
         <v>0</v>
       </c>
       <c r="AD19" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
           <t>无明显信号</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,32 +2817,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>312</v>
+        <v>62.15</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-10.08</v>
+        <v>-10.91</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-17.22</v>
+        <v>-11.84</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-49.52</v>
+        <v>-22.71</v>
       </c>
       <c r="H20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.14</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2851,55 +2851,55 @@
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-10.06</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-6.94</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>39.8</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>-11.4</v>
+        <v>-5.79</v>
       </c>
       <c r="P20" t="n">
-        <v>7.94</v>
+        <v>10.43</v>
       </c>
       <c r="Q20" t="n">
-        <v>287.22</v>
+        <v>55.67</v>
       </c>
       <c r="R20" t="n">
-        <v>346.89</v>
+        <v>66.78</v>
       </c>
       <c r="S20" t="n">
-        <v>710</v>
+        <v>84.5</v>
       </c>
       <c r="T20" t="n">
-        <v>308</v>
+        <v>47.3</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>270104</v>
+        <v>270303</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>371.28</v>
+        <v>171.21</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-10.12</v>
+        <v>-12.21</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-13.46</v>
+        <v>-13.53</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-57.9</v>
+        <v>-23.72</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -2971,15 +2971,15 @@
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-8.75</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2987,39 +2987,39 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>-7.64</v>
+        <v>-7.48</v>
       </c>
       <c r="P21" t="n">
-        <v>10.18</v>
+        <v>11.61</v>
       </c>
       <c r="Q21" t="n">
-        <v>333.5</v>
+        <v>151.33</v>
       </c>
       <c r="R21" t="n">
-        <v>405.14</v>
+        <v>187.62</v>
       </c>
       <c r="S21" t="n">
-        <v>954.1900000000001</v>
+        <v>280.08</v>
       </c>
       <c r="T21" t="n">
-        <v>334</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
+        <v>161.8</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270104</v>
+        <v>270202</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,32 +3057,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>65.43000000000001</v>
+        <v>160.2</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-10.31</v>
+        <v>-12.55</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-12.62</v>
+        <v>-10</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-27.96</v>
+        <v>-39.53</v>
       </c>
       <c r="H22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3093,13 +3093,13 @@
       <c r="K22" s="2" t="n">
         <v>-6.14</v>
       </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>41.4</v>
+        <v>35.7</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -3107,39 +3107,39 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>-6.8</v>
+        <v>-3.95</v>
       </c>
       <c r="P22" t="n">
-        <v>8.460000000000001</v>
+        <v>10.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>59.9</v>
+        <v>143.01</v>
       </c>
       <c r="R22" t="n">
-        <v>69.70999999999999</v>
+        <v>170.67</v>
       </c>
       <c r="S22" t="n">
-        <v>113.82</v>
+        <v>283.02</v>
       </c>
       <c r="T22" t="n">
-        <v>60.79</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
+        <v>133.61</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>270107</v>
+        <v>270401</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3148,16 +3148,16 @@
         <v>0</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
           <t>无明显信号</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,32 +3177,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>197.37</v>
+        <v>166.9</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-13.43</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>2.68</v>
+        <v>-13.86</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-7.23</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-5.69</v>
+        <v>-20.16</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.83</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-6.17</v>
+        <v>-7.23</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -3219,47 +3219,47 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>45.3</v>
+        <v>41.8</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O23" s="3" t="n">
-        <v>8.5</v>
+      <c r="O23" s="2" t="n">
+        <v>-1.18</v>
       </c>
       <c r="P23" t="n">
-        <v>14.74</v>
+        <v>11.61</v>
       </c>
       <c r="Q23" t="n">
-        <v>168.28</v>
+        <v>147.52</v>
       </c>
       <c r="R23" t="n">
-        <v>210.35</v>
+        <v>179.9</v>
       </c>
       <c r="S23" t="n">
-        <v>237.87</v>
+        <v>258.66</v>
       </c>
       <c r="T23" t="n">
-        <v>125.61</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3</v>
+        <v>152.33</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>730206</v>
+        <v>730204</v>
       </c>
       <c r="Z23" t="n">
         <v>3</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="AD23" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>244.8</v>
+        <v>392.91</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-14</v>
+        <v>-13.97</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-6.95</v>
+        <v>-2.23</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-1.92</v>
+        <v>-22.49</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.84</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-6.9</v>
+        <v>-5.61</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
@@ -3339,37 +3339,37 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>39.2</v>
+        <v>43</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O24" s="2" t="n">
-        <v>-1.13</v>
+      <c r="O24" s="3" t="n">
+        <v>3.82</v>
       </c>
       <c r="P24" t="n">
-        <v>12.77</v>
+        <v>11.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>213.54</v>
+        <v>349.44</v>
       </c>
       <c r="R24" t="n">
-        <v>262.96</v>
+        <v>416.25</v>
       </c>
       <c r="S24" t="n">
-        <v>294.5</v>
+        <v>579.42</v>
       </c>
       <c r="T24" t="n">
-        <v>155.05</v>
+        <v>347</v>
       </c>
       <c r="U24" t="n">
         <v>2</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -3379,7 +3379,7 @@
         <v>3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>168.28</v>
+        <v>82.81</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-14.21</v>
+        <v>-6.4</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-13.98</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-27.69</v>
+        <v>-35.07</v>
       </c>
       <c r="H25" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -3451,15 +3451,15 @@
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-10.94</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>死叉(转空)</t>
+        <v>-3.42</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>35.3</v>
+        <v>38.7</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3467,39 +3467,39 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>-8.16</v>
+        <v>-2.81</v>
       </c>
       <c r="P25" t="n">
-        <v>12.2</v>
+        <v>6.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>147.75</v>
+        <v>77.55</v>
       </c>
       <c r="R25" t="n">
-        <v>188.96</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>280.08</v>
+        <v>131.04</v>
       </c>
       <c r="T25" t="n">
-        <v>161.8</v>
-      </c>
-      <c r="U25" s="2" t="n">
-        <v>1</v>
+        <v>80.76000000000001</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>270202</v>
+        <v>630503</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,28 +3537,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>82</v>
+        <v>372.2</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-17.67</v>
+        <v>-10.31</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-6.41</v>
+        <v>-14.73</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-36.75</v>
+        <v>-60.19</v>
       </c>
       <c r="H26" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-12.19</v>
+        <v>-7.39</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>31.5</v>
+        <v>32.8</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3587,39 +3587,39 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>-0.59</v>
+        <v>-8.68</v>
       </c>
       <c r="P26" t="n">
-        <v>11.83</v>
+        <v>9.33</v>
       </c>
       <c r="Q26" t="n">
-        <v>72.3</v>
+        <v>337.48</v>
       </c>
       <c r="R26" t="n">
-        <v>93.39</v>
+        <v>401.92</v>
       </c>
       <c r="S26" t="n">
-        <v>140.68</v>
+        <v>900</v>
       </c>
       <c r="T26" t="n">
-        <v>80.31999999999999</v>
+        <v>334</v>
       </c>
       <c r="U26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>640703</v>
+        <v>270104</v>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,16 +3628,16 @@
         <v>0</v>
       </c>
       <c r="AD26" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,28 +3657,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>35.17</v>
+        <v>55.58</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-10.01</v>
+        <v>-10.69</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-17.25</v>
+        <v>-18.52</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-24.28</v>
+        <v>-24.95</v>
       </c>
       <c r="H27" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>-12.46</v>
+        <v>-10</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>23.8</v>
+        <v>28.6</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -3707,39 +3707,39 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>-11.43</v>
+        <v>-12.47</v>
       </c>
       <c r="P27" t="n">
-        <v>10.47</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>31.49</v>
+        <v>50.92</v>
       </c>
       <c r="R27" t="n">
-        <v>40.18</v>
+        <v>61.76</v>
       </c>
       <c r="S27" t="n">
-        <v>51.14</v>
+        <v>78.5</v>
       </c>
       <c r="T27" t="n">
-        <v>30.54</v>
+        <v>45.82</v>
       </c>
       <c r="U27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>270504</v>
+        <v>640209</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>232.64</v>
+        <v>94.25</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-10.67</v>
+        <v>-13.93</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-2.99</v>
+        <v>-10.02</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-29.97</v>
+        <v>-37.04</v>
       </c>
       <c r="H28" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.82</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3811,52 +3811,52 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-7.98</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>46</v>
+        <v>43.1</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O28" s="3" t="n">
-        <v>2.83</v>
+      <c r="O28" s="2" t="n">
+        <v>-3.97</v>
       </c>
       <c r="P28" t="n">
-        <v>9.92</v>
+        <v>11.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>209.56</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="R28" t="n">
-        <v>239.73</v>
+        <v>102.42</v>
       </c>
       <c r="S28" t="n">
-        <v>385</v>
+        <v>168.98</v>
       </c>
       <c r="T28" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U28" t="n">
-        <v>3</v>
+        <v>90.23</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>270103</v>
+        <v>640703</v>
       </c>
       <c r="Z28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -3868,11 +3868,11 @@
         <v>0</v>
       </c>
       <c r="AD28" s="2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>54.36</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-14.1</v>
+        <v>-15.32</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-15.69</v>
+        <v>-15.17</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-23.9</v>
+        <v>-37.57</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.8</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>-12.87</v>
+        <v>-11.76</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>21.2</v>
+        <v>26.8</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
@@ -3947,33 +3947,33 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>-9.869999999999999</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="P29" t="n">
-        <v>8.83</v>
+        <v>11.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>49.56</v>
+        <v>72.58</v>
       </c>
       <c r="R29" t="n">
-        <v>62.39</v>
+        <v>92.66</v>
       </c>
       <c r="S29" t="n">
-        <v>78.5</v>
+        <v>140.68</v>
       </c>
       <c r="T29" t="n">
-        <v>45.82</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="U29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>640209</v>
+        <v>640703</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,10 +473,10 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="79" customWidth="1" min="31" max="31"/>
-    <col width="41" customWidth="1" min="32" max="32"/>
+    <col width="74" customWidth="1" min="31" max="31"/>
+    <col width="58" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="25" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,32 +657,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>216.2</v>
+        <v>94.92</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-3.35</v>
+        <v>-2.22</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>8.380000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.17</v>
+        <v>-10.44</v>
       </c>
       <c r="H2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.76</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>4.84</v>
+        <v>0.01</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>57.8</v>
+        <v>45.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,39 +707,39 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>14.43</v>
+        <v>6.49</v>
       </c>
       <c r="P2" t="n">
-        <v>12.79</v>
+        <v>11.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>188.54</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>206.21</v>
+        <v>94.91</v>
       </c>
       <c r="S2" t="n">
-        <v>242.99</v>
+        <v>111.63</v>
       </c>
       <c r="T2" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="U2" s="3" t="n">
-        <v>4</v>
+        <v>69.63</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>730204</v>
+        <v>650201</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -748,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>48.1</v>
+        <v>37</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -786,19 +786,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>212.94</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>7.55</v>
+        <v>215.57</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>-1.02</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>9.43</v>
+        <v>5.88</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>21.74</v>
+        <v>13.75</v>
       </c>
       <c r="H3" t="n">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>9.050000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>67.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -827,16 +827,16 @@
         </is>
       </c>
       <c r="O3" s="3" t="n">
-        <v>15.48</v>
+        <v>11.38</v>
       </c>
       <c r="P3" t="n">
-        <v>7.78</v>
+        <v>7.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>196.36</v>
+        <v>199.03</v>
       </c>
       <c r="R3" t="n">
-        <v>195.26</v>
+        <v>195.86</v>
       </c>
       <c r="S3" t="n">
         <v>232.68</v>
@@ -849,14 +849,14 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>270104</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
         <v>3</v>
@@ -868,11 +868,11 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>37</v>
+        <v>33.3</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -897,32 +897,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60.36</v>
+        <v>212.35</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-6.51</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>-8.789999999999999</v>
+        <v>-6.64</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.68</v>
       </c>
       <c r="H4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.71</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -931,73 +931,73 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>2.52</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>56.1</v>
+        <v>55.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>-0.46</v>
+      <c r="O4" s="3" t="n">
+        <v>15.07</v>
       </c>
       <c r="P4" t="n">
-        <v>8.109999999999999</v>
+        <v>12.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>55.47</v>
+        <v>185.22</v>
       </c>
       <c r="R4" t="n">
-        <v>59.52</v>
+        <v>207.14</v>
       </c>
       <c r="S4" t="n">
-        <v>84.7</v>
+        <v>242.99</v>
       </c>
       <c r="T4" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="U4" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>730204</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA4" t="n">
         <v>3</v>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>270107</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>5</v>
-      </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="n">
-        <v>31.5</v>
+      <c r="AD4" s="2" t="n">
+        <v>29.6</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>255.99</v>
+        <v>205.45</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-8.33</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-2.48</v>
+        <v>-6.19</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8.24</v>
+        <v>4.23</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>0.67</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-2.53</v>
+        <v>-3.13</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>42.7</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1067,36 +1067,36 @@
         </is>
       </c>
       <c r="O5" s="3" t="n">
-        <v>3.57</v>
+        <v>16.9</v>
       </c>
       <c r="P5" t="n">
-        <v>12.17</v>
+        <v>13.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>224.83</v>
+        <v>178.09</v>
       </c>
       <c r="R5" t="n">
-        <v>262.63</v>
+        <v>212.08</v>
       </c>
       <c r="S5" t="n">
-        <v>294.5</v>
+        <v>237.87</v>
       </c>
       <c r="T5" t="n">
-        <v>155.05</v>
+        <v>125.61</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>730204</v>
+        <v>730206</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
         <v>8</v>
@@ -1108,11 +1108,11 @@
         <v>0</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>20.4</v>
+        <v>25.9</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.08</v>
+        <v>260.77</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-7.31</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-14.47</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>-36.44</v>
+        <v>-5.46</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>7.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.71</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-6.28</v>
+        <v>-0.89</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,44 +1179,44 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>51.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>-8.42</v>
+      <c r="O6" s="3" t="n">
+        <v>9.279999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>5.89</v>
+        <v>11.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>29.25</v>
+        <v>229.76</v>
       </c>
       <c r="R6" t="n">
-        <v>33.16</v>
+        <v>263.11</v>
       </c>
       <c r="S6" t="n">
-        <v>50.15</v>
+        <v>294.5</v>
       </c>
       <c r="T6" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>1</v>
+        <v>155.05</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>630702</v>
+        <v>730204</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
         <v>8</v>
@@ -1228,11 +1228,11 @@
         <v>0</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>14.8</v>
+        <v>20.4</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1257,89 +1257,89 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>57.3</v>
+        <v>31.2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-11.19</v>
+        <v>-6.33</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3.32</v>
+        <v>-12.14</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-34.09</v>
+        <v>-36.89</v>
       </c>
       <c r="H7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="R7" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="S7" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="T7" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="U7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>50.71</v>
-      </c>
-      <c r="R7" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="S7" t="n">
-        <v>95.95</v>
-      </c>
-      <c r="T7" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>640108</v>
+        <v>630702</v>
       </c>
       <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
         <v>8</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,32 +1377,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52.84</v>
+        <v>56.9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-12.92</v>
+        <v>-10.42</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-16.66</v>
+        <v>-7.3</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-45.19</v>
+        <v>-16.58</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.9</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1411,49 +1411,49 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-4.04</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>29</v>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>46.4</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-10.61</v>
+        <v>-1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>11.17</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>46.94</v>
+        <v>51.75</v>
       </c>
       <c r="R8" t="n">
-        <v>58.47</v>
+        <v>59.3</v>
       </c>
       <c r="S8" t="n">
-        <v>96.3</v>
+        <v>84.7</v>
       </c>
       <c r="T8" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>0</v>
+        <v>51.23</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270203</v>
+        <v>270107</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,28 +1497,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92.7</v>
+        <v>54.44</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-1.62</v>
+        <v>-14.05</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2.76</v>
+        <v>-4.17</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-14.66</v>
+        <v>-38.02</v>
       </c>
       <c r="H9" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1531,15 +1531,15 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-2.28</v>
+        <v>-5.71</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>46.9</v>
+        <v>50</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1547,39 +1547,39 @@
         </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>3.29</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>11.58</v>
+        <v>12.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>81.97</v>
+        <v>47.59</v>
       </c>
       <c r="R9" t="n">
-        <v>94.87</v>
+        <v>57.74</v>
       </c>
       <c r="S9" t="n">
-        <v>111.63</v>
+        <v>95.95</v>
       </c>
       <c r="T9" t="n">
-        <v>69.63</v>
+        <v>43.01</v>
       </c>
       <c r="U9" t="n">
         <v>2</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>650201</v>
+        <v>640108</v>
       </c>
       <c r="Z9" t="n">
         <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>119.07</v>
+        <v>24.4</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-5.5</v>
+        <v>-5.61</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4.68</v>
+        <v>-5.79</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-7.58</v>
+        <v>-28.38</v>
       </c>
       <c r="H10" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.44</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-3.36</v>
+        <v>-2.36</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1659,65 +1659,65 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>40.7</v>
+        <v>42.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O10" s="3" t="n">
-        <v>1.37</v>
+      <c r="O10" s="2" t="n">
+        <v>-0.29</v>
       </c>
       <c r="P10" t="n">
-        <v>9.56</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>107.69</v>
+        <v>22.4</v>
       </c>
       <c r="R10" t="n">
-        <v>123.21</v>
+        <v>24.99</v>
       </c>
       <c r="S10" t="n">
-        <v>142.99</v>
+        <v>34.65</v>
       </c>
       <c r="T10" t="n">
-        <v>94.73</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
+        <v>23.33</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270202</v>
+        <v>270303</v>
       </c>
       <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
         <v>3</v>
       </c>
-      <c r="AA10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
       <c r="AD10" s="2" t="n">
-        <v>11.1</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>极端放量(&gt;2.5倍，需留意)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>无风险扣分项触发</t>
+          <t>换手率处于近60日95分位以上(极端活跃)</t>
         </is>
       </c>
     </row>
@@ -1737,32 +1737,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>201.1</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>2.36</v>
+        <v>-6.47</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>-34.99</v>
       </c>
       <c r="H11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.65</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1771,55 +1771,55 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-3.45</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O11" s="3" t="n">
-        <v>13.3</v>
+      <c r="O11" s="2" t="n">
+        <v>-1.49</v>
       </c>
       <c r="P11" t="n">
-        <v>13.75</v>
+        <v>6.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>173.44</v>
+        <v>77.3</v>
       </c>
       <c r="R11" t="n">
-        <v>211.03</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>237.87</v>
+        <v>129.49</v>
       </c>
       <c r="T11" t="n">
-        <v>125.61</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>730206</v>
+        <v>630503</v>
       </c>
       <c r="Z11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,16 +1828,16 @@
         <v>0</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,32 +1857,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23.51</v>
+        <v>115.93</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-8.199999999999999</v>
+        <v>-7.36</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-11.65</v>
+        <v>-3.97</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-33.68</v>
+        <v>-10.63</v>
       </c>
       <c r="H12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1891,55 +1891,55 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-6.2</v>
+        <v>-5.72</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>37.8</v>
+        <v>31.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>-5.6</v>
+      <c r="O12" s="3" t="n">
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>7.49</v>
+        <v>9.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.75</v>
+        <v>104.6</v>
       </c>
       <c r="R12" t="n">
-        <v>25.06</v>
+        <v>122.97</v>
       </c>
       <c r="S12" t="n">
-        <v>35.78</v>
+        <v>142.99</v>
       </c>
       <c r="T12" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="U12" s="2" t="n">
-        <v>1</v>
+        <v>94.73</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>270303</v>
+        <v>270202</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,28 +1977,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>80.40000000000001</v>
+        <v>34.88</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-4.22</v>
+        <v>-10.29</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-8.92</v>
+        <v>-24.32</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-14.97</v>
+        <v>-25.36</v>
       </c>
       <c r="H13" t="n">
-        <v>0.84</v>
+        <v>0.47</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -2011,15 +2011,15 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>-3.19</v>
+        <v>-10.78</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>39.6</v>
+        <v>30.6</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -2027,33 +2027,33 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-2.87</v>
+        <v>-18.82</v>
       </c>
       <c r="P13" t="n">
-        <v>3.95</v>
+        <v>10.07</v>
       </c>
       <c r="Q13" t="n">
-        <v>77.22</v>
+        <v>31.37</v>
       </c>
       <c r="R13" t="n">
-        <v>83.05</v>
+        <v>39.1</v>
       </c>
       <c r="S13" t="n">
-        <v>113</v>
+        <v>49.37</v>
       </c>
       <c r="T13" t="n">
-        <v>79.88</v>
+        <v>30.54</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>710101</v>
+        <v>270504</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2097,28 +2097,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>50.4</v>
+        <v>164.88</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-7.42</v>
+        <v>-13.39</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-12.53</v>
+        <v>-8.76</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-19.67</v>
+        <v>-25.62</v>
       </c>
       <c r="H14" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-6.72</v>
+        <v>-7.95</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>36.3</v>
+        <v>38.5</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -2147,33 +2147,33 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>-6.48</v>
+        <v>-3.26</v>
       </c>
       <c r="P14" t="n">
-        <v>7.22</v>
+        <v>11.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>46.76</v>
+        <v>146.45</v>
       </c>
       <c r="R14" t="n">
-        <v>54.03</v>
+        <v>179.11</v>
       </c>
       <c r="S14" t="n">
-        <v>65.52</v>
+        <v>258.66</v>
       </c>
       <c r="T14" t="n">
-        <v>49.3</v>
+        <v>152.33</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>270504</v>
+        <v>730204</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2217,28 +2217,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>35.77</v>
+        <v>31.41</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-7.67</v>
+        <v>-13.47</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-22.58</v>
+        <v>-3.18</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-27.69</v>
+        <v>-18.37</v>
       </c>
       <c r="H15" t="n">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>-9.800000000000001</v>
+        <v>-11.49</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2259,47 +2259,47 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>-16.53</v>
+        <v>27.7</v>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>2.32</v>
       </c>
       <c r="P15" t="n">
-        <v>9.66</v>
+        <v>12.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>32.32</v>
+        <v>27.33</v>
       </c>
       <c r="R15" t="n">
-        <v>39.66</v>
+        <v>35.49</v>
       </c>
       <c r="S15" t="n">
-        <v>49.85</v>
+        <v>40.87</v>
       </c>
       <c r="T15" t="n">
-        <v>30.54</v>
+        <v>23.2</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270504</v>
+        <v>640209</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
           <t>无明显信号</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,28 +2337,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>65.7</v>
+        <v>389</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-8.960000000000001</v>
+        <v>-14.51</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-13.21</v>
+        <v>-3.43</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-30.87</v>
+        <v>-23.74</v>
       </c>
       <c r="H16" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -2371,55 +2371,55 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-5.07</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-6.39</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>43</v>
+        <v>42.4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O16" s="2" t="n">
-        <v>-7.16</v>
+      <c r="O16" s="3" t="n">
+        <v>2.07</v>
       </c>
       <c r="P16" t="n">
-        <v>8.300000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.24</v>
+        <v>346.54</v>
       </c>
       <c r="R16" t="n">
-        <v>69.20999999999999</v>
+        <v>415.56</v>
       </c>
       <c r="S16" t="n">
-        <v>113.82</v>
+        <v>579.42</v>
       </c>
       <c r="T16" t="n">
-        <v>60.79</v>
+        <v>347</v>
       </c>
       <c r="U16" t="n">
         <v>2</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>270107</v>
+        <v>730204</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
           <t>无明显信号</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,32 +2457,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>33.48</v>
+        <v>51.32</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-9.609999999999999</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>3.27</v>
+        <v>-15.84</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-13.69</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-16.92</v>
+        <v>-42.03</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.71</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-5.8</v>
+        <v>-11.62</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -2499,47 +2499,47 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>9.32</v>
+        <v>27.5</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>-8.19</v>
       </c>
       <c r="P17" t="n">
-        <v>12.83</v>
+        <v>11.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>29.18</v>
+        <v>45.52</v>
       </c>
       <c r="R17" t="n">
-        <v>35.54</v>
+        <v>58.07</v>
       </c>
       <c r="S17" t="n">
-        <v>41.05</v>
+        <v>96.3</v>
       </c>
       <c r="T17" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
+        <v>50.5</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>640209</v>
+        <v>270203</v>
       </c>
       <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>311.66</v>
+        <v>358.46</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-10.39</v>
+        <v>-12.9</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-18.36</v>
+        <v>-14.25</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-54.29</v>
+        <v>-57.88</v>
       </c>
       <c r="H18" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -2611,45 +2611,45 @@
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-9.24</v>
+        <v>-10.15</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>25</v>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>31.2</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>-12.31</v>
+        <v>-8.75</v>
       </c>
       <c r="P18" t="n">
-        <v>7.54</v>
+        <v>9.73</v>
       </c>
       <c r="Q18" t="n">
-        <v>288.16</v>
+        <v>323.59</v>
       </c>
       <c r="R18" t="n">
-        <v>343.39</v>
+        <v>398.94</v>
       </c>
       <c r="S18" t="n">
-        <v>647.78</v>
+        <v>878.99</v>
       </c>
       <c r="T18" t="n">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W18" t="n">
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="2" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>230.33</v>
+        <v>301.93</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-10.4</v>
+        <v>-13.31</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-5.63</v>
+        <v>-18.22</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-29.53</v>
+        <v>-51.91</v>
       </c>
       <c r="H19" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.84</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2731,56 +2731,56 @@
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>-3.64</v>
+        <v>-11.2</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>0.42</v>
+        <v>25.3</v>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>-12.72</v>
       </c>
       <c r="P19" t="n">
-        <v>9.859999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>207.61</v>
+        <v>278.37</v>
       </c>
       <c r="R19" t="n">
-        <v>239.04</v>
+        <v>340.03</v>
       </c>
       <c r="S19" t="n">
-        <v>385</v>
+        <v>645.09</v>
       </c>
       <c r="T19" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U19" t="n">
+        <v>300.94</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>270104</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2</v>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="W19" t="n">
-        <v>270103</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
@@ -2788,16 +2788,16 @@
         <v>0</v>
       </c>
       <c r="AD19" s="2" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,32 +2817,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>62.15</v>
+        <v>79.52</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-10.91</v>
+        <v>-6.08</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-11.84</v>
+        <v>-8.25</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-22.71</v>
+        <v>-14.95</v>
       </c>
       <c r="H20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.64</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-6.94</v>
+        <v>-3.83</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>39.8</v>
+        <v>36.8</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2867,39 +2867,39 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>-5.79</v>
+        <v>-2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>10.43</v>
+        <v>4.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>55.67</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>66.78</v>
+        <v>82.69</v>
       </c>
       <c r="S20" t="n">
-        <v>84.5</v>
+        <v>113</v>
       </c>
       <c r="T20" t="n">
-        <v>47.3</v>
+        <v>79.25</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>270303</v>
+        <v>710101</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>171.21</v>
+        <v>49.43</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-12.21</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-13.53</v>
+        <v>-13.16</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-23.72</v>
+        <v>-21.71</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-8.75</v>
+        <v>-7.88</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>39.8</v>
+        <v>31.3</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2987,39 +2987,39 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>-7.48</v>
+        <v>-7.66</v>
       </c>
       <c r="P21" t="n">
-        <v>11.61</v>
+        <v>7.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>151.33</v>
+        <v>45.72</v>
       </c>
       <c r="R21" t="n">
-        <v>187.62</v>
+        <v>53.66</v>
       </c>
       <c r="S21" t="n">
-        <v>280.08</v>
+        <v>65.52</v>
       </c>
       <c r="T21" t="n">
-        <v>161.8</v>
+        <v>49.04</v>
       </c>
       <c r="U21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270202</v>
+        <v>270504</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,28 +3057,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>160.2</v>
+        <v>222.78</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-12.55</v>
+        <v>-10.75</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-10</v>
+        <v>-2.64</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-39.53</v>
+        <v>-32.29</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-6.14</v>
+        <v>-6.68</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -3099,44 +3099,44 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>35.7</v>
+        <v>45.2</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O22" s="2" t="n">
-        <v>-3.95</v>
+      <c r="O22" s="3" t="n">
+        <v>2.86</v>
       </c>
       <c r="P22" t="n">
-        <v>10.73</v>
+        <v>10.21</v>
       </c>
       <c r="Q22" t="n">
-        <v>143.01</v>
+        <v>200.03</v>
       </c>
       <c r="R22" t="n">
-        <v>170.67</v>
+        <v>238.74</v>
       </c>
       <c r="S22" t="n">
-        <v>283.02</v>
+        <v>385</v>
       </c>
       <c r="T22" t="n">
-        <v>133.61</v>
-      </c>
-      <c r="U22" s="2" t="n">
-        <v>1</v>
+        <v>183.83</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>270401</v>
+        <v>270103</v>
       </c>
       <c r="Z22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3148,11 +3148,11 @@
         <v>0</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>166.9</v>
+        <v>64.28</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-13.86</v>
+        <v>-10.96</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-7.23</v>
+        <v>-12.23</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-20.16</v>
+        <v>-36.32</v>
       </c>
       <c r="H23" t="n">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -3211,15 +3211,15 @@
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-7.23</v>
+        <v>-6.52</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>41.8</v>
+        <v>40.1</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -3227,36 +3227,36 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>-1.18</v>
+        <v>-6.73</v>
       </c>
       <c r="P23" t="n">
-        <v>11.61</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>147.52</v>
+        <v>58.79</v>
       </c>
       <c r="R23" t="n">
-        <v>179.9</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>258.66</v>
+        <v>113.82</v>
       </c>
       <c r="T23" t="n">
-        <v>152.33</v>
+        <v>60.79</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>730204</v>
+        <v>270107</v>
       </c>
       <c r="Z23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3268,11 +3268,11 @@
         <v>0</v>
       </c>
       <c r="AD23" s="2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>392.91</v>
+        <v>53.95</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-13.97</v>
+        <v>-12.3</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-2.23</v>
+        <v>-18.13</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-22.49</v>
+        <v>-24.32</v>
       </c>
       <c r="H24" t="n">
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3331,52 +3331,52 @@
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-5.61</v>
+        <v>-11.79</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>43</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>3.82</v>
+        <v>26.9</v>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>-12.63</v>
       </c>
       <c r="P24" t="n">
-        <v>11.06</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>349.44</v>
+        <v>49.29</v>
       </c>
       <c r="R24" t="n">
-        <v>416.25</v>
+        <v>61.16</v>
       </c>
       <c r="S24" t="n">
-        <v>579.42</v>
+        <v>78.5</v>
       </c>
       <c r="T24" t="n">
-        <v>347</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
+        <v>45.82</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>730204</v>
+        <v>640209</v>
       </c>
       <c r="Z24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3388,11 +3388,11 @@
         <v>0</v>
       </c>
       <c r="AD24" s="2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>82.81</v>
+        <v>92.25</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-6.4</v>
+        <v>-13.86</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-8.859999999999999</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-35.07</v>
+        <v>-39.94</v>
       </c>
       <c r="H25" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -3451,55 +3451,55 @@
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-9.52</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>28.9</v>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>-2.81</v>
+        <v>-3.64</v>
       </c>
       <c r="P25" t="n">
-        <v>6.35</v>
+        <v>10.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>77.55</v>
+        <v>82.8</v>
       </c>
       <c r="R25" t="n">
-        <v>85.73999999999999</v>
+        <v>101.96</v>
       </c>
       <c r="S25" t="n">
-        <v>131.04</v>
+        <v>168.98</v>
       </c>
       <c r="T25" t="n">
-        <v>80.76000000000001</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
+        <v>90.23</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>630503</v>
+        <v>640703</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,32 +3537,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>372.2</v>
+        <v>60.64</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-10.31</v>
+        <v>-14.77</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-14.73</v>
+        <v>-10.23</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-60.19</v>
+        <v>-20.79</v>
       </c>
       <c r="H26" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.89</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3571,15 +3571,15 @@
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-7.39</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>32.8</v>
+        <v>37.1</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3587,33 +3587,33 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>-8.68</v>
+        <v>-4.73</v>
       </c>
       <c r="P26" t="n">
-        <v>9.33</v>
+        <v>10.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>337.48</v>
+        <v>54.12</v>
       </c>
       <c r="R26" t="n">
-        <v>401.92</v>
+        <v>66.44</v>
       </c>
       <c r="S26" t="n">
-        <v>900</v>
+        <v>84.5</v>
       </c>
       <c r="T26" t="n">
-        <v>334</v>
+        <v>47.3</v>
       </c>
       <c r="U26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270104</v>
+        <v>270303</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -3657,32 +3657,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>55.58</v>
+        <v>80.03</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-10.69</v>
+        <v>-15.1</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-18.52</v>
+        <v>-15.4</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-24.95</v>
+        <v>-38.6</v>
       </c>
       <c r="H27" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.71</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>-10</v>
+        <v>-12.94</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>28.6</v>
+        <v>26</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -3707,33 +3707,33 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>-12.47</v>
+        <v>-9.9</v>
       </c>
       <c r="P27" t="n">
-        <v>8.380000000000001</v>
+        <v>11.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>50.92</v>
+        <v>71</v>
       </c>
       <c r="R27" t="n">
-        <v>61.76</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>78.5</v>
+        <v>140.68</v>
       </c>
       <c r="T27" t="n">
-        <v>45.82</v>
+        <v>79.8</v>
       </c>
       <c r="U27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>640209</v>
+        <v>640703</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3777,28 +3777,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>94.25</v>
+        <v>153.24</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-13.93</v>
+        <v>-15.43</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-10.02</v>
+        <v>-9.67</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-37.04</v>
+        <v>-37.26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.82</v>
+        <v>0.61</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-7.98</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>43.1</v>
+        <v>34.8</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3827,33 +3827,33 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>-3.97</v>
+        <v>-4.17</v>
       </c>
       <c r="P28" t="n">
-        <v>11.07</v>
+        <v>11.13</v>
       </c>
       <c r="Q28" t="n">
-        <v>83.81999999999999</v>
+        <v>136.18</v>
       </c>
       <c r="R28" t="n">
-        <v>102.42</v>
+        <v>169.85</v>
       </c>
       <c r="S28" t="n">
-        <v>168.98</v>
+        <v>283.02</v>
       </c>
       <c r="T28" t="n">
-        <v>90.23</v>
+        <v>133.61</v>
       </c>
       <c r="U28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>640703</v>
+        <v>270401</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3897,28 +3897,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>81.76000000000001</v>
+        <v>167.4</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-15.32</v>
+        <v>-15.51</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-15.17</v>
+        <v>-11.28</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-37.57</v>
+        <v>-29.33</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>-11.76</v>
+        <v>-10.27</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>26.8</v>
+        <v>29.2</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
@@ -3947,33 +3947,33 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>-9.119999999999999</v>
+        <v>-5.78</v>
       </c>
       <c r="P29" t="n">
-        <v>11.23</v>
+        <v>11.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>72.58</v>
+        <v>148.44</v>
       </c>
       <c r="R29" t="n">
-        <v>92.66</v>
+        <v>186.55</v>
       </c>
       <c r="S29" t="n">
-        <v>140.68</v>
+        <v>280.08</v>
       </c>
       <c r="T29" t="n">
-        <v>80.31999999999999</v>
+        <v>161.8</v>
       </c>
       <c r="U29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>640703</v>
+        <v>270202</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,10 +473,10 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="74" customWidth="1" min="31" max="31"/>
-    <col width="58" customWidth="1" min="32" max="32"/>
+    <col width="63" customWidth="1" min="31" max="31"/>
+    <col width="43" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
-    <col width="25" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,28 +657,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>94.92</v>
+        <v>199.56</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-2.22</v>
+        <v>-10.52</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-10.44</v>
+        <v>-0.62</v>
       </c>
       <c r="H2" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -691,15 +691,15 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>1.84</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>45.6</v>
+        <v>60.1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,39 +707,39 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>6.49</v>
+        <v>6.28</v>
       </c>
       <c r="P2" t="n">
-        <v>11.4</v>
+        <v>9.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>84.09999999999999</v>
+        <v>181.29</v>
       </c>
       <c r="R2" t="n">
-        <v>94.91</v>
+        <v>195.96</v>
       </c>
       <c r="S2" t="n">
-        <v>111.63</v>
+        <v>232.68</v>
       </c>
       <c r="T2" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3</v>
+        <v>170.88</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>650201</v>
+        <v>270104</v>
       </c>
       <c r="Z2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -748,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>37</v>
+        <v>31.5</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,49 +777,49 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>215.57</v>
+        <v>32.69</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>13.75</v>
+        <v>-0.46</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>-26.52</v>
       </c>
       <c r="H3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.21</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>10.06</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.53</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>69.59999999999999</v>
+        <v>47.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -827,39 +827,39 @@
         </is>
       </c>
       <c r="O3" s="3" t="n">
-        <v>11.38</v>
+        <v>0.43</v>
       </c>
       <c r="P3" t="n">
-        <v>7.67</v>
+        <v>6.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>199.03</v>
+        <v>30.56</v>
       </c>
       <c r="R3" t="n">
-        <v>195.86</v>
+        <v>32.86</v>
       </c>
       <c r="S3" t="n">
-        <v>232.68</v>
+        <v>44.4</v>
       </c>
       <c r="T3" t="n">
-        <v>170.88</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>4</v>
+        <v>30.34</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270104</v>
+        <v>630702</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -867,17 +867,17 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="n">
-        <v>33.3</v>
+      <c r="AD3" s="2" t="n">
+        <v>22.2</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线10-15%</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>212.35</v>
+        <v>199</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-6.64</v>
+        <v>-12.02</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.68</v>
+        <v>5.27</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>-2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>2.52</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-4.16</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>55.5</v>
+        <v>48</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,16 +947,16 @@
         </is>
       </c>
       <c r="O4" s="3" t="n">
-        <v>15.07</v>
+        <v>10.5</v>
       </c>
       <c r="P4" t="n">
-        <v>12.78</v>
+        <v>13.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>185.22</v>
+        <v>171.53</v>
       </c>
       <c r="R4" t="n">
-        <v>207.14</v>
+        <v>207.64</v>
       </c>
       <c r="S4" t="n">
         <v>242.99</v>
@@ -964,22 +964,22 @@
       <c r="T4" t="n">
         <v>102.3</v>
       </c>
-      <c r="U4" s="3" t="n">
-        <v>4</v>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>730204</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>29.6</v>
+        <v>20.4</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>205.45</v>
+        <v>23.15</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-6.19</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>4.23</v>
+        <v>-11.61</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>-27.52</v>
       </c>
       <c r="H5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.67</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-3.13</v>
+        <v>-6.9</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -1059,47 +1059,47 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>42.7</v>
+        <v>38.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O5" s="3" t="n">
-        <v>16.9</v>
+      <c r="O5" s="2" t="n">
+        <v>-4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>13.32</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>178.09</v>
+        <v>20.98</v>
       </c>
       <c r="R5" t="n">
-        <v>212.08</v>
+        <v>24.87</v>
       </c>
       <c r="S5" t="n">
-        <v>237.87</v>
+        <v>33.89</v>
       </c>
       <c r="T5" t="n">
-        <v>125.61</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
+        <v>22.96</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>730206</v>
+        <v>270303</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1108,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>25.9</v>
+        <v>16.7</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,28 +1137,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>260.77</v>
+        <v>193.1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-5.46</v>
+        <v>-11.49</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.78</v>
+        <v>7.33</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>7.05</v>
+        <v>1.69</v>
       </c>
       <c r="H6" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.89</v>
+        <v>-9.23</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,48 +1179,48 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>27</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O6" s="3" t="n">
-        <v>9.279999999999999</v>
+        <v>12.56</v>
       </c>
       <c r="P6" t="n">
-        <v>11.89</v>
+        <v>13.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>229.76</v>
+        <v>166.36</v>
       </c>
       <c r="R6" t="n">
-        <v>263.11</v>
+        <v>212.74</v>
       </c>
       <c r="S6" t="n">
-        <v>294.5</v>
+        <v>237.87</v>
       </c>
       <c r="T6" t="n">
-        <v>155.05</v>
-      </c>
-      <c r="U6" t="n">
+        <v>125.61</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>730206</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2</v>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>730204</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>8</v>
-      </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>20.4</v>
+        <v>14.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,28 +1257,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.2</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-6.33</v>
+        <v>-7.3</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-12.14</v>
+        <v>-6.15</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-36.89</v>
+        <v>-35.01</v>
       </c>
       <c r="H7" t="n">
-        <v>0.88</v>
+        <v>0.65</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -1291,15 +1291,15 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-5.5</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>33.2</v>
+        <v>38</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,39 +1307,39 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-6.64</v>
+        <v>-0.92</v>
       </c>
       <c r="P7" t="n">
-        <v>6.12</v>
+        <v>6.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>29.29</v>
+        <v>75.22</v>
       </c>
       <c r="R7" t="n">
-        <v>32.95</v>
+        <v>85.17</v>
       </c>
       <c r="S7" t="n">
-        <v>48.97</v>
+        <v>123.96</v>
       </c>
       <c r="T7" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>1</v>
+        <v>80.20999999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>630702</v>
+        <v>630503</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>14.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,32 +1377,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56.9</v>
+        <v>76.78</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-10.42</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-7.3</v>
+        <v>-9.98</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-16.58</v>
+        <v>-21.77</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1411,55 +1411,55 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-4.04</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-6.67</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>29.7</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-1.8</v>
+        <v>-4.75</v>
       </c>
       <c r="P8" t="n">
-        <v>9.050000000000001</v>
+        <v>4.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>51.75</v>
+        <v>73.12</v>
       </c>
       <c r="R8" t="n">
-        <v>59.3</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>84.7</v>
+        <v>113</v>
       </c>
       <c r="T8" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
+        <v>76.2</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270107</v>
+        <v>710101</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>14.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,28 +1497,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54.44</v>
+        <v>90.44</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-14.05</v>
+        <v>-8.15</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-4.17</v>
+        <v>-3.94</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-38.02</v>
+        <v>-11.65</v>
       </c>
       <c r="H9" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1531,15 +1531,15 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-5.71</v>
+        <v>-4.53</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>50</v>
+        <v>37.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1547,36 +1547,36 @@
         </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>12.59</v>
+        <v>12.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.59</v>
+        <v>79.3</v>
       </c>
       <c r="R9" t="n">
-        <v>57.74</v>
+        <v>94.73</v>
       </c>
       <c r="S9" t="n">
-        <v>95.95</v>
+        <v>111.63</v>
       </c>
       <c r="T9" t="n">
-        <v>43.01</v>
+        <v>69.63</v>
       </c>
       <c r="U9" t="n">
         <v>2</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>640108</v>
+        <v>650201</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>5</v>
@@ -1588,11 +1588,11 @@
         <v>0</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>14.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24.4</v>
+        <v>115.88</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-5.61</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5.79</v>
+        <v>-2.12</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-28.38</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.75</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-2.36</v>
+        <v>-5.67</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1659,56 +1659,56 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>42.9</v>
+        <v>30.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>-0.29</v>
+      <c r="O10" s="3" t="n">
+        <v>3.11</v>
       </c>
       <c r="P10" t="n">
-        <v>8.210000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.4</v>
+        <v>104.14</v>
       </c>
       <c r="R10" t="n">
-        <v>24.99</v>
+        <v>122.84</v>
       </c>
       <c r="S10" t="n">
-        <v>34.65</v>
+        <v>142.99</v>
       </c>
       <c r="T10" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>1</v>
+        <v>94.73</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270303</v>
+        <v>270202</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>极端放量(&gt;2.5倍，需留意)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>换手率处于近60日95分位以上(极端活跃)</t>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -1737,32 +1737,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>82.48999999999999</v>
+        <v>235.07</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-6.47</v>
+        <v>-14.64</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-6.99</v>
+        <v>-5.78</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-34.99</v>
+        <v>-4.12</v>
       </c>
       <c r="H11" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.82</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1771,15 +1771,15 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-10.41</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>39.8</v>
+        <v>36.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1787,39 +1787,39 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>-1.49</v>
+        <v>-0.55</v>
       </c>
       <c r="P11" t="n">
-        <v>6.3</v>
+        <v>13.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>77.3</v>
+        <v>203.2</v>
       </c>
       <c r="R11" t="n">
-        <v>85.43000000000001</v>
+        <v>262.38</v>
       </c>
       <c r="S11" t="n">
-        <v>129.49</v>
+        <v>294.5</v>
       </c>
       <c r="T11" t="n">
-        <v>80.76000000000001</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
+        <v>155.05</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>630503</v>
+        <v>730204</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,32 +1857,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>115.93</v>
+        <v>378.5</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-7.36</v>
+        <v>-16.11</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3.97</v>
+        <v>-2.12</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-10.63</v>
+        <v>-25.91</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.88</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-5.72</v>
+        <v>-8.83</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>31.8</v>
+        <v>40.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>1.53</v>
+        <v>3.11</v>
       </c>
       <c r="P12" t="n">
-        <v>9.77</v>
+        <v>11.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>104.6</v>
+        <v>333.28</v>
       </c>
       <c r="R12" t="n">
-        <v>122.97</v>
+        <v>415.15</v>
       </c>
       <c r="S12" t="n">
-        <v>142.99</v>
+        <v>579.42</v>
       </c>
       <c r="T12" t="n">
-        <v>94.73</v>
+        <v>347</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>270202</v>
+        <v>730204</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,28 +1977,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>34.88</v>
+        <v>288.6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-10.29</v>
+        <v>-16.59</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-24.32</v>
+        <v>-20.34</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-25.36</v>
+        <v>-51.31</v>
       </c>
       <c r="H13" t="n">
-        <v>0.47</v>
+        <v>0.85</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>-10.78</v>
+        <v>-14.19</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -2019,47 +2019,47 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>22.4</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-18.82</v>
+        <v>-15.11</v>
       </c>
       <c r="P13" t="n">
-        <v>10.07</v>
+        <v>8.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>31.37</v>
+        <v>263.77</v>
       </c>
       <c r="R13" t="n">
-        <v>39.1</v>
+        <v>336.34</v>
       </c>
       <c r="S13" t="n">
-        <v>49.37</v>
+        <v>645.09</v>
       </c>
       <c r="T13" t="n">
-        <v>30.54</v>
+        <v>285</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270504</v>
+        <v>270104</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,28 +2097,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>164.88</v>
+        <v>49.71</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-13.39</v>
+        <v>-16.94</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-8.76</v>
+        <v>-11.03</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-25.62</v>
+        <v>-40.6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-7.95</v>
+        <v>-13.93</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -2139,47 +2139,47 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>26.5</v>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>-3.26</v>
+        <v>-5.8</v>
       </c>
       <c r="P14" t="n">
-        <v>11.18</v>
+        <v>12.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>146.45</v>
+        <v>43.69</v>
       </c>
       <c r="R14" t="n">
-        <v>179.11</v>
+        <v>57.76</v>
       </c>
       <c r="S14" t="n">
-        <v>258.66</v>
+        <v>96.3</v>
       </c>
       <c r="T14" t="n">
-        <v>152.33</v>
+        <v>49.16</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>730204</v>
+        <v>270203</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="AD14" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,32 +2217,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31.41</v>
+        <v>152.01</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-13.47</v>
+        <v>-19.99</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3.18</v>
+        <v>-12.36</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-18.37</v>
+        <v>-29.89</v>
       </c>
       <c r="H15" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.85</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>-11.49</v>
+        <v>-14.62</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2259,47 +2259,47 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>2.32</v>
+        <v>34.4</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>-7.13</v>
       </c>
       <c r="P15" t="n">
-        <v>12.99</v>
+        <v>12.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>27.33</v>
+        <v>132.39</v>
       </c>
       <c r="R15" t="n">
-        <v>35.49</v>
+        <v>178.04</v>
       </c>
       <c r="S15" t="n">
-        <v>40.87</v>
+        <v>258.66</v>
       </c>
       <c r="T15" t="n">
-        <v>23.2</v>
+        <v>150</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>640209</v>
+        <v>730204</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2308,16 +2308,16 @@
         <v>0</v>
       </c>
       <c r="AD15" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,28 +2337,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>389</v>
+        <v>49.82</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-14.51</v>
+        <v>-22.22</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-3.43</v>
+        <v>-11.23</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-23.74</v>
+        <v>-42.21</v>
       </c>
       <c r="H16" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-6.39</v>
+        <v>-13.24</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -2379,47 +2379,47 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>42.4</v>
+        <v>43.7</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O16" s="3" t="n">
-        <v>2.07</v>
+      <c r="O16" s="2" t="n">
+        <v>-6</v>
       </c>
       <c r="P16" t="n">
-        <v>10.92</v>
+        <v>14.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>346.54</v>
+        <v>42.41</v>
       </c>
       <c r="R16" t="n">
-        <v>415.56</v>
+        <v>57.42</v>
       </c>
       <c r="S16" t="n">
-        <v>579.42</v>
+        <v>95.95</v>
       </c>
       <c r="T16" t="n">
-        <v>347</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
+        <v>43.01</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>730204</v>
+        <v>640108</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         <v>0</v>
       </c>
       <c r="AD16" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>51.32</v>
+        <v>55.93</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-15.84</v>
+        <v>-10.94</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-13.69</v>
+        <v>-6.31</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-42.03</v>
+        <v>-14.75</v>
       </c>
       <c r="H17" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -2491,49 +2491,49 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-11.62</v>
+        <v>-5.38</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>44.3</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>-8.19</v>
+        <v>-1.08</v>
       </c>
       <c r="P17" t="n">
-        <v>11.3</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>45.52</v>
+        <v>50.63</v>
       </c>
       <c r="R17" t="n">
-        <v>58.07</v>
+        <v>59.11</v>
       </c>
       <c r="S17" t="n">
-        <v>96.3</v>
+        <v>84.7</v>
       </c>
       <c r="T17" t="n">
-        <v>50.5</v>
+        <v>51.23</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>270203</v>
+        <v>270107</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2577,32 +2577,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>358.46</v>
+        <v>29.91</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-12.9</v>
+        <v>-16.96</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-14.25</v>
+        <v>-7.77</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-57.88</v>
+        <v>-20.68</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.46</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-10.15</v>
+        <v>-15.42</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -2619,47 +2619,47 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>25.2</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>-8.75</v>
+        <v>-2.54</v>
       </c>
       <c r="P18" t="n">
-        <v>9.73</v>
+        <v>13.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>323.59</v>
+        <v>25.85</v>
       </c>
       <c r="R18" t="n">
-        <v>398.94</v>
+        <v>35.36</v>
       </c>
       <c r="S18" t="n">
-        <v>878.99</v>
+        <v>40.87</v>
       </c>
       <c r="T18" t="n">
-        <v>334</v>
+        <v>23.2</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270104</v>
+        <v>640209</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,16 +2668,16 @@
         <v>0</v>
       </c>
       <c r="AD18" s="2" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
+          <t>20日均线自身向上</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
           <t>无明显信号</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>301.93</v>
+        <v>48.43</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-13.31</v>
+        <v>-10.93</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-18.22</v>
+        <v>-15.15</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-51.91</v>
+        <v>-22.3</v>
       </c>
       <c r="H19" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>-11.2</v>
+        <v>-9.01</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -2739,41 +2739,41 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>32.1</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>-12.72</v>
+        <v>-9.92</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8</v>
+        <v>7.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>278.37</v>
+        <v>44.61</v>
       </c>
       <c r="R19" t="n">
-        <v>340.03</v>
+        <v>53.23</v>
       </c>
       <c r="S19" t="n">
-        <v>645.09</v>
+        <v>65.52</v>
       </c>
       <c r="T19" t="n">
-        <v>300.94</v>
+        <v>47.9</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270104</v>
+        <v>270504</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79.52</v>
+        <v>78.11</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-6.08</v>
+        <v>-15.99</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-8.25</v>
+        <v>-16.36</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-14.95</v>
+        <v>-38.93</v>
       </c>
       <c r="H20" t="n">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-3.83</v>
+        <v>-14.32</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -2859,47 +2859,47 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>24.6</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>-2.75</v>
+        <v>-11.13</v>
       </c>
       <c r="P20" t="n">
-        <v>4.1</v>
+        <v>12.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>76.26000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="R20" t="n">
-        <v>82.69</v>
+        <v>91.16</v>
       </c>
       <c r="S20" t="n">
-        <v>113</v>
+        <v>140.68</v>
       </c>
       <c r="T20" t="n">
-        <v>79.25</v>
+        <v>77.03</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>710101</v>
+        <v>640703</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>49.43</v>
+        <v>209.62</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-9.869999999999999</v>
+        <v>-16.81</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-13.16</v>
+        <v>-7.02</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-21.71</v>
+        <v>-37.21</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-7.88</v>
+        <v>-11.9</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>31.3</v>
+        <v>37.4</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2987,39 +2987,39 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>-7.66</v>
+        <v>-1.79</v>
       </c>
       <c r="P21" t="n">
-        <v>7.51</v>
+        <v>11.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>45.72</v>
+        <v>185.82</v>
       </c>
       <c r="R21" t="n">
-        <v>53.66</v>
+        <v>237.95</v>
       </c>
       <c r="S21" t="n">
-        <v>65.52</v>
+        <v>385</v>
       </c>
       <c r="T21" t="n">
-        <v>49.04</v>
+        <v>183.83</v>
       </c>
       <c r="U21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270504</v>
+        <v>270103</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,28 +3057,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>222.78</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-10.75</v>
+        <v>-17.98</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-2.64</v>
+        <v>-12.4</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-32.29</v>
+        <v>-41.02</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-6.68</v>
+        <v>-14.16</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -3099,48 +3099,48 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>2.86</v>
+        <v>27.3</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>-7.17</v>
       </c>
       <c r="P22" t="n">
-        <v>10.21</v>
+        <v>11.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>200.03</v>
+        <v>77.41</v>
       </c>
       <c r="R22" t="n">
-        <v>238.74</v>
+        <v>101.35</v>
       </c>
       <c r="S22" t="n">
-        <v>385</v>
+        <v>168.98</v>
       </c>
       <c r="T22" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U22" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>640703</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2</v>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="W22" t="n">
-        <v>270103</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,32 +3177,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>64.28</v>
+        <v>56.58</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-10.96</v>
+        <v>-19.09</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-12.23</v>
+        <v>-15.03</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-36.32</v>
+        <v>-25.94</v>
       </c>
       <c r="H23" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.84</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3211,15 +3211,15 @@
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-6.52</v>
+        <v>-14.19</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>40.1</v>
+        <v>30.6</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -3227,39 +3227,39 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>-6.73</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>8.550000000000001</v>
+        <v>12.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>58.79</v>
+        <v>49.63</v>
       </c>
       <c r="R23" t="n">
-        <v>68.76000000000001</v>
+        <v>65.94</v>
       </c>
       <c r="S23" t="n">
-        <v>113.82</v>
+        <v>84.5</v>
       </c>
       <c r="T23" t="n">
-        <v>60.79</v>
+        <v>47.3</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270107</v>
+        <v>270303</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="AD23" s="2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53.95</v>
+        <v>150.66</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-12.3</v>
+        <v>-21.94</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-18.13</v>
+        <v>-17.87</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-24.32</v>
+        <v>-36.58</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.75</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-11.79</v>
+        <v>-18.52</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>26.9</v>
+        <v>24.1</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
@@ -3347,39 +3347,39 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>-12.63</v>
+        <v>-12.64</v>
       </c>
       <c r="P24" t="n">
-        <v>8.640000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>49.29</v>
+        <v>130.32</v>
       </c>
       <c r="R24" t="n">
-        <v>61.16</v>
+        <v>184.92</v>
       </c>
       <c r="S24" t="n">
-        <v>78.5</v>
+        <v>280.08</v>
       </c>
       <c r="T24" t="n">
-        <v>45.82</v>
+        <v>150.66</v>
       </c>
       <c r="U24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>640209</v>
+        <v>270202</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>92.25</v>
+        <v>62.6</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-13.86</v>
+        <v>-12.78</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-9.140000000000001</v>
+        <v>-12.15</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-39.94</v>
+        <v>-33.45</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-9.52</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -3459,41 +3459,41 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>38.1</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>-3.64</v>
+        <v>-6.92</v>
       </c>
       <c r="P25" t="n">
-        <v>10.24</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>82.8</v>
+        <v>56.9</v>
       </c>
       <c r="R25" t="n">
-        <v>101.96</v>
+        <v>68.33</v>
       </c>
       <c r="S25" t="n">
-        <v>168.98</v>
+        <v>113.82</v>
       </c>
       <c r="T25" t="n">
-        <v>90.23</v>
+        <v>60.79</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>640703</v>
+        <v>270107</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -3537,32 +3537,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60.64</v>
+        <v>33.54</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-14.77</v>
+        <v>-14</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-10.23</v>
+        <v>-26.25</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-20.79</v>
+        <v>-24.07</v>
       </c>
       <c r="H26" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.46</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-8.720000000000001</v>
+        <v>-12.88</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>37.1</v>
+        <v>30.6</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3587,33 +3587,33 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>-4.73</v>
+        <v>-21.02</v>
       </c>
       <c r="P26" t="n">
-        <v>10.75</v>
+        <v>10.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>54.12</v>
+        <v>29.94</v>
       </c>
       <c r="R26" t="n">
-        <v>66.44</v>
+        <v>38.5</v>
       </c>
       <c r="S26" t="n">
-        <v>84.5</v>
+        <v>49.37</v>
       </c>
       <c r="T26" t="n">
-        <v>47.3</v>
+        <v>30.54</v>
       </c>
       <c r="U26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270303</v>
+        <v>270504</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -3657,32 +3657,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>80.03</v>
+        <v>51.93</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-15.1</v>
+        <v>-15.22</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-15.4</v>
+        <v>-21.59</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-38.6</v>
+        <v>-28</v>
       </c>
       <c r="H27" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.55</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>-12.94</v>
+        <v>-14.09</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -3707,33 +3707,33 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>-9.9</v>
+        <v>-16.36</v>
       </c>
       <c r="P27" t="n">
-        <v>11.28</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>71</v>
+        <v>47.06</v>
       </c>
       <c r="R27" t="n">
-        <v>91.93000000000001</v>
+        <v>60.44</v>
       </c>
       <c r="S27" t="n">
-        <v>140.68</v>
+        <v>78.5</v>
       </c>
       <c r="T27" t="n">
-        <v>79.8</v>
+        <v>45.82</v>
       </c>
       <c r="U27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>640703</v>
+        <v>640209</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3777,28 +3777,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>153.24</v>
+        <v>341.48</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-15.43</v>
+        <v>-16.78</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-9.67</v>
+        <v>-17.3</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-37.26</v>
+        <v>-58.61</v>
       </c>
       <c r="H28" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-9.779999999999999</v>
+        <v>-13.63</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -3819,41 +3819,41 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>23.5</v>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>-4.17</v>
+        <v>-12.07</v>
       </c>
       <c r="P28" t="n">
-        <v>11.13</v>
+        <v>10.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>136.18</v>
+        <v>306.62</v>
       </c>
       <c r="R28" t="n">
-        <v>169.85</v>
+        <v>395.37</v>
       </c>
       <c r="S28" t="n">
-        <v>283.02</v>
+        <v>878.99</v>
       </c>
       <c r="T28" t="n">
-        <v>133.61</v>
+        <v>334</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>270401</v>
+        <v>270104</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3897,28 +3897,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>167.4</v>
+        <v>144.98</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-15.51</v>
+        <v>-19.02</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-11.28</v>
+        <v>-13.6</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-29.33</v>
+        <v>-40.58</v>
       </c>
       <c r="H29" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>-10.27</v>
+        <v>-14.07</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -3939,41 +3939,41 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>31.7</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>-5.78</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="P29" t="n">
-        <v>11.32</v>
+        <v>12.21</v>
       </c>
       <c r="Q29" t="n">
-        <v>148.44</v>
+        <v>127.28</v>
       </c>
       <c r="R29" t="n">
-        <v>186.55</v>
+        <v>168.71</v>
       </c>
       <c r="S29" t="n">
-        <v>280.08</v>
+        <v>283.02</v>
       </c>
       <c r="T29" t="n">
-        <v>161.8</v>
+        <v>133.61</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>270202</v>
+        <v>270401</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -39,14 +39,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -473,10 +473,10 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="63" customWidth="1" min="31" max="31"/>
-    <col width="43" customWidth="1" min="32" max="32"/>
+    <col width="41" customWidth="1" min="31" max="31"/>
+    <col width="66" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="25" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,32 +657,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>199.56</v>
+        <v>35.68</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-10.52</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>-0.62</v>
+        <v>12.34</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-13.73</v>
       </c>
       <c r="H2" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>2.22</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -690,74 +690,74 @@
           <t>是</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="K2" s="2" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>多头持续</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>60.1</v>
+        <v>66.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O2" s="3" t="n">
-        <v>6.28</v>
+      <c r="O2" s="2" t="n">
+        <v>8.289999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>9.15</v>
+        <v>6.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>181.29</v>
+        <v>33.22</v>
       </c>
       <c r="R2" t="n">
-        <v>195.96</v>
+        <v>32.92</v>
       </c>
       <c r="S2" t="n">
-        <v>232.68</v>
+        <v>44.24</v>
       </c>
       <c r="T2" t="n">
-        <v>170.88</v>
-      </c>
-      <c r="U2" s="3" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="U2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>270104</v>
+        <v>630702</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD2" t="n">
-        <v>31.5</v>
+        <v>35.2</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>均线多头排列(MA5&gt;MA10&gt;MA20)；股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>股价站上20日均线；突破20日新高；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>极端放量(&gt;2.5倍，需留意)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>无风险扣分项触发</t>
+          <t>换手率处于近60日95分位以上(极端活跃)</t>
         </is>
       </c>
     </row>
@@ -777,89 +777,89 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.69</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>-0.46</v>
+        <v>202.72</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>-7.45</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>-26.52</v>
+        <v>4.55</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>-1.67</v>
       </c>
       <c r="H3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.8</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>金叉(转多)</t>
+        <v>3.22</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>47.2</v>
+        <v>63.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O3" s="3" t="n">
-        <v>0.43</v>
+      <c r="O3" s="2" t="n">
+        <v>9.720000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>6.52</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>30.56</v>
+        <v>183.54</v>
       </c>
       <c r="R3" t="n">
-        <v>32.86</v>
+        <v>196.4</v>
       </c>
       <c r="S3" t="n">
-        <v>44.4</v>
+        <v>232.68</v>
       </c>
       <c r="T3" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
+        <v>170.88</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>630702</v>
+        <v>270104</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -867,17 +867,17 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" s="2" t="n">
-        <v>22.2</v>
+      <c r="AD3" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,32 +897,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>199</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>-12.02</v>
+        <v>22.37</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-11.12</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>-2.62</v>
+        <v>-12.38</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-31.76</v>
       </c>
       <c r="H4" t="n">
-        <v>0.74</v>
+        <v>1.87</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>多头排列</t>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -930,16 +930,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="n">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,39 +947,39 @@
         </is>
       </c>
       <c r="O4" s="3" t="n">
-        <v>10.5</v>
+        <v>-7.21</v>
       </c>
       <c r="P4" t="n">
-        <v>13.8</v>
+        <v>10.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>171.53</v>
+        <v>20.13</v>
       </c>
       <c r="R4" t="n">
-        <v>207.64</v>
+        <v>24.71</v>
       </c>
       <c r="S4" t="n">
-        <v>242.99</v>
+        <v>33.89</v>
       </c>
       <c r="T4" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3</v>
+        <v>21.62</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>730204</v>
+        <v>270303</v>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -987,17 +987,17 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="2" t="n">
-        <v>20.4</v>
+      <c r="AD4" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,30 +1017,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.15</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>-11.61</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>-27.52</v>
+        <v>80.68000000000001</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-4.19</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-6.66</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-34.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+        <v>0.77</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1050,56 +1050,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>-6.9</v>
+      <c r="K5" s="3" t="n">
+        <v>-4.95</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>38.5</v>
+        <v>41.7</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>-4.3</v>
+      <c r="O5" s="3" t="n">
+        <v>-1.49</v>
       </c>
       <c r="P5" t="n">
-        <v>9.359999999999999</v>
+        <v>6.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.98</v>
+        <v>75.33</v>
       </c>
       <c r="R5" t="n">
-        <v>24.87</v>
+        <v>84.88</v>
       </c>
       <c r="S5" t="n">
-        <v>33.89</v>
+        <v>123.16</v>
       </c>
       <c r="T5" t="n">
-        <v>22.96</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>1</v>
+        <v>78</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>270303</v>
+        <v>630503</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1107,8 +1107,8 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="2" t="n">
-        <v>16.7</v>
+      <c r="AD5" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>193.1</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>-11.49</v>
+        <v>62.74</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-8.779999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>7.33</v>
+        <v>-11.91</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.69</v>
+        <v>-39.36</v>
       </c>
       <c r="H6" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.7</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1170,56 +1170,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>-9.23</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="K6" s="3" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>27</v>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>39.1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O6" s="3" t="n">
-        <v>12.56</v>
+        <v>-6.74</v>
       </c>
       <c r="P6" t="n">
-        <v>13.85</v>
+        <v>9.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>166.36</v>
+        <v>56.77</v>
       </c>
       <c r="R6" t="n">
-        <v>212.74</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>237.87</v>
+        <v>113.82</v>
       </c>
       <c r="T6" t="n">
-        <v>125.61</v>
-      </c>
-      <c r="U6" s="2" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>730206</v>
+        <v>270107</v>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1227,17 +1227,17 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="2" t="n">
-        <v>14.8</v>
+      <c r="AD6" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80.48999999999999</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>-7.3</v>
+        <v>193</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-7.93</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-6.15</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>-35.01</v>
+        <v>3.64</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-4.41</v>
       </c>
       <c r="H7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.84</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1290,16 +1290,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>-5.5</v>
+      <c r="K7" s="3" t="n">
+        <v>-9.42</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>38</v>
+        <v>30.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,36 +1307,36 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-0.92</v>
+        <v>8.81</v>
       </c>
       <c r="P7" t="n">
-        <v>6.55</v>
+        <v>13.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>75.22</v>
+        <v>167.1</v>
       </c>
       <c r="R7" t="n">
-        <v>85.17</v>
+        <v>213.08</v>
       </c>
       <c r="S7" t="n">
-        <v>123.96</v>
+        <v>237.87</v>
       </c>
       <c r="T7" t="n">
-        <v>80.20999999999999</v>
+        <v>125.61</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>630503</v>
+        <v>730206</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
         <v>5</v>
@@ -1347,17 +1347,17 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD7" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,32 +1377,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76.78</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>-8.050000000000001</v>
+        <v>193.4</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-11.73</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-9.98</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>-21.77</v>
+        <v>2.55</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>-8.27</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1410,53 +1410,53 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>-6.67</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="3" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>46.7</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-4.75</v>
+        <v>7.72</v>
       </c>
       <c r="P8" t="n">
-        <v>4.77</v>
+        <v>14.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>73.12</v>
+        <v>165.22</v>
       </c>
       <c r="R8" t="n">
-        <v>82.26000000000001</v>
+        <v>207.88</v>
       </c>
       <c r="S8" t="n">
-        <v>113</v>
+        <v>242.99</v>
       </c>
       <c r="T8" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>0</v>
+        <v>102.3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>710101</v>
+        <v>730204</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA8" t="n">
         <v>5</v>
@@ -1467,17 +1467,17 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD8" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>90.44</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-8.15</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-3.94</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>-11.65</v>
+        <v>48.1</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-17.01</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-17</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>-46.87</v>
       </c>
       <c r="H9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.8</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1530,56 +1530,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>-4.53</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="K9" s="3" t="n">
+        <v>-16.01</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>24.2</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1.29</v>
+        <v>-11.83</v>
       </c>
       <c r="P9" t="n">
-        <v>12.32</v>
+        <v>12.69</v>
       </c>
       <c r="Q9" t="n">
-        <v>79.3</v>
+        <v>41.99</v>
       </c>
       <c r="R9" t="n">
-        <v>94.73</v>
+        <v>57.27</v>
       </c>
       <c r="S9" t="n">
-        <v>111.63</v>
+        <v>96.3</v>
       </c>
       <c r="T9" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
+        <v>45.26</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>650201</v>
+        <v>270203</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1587,8 +1587,8 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD9" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>115.88</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>-9.539999999999999</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>-9.609999999999999</v>
+        <v>75.37</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>-10.65</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-27.52</v>
       </c>
       <c r="H10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.86</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1650,56 +1650,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K10" s="2" t="n">
-        <v>-5.67</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="3" t="n">
+        <v>-7.88</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>27.1</v>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O10" s="3" t="n">
-        <v>3.11</v>
+        <v>-5.48</v>
       </c>
       <c r="P10" t="n">
-        <v>10.13</v>
+        <v>5.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>104.14</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>122.84</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>142.99</v>
+        <v>113</v>
       </c>
       <c r="T10" t="n">
-        <v>94.73</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
+        <v>72.61</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270202</v>
+        <v>710101</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1707,8 +1707,8 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD10" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,32 +1737,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>235.07</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>-14.64</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-5.78</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>-4.12</v>
+        <v>370.2</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-32.14</v>
       </c>
       <c r="H11" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.99</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1770,16 +1770,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>-10.41</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="3" t="n">
+        <v>-10.67</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>36.3</v>
+        <v>34.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1787,29 +1787,29 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>-0.55</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
-        <v>13.56</v>
+        <v>12.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>203.2</v>
+        <v>323.53</v>
       </c>
       <c r="R11" t="n">
-        <v>262.38</v>
+        <v>414.42</v>
       </c>
       <c r="S11" t="n">
-        <v>294.5</v>
+        <v>579.42</v>
       </c>
       <c r="T11" t="n">
-        <v>155.05</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>1</v>
+        <v>347</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W11" t="n">
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1827,8 +1827,8 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD11" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,30 +1857,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>378.5</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>-16.11</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>-25.91</v>
+        <v>135.09</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-21.85</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-23.07</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-49.57</v>
       </c>
       <c r="H12" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+        <v>0.73</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1890,56 +1890,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K12" s="2" t="n">
-        <v>-8.83</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K12" s="3" t="n">
+        <v>-18.95</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>30</v>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>3.11</v>
+        <v>-17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>11.95</v>
+        <v>13.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>333.28</v>
+        <v>116.79</v>
       </c>
       <c r="R12" t="n">
-        <v>415.15</v>
+        <v>166.68</v>
       </c>
       <c r="S12" t="n">
-        <v>579.42</v>
+        <v>283.02</v>
       </c>
       <c r="T12" t="n">
-        <v>347</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
+        <v>130.6</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>730204</v>
+        <v>270401</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1947,8 +1947,8 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AD12" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD12" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,30 +1977,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>288.6</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>-16.59</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-20.34</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>-51.31</v>
+        <v>145.49</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-21.78</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-18.79</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-44.32</v>
       </c>
       <c r="H13" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+        <v>0.93</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2010,56 +2010,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K13" s="2" t="n">
-        <v>-14.19</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="3" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O13" s="2" t="n">
-        <v>-15.11</v>
+      <c r="O13" s="3" t="n">
+        <v>-13.62</v>
       </c>
       <c r="P13" t="n">
-        <v>8.6</v>
+        <v>13.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>263.77</v>
+        <v>125.25</v>
       </c>
       <c r="R13" t="n">
-        <v>336.34</v>
+        <v>183.23</v>
       </c>
       <c r="S13" t="n">
-        <v>645.09</v>
+        <v>280.08</v>
       </c>
       <c r="T13" t="n">
-        <v>285</v>
-      </c>
-      <c r="U13" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270104</v>
+        <v>270202</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2067,8 +2067,8 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD13" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>明显放量(1.5-2.5倍)</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,30 +2097,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>49.71</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-16.94</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-11.03</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>-40.6</v>
+        <v>47.59</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-8.48</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-15.28</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-26.01</v>
       </c>
       <c r="H14" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+        <v>0.86</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2130,50 +2130,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K14" s="2" t="n">
-        <v>-13.93</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="3" t="n">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n">
-        <v>-5.8</v>
+      <c r="O14" s="3" t="n">
+        <v>-10.11</v>
       </c>
       <c r="P14" t="n">
-        <v>12.1</v>
+        <v>7.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>43.69</v>
+        <v>43.8</v>
       </c>
       <c r="R14" t="n">
-        <v>57.76</v>
+        <v>52.8</v>
       </c>
       <c r="S14" t="n">
-        <v>96.3</v>
+        <v>65.52</v>
       </c>
       <c r="T14" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="U14" s="2" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>270203</v>
+        <v>270504</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" s="2" t="n">
+      <c r="AD14" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,30 +2217,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>152.01</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>-19.99</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-12.36</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>-29.89</v>
+        <v>55.55</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-6.69</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-23.03</v>
       </c>
       <c r="H15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+        <v>0.91</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2250,50 +2250,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K15" s="2" t="n">
-        <v>-14.62</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="K15" s="3" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>34.4</v>
+        <v>44.2</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O15" s="2" t="n">
-        <v>-7.13</v>
+      <c r="O15" s="3" t="n">
+        <v>-1.52</v>
       </c>
       <c r="P15" t="n">
-        <v>12.91</v>
+        <v>9.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>132.39</v>
+        <v>50.12</v>
       </c>
       <c r="R15" t="n">
-        <v>178.04</v>
+        <v>58.91</v>
       </c>
       <c r="S15" t="n">
-        <v>258.66</v>
+        <v>84.7</v>
       </c>
       <c r="T15" t="n">
-        <v>150</v>
-      </c>
-      <c r="U15" s="2" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="U15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>730204</v>
+        <v>270107</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" s="2" t="n">
+      <c r="AD15" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>49.82</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>-22.22</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-11.23</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>-42.21</v>
+        <v>112.29</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-18.22</v>
       </c>
       <c r="H16" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.83</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2370,50 +2370,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K16" s="2" t="n">
-        <v>-13.24</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="K16" s="3" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>27.1</v>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>-6</v>
+        <v>1.62</v>
       </c>
       <c r="P16" t="n">
-        <v>14.87</v>
+        <v>10.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>42.41</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>57.42</v>
+        <v>122.64</v>
       </c>
       <c r="S16" t="n">
-        <v>95.95</v>
+        <v>142.99</v>
       </c>
       <c r="T16" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U16" s="2" t="n">
+        <v>94.73</v>
+      </c>
+      <c r="U16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>640108</v>
+        <v>270202</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2427,7 +2427,7 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" s="2" t="n">
+      <c r="AD16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE16" t="inlineStr">
@@ -2457,32 +2457,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>-10.94</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>-14.75</v>
+        <v>83.51000000000001</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-12.61</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-22.01</v>
       </c>
       <c r="H17" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.79</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2490,56 +2490,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K17" s="2" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>死叉(转空)</t>
+      <c r="K17" s="3" t="n">
+        <v>-11.43</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>44.3</v>
+        <v>35.5</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O17" s="2" t="n">
-        <v>-1.08</v>
+      <c r="O17" s="3" t="n">
+        <v>-4.36</v>
       </c>
       <c r="P17" t="n">
-        <v>9.470000000000001</v>
+        <v>13.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>50.63</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>59.11</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>84.7</v>
+        <v>111.63</v>
       </c>
       <c r="T17" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="U17" s="2" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>270107</v>
+        <v>650201</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2547,8 +2547,8 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" s="2" t="n">
-        <v>5.6</v>
+      <c r="AD17" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,32 +2577,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.91</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>-16.96</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-7.77</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>-20.68</v>
+        <v>284</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-21.03</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-54.19</v>
       </c>
       <c r="H18" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.95</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2610,56 +2610,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K18" s="2" t="n">
-        <v>-15.42</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="K18" s="3" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>25.2</v>
+        <v>23</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>-2.54</v>
+      <c r="O18" s="3" t="n">
+        <v>-15.86</v>
       </c>
       <c r="P18" t="n">
-        <v>13.57</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>25.85</v>
+        <v>259</v>
       </c>
       <c r="R18" t="n">
-        <v>35.36</v>
+        <v>332.56</v>
       </c>
       <c r="S18" t="n">
-        <v>40.87</v>
+        <v>645.09</v>
       </c>
       <c r="T18" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="U18" s="2" t="n">
+        <v>270.39</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>640209</v>
+        <v>270104</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2667,17 +2667,17 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" s="2" t="n">
-        <v>5.6</v>
+      <c r="AD18" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,30 +2697,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48.43</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>-10.93</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-15.15</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>-22.3</v>
+        <v>204.4</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-10.15</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-43.92</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+        <v>0.74</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2730,56 +2730,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K19" s="2" t="n">
-        <v>-9.01</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="K19" s="3" t="n">
+        <v>-13.68</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>32.1</v>
+        <v>36.7</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O19" s="2" t="n">
-        <v>-9.92</v>
+      <c r="O19" s="3" t="n">
+        <v>-4.98</v>
       </c>
       <c r="P19" t="n">
-        <v>7.88</v>
+        <v>11.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.61</v>
+        <v>180.08</v>
       </c>
       <c r="R19" t="n">
-        <v>53.23</v>
+        <v>236.79</v>
       </c>
       <c r="S19" t="n">
-        <v>65.52</v>
+        <v>385</v>
       </c>
       <c r="T19" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="U19" s="2" t="n">
+        <v>183.83</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270504</v>
+        <v>270103</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2787,8 +2787,8 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" s="2" t="n">
-        <v>3.7</v>
+      <c r="AD19" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,30 +2817,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78.11</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>-15.99</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-16.36</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>-38.93</v>
+        <v>148.71</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-18.29</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-14.28</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-37.65</v>
       </c>
       <c r="H20" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+        <v>0.96</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2850,56 +2850,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K20" s="2" t="n">
-        <v>-14.32</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="K20" s="3" t="n">
+        <v>-15.89</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>-11.13</v>
+        <v>33.9</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>-9.109999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>12.24</v>
+        <v>13.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>68.55</v>
+        <v>129.06</v>
       </c>
       <c r="R20" t="n">
-        <v>91.16</v>
+        <v>176.8</v>
       </c>
       <c r="S20" t="n">
-        <v>140.68</v>
+        <v>258.66</v>
       </c>
       <c r="T20" t="n">
-        <v>77.03</v>
-      </c>
-      <c r="U20" s="2" t="n">
-        <v>0</v>
+        <v>141.08</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>640703</v>
+        <v>730204</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2907,8 +2907,8 @@
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" s="2" t="n">
-        <v>3.7</v>
+      <c r="AD20" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,32 +2937,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>209.62</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>-16.81</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-7.02</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>-37.21</v>
+        <v>54.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-19.79</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-17.56</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-32.9</v>
       </c>
       <c r="H21" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.86</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2970,56 +2970,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K21" s="2" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="K21" s="3" t="n">
+        <v>-16.45</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>37.4</v>
+        <v>30.6</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>-1.79</v>
+      <c r="O21" s="3" t="n">
+        <v>-12.39</v>
       </c>
       <c r="P21" t="n">
-        <v>11.36</v>
+        <v>13</v>
       </c>
       <c r="Q21" t="n">
-        <v>185.82</v>
+        <v>47.5</v>
       </c>
       <c r="R21" t="n">
-        <v>237.95</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>385</v>
+        <v>84.5</v>
       </c>
       <c r="T21" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U21" s="2" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="U21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270103</v>
+        <v>270303</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3027,8 +3027,8 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" s="2" t="n">
-        <v>3.7</v>
+      <c r="AD21" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,30 +3057,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>86.98999999999999</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>-17.98</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>-41.02</v>
+        <v>48.47</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-21.82</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-48.95</v>
       </c>
       <c r="H22" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+        <v>0.96</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3090,56 +3090,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K22" s="2" t="n">
-        <v>-14.16</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="K22" s="3" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>-7.17</v>
+        <v>44</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>-9.029999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>11.01</v>
+        <v>15.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>77.41</v>
+        <v>40.89</v>
       </c>
       <c r="R22" t="n">
-        <v>101.35</v>
+        <v>57.02</v>
       </c>
       <c r="S22" t="n">
-        <v>168.98</v>
+        <v>95.95</v>
       </c>
       <c r="T22" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="U22" s="2" t="n">
-        <v>0</v>
+        <v>43.01</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>640703</v>
+        <v>640108</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3147,8 +3147,8 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" s="2" t="n">
-        <v>3.7</v>
+      <c r="AD22" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>56.58</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>-19.09</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-15.03</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>-25.94</v>
+        <v>50.89</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-11.06</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-32.92</v>
       </c>
       <c r="H23" t="n">
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3210,50 +3210,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K23" s="2" t="n">
-        <v>-14.19</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="K23" s="3" t="n">
+        <v>-14.56</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="n">
-        <v>-9.800000000000001</v>
+        <v>25.3</v>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>-20.53</v>
       </c>
       <c r="P23" t="n">
-        <v>12.29</v>
+        <v>10.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>49.63</v>
+        <v>45.75</v>
       </c>
       <c r="R23" t="n">
-        <v>65.94</v>
+        <v>59.56</v>
       </c>
       <c r="S23" t="n">
-        <v>84.5</v>
+        <v>78.5</v>
       </c>
       <c r="T23" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="U23" s="2" t="n">
-        <v>1</v>
+        <v>45.82</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270303</v>
+        <v>640209</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" s="2" t="n">
+      <c r="AD23" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>150.66</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>-21.94</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-17.87</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>-36.58</v>
+        <v>235.04</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-12.28</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-13.27</v>
       </c>
       <c r="H24" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.91</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3330,50 +3330,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K24" s="2" t="n">
-        <v>-18.52</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="K24" s="3" t="n">
+        <v>-10.19</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="n">
-        <v>-12.64</v>
+        <v>38.5</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>-0.17</v>
       </c>
       <c r="P24" t="n">
-        <v>13.5</v>
+        <v>13.43</v>
       </c>
       <c r="Q24" t="n">
-        <v>130.32</v>
+        <v>203.48</v>
       </c>
       <c r="R24" t="n">
-        <v>184.92</v>
+        <v>261.72</v>
       </c>
       <c r="S24" t="n">
-        <v>280.08</v>
+        <v>294.5</v>
       </c>
       <c r="T24" t="n">
-        <v>150.66</v>
-      </c>
-      <c r="U24" s="2" t="n">
-        <v>0</v>
+        <v>155.05</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>270202</v>
+        <v>730204</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3387,7 +3387,7 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" s="2" t="n">
+      <c r="AD24" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="AE24" t="inlineStr">
@@ -3417,30 +3417,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>-12.78</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-12.15</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>-33.45</v>
+        <v>32.65</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-12.86</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-28.81</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-30.34</v>
       </c>
       <c r="H25" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+        <v>0.52</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3450,56 +3450,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K25" s="2" t="n">
-        <v>-8.380000000000001</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="K25" s="3" t="n">
+        <v>-13.71</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>38.1</v>
+        <v>32.4</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O25" s="2" t="n">
-        <v>-6.92</v>
+      <c r="O25" s="3" t="n">
+        <v>-23.64</v>
       </c>
       <c r="P25" t="n">
-        <v>9.109999999999999</v>
+        <v>10.99</v>
       </c>
       <c r="Q25" t="n">
-        <v>56.9</v>
+        <v>29.06</v>
       </c>
       <c r="R25" t="n">
-        <v>68.33</v>
+        <v>37.84</v>
       </c>
       <c r="S25" t="n">
-        <v>113.82</v>
+        <v>49.37</v>
       </c>
       <c r="T25" t="n">
-        <v>60.79</v>
-      </c>
-      <c r="U25" s="2" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="U25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>270107</v>
+        <v>270504</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3507,8 +3507,8 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" s="2" t="n">
-        <v>0</v>
+      <c r="AD25" s="3" t="n">
+        <v>3.7</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,30 +3537,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33.54</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>-14</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-26.25</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>-24.07</v>
+        <v>336.91</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-14.58</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-16.82</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-60.85</v>
       </c>
       <c r="H26" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+        <v>0.78</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3570,56 +3570,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K26" s="2" t="n">
-        <v>-12.88</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="K26" s="3" t="n">
+        <v>-14.05</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="n">
-        <v>-21.02</v>
+        <v>25.4</v>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>-11.65</v>
       </c>
       <c r="P26" t="n">
-        <v>10.72</v>
+        <v>10.13</v>
       </c>
       <c r="Q26" t="n">
-        <v>29.94</v>
+        <v>302.77</v>
       </c>
       <c r="R26" t="n">
-        <v>38.5</v>
+        <v>391.96</v>
       </c>
       <c r="S26" t="n">
-        <v>49.37</v>
+        <v>878.99</v>
       </c>
       <c r="T26" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="U26" s="2" t="n">
-        <v>1</v>
+        <v>319.62</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270504</v>
+        <v>270104</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3627,8 +3627,8 @@
       <c r="AC26" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="2" t="n">
-        <v>0</v>
+      <c r="AD26" s="3" t="n">
+        <v>3.7</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>51.93</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>-15.22</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-21.59</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>-28</v>
+        <v>75.5</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-15.25</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-18.82</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-42.32</v>
       </c>
       <c r="H27" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.79</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3690,56 +3690,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K27" s="2" t="n">
-        <v>-14.09</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="K27" s="3" t="n">
+        <v>-16.38</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>26</v>
+        <v>24.1</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O27" s="2" t="n">
-        <v>-16.36</v>
+      <c r="O27" s="3" t="n">
+        <v>-13.65</v>
       </c>
       <c r="P27" t="n">
-        <v>9.380000000000001</v>
+        <v>12.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>47.06</v>
+        <v>65.91</v>
       </c>
       <c r="R27" t="n">
-        <v>60.44</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>78.5</v>
+        <v>140.68</v>
       </c>
       <c r="T27" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="U27" s="2" t="n">
+        <v>72.84999999999999</v>
+      </c>
+      <c r="U27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>640209</v>
+        <v>640703</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3747,8 +3747,8 @@
       <c r="AC27" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="2" t="n">
-        <v>0</v>
+      <c r="AD27" s="3" t="n">
+        <v>3.7</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,30 +3777,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>341.48</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>-16.78</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-17.3</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>-58.61</v>
+        <v>85.97</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-16.45</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>-13.14</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-45.93</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+        <v>0.85</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3810,56 +3810,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K28" s="2" t="n">
-        <v>-13.63</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="K28" s="3" t="n">
+        <v>-14.62</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>23.5</v>
+        <v>27.9</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O28" s="2" t="n">
-        <v>-12.07</v>
+      <c r="O28" s="3" t="n">
+        <v>-7.97</v>
       </c>
       <c r="P28" t="n">
-        <v>10.21</v>
+        <v>11</v>
       </c>
       <c r="Q28" t="n">
-        <v>306.62</v>
+        <v>76.52</v>
       </c>
       <c r="R28" t="n">
-        <v>395.37</v>
+        <v>100.7</v>
       </c>
       <c r="S28" t="n">
-        <v>878.99</v>
+        <v>168.98</v>
       </c>
       <c r="T28" t="n">
-        <v>334</v>
-      </c>
-      <c r="U28" s="2" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="U28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>270104</v>
+        <v>640703</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3867,8 +3867,8 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" s="2" t="n">
-        <v>0</v>
+      <c r="AD28" s="3" t="n">
+        <v>3.7</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>144.98</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>-19.02</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-13.6</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>-40.58</v>
+        <v>28.68</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-20.16</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-15.25</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-26.63</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.5</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3930,50 +3930,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K29" s="2" t="n">
-        <v>-14.07</v>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="K29" s="3" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="n">
-        <v>-8.369999999999999</v>
+        <v>26</v>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>-10.08</v>
       </c>
       <c r="P29" t="n">
-        <v>12.21</v>
+        <v>14.09</v>
       </c>
       <c r="Q29" t="n">
-        <v>127.28</v>
+        <v>24.64</v>
       </c>
       <c r="R29" t="n">
-        <v>168.71</v>
+        <v>35.11</v>
       </c>
       <c r="S29" t="n">
-        <v>283.02</v>
+        <v>40.87</v>
       </c>
       <c r="T29" t="n">
-        <v>133.61</v>
-      </c>
-      <c r="U29" s="2" t="n">
-        <v>1</v>
+        <v>23.2</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>270401</v>
+        <v>640209</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       <c r="AC29" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" s="2" t="n">
+      <c r="AD29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -39,14 +39,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -473,7 +473,7 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="41" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
     <col width="66" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="25" customWidth="1" min="34" max="34"/>
@@ -657,49 +657,49 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>35.68</v>
+        <v>49.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.34</v>
+        <v>-13.09</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>-13.73</v>
+        <v>-10.32</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-37.33</v>
       </c>
       <c r="H2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
+        <v>1.32</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>8.390000000000001</v>
+        <v>-11.89</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>66.2</v>
+        <v>39.4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,57 +707,57 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>-3.78</v>
       </c>
       <c r="P2" t="n">
-        <v>6.89</v>
+        <v>16.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>33.22</v>
+        <v>41.61</v>
       </c>
       <c r="R2" t="n">
-        <v>32.92</v>
+        <v>56.52</v>
       </c>
       <c r="S2" t="n">
-        <v>44.24</v>
+        <v>81.66</v>
       </c>
       <c r="T2" t="n">
-        <v>30.34</v>
+        <v>43.01</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>630702</v>
+        <v>640108</v>
       </c>
       <c r="Z2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>35.2</v>
+        <v>0</v>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v>27.8</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>股价站上20日均线；突破20日新高；距20日均线5-10%</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>极端放量(&gt;2.5倍，需留意)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>换手率处于近60日95分位以上(极端活跃)</t>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -777,28 +777,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>202.72</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>-7.45</v>
+        <v>115.9</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>-2.66</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>-1.67</v>
+        <v>-5.5</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>-7.03</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -807,59 +807,59 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3.22</v>
+        <v>-5.16</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>63.3</v>
+        <v>37.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>9.720000000000001</v>
+      <c r="O3" s="3" t="n">
+        <v>1.04</v>
       </c>
       <c r="P3" t="n">
-        <v>9.460000000000001</v>
+        <v>11.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>183.54</v>
+        <v>102.42</v>
       </c>
       <c r="R3" t="n">
-        <v>196.4</v>
+        <v>122.2</v>
       </c>
       <c r="S3" t="n">
-        <v>232.68</v>
+        <v>142.99</v>
       </c>
       <c r="T3" t="n">
-        <v>170.88</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>4</v>
+        <v>94.73</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270104</v>
+        <v>270202</v>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -867,17 +867,17 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="n">
-        <v>33.3</v>
+      <c r="AD3" s="2" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,30 +897,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.37</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-11.12</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-12.38</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>-31.76</v>
+        <v>139.75</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>-18.38</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-26.66</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>-40.96</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+        <v>1.11</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -930,56 +930,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="K4" s="2" t="n">
+        <v>-21.73</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>37</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-7.21</v>
+        <v>25.9</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>-20.12</v>
       </c>
       <c r="P4" t="n">
-        <v>10.03</v>
+        <v>15.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.13</v>
+        <v>118.72</v>
       </c>
       <c r="R4" t="n">
-        <v>24.71</v>
+        <v>178.55</v>
       </c>
       <c r="S4" t="n">
-        <v>33.89</v>
+        <v>280.08</v>
       </c>
       <c r="T4" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1</v>
+        <v>130.14</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270303</v>
+        <v>270202</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -987,8 +987,8 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="3" t="n">
-        <v>22.2</v>
+      <c r="AD4" s="2" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80.68000000000001</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-4.19</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-6.66</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>-34.6</v>
+        <v>246.7</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>-4.68</v>
       </c>
       <c r="H5" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1050,50 +1050,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>-4.95</v>
+      <c r="K5" s="2" t="n">
+        <v>-5.04</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>41.7</v>
+        <v>46.1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O5" s="3" t="n">
-        <v>-1.49</v>
+      <c r="O5" s="2" t="n">
+        <v>-0.89</v>
       </c>
       <c r="P5" t="n">
-        <v>6.63</v>
+        <v>13.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>75.33</v>
+        <v>212.87</v>
       </c>
       <c r="R5" t="n">
-        <v>84.88</v>
+        <v>259.8</v>
       </c>
       <c r="S5" t="n">
-        <v>123.16</v>
+        <v>294.5</v>
       </c>
       <c r="T5" t="n">
-        <v>78</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
+        <v>155.05</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>630503</v>
+        <v>730204</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1107,7 +1107,7 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="3" t="n">
+      <c r="AD5" s="2" t="n">
         <v>20.4</v>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>62.74</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-8.779999999999999</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-11.91</v>
+        <v>201.23</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>-6.92</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-2.36</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-39.36</v>
+        <v>5.52</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1170,16 +1170,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>39.1</v>
+        <v>52.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1187,39 +1187,39 @@
         </is>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-6.74</v>
+        <v>4.18</v>
       </c>
       <c r="P6" t="n">
-        <v>9.51</v>
+        <v>15.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>56.77</v>
+        <v>169.2</v>
       </c>
       <c r="R6" t="n">
-        <v>67.90000000000001</v>
+        <v>207.89</v>
       </c>
       <c r="S6" t="n">
-        <v>113.82</v>
+        <v>242.99</v>
       </c>
       <c r="T6" t="n">
-        <v>58.73</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>1</v>
+        <v>102.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>270107</v>
+        <v>730204</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1227,17 +1227,17 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="3" t="n">
+      <c r="AD6" s="2" t="n">
         <v>20.4</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1266,19 +1266,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>193</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>-7.93</v>
+        <v>186.11</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>-7.45</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3.64</v>
+        <v>-10.14</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-4.41</v>
+        <v>0.48</v>
       </c>
       <c r="H7" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1290,16 +1290,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>-9.42</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="n">
+        <v>-11.97</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>30.3</v>
+        <v>34.7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>8.81</v>
+        <v>-3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>13.42</v>
+        <v>14.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>167.1</v>
+        <v>158.49</v>
       </c>
       <c r="R7" t="n">
-        <v>213.08</v>
+        <v>211.41</v>
       </c>
       <c r="S7" t="n">
         <v>237.87</v>
@@ -1324,12 +1324,12 @@
       <c r="T7" t="n">
         <v>125.61</v>
       </c>
-      <c r="U7" t="n">
-        <v>2</v>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1347,8 +1347,8 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="3" t="n">
-        <v>14.8</v>
+      <c r="AD7" s="2" t="n">
+        <v>20.4</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,32 +1377,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>193.4</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-11.73</v>
+        <v>145.86</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>-12.61</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>-8.27</v>
+        <v>-20.93</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>-32.47</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.92</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1410,16 +1410,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
-        <v>-6.96</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="K8" s="2" t="n">
+        <v>-15.93</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>46.7</v>
+        <v>38</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,39 +1427,39 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>7.72</v>
+        <v>-14.39</v>
       </c>
       <c r="P8" t="n">
         <v>14.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>165.22</v>
+        <v>124.61</v>
       </c>
       <c r="R8" t="n">
-        <v>207.88</v>
+        <v>173.5</v>
       </c>
       <c r="S8" t="n">
-        <v>242.99</v>
+        <v>235.11</v>
       </c>
       <c r="T8" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
+        <v>132.7</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>730204</v>
       </c>
       <c r="Z8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1467,17 +1467,17 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="3" t="n">
-        <v>14.8</v>
+      <c r="AD8" s="2" t="n">
+        <v>20.4</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,30 +1497,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-17.01</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-17</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>-46.87</v>
+        <v>128.65</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>-19.69</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-27.25</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>-40.64</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
+        <v>0.83</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1530,56 +1530,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K9" s="3" t="n">
-        <v>-16.01</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="K9" s="2" t="n">
+        <v>-20.79</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>24.2</v>
+        <v>30</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O9" s="3" t="n">
-        <v>-11.83</v>
+      <c r="O9" s="2" t="n">
+        <v>-20.71</v>
       </c>
       <c r="P9" t="n">
-        <v>12.69</v>
+        <v>14.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.99</v>
+        <v>109.89</v>
       </c>
       <c r="R9" t="n">
-        <v>57.27</v>
+        <v>162.43</v>
       </c>
       <c r="S9" t="n">
-        <v>96.3</v>
+        <v>242.81</v>
       </c>
       <c r="T9" t="n">
-        <v>45.26</v>
-      </c>
-      <c r="U9" s="3" t="n">
+        <v>120.66</v>
+      </c>
+      <c r="U9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>270203</v>
+        <v>270401</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1587,8 +1587,8 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="3" t="n">
-        <v>14.8</v>
+      <c r="AD9" s="2" t="n">
+        <v>20.4</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,30 +1617,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>-10.65</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>-27.52</v>
+        <v>21.04</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>-10.51</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>-28.82</v>
       </c>
       <c r="H10" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+        <v>2.05</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1650,56 +1650,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>-7.88</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="n">
+        <v>-13.43</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-5.48</v>
+        <v>34.8</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>-11.56</v>
       </c>
       <c r="P10" t="n">
-        <v>5.33</v>
+        <v>11.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>71.34999999999999</v>
+        <v>18.68</v>
       </c>
       <c r="R10" t="n">
-        <v>81.81999999999999</v>
+        <v>24.3</v>
       </c>
       <c r="S10" t="n">
-        <v>113</v>
+        <v>31.89</v>
       </c>
       <c r="T10" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>0</v>
+        <v>20.42</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>710101</v>
+        <v>270303</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1707,8 +1707,8 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" s="3" t="n">
-        <v>13</v>
+      <c r="AD10" s="2" t="n">
+        <v>18.5</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>370.2</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>-32.14</v>
+        <v>351.3</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>-10.59</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>-31.45</v>
       </c>
       <c r="H11" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+        <v>1.08</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1770,16 +1770,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K11" s="3" t="n">
-        <v>-10.67</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="K11" s="2" t="n">
+        <v>-14.15</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>34.7</v>
+        <v>36.8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1787,29 +1787,29 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>1.39</v>
+        <v>-9.26</v>
       </c>
       <c r="P11" t="n">
-        <v>12.61</v>
+        <v>14.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>323.53</v>
+        <v>302.08</v>
       </c>
       <c r="R11" t="n">
-        <v>414.42</v>
+        <v>409.21</v>
       </c>
       <c r="S11" t="n">
         <v>579.42</v>
       </c>
       <c r="T11" t="n">
-        <v>347</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
+        <v>329.12</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W11" t="n">
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1827,8 +1827,8 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="3" t="n">
-        <v>13</v>
+      <c r="AD11" s="2" t="n">
+        <v>18.5</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,30 +1857,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>135.09</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>-21.85</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>-23.07</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>-49.57</v>
+        <v>233.78</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>-11.71</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-18.68</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>-54.45</v>
       </c>
       <c r="H12" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+        <v>0.88</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1890,56 +1890,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>-18.95</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="K12" s="2" t="n">
+        <v>-14.59</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>30</v>
+        <v>29.6</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O12" s="3" t="n">
-        <v>-17.9</v>
+      <c r="O12" s="2" t="n">
+        <v>-12.14</v>
       </c>
       <c r="P12" t="n">
-        <v>13.55</v>
+        <v>11.09</v>
       </c>
       <c r="Q12" t="n">
-        <v>116.79</v>
+        <v>207.85</v>
       </c>
       <c r="R12" t="n">
-        <v>166.68</v>
+        <v>273.72</v>
       </c>
       <c r="S12" t="n">
-        <v>283.02</v>
+        <v>527.5</v>
       </c>
       <c r="T12" t="n">
-        <v>130.6</v>
-      </c>
-      <c r="U12" s="3" t="n">
+        <v>218.03</v>
+      </c>
+      <c r="U12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>270401</v>
+        <v>270104</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1947,8 +1947,8 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AD12" s="3" t="n">
-        <v>13</v>
+      <c r="AD12" s="2" t="n">
+        <v>18.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,30 +1977,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>145.49</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-21.78</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-18.79</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>-44.32</v>
+        <v>79.91</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>-25.57</v>
       </c>
       <c r="H13" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
+        <v>0.97</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2010,56 +2010,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K13" s="3" t="n">
-        <v>-20.6</v>
+      <c r="K13" s="2" t="n">
+        <v>-5.1</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>-13.62</v>
+        <v>41.1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>-2.77</v>
       </c>
       <c r="P13" t="n">
-        <v>13.91</v>
+        <v>7.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>125.25</v>
+        <v>74</v>
       </c>
       <c r="R13" t="n">
-        <v>183.23</v>
+        <v>84.2</v>
       </c>
       <c r="S13" t="n">
-        <v>280.08</v>
+        <v>121.57</v>
       </c>
       <c r="T13" t="n">
-        <v>139</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270202</v>
+        <v>630503</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2067,8 +2067,8 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" s="3" t="n">
-        <v>11.1</v>
+      <c r="AD13" s="2" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,30 +2097,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>47.59</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-8.48</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-15.28</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>-26.01</v>
+        <v>60.16</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>-8.43</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>-39.23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
+        <v>0.72</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2130,56 +2130,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="K14" s="2" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>-10.11</v>
+        <v>36</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>-6.21</v>
       </c>
       <c r="P14" t="n">
-        <v>7.97</v>
+        <v>10.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>43.8</v>
+        <v>53.87</v>
       </c>
       <c r="R14" t="n">
-        <v>52.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>65.52</v>
+        <v>105</v>
       </c>
       <c r="T14" t="n">
-        <v>46.02</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>0</v>
+        <v>57.4</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>270504</v>
+        <v>270107</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2187,8 +2187,8 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD14" s="2" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,30 +2217,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55.55</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>-6.69</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>-23.03</v>
+        <v>32.01</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>-10.51</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-24.18</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>-20.71</v>
       </c>
       <c r="H15" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+        <v>0.6</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2250,56 +2250,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="K15" s="2" t="n">
+        <v>-12.95</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>-1.52</v>
+        <v>27.9</v>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>-17.64</v>
       </c>
       <c r="P15" t="n">
-        <v>9.77</v>
+        <v>11.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>50.12</v>
+        <v>28.35</v>
       </c>
       <c r="R15" t="n">
-        <v>58.91</v>
+        <v>36.77</v>
       </c>
       <c r="S15" t="n">
-        <v>84.7</v>
+        <v>46.74</v>
       </c>
       <c r="T15" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>1</v>
+        <v>30.05</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270107</v>
+        <v>270504</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2307,8 +2307,8 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD15" s="2" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,28 +2337,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>112.29</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>-9.48</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>-3.55</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>-18.22</v>
+        <v>54.37</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>-12.52</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-20.38</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>-23.52</v>
       </c>
       <c r="H16" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2370,56 +2370,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
-        <v>-8.44</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="K16" s="2" t="n">
+        <v>-15.17</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>33.7</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1.62</v>
+        <v>-13.84</v>
       </c>
       <c r="P16" t="n">
-        <v>10.98</v>
+        <v>13.49</v>
       </c>
       <c r="Q16" t="n">
-        <v>99.95999999999999</v>
+        <v>47.03</v>
       </c>
       <c r="R16" t="n">
-        <v>122.64</v>
+        <v>64.09</v>
       </c>
       <c r="S16" t="n">
-        <v>142.99</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>94.73</v>
-      </c>
-      <c r="U16" s="3" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="U16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>270202</v>
+        <v>270303</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2427,8 +2427,8 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD16" s="2" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,32 +2457,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>83.51000000000001</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-12.61</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>-22.01</v>
+        <v>70.92</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>-13.26</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-24.37</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>-39.52</v>
       </c>
       <c r="H17" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.87</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2490,56 +2490,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>-11.43</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="K17" s="2" t="n">
+        <v>-19.66</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>-4.36</v>
+        <v>19.9</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>-17.83</v>
       </c>
       <c r="P17" t="n">
-        <v>13.83</v>
+        <v>13.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>71.95999999999999</v>
+        <v>61.13</v>
       </c>
       <c r="R17" t="n">
-        <v>94.29000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="S17" t="n">
-        <v>111.63</v>
+        <v>122.2</v>
       </c>
       <c r="T17" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>1</v>
+        <v>66.3</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>650201</v>
+        <v>640703</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2547,8 +2547,8 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD17" s="2" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,30 +2577,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>284</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-14.4</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>-21.03</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>-54.19</v>
+        <v>45.65</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>-13.61</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-26.31</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>-41.74</v>
       </c>
       <c r="H18" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
+        <v>0.79</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2610,56 +2610,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="K18" s="2" t="n">
+        <v>-18.31</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>23</v>
+        <v>20.3</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O18" s="3" t="n">
-        <v>-15.86</v>
+      <c r="O18" s="2" t="n">
+        <v>-19.77</v>
       </c>
       <c r="P18" t="n">
-        <v>8.800000000000001</v>
+        <v>13.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>259</v>
+        <v>39.46</v>
       </c>
       <c r="R18" t="n">
-        <v>332.56</v>
+        <v>55.88</v>
       </c>
       <c r="S18" t="n">
-        <v>645.09</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>270.39</v>
-      </c>
-      <c r="U18" s="3" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="U18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270104</v>
+        <v>270203</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2667,8 +2667,8 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD18" s="2" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,30 +2697,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>204.4</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-16.1</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>-10.15</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>-43.92</v>
+        <v>72.8</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-12.69</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>-31.4</v>
       </c>
       <c r="H19" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
+        <v>1.02</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2730,56 +2730,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>-13.68</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="K19" s="2" t="n">
+        <v>-9.93</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>-4.98</v>
+        <v>23.1</v>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>-6.15</v>
       </c>
       <c r="P19" t="n">
-        <v>11.9</v>
+        <v>5.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>180.08</v>
+        <v>68.45</v>
       </c>
       <c r="R19" t="n">
-        <v>236.79</v>
+        <v>80.83</v>
       </c>
       <c r="S19" t="n">
-        <v>385</v>
+        <v>108.39</v>
       </c>
       <c r="T19" t="n">
-        <v>183.83</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>1</v>
+        <v>70.26000000000001</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270103</v>
+        <v>710101</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2787,8 +2787,8 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD19" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,32 +2817,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>148.71</v>
+        <v>32.8</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-18.29</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-14.28</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>-37.65</v>
+        <v>5.53</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>-11.57</v>
       </c>
       <c r="H20" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>3.62</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2850,16 +2850,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>-15.89</v>
+      <c r="K20" s="2" t="n">
+        <v>-0.31</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>33.9</v>
+        <v>50</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2867,48 +2867,48 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-9.109999999999999</v>
+        <v>3.01</v>
       </c>
       <c r="P20" t="n">
-        <v>13.22</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>129.06</v>
+        <v>30</v>
       </c>
       <c r="R20" t="n">
-        <v>176.8</v>
+        <v>32.9</v>
       </c>
       <c r="S20" t="n">
-        <v>258.66</v>
+        <v>40.38</v>
       </c>
       <c r="T20" t="n">
-        <v>141.08</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>1</v>
+        <v>30.34</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>730204</v>
+        <v>630702</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>3</v>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>无风险扣分项触发</t>
+          <t>换手率处于近60日95分位以上(极端活跃)</t>
         </is>
       </c>
     </row>
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-19.79</v>
+        <v>196.58</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>-7.68</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-17.56</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>-32.9</v>
+        <v>2.02</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>-9.74</v>
       </c>
       <c r="H21" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2970,16 +2970,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>-16.45</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+      <c r="K21" s="2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>30.6</v>
+        <v>61.1</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2987,39 +2987,39 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-12.39</v>
+        <v>8.56</v>
       </c>
       <c r="P21" t="n">
-        <v>13</v>
+        <v>10.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>47.5</v>
+        <v>175.79</v>
       </c>
       <c r="R21" t="n">
-        <v>65.34999999999999</v>
+        <v>197.12</v>
       </c>
       <c r="S21" t="n">
-        <v>84.5</v>
+        <v>232.68</v>
       </c>
       <c r="T21" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>1</v>
+        <v>170.88</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270303</v>
+        <v>270104</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3027,17 +3027,17 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD21" s="2" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,32 +3057,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>48.47</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-21.82</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>-48.95</v>
+        <v>28.5</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>-14.87</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-20.63</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>-18.06</v>
       </c>
       <c r="H22" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.53</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3090,56 +3090,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="K22" s="2" t="n">
+        <v>-17.34</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>44</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>-9.029999999999999</v>
+        <v>9.1</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>-14.09</v>
       </c>
       <c r="P22" t="n">
-        <v>15.63</v>
+        <v>13.51</v>
       </c>
       <c r="Q22" t="n">
-        <v>40.89</v>
+        <v>24.65</v>
       </c>
       <c r="R22" t="n">
-        <v>57.02</v>
+        <v>34.48</v>
       </c>
       <c r="S22" t="n">
-        <v>95.95</v>
+        <v>39.58</v>
       </c>
       <c r="T22" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>1</v>
+        <v>23.2</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>640108</v>
+        <v>640209</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3147,8 +3147,8 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD22" s="2" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,32 +3177,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>50.89</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>-11.06</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>-25.7</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>-32.92</v>
+        <v>46.15</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>-8.43</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-17.49</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>-21.57</v>
       </c>
       <c r="H23" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3210,50 +3210,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K23" s="3" t="n">
-        <v>-14.56</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="K23" s="2" t="n">
+        <v>-11.09</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>-20.53</v>
+        <v>30.9</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>-10.95</v>
       </c>
       <c r="P23" t="n">
-        <v>10.09</v>
+        <v>8.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>45.75</v>
+        <v>42.45</v>
       </c>
       <c r="R23" t="n">
-        <v>59.56</v>
+        <v>51.91</v>
       </c>
       <c r="S23" t="n">
-        <v>78.5</v>
+        <v>64.2</v>
       </c>
       <c r="T23" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>0</v>
+        <v>44.7</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>640209</v>
+        <v>270504</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" s="3" t="n">
+      <c r="AD23" s="2" t="n">
         <v>3.7</v>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>235.04</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-12.28</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>-5.34</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>-13.27</v>
+        <v>53.82</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>-10.83</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-9.01</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>-26.85</v>
       </c>
       <c r="H24" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.88</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3330,50 +3330,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>-10.19</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="K24" s="2" t="n">
+        <v>-7.94</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>38.5</v>
+        <v>42.2</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O24" s="3" t="n">
-        <v>-0.17</v>
+      <c r="O24" s="2" t="n">
+        <v>-2.47</v>
       </c>
       <c r="P24" t="n">
-        <v>13.43</v>
+        <v>10.72</v>
       </c>
       <c r="Q24" t="n">
-        <v>203.48</v>
+        <v>48.05</v>
       </c>
       <c r="R24" t="n">
-        <v>261.72</v>
+        <v>58.46</v>
       </c>
       <c r="S24" t="n">
-        <v>294.5</v>
+        <v>84.7</v>
       </c>
       <c r="T24" t="n">
-        <v>155.05</v>
-      </c>
-      <c r="U24" s="3" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="U24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>730204</v>
+        <v>270107</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3387,7 +3387,7 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" s="3" t="n">
+      <c r="AD24" s="2" t="n">
         <v>3.7</v>
       </c>
       <c r="AE24" t="inlineStr">
@@ -3417,30 +3417,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>32.65</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-12.86</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>-28.81</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>-30.34</v>
+        <v>271.2</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>-12.98</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-24.29</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>-48.05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
+        <v>0.98</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3450,50 +3450,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>-13.71</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="K25" s="2" t="n">
+        <v>-16.41</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>-23.64</v>
+        <v>22.6</v>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>-17.75</v>
       </c>
       <c r="P25" t="n">
-        <v>10.99</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>29.06</v>
+        <v>244.44</v>
       </c>
       <c r="R25" t="n">
-        <v>37.84</v>
+        <v>324.45</v>
       </c>
       <c r="S25" t="n">
-        <v>49.37</v>
+        <v>557</v>
       </c>
       <c r="T25" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>1</v>
+        <v>258</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>270504</v>
+        <v>270104</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" s="3" t="n">
+      <c r="AD25" s="2" t="n">
         <v>3.7</v>
       </c>
       <c r="AE25" t="inlineStr">
@@ -3537,30 +3537,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>336.91</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-14.58</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-16.82</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>-60.85</v>
+        <v>199.31</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>-13.47</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-16.69</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>-37.39</v>
       </c>
       <c r="H26" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3570,50 +3570,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>-14.05</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="K26" s="2" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>25.4</v>
+        <v>24.4</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O26" s="3" t="n">
-        <v>-11.65</v>
+      <c r="O26" s="2" t="n">
+        <v>-10.15</v>
       </c>
       <c r="P26" t="n">
-        <v>10.13</v>
+        <v>11.77</v>
       </c>
       <c r="Q26" t="n">
-        <v>302.77</v>
+        <v>175.85</v>
       </c>
       <c r="R26" t="n">
-        <v>391.96</v>
+        <v>233.8</v>
       </c>
       <c r="S26" t="n">
-        <v>878.99</v>
+        <v>324.99</v>
       </c>
       <c r="T26" t="n">
-        <v>319.62</v>
-      </c>
-      <c r="U26" s="3" t="n">
+        <v>183.83</v>
+      </c>
+      <c r="U26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270104</v>
+        <v>270103</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -3627,7 +3627,7 @@
       <c r="AC26" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="3" t="n">
+      <c r="AD26" s="2" t="n">
         <v>3.7</v>
       </c>
       <c r="AE26" t="inlineStr">
@@ -3657,30 +3657,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>-15.25</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>-18.82</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>-42.32</v>
+        <v>83.61</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>-11.29</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-17.96</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>-45.79</v>
       </c>
       <c r="H27" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
+        <v>0.68</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3690,46 +3690,46 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K27" s="3" t="n">
-        <v>-16.38</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="K27" s="2" t="n">
+        <v>-15.66</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>24.1</v>
+        <v>29.7</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O27" s="3" t="n">
-        <v>-13.65</v>
+      <c r="O27" s="2" t="n">
+        <v>-11.42</v>
       </c>
       <c r="P27" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>65.91</v>
+        <v>74.08</v>
       </c>
       <c r="R27" t="n">
-        <v>90.29000000000001</v>
+        <v>99.13</v>
       </c>
       <c r="S27" t="n">
-        <v>140.68</v>
+        <v>160</v>
       </c>
       <c r="T27" t="n">
-        <v>72.84999999999999</v>
-      </c>
-      <c r="U27" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="U27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W27" t="n">
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3747,8 +3747,8 @@
       <c r="AC27" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="3" t="n">
-        <v>3.7</v>
+      <c r="AD27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,30 +3777,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>85.97</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>-16.45</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>-13.14</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>-45.93</v>
+        <v>48.95</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>-11.93</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-24.07</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>-26.92</v>
       </c>
       <c r="H28" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
+        <v>0.55</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3810,56 +3810,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K28" s="3" t="n">
-        <v>-14.62</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="K28" s="2" t="n">
+        <v>-15.65</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>27.9</v>
+        <v>24</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O28" s="3" t="n">
-        <v>-7.97</v>
+      <c r="O28" s="2" t="n">
+        <v>-17.53</v>
       </c>
       <c r="P28" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>76.52</v>
+        <v>43.66</v>
       </c>
       <c r="R28" t="n">
-        <v>100.7</v>
+        <v>58.04</v>
       </c>
       <c r="S28" t="n">
-        <v>168.98</v>
+        <v>71.59</v>
       </c>
       <c r="T28" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="U28" s="3" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="U28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>640703</v>
+        <v>640209</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3867,8 +3867,8 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" s="3" t="n">
-        <v>3.7</v>
+      <c r="AD28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3897,28 +3897,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28.68</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-20.16</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-15.25</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>-26.63</v>
+        <v>80.06</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>-13.64</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-14.08</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>-18.51</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3930,50 +3930,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>-18.3</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="K29" s="2" t="n">
+        <v>-14.03</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>26</v>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>-10.08</v>
+        <v>32.2</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>-7.54</v>
       </c>
       <c r="P29" t="n">
-        <v>14.09</v>
+        <v>14.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>24.64</v>
+        <v>68.08</v>
       </c>
       <c r="R29" t="n">
-        <v>35.11</v>
+        <v>93.13</v>
       </c>
       <c r="S29" t="n">
-        <v>40.87</v>
+        <v>104.39</v>
       </c>
       <c r="T29" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>0</v>
+        <v>69.63</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>640209</v>
+        <v>650201</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       <c r="AC29" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="n">
+      <c r="AD29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,10 +473,10 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="66" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="31" max="31"/>
+    <col width="58" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
-    <col width="25" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,32 +657,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49.8</v>
+        <v>195.5</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-13.09</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>-10.32</v>
+        <v>-9.31</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>3.66</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-37.33</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.84</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-11.89</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,47 +699,47 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>39.4</v>
+        <v>58.9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>-3.78</v>
+      <c r="O2" s="3" t="n">
+        <v>11.14</v>
       </c>
       <c r="P2" t="n">
-        <v>16.45</v>
+        <v>10.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.61</v>
+        <v>174.3</v>
       </c>
       <c r="R2" t="n">
-        <v>56.52</v>
+        <v>197.47</v>
       </c>
       <c r="S2" t="n">
-        <v>81.66</v>
+        <v>232.68</v>
       </c>
       <c r="T2" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>1</v>
+        <v>170.88</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>640108</v>
+        <v>270104</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -748,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>27.8</v>
+        <v>20.4</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,28 +777,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115.9</v>
+        <v>30.9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2.66</v>
+        <v>-0.96</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-5.5</v>
+        <v>-8.23</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-7.03</v>
+        <v>-18.83</v>
       </c>
       <c r="H3" t="n">
-        <v>0.99</v>
+        <v>3.94</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -811,55 +811,55 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-5.69</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>37.9</v>
+        <v>42.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O3" s="3" t="n">
-        <v>1.04</v>
+      <c r="O3" s="2" t="n">
+        <v>-0.75</v>
       </c>
       <c r="P3" t="n">
-        <v>11.63</v>
+        <v>9.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>102.42</v>
+        <v>27.92</v>
       </c>
       <c r="R3" t="n">
-        <v>122.2</v>
+        <v>32.76</v>
       </c>
       <c r="S3" t="n">
-        <v>142.99</v>
+        <v>40.38</v>
       </c>
       <c r="T3" t="n">
-        <v>94.73</v>
+        <v>30.34</v>
       </c>
       <c r="U3" t="n">
         <v>2</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270202</v>
+        <v>630702</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>24.1</v>
+        <v>18.5</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,32 +897,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>139.75</v>
+        <v>115</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-18.38</v>
+        <v>-0.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-26.66</v>
+        <v>-7.93</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-40.96</v>
+        <v>-16.14</v>
       </c>
       <c r="H4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.07</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-21.73</v>
+        <v>-5.51</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,37 +939,37 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>34</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-20.12</v>
+        <v>-0.45</v>
       </c>
       <c r="P4" t="n">
-        <v>15.05</v>
+        <v>11.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>118.72</v>
+        <v>101.69</v>
       </c>
       <c r="R4" t="n">
-        <v>178.55</v>
+        <v>121.71</v>
       </c>
       <c r="S4" t="n">
-        <v>280.08</v>
+        <v>142.99</v>
       </c>
       <c r="T4" t="n">
-        <v>130.14</v>
+        <v>94.73</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>246.7</v>
+        <v>47.51</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-3.63</v>
+        <v>-12.73</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-7.43</v>
+        <v>-13.84</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-4.68</v>
+        <v>-39.65</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.38</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-5.04</v>
+        <v>-15.37</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -1059,47 +1059,47 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>26.5</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-0.89</v>
+        <v>-6.36</v>
       </c>
       <c r="P5" t="n">
-        <v>13.71</v>
+        <v>16.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>212.87</v>
+        <v>39.71</v>
       </c>
       <c r="R5" t="n">
-        <v>259.8</v>
+        <v>56.14</v>
       </c>
       <c r="S5" t="n">
-        <v>294.5</v>
+        <v>81.66</v>
       </c>
       <c r="T5" t="n">
-        <v>155.05</v>
+        <v>43.01</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>730204</v>
+        <v>640108</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>20.4</v>
+        <v>14.8</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>201.23</v>
+        <v>69.03</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-6.92</v>
+        <v>-13.19</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-2.36</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>5.52</v>
+        <v>-16.37</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>-32.26</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.2</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-3.2</v>
+        <v>-13.88</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,47 +1179,47 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>4.18</v>
+        <v>13.8</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>-8.890000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>15.92</v>
+        <v>6.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>169.2</v>
+        <v>64.39</v>
       </c>
       <c r="R6" t="n">
-        <v>207.89</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>242.99</v>
+        <v>105.43</v>
       </c>
       <c r="T6" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
+        <v>69</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>730204</v>
+        <v>710101</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>20.4</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,28 +1257,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>186.11</v>
+        <v>192.8</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-7.45</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-10.14</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0.48</v>
+        <v>-4.34</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>-5.43</v>
       </c>
       <c r="H7" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-11.97</v>
+        <v>-7.06</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1299,47 +1299,47 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>34.7</v>
+        <v>44.6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>-3.6</v>
+      <c r="O7" s="3" t="n">
+        <v>3.14</v>
       </c>
       <c r="P7" t="n">
-        <v>14.84</v>
+        <v>16.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>158.49</v>
+        <v>161.46</v>
       </c>
       <c r="R7" t="n">
-        <v>211.41</v>
+        <v>207.45</v>
       </c>
       <c r="S7" t="n">
-        <v>237.87</v>
+        <v>242.99</v>
       </c>
       <c r="T7" t="n">
-        <v>125.61</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>1</v>
+        <v>102.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>730206</v>
+        <v>730204</v>
       </c>
       <c r="Z7" t="n">
         <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>20.4</v>
+        <v>11.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,28 +1377,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>145.86</v>
+        <v>225.5</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-12.61</v>
+        <v>-11.56</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-20.93</v>
+        <v>-23.99</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-32.47</v>
+        <v>-57.02</v>
       </c>
       <c r="H8" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-15.93</v>
+        <v>-16.53</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1419,47 +1419,47 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>38</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>19.3</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-14.39</v>
+        <v>-16.51</v>
       </c>
       <c r="P8" t="n">
-        <v>14.57</v>
+        <v>11.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>124.61</v>
+        <v>200.13</v>
       </c>
       <c r="R8" t="n">
-        <v>173.5</v>
+        <v>270.16</v>
       </c>
       <c r="S8" t="n">
-        <v>235.11</v>
+        <v>472.07</v>
       </c>
       <c r="T8" t="n">
-        <v>132.7</v>
+        <v>218.03</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>730204</v>
+        <v>270104</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>20.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>128.65</v>
+        <v>229</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-19.69</v>
+        <v>-12.18</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-27.25</v>
+        <v>-11.24</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-40.64</v>
+        <v>-16.12</v>
       </c>
       <c r="H9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.95</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-20.79</v>
+        <v>-11.36</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -1539,47 +1539,47 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>30</v>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>35.7</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>-20.71</v>
+        <v>-3.76</v>
       </c>
       <c r="P9" t="n">
-        <v>14.58</v>
+        <v>14.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>109.89</v>
+        <v>194.93</v>
       </c>
       <c r="R9" t="n">
-        <v>162.43</v>
+        <v>258.35</v>
       </c>
       <c r="S9" t="n">
-        <v>242.81</v>
+        <v>294.5</v>
       </c>
       <c r="T9" t="n">
-        <v>120.66</v>
+        <v>155.05</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>270401</v>
+        <v>730204</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>20.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,28 +1617,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21.04</v>
+        <v>141.09</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-10.51</v>
+        <v>-14.43</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-18.1</v>
+        <v>-21.58</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-28.82</v>
+        <v>-39.43</v>
       </c>
       <c r="H10" t="n">
-        <v>2.05</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-13.43</v>
+        <v>-17.76</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1659,47 +1659,47 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>23.1</v>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>-11.56</v>
+        <v>-14.1</v>
       </c>
       <c r="P10" t="n">
-        <v>11.2</v>
+        <v>14.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>18.68</v>
+        <v>120.94</v>
       </c>
       <c r="R10" t="n">
-        <v>24.3</v>
+        <v>171.55</v>
       </c>
       <c r="S10" t="n">
-        <v>31.89</v>
+        <v>233.62</v>
       </c>
       <c r="T10" t="n">
-        <v>20.42</v>
+        <v>132.7</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270303</v>
+        <v>730204</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>18.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1746,19 +1746,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>351.3</v>
+        <v>330.8</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-10.59</v>
+        <v>-14.96</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-15.8</v>
+        <v>-20.56</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-31.45</v>
+        <v>-41.84</v>
       </c>
       <c r="H11" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-14.15</v>
+        <v>-18.31</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1779,24 +1779,24 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>22.1</v>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>-9.26</v>
+        <v>-13.08</v>
       </c>
       <c r="P11" t="n">
-        <v>14.01</v>
+        <v>14.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>302.08</v>
+        <v>283.44</v>
       </c>
       <c r="R11" t="n">
-        <v>409.21</v>
+        <v>404.93</v>
       </c>
       <c r="S11" t="n">
         <v>579.42</v>
@@ -1805,11 +1805,11 @@
         <v>329.12</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W11" t="n">
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>18.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,28 +1857,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>233.78</v>
+        <v>131.41</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-11.71</v>
+        <v>-21.5</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-18.68</v>
+        <v>-29.51</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-54.45</v>
+        <v>-49.53</v>
       </c>
       <c r="H12" t="n">
-        <v>0.88</v>
+        <v>1.24</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-14.59</v>
+        <v>-25.25</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>29.6</v>
+        <v>15.8</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>-12.14</v>
+        <v>-22.03</v>
       </c>
       <c r="P12" t="n">
-        <v>11.09</v>
+        <v>15.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>207.85</v>
+        <v>110.91</v>
       </c>
       <c r="R12" t="n">
-        <v>273.72</v>
+        <v>175.8</v>
       </c>
       <c r="S12" t="n">
-        <v>527.5</v>
+        <v>280.08</v>
       </c>
       <c r="T12" t="n">
-        <v>218.03</v>
+        <v>130.14</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>270104</v>
+        <v>270202</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>18.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1986,19 +1986,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>79.91</v>
+        <v>78.08</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-3.5</v>
+        <v>-5.35</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-9.31</v>
+        <v>-10.47</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-25.57</v>
+        <v>-27.47</v>
       </c>
       <c r="H13" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>-5.1</v>
+        <v>-6.76</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>41.1</v>
+        <v>35.7</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -2027,16 +2027,16 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-2.77</v>
+        <v>-2.99</v>
       </c>
       <c r="P13" t="n">
-        <v>7.4</v>
+        <v>7.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>74</v>
+        <v>72.16</v>
       </c>
       <c r="R13" t="n">
-        <v>84.2</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>121.57</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W13" t="n">
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="2" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2106,19 +2106,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60.16</v>
+        <v>58.65</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-8.43</v>
+        <v>-8.76</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-12.75</v>
+        <v>-14.44</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-39.23</v>
+        <v>-42.86</v>
       </c>
       <c r="H14" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-10.34</v>
+        <v>-11.94</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -2139,24 +2139,24 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>36</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>25.9</v>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>-6.21</v>
+        <v>-6.96</v>
       </c>
       <c r="P14" t="n">
-        <v>10.45</v>
+        <v>10.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>53.87</v>
+        <v>52.45</v>
       </c>
       <c r="R14" t="n">
-        <v>67.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>105</v>
@@ -2165,11 +2165,11 @@
         <v>57.4</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W14" t="n">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="AD14" s="2" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,28 +2217,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>32.01</v>
+        <v>51.73</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-10.51</v>
+        <v>-9.09</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-24.18</v>
+        <v>-11.3</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-20.71</v>
+        <v>-33.57</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>-12.95</v>
+        <v>-11.01</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2259,47 +2259,47 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>33.3</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>-17.64</v>
+        <v>-3.82</v>
       </c>
       <c r="P15" t="n">
-        <v>11.43</v>
+        <v>11.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.35</v>
+        <v>46.02</v>
       </c>
       <c r="R15" t="n">
-        <v>36.77</v>
+        <v>58.13</v>
       </c>
       <c r="S15" t="n">
-        <v>46.74</v>
+        <v>84.7</v>
       </c>
       <c r="T15" t="n">
-        <v>30.05</v>
+        <v>51.2</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270504</v>
+        <v>270107</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="2" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>54.37</v>
+        <v>31.39</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-12.52</v>
+        <v>-10.01</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-20.38</v>
+        <v>-21.01</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-23.52</v>
+        <v>-26.49</v>
       </c>
       <c r="H16" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.64</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-15.17</v>
+        <v>-13.66</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -2379,47 +2379,47 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>16.3</v>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>-13.84</v>
+        <v>-13.53</v>
       </c>
       <c r="P16" t="n">
-        <v>13.49</v>
+        <v>11.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.03</v>
+        <v>27.9</v>
       </c>
       <c r="R16" t="n">
-        <v>64.09</v>
+        <v>36.36</v>
       </c>
       <c r="S16" t="n">
-        <v>74.34999999999999</v>
+        <v>46.74</v>
       </c>
       <c r="T16" t="n">
-        <v>47.3</v>
+        <v>30.05</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>270303</v>
+        <v>270504</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="AD16" s="2" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,32 +2457,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>70.92</v>
+        <v>181.7</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-13.26</v>
+        <v>-11.56</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-24.37</v>
+        <v>-18.26</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-39.52</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.89</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-19.66</v>
+        <v>-13.22</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>19.9</v>
+        <v>28.3</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
@@ -2507,39 +2507,39 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>-17.83</v>
+        <v>-10.78</v>
       </c>
       <c r="P17" t="n">
-        <v>13.81</v>
+        <v>14.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>61.13</v>
+        <v>154.79</v>
       </c>
       <c r="R17" t="n">
-        <v>88.27</v>
+        <v>209.38</v>
       </c>
       <c r="S17" t="n">
-        <v>122.2</v>
+        <v>237.87</v>
       </c>
       <c r="T17" t="n">
-        <v>66.3</v>
+        <v>125.61</v>
       </c>
       <c r="U17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>640703</v>
+        <v>730206</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="2" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,32 +2577,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45.65</v>
+        <v>27.41</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-13.61</v>
+        <v>-12.73</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-26.31</v>
+        <v>-19.29</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-41.74</v>
+        <v>-22.79</v>
       </c>
       <c r="H18" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.47</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-18.31</v>
+        <v>-19.74</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>20.3</v>
+        <v>5.9</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
@@ -2627,39 +2627,39 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>-19.77</v>
+        <v>-11.81</v>
       </c>
       <c r="P18" t="n">
-        <v>13.57</v>
+        <v>13.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>39.46</v>
+        <v>23.64</v>
       </c>
       <c r="R18" t="n">
-        <v>55.88</v>
+        <v>34.15</v>
       </c>
       <c r="S18" t="n">
-        <v>93.68000000000001</v>
+        <v>39.58</v>
       </c>
       <c r="T18" t="n">
-        <v>42.12</v>
+        <v>23.2</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270203</v>
+        <v>640209</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="2" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>72.8</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-9.449999999999999</v>
+        <v>-13.12</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-12.69</v>
+        <v>-20.27</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-31.4</v>
+        <v>-49.86</v>
       </c>
       <c r="H19" t="n">
-        <v>1.02</v>
+        <v>0.68</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>-9.93</v>
+        <v>-18.31</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>23.1</v>
+        <v>16.6</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -2747,39 +2747,39 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>-6.15</v>
+        <v>-12.79</v>
       </c>
       <c r="P19" t="n">
-        <v>5.97</v>
+        <v>11.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>68.45</v>
+        <v>71.14</v>
       </c>
       <c r="R19" t="n">
-        <v>80.83</v>
+        <v>98.11</v>
       </c>
       <c r="S19" t="n">
-        <v>108.39</v>
+        <v>154.36</v>
       </c>
       <c r="T19" t="n">
-        <v>70.26000000000001</v>
+        <v>79</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>710101</v>
+        <v>640703</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="2" t="n">
-        <v>13</v>
+        <v>5.6</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>5.53</v>
+        <v>52.19</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>-13.93</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-3.53</v>
+        <v>-21.51</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-11.57</v>
+        <v>-28.62</v>
       </c>
       <c r="H20" t="n">
-        <v>3.62</v>
+        <v>0.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2851,64 +2851,64 @@
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-17.65</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>50</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>3.01</v>
+        <v>17.2</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>-14.03</v>
       </c>
       <c r="P20" t="n">
-        <v>8.550000000000001</v>
+        <v>12.93</v>
       </c>
       <c r="Q20" t="n">
-        <v>30</v>
+        <v>45.44</v>
       </c>
       <c r="R20" t="n">
-        <v>32.9</v>
+        <v>63.38</v>
       </c>
       <c r="S20" t="n">
-        <v>40.38</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="U20" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>270303</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>3</v>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="W20" t="n">
-        <v>630702</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>9</v>
-      </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="2" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>换手率处于近60日95分位以上(极端活跃)</t>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -2937,32 +2937,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>196.58</v>
+        <v>44.11</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-7.68</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>2.02</v>
+        <v>-14.05</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-25.99</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-9.74</v>
+        <v>-48.82</v>
       </c>
       <c r="H21" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.83</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2971,52 +2971,52 @@
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-0.28</v>
+        <v>-19.95</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>8.56</v>
+        <v>14</v>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>-18.51</v>
       </c>
       <c r="P21" t="n">
-        <v>10.57</v>
+        <v>13.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>175.79</v>
+        <v>37.96</v>
       </c>
       <c r="R21" t="n">
-        <v>197.12</v>
+        <v>55.11</v>
       </c>
       <c r="S21" t="n">
-        <v>232.68</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>170.88</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
+        <v>42.12</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270104</v>
+        <v>270203</v>
       </c>
       <c r="Z21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>3</v>
@@ -3028,11 +3028,11 @@
         <v>0</v>
       </c>
       <c r="AD21" s="2" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3057,32 +3057,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>28.5</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-14.87</v>
+        <v>-15.08</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-20.63</v>
+        <v>-29</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-18.06</v>
+        <v>-43.13</v>
       </c>
       <c r="H22" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.93</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-17.34</v>
+        <v>-21.78</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
@@ -3107,39 +3107,39 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>-14.09</v>
+        <v>-21.52</v>
       </c>
       <c r="P22" t="n">
-        <v>13.51</v>
+        <v>14.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>24.65</v>
+        <v>58.18</v>
       </c>
       <c r="R22" t="n">
-        <v>34.48</v>
+        <v>86.88</v>
       </c>
       <c r="S22" t="n">
-        <v>39.58</v>
+        <v>122.2</v>
       </c>
       <c r="T22" t="n">
-        <v>23.2</v>
+        <v>66.3</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>640209</v>
+        <v>640703</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>46.15</v>
+        <v>121.91</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-8.43</v>
+        <v>-20.45</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-17.49</v>
+        <v>-32.14</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-21.57</v>
+        <v>-47.18</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-11.09</v>
+        <v>-23.59</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -3219,47 +3219,47 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>24</v>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>-10.95</v>
+        <v>-24.66</v>
       </c>
       <c r="P23" t="n">
-        <v>8.02</v>
+        <v>15.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>42.45</v>
+        <v>103.22</v>
       </c>
       <c r="R23" t="n">
-        <v>51.91</v>
+        <v>159.54</v>
       </c>
       <c r="S23" t="n">
-        <v>64.2</v>
+        <v>242.81</v>
       </c>
       <c r="T23" t="n">
-        <v>44.7</v>
+        <v>120.66</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270504</v>
+        <v>270401</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="AD23" s="2" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53.82</v>
+        <v>44.94</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-10.83</v>
+        <v>-9.08</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-9.01</v>
+        <v>-18.38</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-26.85</v>
+        <v>-26.96</v>
       </c>
       <c r="H24" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-7.94</v>
+        <v>-12.57</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
@@ -3339,47 +3339,47 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>22.3</v>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>-2.47</v>
+        <v>-10.9</v>
       </c>
       <c r="P24" t="n">
-        <v>10.72</v>
+        <v>8.19</v>
       </c>
       <c r="Q24" t="n">
-        <v>48.05</v>
+        <v>41.26</v>
       </c>
       <c r="R24" t="n">
-        <v>58.46</v>
+        <v>51.4</v>
       </c>
       <c r="S24" t="n">
-        <v>84.7</v>
+        <v>64.2</v>
       </c>
       <c r="T24" t="n">
-        <v>51.2</v>
+        <v>44.7</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>270107</v>
+        <v>270504</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>271.2</v>
+        <v>47.26</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-12.98</v>
+        <v>-12.4</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-24.29</v>
+        <v>-24.98</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-48.05</v>
+        <v>-32.61</v>
       </c>
       <c r="H25" t="n">
-        <v>0.98</v>
+        <v>0.57</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-16.41</v>
+        <v>-17.45</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>22.6</v>
+        <v>13.9</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
@@ -3467,39 +3467,39 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>-17.75</v>
+        <v>-17.5</v>
       </c>
       <c r="P25" t="n">
-        <v>9.869999999999999</v>
+        <v>10.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>244.44</v>
+        <v>42.13</v>
       </c>
       <c r="R25" t="n">
-        <v>324.45</v>
+        <v>57.25</v>
       </c>
       <c r="S25" t="n">
-        <v>557</v>
+        <v>70.89</v>
       </c>
       <c r="T25" t="n">
-        <v>258</v>
+        <v>45.82</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>270104</v>
+        <v>640209</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,28 +3537,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>199.31</v>
+        <v>259.97</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-13.47</v>
+        <v>-13.9</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-16.69</v>
+        <v>-27.56</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-37.39</v>
+        <v>-51.72</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-14.75</v>
+        <v>-18.63</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>24.4</v>
+        <v>12.5</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
@@ -3587,39 +3587,39 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>-10.15</v>
+        <v>-20.08</v>
       </c>
       <c r="P26" t="n">
-        <v>11.77</v>
+        <v>10.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>175.85</v>
+        <v>233.26</v>
       </c>
       <c r="R26" t="n">
-        <v>233.8</v>
+        <v>319.5</v>
       </c>
       <c r="S26" t="n">
-        <v>324.99</v>
+        <v>557</v>
       </c>
       <c r="T26" t="n">
-        <v>183.83</v>
+        <v>258</v>
       </c>
       <c r="U26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270103</v>
+        <v>270104</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,28 +3657,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>83.61</v>
+        <v>190.21</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-11.29</v>
+        <v>-14.62</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-17.96</v>
+        <v>-18.96</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-45.79</v>
+        <v>-38.92</v>
       </c>
       <c r="H27" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>-15.66</v>
+        <v>-17.86</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>29.7</v>
+        <v>15</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -3707,33 +3707,33 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>-11.42</v>
+        <v>-11.48</v>
       </c>
       <c r="P27" t="n">
-        <v>11.4</v>
+        <v>12.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>74.08</v>
+        <v>166.91</v>
       </c>
       <c r="R27" t="n">
-        <v>99.13</v>
+        <v>231.58</v>
       </c>
       <c r="S27" t="n">
-        <v>160</v>
+        <v>316.98</v>
       </c>
       <c r="T27" t="n">
-        <v>79</v>
+        <v>183.83</v>
       </c>
       <c r="U27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>640703</v>
+        <v>270103</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3777,28 +3777,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>48.95</v>
+        <v>20.46</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-11.93</v>
+        <v>-16.15</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-24.07</v>
+        <v>-18.87</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-26.92</v>
+        <v>-34.34</v>
       </c>
       <c r="H28" t="n">
-        <v>0.55</v>
+        <v>1.49</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-15.65</v>
+        <v>-14.99</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -3827,33 +3827,33 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>-17.53</v>
+        <v>-11.39</v>
       </c>
       <c r="P28" t="n">
-        <v>10.8</v>
+        <v>11.29</v>
       </c>
       <c r="Q28" t="n">
-        <v>43.66</v>
+        <v>18.15</v>
       </c>
       <c r="R28" t="n">
-        <v>58.04</v>
+        <v>24.07</v>
       </c>
       <c r="S28" t="n">
-        <v>71.59</v>
+        <v>31.89</v>
       </c>
       <c r="T28" t="n">
-        <v>45.82</v>
+        <v>20.42</v>
       </c>
       <c r="U28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>640209</v>
+        <v>270303</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3906,19 +3906,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>80.06</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-13.64</v>
+        <v>-17.14</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-14.08</v>
+        <v>-17.31</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-18.51</v>
+        <v>-22.88</v>
       </c>
       <c r="H29" t="n">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>-14.03</v>
+        <v>-14.79</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -3939,24 +3939,24 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>28.1</v>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>-7.54</v>
+        <v>-9.83</v>
       </c>
       <c r="P29" t="n">
-        <v>14.96</v>
+        <v>15.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>68.08</v>
+        <v>66.83</v>
       </c>
       <c r="R29" t="n">
-        <v>93.13</v>
+        <v>92.31</v>
       </c>
       <c r="S29" t="n">
         <v>104.39</v>
@@ -3965,11 +3965,11 @@
         <v>69.63</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="W29" t="n">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>195.5</v>
+        <v>190</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-9.31</v>
+        <v>-4.79</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3.66</v>
+        <v>1.41</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-9.369999999999999</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1</v>
+        <v>-3.85</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>58.9</v>
+        <v>54.9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>11.14</v>
+        <v>10.3</v>
       </c>
       <c r="P2" t="n">
-        <v>10.84</v>
+        <v>11.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>174.3</v>
+        <v>168.15</v>
       </c>
       <c r="R2" t="n">
-        <v>197.47</v>
+        <v>197.6</v>
       </c>
       <c r="S2" t="n">
         <v>232.68</v>
@@ -729,7 +729,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -739,7 +739,7 @@
         <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>20.4</v>
+        <v>25.9</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,28 +777,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>-0.96</v>
+        <v>116.18</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.26</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-8.23</v>
+        <v>-8.91</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-18.83</v>
+        <v>-15.34</v>
       </c>
       <c r="H3" t="n">
-        <v>3.94</v>
+        <v>1.18</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -811,15 +811,15 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-5.69</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-4.1</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>42.1</v>
+        <v>40.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -827,39 +827,39 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-0.75</v>
+        <v>-0.02</v>
       </c>
       <c r="P3" t="n">
-        <v>9.65</v>
+        <v>11.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>27.92</v>
+        <v>102.91</v>
       </c>
       <c r="R3" t="n">
-        <v>32.76</v>
+        <v>121.14</v>
       </c>
       <c r="S3" t="n">
-        <v>40.38</v>
+        <v>142.99</v>
       </c>
       <c r="T3" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2</v>
+        <v>94.73</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>630702</v>
+        <v>270202</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>18.5</v>
+        <v>22.2</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,32 +897,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>115</v>
+        <v>47.51</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.8</v>
+        <v>-4.64</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-7.93</v>
+        <v>-12.75</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-16.14</v>
+        <v>-35.25</v>
       </c>
       <c r="H4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.5</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-5.51</v>
+        <v>-14.85</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,47 +939,47 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>34</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>24.7</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-0.45</v>
+        <v>-3.86</v>
       </c>
       <c r="P4" t="n">
-        <v>11.57</v>
+        <v>16.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>101.69</v>
+        <v>39.55</v>
       </c>
       <c r="R4" t="n">
-        <v>121.71</v>
+        <v>55.79</v>
       </c>
       <c r="S4" t="n">
-        <v>142.99</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>94.73</v>
+        <v>43.01</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270202</v>
+        <v>640108</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>14.8</v>
+        <v>18.5</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>47.51</v>
+        <v>29.46</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-12.73</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-13.84</v>
+        <v>-12.48</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-39.65</v>
+        <v>-21.34</v>
       </c>
       <c r="H5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>3.69</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1051,55 +1051,55 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-15.37</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-9.51</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>38.7</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-6.36</v>
+        <v>-3.59</v>
       </c>
       <c r="P5" t="n">
-        <v>16.43</v>
+        <v>10.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.71</v>
+        <v>26.27</v>
       </c>
       <c r="R5" t="n">
-        <v>56.14</v>
+        <v>32.55</v>
       </c>
       <c r="S5" t="n">
-        <v>81.66</v>
+        <v>40.38</v>
       </c>
       <c r="T5" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
+        <v>28.85</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>640108</v>
+        <v>630702</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>14.8</v>
+        <v>18.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,28 +1137,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69.03</v>
+        <v>211.05</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-13.19</v>
+        <v>-13.09</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-16.37</v>
+        <v>-27.61</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-32.26</v>
+        <v>-55.29</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-13.88</v>
+        <v>-20.7</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>13.8</v>
+        <v>17.3</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -1187,39 +1187,39 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-8.890000000000001</v>
+        <v>-18.72</v>
       </c>
       <c r="P6" t="n">
-        <v>6.73</v>
+        <v>12.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>64.39</v>
+        <v>184.75</v>
       </c>
       <c r="R6" t="n">
-        <v>80.15000000000001</v>
+        <v>266.14</v>
       </c>
       <c r="S6" t="n">
-        <v>105.43</v>
+        <v>424.76</v>
       </c>
       <c r="T6" t="n">
-        <v>69</v>
+        <v>208.61</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>710101</v>
+        <v>270104</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>192.8</v>
+        <v>306.01</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-9.210000000000001</v>
+        <v>-19.15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4.34</v>
+        <v>-26.23</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-5.43</v>
+        <v>-44.96</v>
       </c>
       <c r="H7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.24</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-7.06</v>
+        <v>-23.4</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1299,47 +1299,47 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>3.14</v>
+        <v>18.9</v>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>-17.34</v>
       </c>
       <c r="P7" t="n">
-        <v>16.25</v>
+        <v>16.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>161.46</v>
+        <v>256.69</v>
       </c>
       <c r="R7" t="n">
-        <v>207.45</v>
+        <v>399.49</v>
       </c>
       <c r="S7" t="n">
-        <v>242.99</v>
+        <v>558</v>
       </c>
       <c r="T7" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
+        <v>299.23</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>730204</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1348,16 +1348,16 @@
         <v>0</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,28 +1377,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>225.5</v>
+        <v>57.5</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-11.56</v>
+        <v>-8.15</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-23.99</v>
+        <v>-16.17</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-57.02</v>
+        <v>-37.78</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-16.53</v>
+        <v>-12.94</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>19.3</v>
+        <v>26.7</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
@@ -1427,39 +1427,39 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-16.51</v>
+        <v>-7.28</v>
       </c>
       <c r="P8" t="n">
-        <v>11.25</v>
+        <v>10.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>200.13</v>
+        <v>51.25</v>
       </c>
       <c r="R8" t="n">
-        <v>270.16</v>
+        <v>66.05</v>
       </c>
       <c r="S8" t="n">
-        <v>472.07</v>
+        <v>90.36</v>
       </c>
       <c r="T8" t="n">
-        <v>218.03</v>
+        <v>55.64</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270104</v>
+        <v>270107</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>229</v>
+        <v>124.2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-12.18</v>
+        <v>-17.56</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-11.24</v>
+        <v>-36.65</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-16.12</v>
+        <v>-52.68</v>
       </c>
       <c r="H9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.28</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-11.36</v>
+        <v>-27.88</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -1539,47 +1539,47 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>13.3</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>-3.76</v>
+        <v>-27.76</v>
       </c>
       <c r="P9" t="n">
-        <v>14.88</v>
+        <v>16.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>194.93</v>
+        <v>103.77</v>
       </c>
       <c r="R9" t="n">
-        <v>258.35</v>
+        <v>172.21</v>
       </c>
       <c r="S9" t="n">
-        <v>294.5</v>
+        <v>276</v>
       </c>
       <c r="T9" t="n">
-        <v>155.05</v>
+        <v>122.53</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>730204</v>
+        <v>270202</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,28 +1617,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>141.09</v>
+        <v>179.94</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-14.43</v>
+        <v>-14.16</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-21.58</v>
+        <v>-22.11</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-39.43</v>
+        <v>-36.22</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-17.76</v>
+        <v>-21.43</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>23.1</v>
+        <v>13.9</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
@@ -1667,39 +1667,39 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>-14.1</v>
+        <v>-13.22</v>
       </c>
       <c r="P10" t="n">
-        <v>14.28</v>
+        <v>13.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>120.94</v>
+        <v>155.84</v>
       </c>
       <c r="R10" t="n">
-        <v>171.55</v>
+        <v>229.03</v>
       </c>
       <c r="S10" t="n">
-        <v>233.62</v>
+        <v>279.78</v>
       </c>
       <c r="T10" t="n">
-        <v>132.7</v>
+        <v>175.88</v>
       </c>
       <c r="U10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>730204</v>
+        <v>270103</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>330.8</v>
+        <v>244</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-14.96</v>
+        <v>-15.45</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-20.56</v>
+        <v>-29.89</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-41.84</v>
+        <v>-50</v>
       </c>
       <c r="H11" t="n">
-        <v>1.13</v>
+        <v>0.98</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-18.31</v>
+        <v>-22.37</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>22.1</v>
+        <v>11.2</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -1787,39 +1787,39 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>-13.08</v>
+        <v>-21</v>
       </c>
       <c r="P11" t="n">
-        <v>14.32</v>
+        <v>11.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>283.44</v>
+        <v>215.82</v>
       </c>
       <c r="R11" t="n">
-        <v>404.93</v>
+        <v>314.3</v>
       </c>
       <c r="S11" t="n">
-        <v>579.42</v>
+        <v>493</v>
       </c>
       <c r="T11" t="n">
-        <v>329.12</v>
+        <v>241.42</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>730204</v>
+        <v>270104</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,28 +1857,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>131.41</v>
+        <v>63.37</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-21.5</v>
+        <v>-18.87</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-29.51</v>
+        <v>-33.19</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-49.53</v>
+        <v>-44.59</v>
       </c>
       <c r="H12" t="n">
-        <v>1.24</v>
+        <v>0.97</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-25.25</v>
+        <v>-25.72</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>15.8</v>
+        <v>13</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
@@ -1907,39 +1907,39 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>-22.03</v>
+        <v>-24.3</v>
       </c>
       <c r="P12" t="n">
-        <v>15.6</v>
+        <v>15.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>110.91</v>
+        <v>53.4</v>
       </c>
       <c r="R12" t="n">
-        <v>175.8</v>
+        <v>85.31</v>
       </c>
       <c r="S12" t="n">
-        <v>280.08</v>
+        <v>115.13</v>
       </c>
       <c r="T12" t="n">
-        <v>130.14</v>
+        <v>62.66</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>270202</v>
+        <v>640703</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,28 +1977,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>78.08</v>
+        <v>112.6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-5.35</v>
+        <v>-22.33</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-10.47</v>
+        <v>-35.48</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-27.47</v>
+        <v>-49.08</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -2011,55 +2011,55 @@
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>-6.76</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-28.02</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>22.1</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-2.99</v>
+        <v>-26.59</v>
       </c>
       <c r="P13" t="n">
-        <v>7.58</v>
+        <v>17.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>72.16</v>
+        <v>93.33</v>
       </c>
       <c r="R13" t="n">
-        <v>83.73999999999999</v>
+        <v>156.44</v>
       </c>
       <c r="S13" t="n">
-        <v>121.57</v>
+        <v>216.99</v>
       </c>
       <c r="T13" t="n">
-        <v>78</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
+        <v>111.55</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>630503</v>
+        <v>270401</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="2" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58.65</v>
+        <v>223.33</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-8.76</v>
+        <v>-4.99</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-14.44</v>
+        <v>-13.28</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-42.86</v>
+        <v>-13.74</v>
       </c>
       <c r="H14" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.89</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>-11.94</v>
+        <v>-12.98</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>25.9</v>
+        <v>29.8</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
@@ -2147,39 +2147,39 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>-6.96</v>
+        <v>-4.39</v>
       </c>
       <c r="P14" t="n">
-        <v>10.57</v>
+        <v>15.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>52.45</v>
+        <v>189.6</v>
       </c>
       <c r="R14" t="n">
-        <v>66.59999999999999</v>
+        <v>256.64</v>
       </c>
       <c r="S14" t="n">
-        <v>105</v>
+        <v>294.5</v>
       </c>
       <c r="T14" t="n">
-        <v>57.4</v>
+        <v>155.05</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>270107</v>
+        <v>730204</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="AD14" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,32 +2217,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>51.73</v>
+        <v>188.46</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-9.09</v>
+        <v>-5.3</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-11.3</v>
+        <v>-6.49</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-33.57</v>
+        <v>-4.25</v>
       </c>
       <c r="H15" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>-11.01</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2259,47 +2259,47 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>33.3</v>
+        <v>38.7</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O15" s="2" t="n">
-        <v>-3.82</v>
+      <c r="O15" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="P15" t="n">
-        <v>11.04</v>
+        <v>16.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>46.02</v>
+        <v>156.56</v>
       </c>
       <c r="R15" t="n">
-        <v>58.13</v>
+        <v>206.8</v>
       </c>
       <c r="S15" t="n">
-        <v>84.7</v>
+        <v>242.99</v>
       </c>
       <c r="T15" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>1</v>
+        <v>102.3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270107</v>
+        <v>730204</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,28 +2337,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31.39</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-10.01</v>
+        <v>-5.45</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-21.01</v>
+        <v>-11.88</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-26.49</v>
+        <v>-29.74</v>
       </c>
       <c r="H16" t="n">
-        <v>0.64</v>
+        <v>1.06</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -2371,55 +2371,55 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-13.66</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-8.57</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>33.5</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>-13.53</v>
+        <v>-2.99</v>
       </c>
       <c r="P16" t="n">
-        <v>11.1</v>
+        <v>7.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>27.9</v>
+        <v>70.03</v>
       </c>
       <c r="R16" t="n">
-        <v>36.36</v>
+        <v>83.23</v>
       </c>
       <c r="S16" t="n">
-        <v>46.74</v>
+        <v>121.57</v>
       </c>
       <c r="T16" t="n">
-        <v>30.05</v>
-      </c>
-      <c r="U16" s="2" t="n">
-        <v>0</v>
+        <v>75.12</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>270504</v>
+        <v>630503</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="AD16" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,32 +2457,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>181.7</v>
+        <v>44.65</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-11.56</v>
+        <v>-7.81</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-18.26</v>
+        <v>-20.07</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-9.210000000000001</v>
+        <v>-25.99</v>
       </c>
       <c r="H17" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.07</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-13.22</v>
+        <v>-12.18</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>28.3</v>
+        <v>23</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
@@ -2507,39 +2507,39 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>-10.78</v>
+        <v>-11.18</v>
       </c>
       <c r="P17" t="n">
-        <v>14.81</v>
+        <v>8.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>154.79</v>
+        <v>40.92</v>
       </c>
       <c r="R17" t="n">
-        <v>209.38</v>
+        <v>50.84</v>
       </c>
       <c r="S17" t="n">
-        <v>237.87</v>
+        <v>64.2</v>
       </c>
       <c r="T17" t="n">
-        <v>125.61</v>
+        <v>43.56</v>
       </c>
       <c r="U17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>730206</v>
+        <v>270504</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,32 +2577,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27.41</v>
+        <v>49.75</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-12.73</v>
+        <v>-11.05</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-19.29</v>
+        <v>-14.74</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-22.79</v>
+        <v>-36.79</v>
       </c>
       <c r="H18" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.77</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-19.74</v>
+        <v>-13.78</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -2619,47 +2619,47 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>31.8</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>-11.81</v>
+        <v>-5.85</v>
       </c>
       <c r="P18" t="n">
-        <v>13.74</v>
+        <v>11.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>23.64</v>
+        <v>43.83</v>
       </c>
       <c r="R18" t="n">
-        <v>34.15</v>
+        <v>57.7</v>
       </c>
       <c r="S18" t="n">
-        <v>39.58</v>
+        <v>80.8</v>
       </c>
       <c r="T18" t="n">
-        <v>23.2</v>
+        <v>48.91</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>640209</v>
+        <v>270107</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>80.15000000000001</v>
+        <v>29.8</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-13.12</v>
+        <v>-11.15</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-20.27</v>
+        <v>-24.94</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-49.86</v>
+        <v>-26.56</v>
       </c>
       <c r="H19" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>-18.31</v>
+        <v>-16.9</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>16.6</v>
+        <v>14.6</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -2747,39 +2747,39 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>-12.79</v>
+        <v>-16.05</v>
       </c>
       <c r="P19" t="n">
-        <v>11.25</v>
+        <v>11.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>71.14</v>
+        <v>26.28</v>
       </c>
       <c r="R19" t="n">
-        <v>98.11</v>
+        <v>35.86</v>
       </c>
       <c r="S19" t="n">
-        <v>154.36</v>
+        <v>46.74</v>
       </c>
       <c r="T19" t="n">
-        <v>79</v>
+        <v>29.58</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>640703</v>
+        <v>270504</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,32 +2817,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>52.19</v>
+        <v>76.27</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-13.93</v>
+        <v>-12.32</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-21.51</v>
+        <v>-29.89</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-28.62</v>
+        <v>-47.48</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.64</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-17.65</v>
+        <v>-20.95</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>17.2</v>
+        <v>15.1</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -2867,39 +2867,39 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>-14.03</v>
+        <v>-21</v>
       </c>
       <c r="P20" t="n">
-        <v>12.93</v>
+        <v>12.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>45.44</v>
+        <v>67.06</v>
       </c>
       <c r="R20" t="n">
-        <v>63.38</v>
+        <v>96.48</v>
       </c>
       <c r="S20" t="n">
-        <v>74.34999999999999</v>
+        <v>140</v>
       </c>
       <c r="T20" t="n">
-        <v>47.3</v>
+        <v>75.36</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>270303</v>
+        <v>640703</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>44.11</v>
+        <v>132.96</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-14.05</v>
+        <v>-12.53</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-25.99</v>
+        <v>-27.26</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-48.82</v>
+        <v>-38.15</v>
       </c>
       <c r="H21" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-19.95</v>
+        <v>-21.35</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>14</v>
+        <v>15.4</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -2987,39 +2987,39 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>-18.51</v>
+        <v>-18.37</v>
       </c>
       <c r="P21" t="n">
-        <v>13.95</v>
+        <v>14.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>37.96</v>
+        <v>113.16</v>
       </c>
       <c r="R21" t="n">
-        <v>55.11</v>
+        <v>169.06</v>
       </c>
       <c r="S21" t="n">
-        <v>93.68000000000001</v>
+        <v>220.66</v>
       </c>
       <c r="T21" t="n">
-        <v>42.12</v>
+        <v>131.8</v>
       </c>
       <c r="U21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270203</v>
+        <v>730204</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,32 +3057,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>67.95999999999999</v>
+        <v>167.2</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-15.08</v>
+        <v>-13.41</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-29</v>
+        <v>-23.65</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-43.13</v>
+        <v>-19.62</v>
       </c>
       <c r="H22" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.86</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-21.78</v>
+        <v>-19.15</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>14.3</v>
+        <v>25.6</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
@@ -3107,39 +3107,39 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>-21.52</v>
+        <v>-14.76</v>
       </c>
       <c r="P22" t="n">
-        <v>14.39</v>
+        <v>16.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>58.18</v>
+        <v>139.44</v>
       </c>
       <c r="R22" t="n">
-        <v>86.88</v>
+        <v>206.79</v>
       </c>
       <c r="S22" t="n">
-        <v>122.2</v>
+        <v>237.87</v>
       </c>
       <c r="T22" t="n">
-        <v>66.3</v>
+        <v>125.61</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>640703</v>
+        <v>730206</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>121.91</v>
+        <v>19.52</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-20.45</v>
+        <v>-15.68</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-32.14</v>
+        <v>-23.42</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-47.18</v>
+        <v>-34.23</v>
       </c>
       <c r="H23" t="n">
-        <v>0.84</v>
+        <v>1.23</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-23.59</v>
+        <v>-17.87</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
@@ -3227,39 +3227,39 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>-24.66</v>
+        <v>-14.53</v>
       </c>
       <c r="P23" t="n">
-        <v>15.33</v>
+        <v>12.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>103.22</v>
+        <v>17.16</v>
       </c>
       <c r="R23" t="n">
-        <v>159.54</v>
+        <v>23.77</v>
       </c>
       <c r="S23" t="n">
-        <v>242.81</v>
+        <v>30.67</v>
       </c>
       <c r="T23" t="n">
-        <v>120.66</v>
+        <v>19.36</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270401</v>
+        <v>270303</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="AD23" s="2" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>44.94</v>
+        <v>41.27</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-9.08</v>
+        <v>-16.98</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-18.38</v>
+        <v>-30.02</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-26.96</v>
+        <v>-53.03</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-12.57</v>
+        <v>-23.88</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>22.3</v>
+        <v>12.5</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
@@ -3347,39 +3347,39 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>-10.9</v>
+        <v>-21.13</v>
       </c>
       <c r="P24" t="n">
-        <v>8.19</v>
+        <v>15.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>41.26</v>
+        <v>34.98</v>
       </c>
       <c r="R24" t="n">
-        <v>51.4</v>
+        <v>54.22</v>
       </c>
       <c r="S24" t="n">
-        <v>64.2</v>
+        <v>86.16</v>
       </c>
       <c r="T24" t="n">
-        <v>44.7</v>
+        <v>40.9</v>
       </c>
       <c r="U24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>270504</v>
+        <v>270203</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="2" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>47.26</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-12.4</v>
+        <v>-12.75</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-24.98</v>
+        <v>-18.73</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-32.61</v>
+        <v>-30.77</v>
       </c>
       <c r="H25" t="n">
-        <v>0.57</v>
+        <v>1.28</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-17.45</v>
+        <v>-15.61</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>13.9</v>
+        <v>12.9</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
@@ -3467,39 +3467,39 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>-17.5</v>
+        <v>-9.84</v>
       </c>
       <c r="P25" t="n">
-        <v>10.85</v>
+        <v>7.31</v>
       </c>
       <c r="Q25" t="n">
-        <v>42.13</v>
+        <v>62.09</v>
       </c>
       <c r="R25" t="n">
-        <v>57.25</v>
+        <v>79.38</v>
       </c>
       <c r="S25" t="n">
-        <v>70.89</v>
+        <v>105.43</v>
       </c>
       <c r="T25" t="n">
-        <v>45.82</v>
+        <v>66.11</v>
       </c>
       <c r="U25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>640209</v>
+        <v>710101</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能放大(1.2-1.5倍)</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,32 +3537,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>259.97</v>
+        <v>50.03</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-13.9</v>
+        <v>-11.58</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-27.56</v>
+        <v>-24.78</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-51.72</v>
+        <v>-28.33</v>
       </c>
       <c r="H26" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.77</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-18.63</v>
+        <v>-20.02</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
@@ -3587,39 +3587,39 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>-20.08</v>
+        <v>-15.89</v>
       </c>
       <c r="P26" t="n">
-        <v>10.27</v>
+        <v>13.68</v>
       </c>
       <c r="Q26" t="n">
-        <v>233.26</v>
+        <v>43.19</v>
       </c>
       <c r="R26" t="n">
-        <v>319.5</v>
+        <v>62.55</v>
       </c>
       <c r="S26" t="n">
-        <v>557</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>258</v>
+        <v>47.3</v>
       </c>
       <c r="U26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270104</v>
+        <v>270303</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>190.21</v>
+        <v>26.18</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-14.62</v>
+        <v>-12.47</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-18.96</v>
+        <v>-28.9</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-38.92</v>
+        <v>-21.17</v>
       </c>
       <c r="H27" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.47</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>-17.86</v>
+        <v>-22.13</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>15</v>
+        <v>4.8</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -3707,39 +3707,39 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>-11.48</v>
+        <v>-20.01</v>
       </c>
       <c r="P27" t="n">
-        <v>12.25</v>
+        <v>14.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>166.91</v>
+        <v>22.45</v>
       </c>
       <c r="R27" t="n">
-        <v>231.58</v>
+        <v>33.62</v>
       </c>
       <c r="S27" t="n">
-        <v>316.98</v>
+        <v>39.58</v>
       </c>
       <c r="T27" t="n">
-        <v>183.83</v>
+        <v>23.2</v>
       </c>
       <c r="U27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>270103</v>
+        <v>640209</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20.46</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-16.15</v>
+        <v>-17.27</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-18.87</v>
+        <v>-23.82</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-34.34</v>
+        <v>-23.25</v>
       </c>
       <c r="H28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.65</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-14.99</v>
+        <v>-17.9</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -3827,39 +3827,39 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>-11.39</v>
+        <v>-14.93</v>
       </c>
       <c r="P28" t="n">
-        <v>11.29</v>
+        <v>15.46</v>
       </c>
       <c r="Q28" t="n">
-        <v>18.15</v>
+        <v>63.25</v>
       </c>
       <c r="R28" t="n">
-        <v>24.07</v>
+        <v>91.14</v>
       </c>
       <c r="S28" t="n">
-        <v>31.89</v>
+        <v>102.82</v>
       </c>
       <c r="T28" t="n">
-        <v>20.42</v>
+        <v>69.63</v>
       </c>
       <c r="U28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>270303</v>
+        <v>650201</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="AD28" s="2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>78.65000000000001</v>
+        <v>44.67</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-17.14</v>
+        <v>-13.98</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-17.31</v>
+        <v>-28.45</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-22.88</v>
+        <v>-34.06</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.62</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>-14.79</v>
+        <v>-20.74</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>28.1</v>
+        <v>12.5</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
@@ -3947,39 +3947,39 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>-9.83</v>
+        <v>-19.56</v>
       </c>
       <c r="P29" t="n">
-        <v>15.03</v>
+        <v>11.79</v>
       </c>
       <c r="Q29" t="n">
-        <v>66.83</v>
+        <v>39.4</v>
       </c>
       <c r="R29" t="n">
-        <v>92.31</v>
+        <v>56.36</v>
       </c>
       <c r="S29" t="n">
-        <v>104.39</v>
+        <v>70.77</v>
       </c>
       <c r="T29" t="n">
-        <v>69.63</v>
+        <v>44.48</v>
       </c>
       <c r="U29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>650201</v>
+        <v>640209</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -39,14 +39,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -473,8 +473,8 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="29" customWidth="1" min="31" max="31"/>
-    <col width="58" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="66" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
@@ -657,32 +657,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>190</v>
+        <v>49.51</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-4.79</v>
+        <v>2.15</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>-9.220000000000001</v>
+        <v>-7.63</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-27</v>
       </c>
       <c r="H2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.72</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -690,56 +690,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="n">
+        <v>-10.93</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>10.3</v>
+        <v>18.4</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.68</v>
       </c>
       <c r="P2" t="n">
-        <v>11.5</v>
+        <v>15.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>168.15</v>
+        <v>41.68</v>
       </c>
       <c r="R2" t="n">
-        <v>197.6</v>
+        <v>55.59</v>
       </c>
       <c r="S2" t="n">
-        <v>232.68</v>
+        <v>68.5</v>
       </c>
       <c r="T2" t="n">
-        <v>170.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2</v>
+        <v>43.01</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>270104</v>
+        <v>640108</v>
       </c>
       <c r="Z2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -747,17 +747,17 @@
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" s="2" t="n">
-        <v>25.9</v>
+      <c r="AD2" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,32 +777,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>116.18</v>
+        <v>70.48</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>-8.91</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>-15.34</v>
+        <v>-6.49</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>-14.41</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>-27.83</v>
       </c>
       <c r="H3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.41</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -810,50 +810,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="n">
+        <v>-10.54</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>-0.02</v>
+        <v>20</v>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-6.1</v>
       </c>
       <c r="P3" t="n">
-        <v>11.42</v>
+        <v>7.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>102.91</v>
+        <v>65.17</v>
       </c>
       <c r="R3" t="n">
-        <v>121.14</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>142.99</v>
+        <v>105.43</v>
       </c>
       <c r="T3" t="n">
-        <v>94.73</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>1</v>
+        <v>66.11</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270202</v>
+        <v>710101</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -867,7 +867,7 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" s="2" t="n">
+      <c r="AD3" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="AE3" t="inlineStr">
@@ -897,32 +897,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47.51</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>-4.64</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-12.75</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>-35.25</v>
+        <v>171.01</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-15.64</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>-6.38</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-22.63</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.03</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -930,56 +930,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>-14.85</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>40.5</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-3.86</v>
+        <v>1.93</v>
       </c>
       <c r="P4" t="n">
-        <v>16.76</v>
+        <v>13.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>39.55</v>
+        <v>147.74</v>
       </c>
       <c r="R4" t="n">
-        <v>55.79</v>
+        <v>197.02</v>
       </c>
       <c r="S4" t="n">
-        <v>72.90000000000001</v>
+        <v>232.68</v>
       </c>
       <c r="T4" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0</v>
+        <v>170.88</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>640108</v>
+        <v>270104</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -987,17 +987,17 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="2" t="n">
-        <v>18.5</v>
+      <c r="AD4" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.46</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>-9.880000000000001</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-12.48</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>-21.34</v>
+        <v>63.85</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-15.43</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-32.63</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-40.93</v>
       </c>
       <c r="H5" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1050,56 +1050,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>-9.51</v>
+      <c r="K5" s="3" t="n">
+        <v>-23.77</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>-3.59</v>
+        <v>3.2</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-24.32</v>
       </c>
       <c r="P5" t="n">
-        <v>10.82</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.27</v>
+        <v>54.27</v>
       </c>
       <c r="R5" t="n">
-        <v>32.55</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>40.38</v>
+        <v>109.88</v>
       </c>
       <c r="T5" t="n">
-        <v>28.85</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
+        <v>62.66</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>630702</v>
+        <v>640703</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1107,8 +1107,8 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="2" t="n">
-        <v>18.5</v>
+      <c r="AD5" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>211.05</v>
+        <v>113.38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-13.09</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-27.61</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>-55.29</v>
+        <v>0.97</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-11.37</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>-17.07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.16</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1170,56 +1170,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>-20.7</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="K6" s="3" t="n">
+        <v>-5.84</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>-18.72</v>
+        <v>37.3</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-3.06</v>
       </c>
       <c r="P6" t="n">
-        <v>12.46</v>
+        <v>11.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>184.75</v>
+        <v>100.07</v>
       </c>
       <c r="R6" t="n">
-        <v>266.14</v>
+        <v>120.41</v>
       </c>
       <c r="S6" t="n">
-        <v>424.76</v>
+        <v>136.45</v>
       </c>
       <c r="T6" t="n">
-        <v>208.61</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>0</v>
+        <v>94.73</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>270104</v>
+        <v>270202</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1227,8 +1227,8 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="2" t="n">
-        <v>18.5</v>
+      <c r="AD6" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>306.01</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>-19.15</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-26.23</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>-44.96</v>
+        <v>173.99</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-10.04</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-3.71</v>
       </c>
       <c r="H7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.85</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1290,46 +1290,46 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>-23.4</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="3" t="n">
+        <v>-15.26</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>18.9</v>
+        <v>27.5</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>-17.34</v>
+      <c r="O7" s="3" t="n">
+        <v>-6.09</v>
       </c>
       <c r="P7" t="n">
-        <v>16.12</v>
+        <v>18.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>256.69</v>
+        <v>142.39</v>
       </c>
       <c r="R7" t="n">
-        <v>399.49</v>
+        <v>205.33</v>
       </c>
       <c r="S7" t="n">
-        <v>558</v>
+        <v>242.99</v>
       </c>
       <c r="T7" t="n">
-        <v>299.23</v>
-      </c>
-      <c r="U7" s="2" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="U7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1347,8 +1347,8 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="2" t="n">
-        <v>16.7</v>
+      <c r="AD7" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,30 +1377,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>-8.15</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-16.17</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>-37.78</v>
+        <v>111.7</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-17.31</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>-45.78</v>
       </c>
       <c r="H8" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+        <v>0.89</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1410,50 +1410,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>-12.94</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="3" t="n">
+        <v>-27.17</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>26.7</v>
+        <v>12.2</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>-7.28</v>
+      <c r="O8" s="3" t="n">
+        <v>-27.19</v>
       </c>
       <c r="P8" t="n">
-        <v>10.87</v>
+        <v>16.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>51.25</v>
+        <v>93.27</v>
       </c>
       <c r="R8" t="n">
-        <v>66.05</v>
+        <v>153.37</v>
       </c>
       <c r="S8" t="n">
-        <v>90.36</v>
+        <v>203.5</v>
       </c>
       <c r="T8" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="U8" s="2" t="n">
+        <v>110.92</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270107</v>
+        <v>270401</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1467,7 +1467,7 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="2" t="n">
+      <c r="AD8" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="AE8" t="inlineStr">
@@ -1497,30 +1497,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-17.56</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-36.65</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>-52.68</v>
+        <v>206.01</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-14.01</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-30.79</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>-51.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+        <v>1.06</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1530,56 +1530,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>-27.88</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="K9" s="3" t="n">
+        <v>-21.24</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13.3</v>
+        <v>7.1</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>-27.76</v>
+      <c r="O9" s="3" t="n">
+        <v>-22.48</v>
       </c>
       <c r="P9" t="n">
-        <v>16.45</v>
+        <v>12.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.77</v>
+        <v>180.1</v>
       </c>
       <c r="R9" t="n">
-        <v>172.21</v>
+        <v>261.56</v>
       </c>
       <c r="S9" t="n">
-        <v>276</v>
+        <v>382.17</v>
       </c>
       <c r="T9" t="n">
-        <v>122.53</v>
-      </c>
-      <c r="U9" s="2" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="U9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>270202</v>
+        <v>270104</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1587,8 +1587,8 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="2" t="n">
-        <v>14.8</v>
+      <c r="AD9" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,30 +1617,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>179.94</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>-14.16</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-22.11</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>-36.22</v>
+        <v>241.65</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-14.91</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>-30.36</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-47.87</v>
       </c>
       <c r="H10" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+        <v>0.99</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1650,50 +1650,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K10" s="2" t="n">
-        <v>-21.43</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="3" t="n">
+        <v>-21.81</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>13.9</v>
+        <v>1.2</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>-13.22</v>
+      <c r="O10" s="3" t="n">
+        <v>-22.05</v>
       </c>
       <c r="P10" t="n">
-        <v>13.39</v>
+        <v>11.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>155.84</v>
+        <v>213.67</v>
       </c>
       <c r="R10" t="n">
-        <v>229.03</v>
+        <v>309.04</v>
       </c>
       <c r="S10" t="n">
-        <v>279.78</v>
+        <v>459.89</v>
       </c>
       <c r="T10" t="n">
-        <v>175.88</v>
-      </c>
-      <c r="U10" s="2" t="n">
+        <v>239.01</v>
+      </c>
+      <c r="U10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270103</v>
+        <v>270104</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" s="2" t="n">
+      <c r="AD10" s="3" t="n">
         <v>13</v>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1737,30 +1737,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>244</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>-15.45</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-29.89</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>-50</v>
+        <v>44.7</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-12.16</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-26.82</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-34.13</v>
       </c>
       <c r="H11" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+        <v>0.6</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1770,56 +1770,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>-22.37</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="3" t="n">
+        <v>-19.52</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>11.2</v>
+        <v>6.3</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O11" s="2" t="n">
-        <v>-21</v>
+      <c r="O11" s="3" t="n">
+        <v>-18.51</v>
       </c>
       <c r="P11" t="n">
-        <v>11.55</v>
+        <v>11.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>215.82</v>
+        <v>39.45</v>
       </c>
       <c r="R11" t="n">
-        <v>314.3</v>
+        <v>55.54</v>
       </c>
       <c r="S11" t="n">
-        <v>493</v>
+        <v>70.62</v>
       </c>
       <c r="T11" t="n">
-        <v>241.42</v>
-      </c>
-      <c r="U11" s="2" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>270104</v>
+        <v>640209</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1827,8 +1827,8 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="2" t="n">
-        <v>13</v>
+      <c r="AD11" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,30 +1857,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>63.37</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>-18.87</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-33.19</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>-44.59</v>
+        <v>76.86</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-4.73</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-26.94</v>
       </c>
       <c r="H12" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1890,56 +1890,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K12" s="2" t="n">
-        <v>-25.72</v>
+      <c r="K12" s="3" t="n">
+        <v>-7.19</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>13</v>
+        <v>25.9</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>-24.3</v>
+      <c r="O12" s="3" t="n">
+        <v>-1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>15.73</v>
+        <v>7.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>53.4</v>
+        <v>70.81</v>
       </c>
       <c r="R12" t="n">
-        <v>85.31</v>
+        <v>82.81</v>
       </c>
       <c r="S12" t="n">
-        <v>115.13</v>
+        <v>121.57</v>
       </c>
       <c r="T12" t="n">
-        <v>62.66</v>
-      </c>
-      <c r="U12" s="2" t="n">
-        <v>0</v>
+        <v>75.12</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>640703</v>
+        <v>630503</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1947,8 +1947,8 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AD12" s="2" t="n">
-        <v>13</v>
+      <c r="AD12" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>112.6</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>-22.33</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-35.48</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>-49.08</v>
+        <v>212.8</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-20.74</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-12.65</v>
       </c>
       <c r="H13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.89</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2010,56 +2010,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K13" s="2" t="n">
-        <v>-28.02</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="3" t="n">
+        <v>-16.17</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>22.1</v>
+        <v>24</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O13" s="2" t="n">
-        <v>-26.59</v>
+      <c r="O13" s="3" t="n">
+        <v>-12.43</v>
       </c>
       <c r="P13" t="n">
-        <v>17.12</v>
+        <v>16.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>93.33</v>
+        <v>178.16</v>
       </c>
       <c r="R13" t="n">
-        <v>156.44</v>
+        <v>253.85</v>
       </c>
       <c r="S13" t="n">
-        <v>216.99</v>
+        <v>294.5</v>
       </c>
       <c r="T13" t="n">
-        <v>111.55</v>
-      </c>
-      <c r="U13" s="2" t="n">
+        <v>155.05</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270401</v>
+        <v>730204</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2067,8 +2067,8 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" s="2" t="n">
-        <v>13</v>
+      <c r="AD13" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>223.33</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-4.99</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-13.28</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>-13.74</v>
+        <v>133.75</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-10.06</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-25.44</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-36.46</v>
       </c>
       <c r="H14" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.85</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2130,46 +2130,46 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K14" s="2" t="n">
-        <v>-12.98</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="3" t="n">
+        <v>-19.81</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>29.8</v>
+        <v>11.9</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n">
-        <v>-4.39</v>
+      <c r="O14" s="3" t="n">
+        <v>-17.13</v>
       </c>
       <c r="P14" t="n">
-        <v>15.1</v>
+        <v>14.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>189.6</v>
+        <v>114.03</v>
       </c>
       <c r="R14" t="n">
-        <v>256.64</v>
+        <v>166.78</v>
       </c>
       <c r="S14" t="n">
-        <v>294.5</v>
+        <v>209.66</v>
       </c>
       <c r="T14" t="n">
-        <v>155.05</v>
-      </c>
-      <c r="U14" s="2" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W14" t="n">
@@ -2187,7 +2187,7 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" s="2" t="n">
+      <c r="AD14" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2217,28 +2217,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>188.46</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-6.49</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>-4.25</v>
+        <v>168.51</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-12.69</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-28.12</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-13.85</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2250,50 +2250,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K15" s="2" t="n">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="K15" s="3" t="n">
+        <v>-17.19</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>19.9</v>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>2.4</v>
+        <v>-19.81</v>
       </c>
       <c r="P15" t="n">
-        <v>16.92</v>
+        <v>15.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>156.56</v>
+        <v>141.97</v>
       </c>
       <c r="R15" t="n">
-        <v>206.8</v>
+        <v>203.5</v>
       </c>
       <c r="S15" t="n">
-        <v>242.99</v>
+        <v>237.87</v>
       </c>
       <c r="T15" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
+        <v>125.61</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>730204</v>
+        <v>730206</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" s="2" t="n">
+      <c r="AD15" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2337,30 +2337,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>-5.45</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-11.88</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>-29.74</v>
+        <v>28.73</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-19.48</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-13.33</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-21.31</v>
       </c>
       <c r="H16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+        <v>2.33</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2370,50 +2370,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K16" s="2" t="n">
-        <v>-8.57</v>
+      <c r="K16" s="3" t="n">
+        <v>-11.14</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>33.5</v>
+        <v>35</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O16" s="2" t="n">
-        <v>-2.99</v>
+      <c r="O16" s="3" t="n">
+        <v>-5.02</v>
       </c>
       <c r="P16" t="n">
-        <v>7.98</v>
+        <v>11.61</v>
       </c>
       <c r="Q16" t="n">
-        <v>70.03</v>
+        <v>25.39</v>
       </c>
       <c r="R16" t="n">
-        <v>83.23</v>
+        <v>32.33</v>
       </c>
       <c r="S16" t="n">
-        <v>121.57</v>
+        <v>40.38</v>
       </c>
       <c r="T16" t="n">
-        <v>75.12</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
+        <v>28.43</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>630503</v>
+        <v>630702</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2427,7 +2427,7 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" s="2" t="n">
+      <c r="AD16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE16" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,32 +2457,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>44.65</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>-7.81</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-20.07</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>-25.99</v>
+        <v>76.27</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-8.67</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-23.97</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-17.93</v>
       </c>
       <c r="H17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.57</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2490,56 +2490,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K17" s="2" t="n">
-        <v>-12.18</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="K17" s="3" t="n">
+        <v>-15.19</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>23</v>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>-11.18</v>
+        <v>31.2</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>-15.66</v>
       </c>
       <c r="P17" t="n">
-        <v>8.35</v>
+        <v>14.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>40.92</v>
+        <v>65.17</v>
       </c>
       <c r="R17" t="n">
-        <v>50.84</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>64.2</v>
+        <v>102.82</v>
       </c>
       <c r="T17" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="U17" s="2" t="n">
-        <v>0</v>
+        <v>69.63</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>270504</v>
+        <v>650201</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2547,8 +2547,8 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD17" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,30 +2577,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>49.75</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>-11.05</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-14.74</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>-36.79</v>
+        <v>29.7</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-22.6</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-27.61</v>
       </c>
       <c r="H18" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+        <v>0.63</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2610,56 +2610,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K18" s="2" t="n">
-        <v>-13.78</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="K18" s="3" t="n">
+        <v>-16.17</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>-5.85</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>-14.29</v>
       </c>
       <c r="P18" t="n">
-        <v>11.9</v>
+        <v>11.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>43.83</v>
+        <v>26.18</v>
       </c>
       <c r="R18" t="n">
-        <v>57.7</v>
+        <v>35.43</v>
       </c>
       <c r="S18" t="n">
-        <v>80.8</v>
+        <v>46.74</v>
       </c>
       <c r="T18" t="n">
-        <v>48.91</v>
-      </c>
-      <c r="U18" s="2" t="n">
-        <v>1</v>
+        <v>29.45</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270107</v>
+        <v>270504</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2667,8 +2667,8 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD18" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,30 +2697,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>-11.15</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-24.94</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>-26.56</v>
+        <v>56.96</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-16.32</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-31.51</v>
       </c>
       <c r="H19" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+        <v>0.7</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2730,56 +2730,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K19" s="2" t="n">
-        <v>-16.9</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="K19" s="3" t="n">
+        <v>-13.03</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>14.6</v>
+        <v>3.5</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O19" s="2" t="n">
-        <v>-16.05</v>
+      <c r="O19" s="3" t="n">
+        <v>-8.01</v>
       </c>
       <c r="P19" t="n">
-        <v>11.81</v>
+        <v>9.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.28</v>
+        <v>51.31</v>
       </c>
       <c r="R19" t="n">
-        <v>35.86</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>46.74</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="U19" s="2" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270504</v>
+        <v>270107</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2787,8 +2787,8 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD19" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,30 +2817,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>76.27</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>-12.32</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-29.89</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>-47.48</v>
+        <v>49.54</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-9.27</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-25.89</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-24.86</v>
       </c>
       <c r="H20" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+        <v>0.67</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2850,56 +2850,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K20" s="2" t="n">
-        <v>-20.95</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="K20" s="3" t="n">
+        <v>-19.69</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>15.1</v>
+        <v>12</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O20" s="2" t="n">
-        <v>-21</v>
+      <c r="O20" s="3" t="n">
+        <v>-17.58</v>
       </c>
       <c r="P20" t="n">
-        <v>12.08</v>
+        <v>14.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>67.06</v>
+        <v>42.57</v>
       </c>
       <c r="R20" t="n">
-        <v>96.48</v>
+        <v>61.69</v>
       </c>
       <c r="S20" t="n">
-        <v>140</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>75.36</v>
-      </c>
-      <c r="U20" s="2" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="U20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>640703</v>
+        <v>270303</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2907,8 +2907,8 @@
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD20" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,32 +2937,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>132.96</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>-12.53</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-27.26</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>-38.15</v>
+        <v>25.91</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-9.66</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-29.07</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-21.67</v>
       </c>
       <c r="H21" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.4</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2970,56 +2970,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K21" s="2" t="n">
-        <v>-21.35</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="K21" s="3" t="n">
+        <v>-21.69</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>15.4</v>
+        <v>4.9</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>-18.37</v>
+      <c r="O21" s="3" t="n">
+        <v>-20.76</v>
       </c>
       <c r="P21" t="n">
-        <v>14.89</v>
+        <v>13.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>113.16</v>
+        <v>22.3</v>
       </c>
       <c r="R21" t="n">
-        <v>169.06</v>
+        <v>33.09</v>
       </c>
       <c r="S21" t="n">
-        <v>220.66</v>
+        <v>39.58</v>
       </c>
       <c r="T21" t="n">
-        <v>131.8</v>
-      </c>
-      <c r="U21" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="U21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>730204</v>
+        <v>640209</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3027,8 +3027,8 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD21" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,32 +3057,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>167.2</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>-13.41</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-23.65</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>-19.62</v>
+        <v>75.7</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-11.95</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>-28.45</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-42.08</v>
       </c>
       <c r="H22" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.57</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3090,56 +3090,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K22" s="2" t="n">
-        <v>-19.15</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="K22" s="3" t="n">
+        <v>-20.3</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>25.6</v>
+        <v>10.7</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O22" s="2" t="n">
-        <v>-14.76</v>
+      <c r="O22" s="3" t="n">
+        <v>-20.14</v>
       </c>
       <c r="P22" t="n">
-        <v>16.6</v>
+        <v>12.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>139.44</v>
+        <v>66.52</v>
       </c>
       <c r="R22" t="n">
-        <v>206.79</v>
+        <v>94.98</v>
       </c>
       <c r="S22" t="n">
-        <v>237.87</v>
+        <v>130</v>
       </c>
       <c r="T22" t="n">
-        <v>125.61</v>
-      </c>
-      <c r="U22" s="2" t="n">
+        <v>74.76000000000001</v>
+      </c>
+      <c r="U22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>730206</v>
+        <v>640703</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3147,8 +3147,8 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD22" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,30 +3177,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>-15.68</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-23.42</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>-34.23</v>
+        <v>48.67</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-12.39</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-16.58</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-35.92</v>
       </c>
       <c r="H23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+        <v>0.71</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3210,56 +3210,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K23" s="2" t="n">
-        <v>-17.87</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="K23" s="3" t="n">
+        <v>-14.94</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>24.9</v>
+        <v>20.5</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O23" s="2" t="n">
-        <v>-14.53</v>
+      <c r="O23" s="3" t="n">
+        <v>-8.27</v>
       </c>
       <c r="P23" t="n">
-        <v>12.1</v>
+        <v>11.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>17.16</v>
+        <v>42.87</v>
       </c>
       <c r="R23" t="n">
-        <v>23.77</v>
+        <v>57.22</v>
       </c>
       <c r="S23" t="n">
-        <v>30.67</v>
+        <v>76.8</v>
       </c>
       <c r="T23" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="U23" s="2" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="U23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270303</v>
+        <v>270107</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3267,8 +3267,8 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD23" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3306,21 +3306,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41.27</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>-16.98</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-30.02</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>-53.03</v>
+        <v>40.88</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-15.01</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-29.53</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-49.79</v>
       </c>
       <c r="H24" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+        <v>0.82</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3330,46 +3330,46 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K24" s="2" t="n">
-        <v>-23.88</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="K24" s="3" t="n">
+        <v>-23.39</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O24" s="2" t="n">
-        <v>-21.13</v>
+      <c r="O24" s="3" t="n">
+        <v>-21.22</v>
       </c>
       <c r="P24" t="n">
-        <v>15.24</v>
+        <v>15.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>34.98</v>
+        <v>34.62</v>
       </c>
       <c r="R24" t="n">
-        <v>54.22</v>
+        <v>53.36</v>
       </c>
       <c r="S24" t="n">
-        <v>86.16</v>
+        <v>80</v>
       </c>
       <c r="T24" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="U24" s="2" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="U24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -3379,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3387,8 +3387,8 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD24" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,30 +3417,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66.98999999999999</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>-12.75</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-18.73</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>-30.77</v>
+        <v>122.67</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-15.68</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-36.68</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-54.36</v>
       </c>
       <c r="H25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+        <v>1.08</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3450,56 +3450,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K25" s="2" t="n">
-        <v>-15.61</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="K25" s="3" t="n">
+        <v>-27.27</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>12.9</v>
+        <v>10.6</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O25" s="2" t="n">
-        <v>-9.84</v>
+      <c r="O25" s="3" t="n">
+        <v>-28.37</v>
       </c>
       <c r="P25" t="n">
-        <v>7.31</v>
+        <v>16.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>62.09</v>
+        <v>102.78</v>
       </c>
       <c r="R25" t="n">
-        <v>79.38</v>
+        <v>168.66</v>
       </c>
       <c r="S25" t="n">
-        <v>105.43</v>
+        <v>260</v>
       </c>
       <c r="T25" t="n">
-        <v>66.11</v>
-      </c>
-      <c r="U25" s="2" t="n">
+        <v>121.31</v>
+      </c>
+      <c r="U25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>710101</v>
+        <v>270202</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3507,8 +3507,8 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" s="2" t="n">
-        <v>7.4</v>
+      <c r="AD25" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,32 +3537,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>50.03</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>-11.58</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-24.78</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>-28.33</v>
+        <v>19.4</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-13.28</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-22.77</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-32.83</v>
       </c>
       <c r="H26" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.02</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3570,46 +3570,46 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K26" s="2" t="n">
-        <v>-20.02</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="K26" s="3" t="n">
+        <v>-17.38</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>15.5</v>
+        <v>17.3</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O26" s="2" t="n">
-        <v>-15.89</v>
+      <c r="O26" s="3" t="n">
+        <v>-14.46</v>
       </c>
       <c r="P26" t="n">
-        <v>13.68</v>
+        <v>11.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>43.19</v>
+        <v>17.09</v>
       </c>
       <c r="R26" t="n">
-        <v>62.55</v>
+        <v>23.48</v>
       </c>
       <c r="S26" t="n">
-        <v>72.68000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="T26" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="U26" s="2" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="U26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3627,8 +3627,8 @@
       <c r="AC26" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="2" t="n">
-        <v>5.6</v>
+      <c r="AD26" s="3" t="n">
+        <v>3.7</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>-12.47</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-28.9</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>-21.17</v>
+        <v>176.4</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-24.52</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-26.5</v>
       </c>
       <c r="H27" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.85</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3690,56 +3690,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K27" s="2" t="n">
-        <v>-22.13</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="K27" s="3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O27" s="2" t="n">
-        <v>-20.01</v>
+      <c r="O27" s="3" t="n">
+        <v>-16.21</v>
       </c>
       <c r="P27" t="n">
-        <v>14.25</v>
+        <v>13.51</v>
       </c>
       <c r="Q27" t="n">
-        <v>22.45</v>
+        <v>152.57</v>
       </c>
       <c r="R27" t="n">
-        <v>33.62</v>
+        <v>226.16</v>
       </c>
       <c r="S27" t="n">
-        <v>39.58</v>
+        <v>279.78</v>
       </c>
       <c r="T27" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="U27" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="U27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>640209</v>
+        <v>270103</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3747,8 +3747,8 @@
       <c r="AC27" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="2" t="n">
-        <v>5.6</v>
+      <c r="AD27" s="3" t="n">
+        <v>3.7</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>74.81999999999999</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>-17.27</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-23.82</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>-23.25</v>
+        <v>306.91</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>-25.31</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-43.44</v>
       </c>
       <c r="H28" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.18</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3810,56 +3810,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K28" s="2" t="n">
-        <v>-17.9</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="K28" s="3" t="n">
+        <v>-22.16</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>27.4</v>
+        <v>9.6</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O28" s="2" t="n">
-        <v>-14.93</v>
+      <c r="O28" s="3" t="n">
+        <v>-17</v>
       </c>
       <c r="P28" t="n">
-        <v>15.46</v>
+        <v>15.29</v>
       </c>
       <c r="Q28" t="n">
-        <v>63.25</v>
+        <v>260</v>
       </c>
       <c r="R28" t="n">
-        <v>91.14</v>
+        <v>394.29</v>
       </c>
       <c r="S28" t="n">
-        <v>102.82</v>
+        <v>554.4</v>
       </c>
       <c r="T28" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="U28" s="2" t="n">
+        <v>299.23</v>
+      </c>
+      <c r="U28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>650201</v>
+        <v>730204</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3867,8 +3867,8 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" s="2" t="n">
-        <v>5.6</v>
+      <c r="AD28" s="3" t="n">
+        <v>3.7</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3897,30 +3897,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>44.67</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>-13.98</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-28.45</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>-34.06</v>
+      <c r="E29" s="3" t="n">
+        <v>-6.14</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-17.96</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-27.29</v>
       </c>
       <c r="H29" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3930,56 +3930,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K29" s="2" t="n">
-        <v>-20.74</v>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="K29" s="3" t="n">
+        <v>-11.29</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O29" s="2" t="n">
-        <v>-19.56</v>
+      <c r="O29" s="3" t="n">
+        <v>-9.65</v>
       </c>
       <c r="P29" t="n">
-        <v>11.79</v>
+        <v>8</v>
       </c>
       <c r="Q29" t="n">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="R29" t="n">
-        <v>56.36</v>
+        <v>50.35</v>
       </c>
       <c r="S29" t="n">
-        <v>70.77</v>
+        <v>63.02</v>
       </c>
       <c r="T29" t="n">
-        <v>44.48</v>
-      </c>
-      <c r="U29" s="2" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="U29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>640209</v>
+        <v>270504</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3987,8 +3987,8 @@
       <c r="AC29" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" s="2" t="n">
-        <v>3.7</v>
+      <c r="AD29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,7 +473,7 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
     <col width="66" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
@@ -657,25 +657,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49.51</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.15</v>
+        <v>0.63</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-7.63</v>
+        <v>-10.08</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-27</v>
+        <v>-15.85</v>
       </c>
       <c r="H2" t="n">
         <v>1.72</v>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-10.93</v>
+        <v>-5.63</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -699,41 +699,41 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>0.68</v>
+        <v>30.9</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-2.64</v>
       </c>
       <c r="P2" t="n">
-        <v>15.81</v>
+        <v>7.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.68</v>
+        <v>68.23</v>
       </c>
       <c r="R2" t="n">
-        <v>55.59</v>
+        <v>78.37</v>
       </c>
       <c r="S2" t="n">
-        <v>68.5</v>
+        <v>105.43</v>
       </c>
       <c r="T2" t="n">
-        <v>43.01</v>
+        <v>66.11</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>640108</v>
+        <v>710101</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -777,28 +777,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>70.48</v>
+        <v>219.19</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-6.49</v>
+        <v>-4.08</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-14.41</v>
+        <v>-23.52</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-27.83</v>
+        <v>-42.65</v>
       </c>
       <c r="H3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-10.54</v>
+        <v>-15.1</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
@@ -827,33 +827,33 @@
         </is>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-6.1</v>
+        <v>-16.08</v>
       </c>
       <c r="P3" t="n">
-        <v>7.54</v>
+        <v>12.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>65.17</v>
+        <v>191.72</v>
       </c>
       <c r="R3" t="n">
-        <v>78.79000000000001</v>
+        <v>258.19</v>
       </c>
       <c r="S3" t="n">
-        <v>105.43</v>
+        <v>377.5</v>
       </c>
       <c r="T3" t="n">
-        <v>66.11</v>
+        <v>204.5</v>
       </c>
       <c r="U3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>710101</v>
+        <v>270104</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -897,32 +897,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>171.01</v>
+        <v>20.22</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-15.64</v>
+        <v>-5.34</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-6.38</v>
+        <v>-18.04</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-22.63</v>
+        <v>-23.84</v>
       </c>
       <c r="H4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.01</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>-13.2</v>
+        <v>-13.07</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -939,47 +939,47 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>1.93</v>
+        <v>23</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-10.6</v>
       </c>
       <c r="P4" t="n">
-        <v>13.61</v>
+        <v>11.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>147.74</v>
+        <v>17.82</v>
       </c>
       <c r="R4" t="n">
-        <v>197.02</v>
+        <v>23.26</v>
       </c>
       <c r="S4" t="n">
-        <v>232.68</v>
+        <v>29.4</v>
       </c>
       <c r="T4" t="n">
-        <v>170.88</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2</v>
+        <v>19.08</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270104</v>
+        <v>270303</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>22.2</v>
+        <v>20.4</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>20日均线自身向上</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,28 +1017,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.85</v>
+        <v>114</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-15.43</v>
+        <v>-10.85</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-32.63</v>
+        <v>-32</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-40.93</v>
+        <v>-34.52</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-23.77</v>
+        <v>-24.35</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1067,33 +1067,33 @@
         </is>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-24.32</v>
+        <v>-24.56</v>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>15.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>54.27</v>
+        <v>96.66</v>
       </c>
       <c r="R5" t="n">
-        <v>83.76000000000001</v>
+        <v>150.69</v>
       </c>
       <c r="S5" t="n">
-        <v>109.88</v>
+        <v>189.92</v>
       </c>
       <c r="T5" t="n">
-        <v>62.66</v>
+        <v>107.9</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>640703</v>
+        <v>270401</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1137,25 +1137,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>113.38</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.97</v>
+        <v>171.85</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-13.86</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-11.37</v>
+        <v>-4.69</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-17.07</v>
+        <v>-14.42</v>
       </c>
       <c r="H6" t="n">
         <v>1.16</v>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-5.84</v>
+        <v>-12.59</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -1179,47 +1179,47 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>37.3</v>
+        <v>35.9</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O6" s="3" t="n">
-        <v>-3.06</v>
+      <c r="O6" s="2" t="n">
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>11.74</v>
+        <v>13.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>100.07</v>
+        <v>147.95</v>
       </c>
       <c r="R6" t="n">
-        <v>120.41</v>
+        <v>196.59</v>
       </c>
       <c r="S6" t="n">
-        <v>136.45</v>
+        <v>232.68</v>
       </c>
       <c r="T6" t="n">
-        <v>94.73</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>1</v>
+        <v>159.34</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>270202</v>
+        <v>270104</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>14.8</v>
+        <v>20.4</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>173.99</v>
+        <v>46.15</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-10.04</v>
+        <v>-6.56</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-14.4</v>
+        <v>-11.32</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-3.71</v>
+        <v>-26.17</v>
       </c>
       <c r="H7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.57</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-15.26</v>
+        <v>-16.54</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>27.5</v>
+        <v>15.3</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
@@ -1307,39 +1307,39 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-6.09</v>
+        <v>-3.88</v>
       </c>
       <c r="P7" t="n">
-        <v>18.16</v>
+        <v>17.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>142.39</v>
+        <v>38.22</v>
       </c>
       <c r="R7" t="n">
-        <v>205.33</v>
+        <v>55.29</v>
       </c>
       <c r="S7" t="n">
-        <v>242.99</v>
+        <v>67.05</v>
       </c>
       <c r="T7" t="n">
-        <v>102.3</v>
+        <v>43.01</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>730204</v>
+        <v>640108</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>14.8</v>
+        <v>18.5</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,28 +1377,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>111.7</v>
+        <v>242.8</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-17.31</v>
+        <v>-10.67</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-35.5</v>
+        <v>-28.49</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-45.78</v>
+        <v>-38.69</v>
       </c>
       <c r="H8" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-27.17</v>
+        <v>-20.18</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12.2</v>
+        <v>1.5</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
@@ -1427,39 +1427,39 @@
         </is>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-27.19</v>
+        <v>-21.05</v>
       </c>
       <c r="P8" t="n">
-        <v>16.5</v>
+        <v>11.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>93.27</v>
+        <v>214.49</v>
       </c>
       <c r="R8" t="n">
-        <v>153.37</v>
+        <v>304.2</v>
       </c>
       <c r="S8" t="n">
-        <v>203.5</v>
+        <v>442</v>
       </c>
       <c r="T8" t="n">
-        <v>110.92</v>
+        <v>234.98</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270401</v>
+        <v>270104</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>14.8</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>206.01</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-14.01</v>
+        <v>111.75</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1.94</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-30.79</v>
+        <v>-12.87</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-51.5</v>
+        <v>-12.56</v>
       </c>
       <c r="H9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.22</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-21.24</v>
+        <v>-6.56</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1539,47 +1539,47 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>31.7</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-22.48</v>
+        <v>-5.43</v>
       </c>
       <c r="P9" t="n">
-        <v>12.58</v>
+        <v>12.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>180.1</v>
+        <v>97.86</v>
       </c>
       <c r="R9" t="n">
-        <v>261.56</v>
+        <v>119.59</v>
       </c>
       <c r="S9" t="n">
-        <v>382.17</v>
+        <v>131.48</v>
       </c>
       <c r="T9" t="n">
-        <v>204.5</v>
+        <v>94.73</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>270104</v>
+        <v>270202</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,28 +1617,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>241.65</v>
+        <v>46.2</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-14.91</v>
+        <v>-0.26</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-30.36</v>
+        <v>-16.59</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-47.87</v>
+        <v>-20.22</v>
       </c>
       <c r="H10" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-21.81</v>
+        <v>-7.4</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.2</v>
+        <v>18.5</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
@@ -1667,39 +1667,39 @@
         </is>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-22.05</v>
+        <v>-9.15</v>
       </c>
       <c r="P10" t="n">
-        <v>11.58</v>
+        <v>8.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>213.67</v>
+        <v>42.4</v>
       </c>
       <c r="R10" t="n">
-        <v>309.04</v>
+        <v>49.89</v>
       </c>
       <c r="S10" t="n">
-        <v>459.89</v>
+        <v>63.02</v>
       </c>
       <c r="T10" t="n">
-        <v>239.01</v>
+        <v>43.56</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270104</v>
+        <v>270504</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>44.7</v>
+        <v>30.52</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-12.16</v>
+        <v>-3.78</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-26.82</v>
+        <v>-17</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-34.13</v>
+        <v>-16.63</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-19.52</v>
+        <v>-13.09</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>6.3</v>
+        <v>16.2</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -1787,39 +1787,39 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-18.51</v>
+        <v>-9.56</v>
       </c>
       <c r="P11" t="n">
-        <v>11.74</v>
+        <v>11.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>39.45</v>
+        <v>27.02</v>
       </c>
       <c r="R11" t="n">
-        <v>55.54</v>
+        <v>35.12</v>
       </c>
       <c r="S11" t="n">
-        <v>70.62</v>
+        <v>46.74</v>
       </c>
       <c r="T11" t="n">
-        <v>44.25</v>
+        <v>29.37</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>640209</v>
+        <v>270504</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,28 +1857,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>76.86</v>
+        <v>132.52</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-4.73</v>
+        <v>-5.46</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-9.880000000000001</v>
+        <v>-25.28</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-26.94</v>
+        <v>-30.05</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
@@ -1891,15 +1891,15 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>-7.19</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-19.46</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>25.9</v>
+        <v>11.9</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
@@ -1907,33 +1907,33 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>-1.57</v>
+        <v>-17.84</v>
       </c>
       <c r="P12" t="n">
-        <v>7.87</v>
+        <v>14.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>70.81</v>
+        <v>112.85</v>
       </c>
       <c r="R12" t="n">
-        <v>82.81</v>
+        <v>164.54</v>
       </c>
       <c r="S12" t="n">
-        <v>121.57</v>
+        <v>203.97</v>
       </c>
       <c r="T12" t="n">
-        <v>75.12</v>
+        <v>126.7</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>630503</v>
+        <v>730204</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>212.8</v>
+        <v>56.34</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-9.460000000000001</v>
+        <v>-6.08</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-20.74</v>
+        <v>-16.77</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-12.65</v>
+        <v>-34.06</v>
       </c>
       <c r="H13" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.77</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-16.17</v>
+        <v>-13.22</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>24</v>
+        <v>3.5</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
@@ -2027,33 +2027,33 @@
         </is>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-12.43</v>
+        <v>-9.33</v>
       </c>
       <c r="P13" t="n">
-        <v>16.28</v>
+        <v>10.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>178.16</v>
+        <v>50.55</v>
       </c>
       <c r="R13" t="n">
-        <v>253.85</v>
+        <v>64.92</v>
       </c>
       <c r="S13" t="n">
-        <v>294.5</v>
+        <v>89.83</v>
       </c>
       <c r="T13" t="n">
-        <v>155.05</v>
+        <v>54.23</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>730204</v>
+        <v>270107</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2097,32 +2097,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>133.75</v>
+        <v>163.81</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-10.06</v>
+        <v>-6.86</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-25.44</v>
+        <v>-27.02</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-36.46</v>
+        <v>-6.95</v>
       </c>
       <c r="H14" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.82</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>-19.81</v>
+        <v>-18.28</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
@@ -2147,33 +2147,33 @@
         </is>
       </c>
       <c r="O14" s="3" t="n">
-        <v>-17.13</v>
+        <v>-19.58</v>
       </c>
       <c r="P14" t="n">
-        <v>14.74</v>
+        <v>16.31</v>
       </c>
       <c r="Q14" t="n">
-        <v>114.03</v>
+        <v>137.09</v>
       </c>
       <c r="R14" t="n">
-        <v>166.78</v>
+        <v>200.46</v>
       </c>
       <c r="S14" t="n">
-        <v>209.66</v>
+        <v>237.87</v>
       </c>
       <c r="T14" t="n">
-        <v>131.8</v>
+        <v>125.61</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>730204</v>
+        <v>730206</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2217,32 +2217,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>168.51</v>
+        <v>48.49</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-12.69</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-28.12</v>
+        <v>-25.31</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-13.85</v>
+        <v>-19.25</v>
       </c>
       <c r="H15" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.74</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-17.19</v>
+        <v>-20.33</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>19.9</v>
+        <v>11.4</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
@@ -2267,33 +2267,33 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-19.81</v>
+        <v>-17.87</v>
       </c>
       <c r="P15" t="n">
-        <v>15.75</v>
+        <v>14.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>141.97</v>
+        <v>41.42</v>
       </c>
       <c r="R15" t="n">
-        <v>203.5</v>
+        <v>60.87</v>
       </c>
       <c r="S15" t="n">
-        <v>237.87</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>125.61</v>
+        <v>46.88</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>730206</v>
+        <v>270303</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2337,32 +2337,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>28.73</v>
+        <v>167.38</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-19.48</v>
+        <v>-9.58</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-13.33</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>-21.31</v>
+        <v>-16.67</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>5.88</v>
       </c>
       <c r="H16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.88</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2371,49 +2371,49 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-11.14</v>
+        <v>-17.81</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>35</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>27.2</v>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-5.02</v>
+        <v>-9.23</v>
       </c>
       <c r="P16" t="n">
-        <v>11.61</v>
+        <v>19.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>25.39</v>
+        <v>135.38</v>
       </c>
       <c r="R16" t="n">
-        <v>32.33</v>
+        <v>203.66</v>
       </c>
       <c r="S16" t="n">
-        <v>40.38</v>
+        <v>242.99</v>
       </c>
       <c r="T16" t="n">
-        <v>28.43</v>
+        <v>102.3</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>630702</v>
+        <v>730204</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,32 +2457,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>76.27</v>
+        <v>63.2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-8.67</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-23.97</v>
+        <v>-31.93</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-17.93</v>
+        <v>-37.98</v>
       </c>
       <c r="H17" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.96</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-15.19</v>
+        <v>-23.19</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2499,47 +2499,47 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>3.4</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-15.66</v>
+        <v>-24.49</v>
       </c>
       <c r="P17" t="n">
-        <v>14.55</v>
+        <v>14.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>65.17</v>
+        <v>53.83</v>
       </c>
       <c r="R17" t="n">
-        <v>89.93000000000001</v>
+        <v>82.28</v>
       </c>
       <c r="S17" t="n">
-        <v>102.82</v>
+        <v>109.88</v>
       </c>
       <c r="T17" t="n">
-        <v>69.63</v>
+        <v>60.4</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>650201</v>
+        <v>640703</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.7</v>
+        <v>122.15</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-9.039999999999999</v>
+        <v>-10.12</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-22.6</v>
+        <v>-37.17</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-27.61</v>
+        <v>-49.51</v>
       </c>
       <c r="H18" t="n">
-        <v>0.63</v>
+        <v>0.97</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-16.17</v>
+        <v>-25.99</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
@@ -2627,39 +2627,39 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>-14.29</v>
+        <v>-29.73</v>
       </c>
       <c r="P18" t="n">
-        <v>11.84</v>
+        <v>16.29</v>
       </c>
       <c r="Q18" t="n">
-        <v>26.18</v>
+        <v>102.26</v>
       </c>
       <c r="R18" t="n">
-        <v>35.43</v>
+        <v>165.04</v>
       </c>
       <c r="S18" t="n">
-        <v>46.74</v>
+        <v>246</v>
       </c>
       <c r="T18" t="n">
-        <v>29.45</v>
+        <v>117.2</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270504</v>
+        <v>270202</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>56.96</v>
+        <v>203.3</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-9.210000000000001</v>
+        <v>-11.43</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-16.32</v>
+        <v>-22.24</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-31.51</v>
+        <v>-3.59</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.91</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-13.03</v>
+        <v>-18.99</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>23.3</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -2747,39 +2747,39 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>-8.01</v>
+        <v>-14.8</v>
       </c>
       <c r="P19" t="n">
-        <v>9.92</v>
+        <v>17.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>51.31</v>
+        <v>168.53</v>
       </c>
       <c r="R19" t="n">
-        <v>65.48999999999999</v>
+        <v>250.95</v>
       </c>
       <c r="S19" t="n">
-        <v>90.09999999999999</v>
+        <v>294.5</v>
       </c>
       <c r="T19" t="n">
-        <v>55.64</v>
+        <v>155.05</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270107</v>
+        <v>730204</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>49.54</v>
+        <v>27.91</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-9.27</v>
+        <v>-19.66</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-25.89</v>
+        <v>-13.62</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-24.86</v>
+        <v>-21.42</v>
       </c>
       <c r="H20" t="n">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-19.69</v>
+        <v>-13.09</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -2859,47 +2859,47 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>32.5</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-17.58</v>
+        <v>-6.18</v>
       </c>
       <c r="P20" t="n">
-        <v>14.06</v>
+        <v>12.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>42.57</v>
+        <v>24.46</v>
       </c>
       <c r="R20" t="n">
-        <v>61.69</v>
+        <v>32.11</v>
       </c>
       <c r="S20" t="n">
-        <v>72.68000000000001</v>
+        <v>40.38</v>
       </c>
       <c r="T20" t="n">
-        <v>47.3</v>
+        <v>27.51</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>270303</v>
+        <v>630702</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.91</v>
+        <v>75.47</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-9.66</v>
+        <v>-4.56</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-29.07</v>
+        <v>-21.32</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-21.67</v>
+        <v>-10.64</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-21.69</v>
+        <v>-15.12</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>4.9</v>
+        <v>29.1</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -2987,33 +2987,33 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-20.76</v>
+        <v>-13.88</v>
       </c>
       <c r="P21" t="n">
-        <v>13.95</v>
+        <v>14.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.3</v>
+        <v>64.25</v>
       </c>
       <c r="R21" t="n">
-        <v>33.09</v>
+        <v>88.91</v>
       </c>
       <c r="S21" t="n">
-        <v>39.58</v>
+        <v>102.82</v>
       </c>
       <c r="T21" t="n">
-        <v>23.2</v>
+        <v>69.63</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>640209</v>
+        <v>650201</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3057,32 +3057,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>75.7</v>
+        <v>25.95</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-11.95</v>
+        <v>-6.86</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-28.45</v>
+        <v>-25.64</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-42.08</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.41</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>-20.3</v>
+        <v>-20.5</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>10.7</v>
+        <v>5.5</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
@@ -3107,33 +3107,33 @@
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>-20.14</v>
+        <v>-18.2</v>
       </c>
       <c r="P22" t="n">
-        <v>12.13</v>
+        <v>13.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>66.52</v>
+        <v>22.36</v>
       </c>
       <c r="R22" t="n">
-        <v>94.98</v>
+        <v>32.64</v>
       </c>
       <c r="S22" t="n">
-        <v>130</v>
+        <v>39.58</v>
       </c>
       <c r="T22" t="n">
-        <v>74.76000000000001</v>
+        <v>23.2</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>640703</v>
+        <v>640209</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>48.67</v>
+        <v>75.22</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-12.39</v>
+        <v>-8.91</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-16.58</v>
+        <v>-27.59</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-35.92</v>
+        <v>-36.05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-14.94</v>
+        <v>-19.59</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>20.5</v>
+        <v>6.7</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
@@ -3227,33 +3227,33 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-8.27</v>
+        <v>-20.15</v>
       </c>
       <c r="P23" t="n">
-        <v>11.92</v>
+        <v>12.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>42.87</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>57.22</v>
+        <v>93.55</v>
       </c>
       <c r="S23" t="n">
-        <v>76.8</v>
+        <v>119.51</v>
       </c>
       <c r="T23" t="n">
-        <v>48.05</v>
+        <v>72.13</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270107</v>
+        <v>640703</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>40.88</v>
+        <v>44.46</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-15.01</v>
+        <v>-8.99</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-29.53</v>
+        <v>-26.57</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-49.79</v>
+        <v>-27.79</v>
       </c>
       <c r="H24" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-23.39</v>
+        <v>-18.77</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
@@ -3347,33 +3347,33 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-21.22</v>
+        <v>-19.13</v>
       </c>
       <c r="P24" t="n">
-        <v>15.32</v>
+        <v>11.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>34.62</v>
+        <v>39.18</v>
       </c>
       <c r="R24" t="n">
-        <v>53.36</v>
+        <v>54.74</v>
       </c>
       <c r="S24" t="n">
-        <v>80</v>
+        <v>70.62</v>
       </c>
       <c r="T24" t="n">
-        <v>40.4</v>
+        <v>43.04</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>270203</v>
+        <v>640209</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>122.67</v>
+        <v>40.54</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-15.68</v>
+        <v>-9.73</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-36.68</v>
+        <v>-30.13</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-54.36</v>
+        <v>-44.68</v>
       </c>
       <c r="H25" t="n">
-        <v>1.08</v>
+        <v>0.78</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-27.27</v>
+        <v>-22.77</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>10.6</v>
+        <v>7.3</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
@@ -3467,33 +3467,33 @@
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-28.37</v>
+        <v>-22.69</v>
       </c>
       <c r="P25" t="n">
-        <v>16.22</v>
+        <v>15.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>102.78</v>
+        <v>34.32</v>
       </c>
       <c r="R25" t="n">
-        <v>168.66</v>
+        <v>52.49</v>
       </c>
       <c r="S25" t="n">
-        <v>260</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>121.31</v>
+        <v>39.04</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>270202</v>
+        <v>270203</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -3537,28 +3537,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19.4</v>
+        <v>47.65</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-13.28</v>
+        <v>-10.45</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-22.77</v>
+        <v>-17.84</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-32.83</v>
+        <v>-30.3</v>
       </c>
       <c r="H26" t="n">
-        <v>1.02</v>
+        <v>0.73</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-17.38</v>
+        <v>-15.96</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>17.3</v>
+        <v>19.7</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
@@ -3587,39 +3587,39 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-14.46</v>
+        <v>-10.4</v>
       </c>
       <c r="P26" t="n">
-        <v>11.91</v>
+        <v>12.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>17.09</v>
+        <v>41.72</v>
       </c>
       <c r="R26" t="n">
-        <v>23.48</v>
+        <v>56.7</v>
       </c>
       <c r="S26" t="n">
-        <v>29.4</v>
+        <v>76.8</v>
       </c>
       <c r="T26" t="n">
-        <v>19.21</v>
+        <v>46.53</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270303</v>
+        <v>270107</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,28 +3657,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>176.4</v>
+        <v>308</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-13.7</v>
+        <v>-11.39</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-24.52</v>
+        <v>-27.19</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-26.5</v>
+        <v>-36.22</v>
       </c>
       <c r="H27" t="n">
-        <v>0.85</v>
+        <v>1.16</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-22</v>
+        <v>-20.73</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -3707,33 +3707,33 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-16.21</v>
+        <v>-19.75</v>
       </c>
       <c r="P27" t="n">
-        <v>13.51</v>
+        <v>14.77</v>
       </c>
       <c r="Q27" t="n">
-        <v>152.57</v>
+        <v>262.51</v>
       </c>
       <c r="R27" t="n">
-        <v>226.16</v>
+        <v>388.54</v>
       </c>
       <c r="S27" t="n">
-        <v>279.78</v>
+        <v>554.4</v>
       </c>
       <c r="T27" t="n">
-        <v>174</v>
+        <v>297.49</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>270103</v>
+        <v>730204</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3777,28 +3777,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>306.91</v>
+        <v>171.37</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-17.1</v>
+        <v>-14.49</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-25.31</v>
+        <v>-25.64</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-43.44</v>
+        <v>-21.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.18</v>
+        <v>0.89</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-22.16</v>
+        <v>-23.22</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -3827,33 +3827,33 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>-17</v>
+        <v>-18.2</v>
       </c>
       <c r="P28" t="n">
-        <v>15.29</v>
+        <v>14.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>260</v>
+        <v>147.17</v>
       </c>
       <c r="R28" t="n">
-        <v>394.29</v>
+        <v>223.21</v>
       </c>
       <c r="S28" t="n">
-        <v>554.4</v>
+        <v>279.78</v>
       </c>
       <c r="T28" t="n">
-        <v>299.23</v>
+        <v>167</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>730204</v>
+        <v>270103</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3897,28 +3897,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>44.67</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.14</v>
+        <v>-5.67</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-17.96</v>
+        <v>-7.26</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-27.29</v>
+        <v>-23.07</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
@@ -3931,49 +3931,49 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-11.29</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-5.85</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>10.4</v>
+        <v>24.5</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O29" s="3" t="n">
-        <v>-9.65</v>
+      <c r="O29" s="2" t="n">
+        <v>0.18</v>
       </c>
       <c r="P29" t="n">
-        <v>8</v>
+        <v>7.55</v>
       </c>
       <c r="Q29" t="n">
-        <v>41.1</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="R29" t="n">
-        <v>50.35</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>63.02</v>
+        <v>121.57</v>
       </c>
       <c r="T29" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>0</v>
+        <v>75.12</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>270504</v>
+        <v>630503</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -39,14 +39,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -473,7 +473,7 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="31" max="31"/>
     <col width="66" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
@@ -657,32 +657,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>73.95999999999999</v>
+        <v>189.04</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.63</v>
+        <v>-3.84</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-10.08</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>-15.85</v>
+        <v>5.76</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-8.59</v>
       </c>
       <c r="H2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.38</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -690,16 +690,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>-5.63</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="K2" s="2" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>30.9</v>
+        <v>34</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,39 +707,39 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-2.64</v>
+        <v>13.08</v>
       </c>
       <c r="P2" t="n">
-        <v>7.75</v>
+        <v>12.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>68.23</v>
+        <v>164.68</v>
       </c>
       <c r="R2" t="n">
-        <v>78.37</v>
+        <v>197.11</v>
       </c>
       <c r="S2" t="n">
-        <v>105.43</v>
+        <v>232.68</v>
       </c>
       <c r="T2" t="n">
-        <v>66.11</v>
-      </c>
-      <c r="U2" s="3" t="n">
-        <v>1</v>
+        <v>159.34</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>710101</v>
+        <v>270104</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -747,17 +747,17 @@
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" s="3" t="n">
-        <v>22.2</v>
+      <c r="AD2" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,30 +777,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>219.19</v>
+        <v>47.6</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-4.08</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>-23.52</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>-42.65</v>
+        <v>3.14</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>-16.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+        <v>1.02</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -810,56 +810,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>-15.1</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="2" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>16.7</v>
+        <v>24.3</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O3" s="3" t="n">
-        <v>-16.08</v>
+      <c r="O3" s="2" t="n">
+        <v>-2.49</v>
       </c>
       <c r="P3" t="n">
-        <v>12.53</v>
+        <v>8.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>191.72</v>
+        <v>43.67</v>
       </c>
       <c r="R3" t="n">
-        <v>258.19</v>
+        <v>49.64</v>
       </c>
       <c r="S3" t="n">
-        <v>377.5</v>
+        <v>63.02</v>
       </c>
       <c r="T3" t="n">
-        <v>204.5</v>
-      </c>
-      <c r="U3" s="3" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="U3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270104</v>
+        <v>270504</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -867,8 +867,8 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" s="3" t="n">
-        <v>22.2</v>
+      <c r="AD3" s="2" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-5.34</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-18.04</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>-23.84</v>
+        <v>20.99</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-14.19</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>-15.87</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+        <v>1.03</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -930,33 +930,33 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>-13.07</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="K4" s="2" t="n">
+        <v>-9.08</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>23</v>
+        <v>26.9</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>-10.6</v>
+      <c r="O4" s="2" t="n">
+        <v>-6.87</v>
       </c>
       <c r="P4" t="n">
-        <v>11.86</v>
+        <v>11.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.82</v>
+        <v>18.55</v>
       </c>
       <c r="R4" t="n">
-        <v>23.26</v>
+        <v>23.09</v>
       </c>
       <c r="S4" t="n">
         <v>29.4</v>
@@ -964,12 +964,12 @@
       <c r="T4" t="n">
         <v>19.08</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -987,8 +987,8 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="3" t="n">
-        <v>20.4</v>
+      <c r="AD4" s="2" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,30 +1017,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>114</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-10.85</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-32</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>-34.52</v>
+        <v>245</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>-9.66</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-25.98</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>-34.93</v>
       </c>
       <c r="H5" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+        <v>1.21</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1050,56 +1050,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>-24.35</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="K5" s="2" t="n">
+        <v>-18.31</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O5" s="3" t="n">
-        <v>-24.56</v>
+      <c r="O5" s="2" t="n">
+        <v>-18.66</v>
       </c>
       <c r="P5" t="n">
-        <v>15.21</v>
+        <v>11.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>96.66</v>
+        <v>217.02</v>
       </c>
       <c r="R5" t="n">
-        <v>150.69</v>
+        <v>299.9</v>
       </c>
       <c r="S5" t="n">
-        <v>189.92</v>
+        <v>442</v>
       </c>
       <c r="T5" t="n">
-        <v>107.9</v>
-      </c>
-      <c r="U5" s="3" t="n">
+        <v>234.98</v>
+      </c>
+      <c r="U5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>270401</v>
+        <v>270104</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1107,8 +1107,8 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="3" t="n">
-        <v>20.4</v>
+      <c r="AD5" s="2" t="n">
+        <v>24.1</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>171.85</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-13.86</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-4.69</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>-14.42</v>
+        <v>219.55</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>-6.09</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-20.45</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>-36.15</v>
       </c>
       <c r="H6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.58</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1170,46 +1170,46 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>-12.59</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="n">
+        <v>-14.02</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>17.3</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>2.75</v>
+        <v>-13.13</v>
       </c>
       <c r="P6" t="n">
-        <v>13.91</v>
+        <v>12.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>147.95</v>
+        <v>191.99</v>
       </c>
       <c r="R6" t="n">
-        <v>196.59</v>
+        <v>255.36</v>
       </c>
       <c r="S6" t="n">
-        <v>232.68</v>
+        <v>377.5</v>
       </c>
       <c r="T6" t="n">
-        <v>159.34</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
+        <v>204.5</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1227,8 +1227,8 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="3" t="n">
-        <v>20.4</v>
+      <c r="AD6" s="2" t="n">
+        <v>22.2</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,30 +1257,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>46.15</v>
+        <v>74.86</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-6.56</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>-11.32</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>-26.17</v>
+        <v>2.83</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-8.67</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>-17.77</v>
       </c>
       <c r="H7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+        <v>1.76</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1290,50 +1290,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>-16.54</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-3.88</v>
+        <v>31.4</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>-1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>17.19</v>
+        <v>7.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>38.22</v>
+        <v>69.22</v>
       </c>
       <c r="R7" t="n">
-        <v>55.29</v>
+        <v>78.02</v>
       </c>
       <c r="S7" t="n">
-        <v>67.05</v>
+        <v>105.43</v>
       </c>
       <c r="T7" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0</v>
+        <v>66.11</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>640108</v>
+        <v>710101</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="3" t="n">
+      <c r="AD7" s="2" t="n">
         <v>18.5</v>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1377,30 +1377,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>242.8</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-10.67</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>-28.49</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>-38.69</v>
+        <v>31.45</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-16.27</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>-8.039999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
+        <v>0.72</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1410,56 +1410,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
-        <v>-20.18</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="K8" s="2" t="n">
+        <v>-9.65</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1.5</v>
+        <v>21.3</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O8" s="3" t="n">
-        <v>-21.05</v>
+      <c r="O8" s="2" t="n">
+        <v>-8.949999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>11.66</v>
+        <v>11.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>214.49</v>
+        <v>27.88</v>
       </c>
       <c r="R8" t="n">
-        <v>304.2</v>
+        <v>34.81</v>
       </c>
       <c r="S8" t="n">
-        <v>442</v>
+        <v>46.74</v>
       </c>
       <c r="T8" t="n">
-        <v>234.98</v>
-      </c>
-      <c r="U8" s="3" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270104</v>
+        <v>270504</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1467,8 +1467,8 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="3" t="n">
-        <v>18.5</v>
+      <c r="AD8" s="2" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>111.75</v>
+        <v>47.17</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-12.87</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>-12.56</v>
+        <v>-5.28</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-11.91</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>-12.65</v>
       </c>
       <c r="H9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.47</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1530,50 +1530,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K9" s="3" t="n">
-        <v>-6.56</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="K9" s="2" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-5.43</v>
+        <v>19.2</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>-4.59</v>
       </c>
       <c r="P9" t="n">
-        <v>12.43</v>
+        <v>16.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>97.86</v>
+        <v>39.34</v>
       </c>
       <c r="R9" t="n">
-        <v>119.59</v>
+        <v>54.98</v>
       </c>
       <c r="S9" t="n">
-        <v>131.48</v>
+        <v>67.05</v>
       </c>
       <c r="T9" t="n">
-        <v>94.73</v>
-      </c>
-      <c r="U9" s="3" t="n">
-        <v>1</v>
+        <v>43.01</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>270202</v>
+        <v>640108</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="3" t="n">
+      <c r="AD9" s="2" t="n">
         <v>14.8</v>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1617,30 +1617,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>-16.59</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>-20.22</v>
+        <v>114.44</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>-11.05</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-29.09</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>-25.53</v>
       </c>
       <c r="H10" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+        <v>0.98</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1650,50 +1650,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="n">
+        <v>-22.85</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>18.5</v>
+        <v>5.4</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O10" s="3" t="n">
-        <v>-9.15</v>
+      <c r="O10" s="2" t="n">
+        <v>-21.77</v>
       </c>
       <c r="P10" t="n">
-        <v>8.23</v>
+        <v>14.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>42.4</v>
+        <v>97.62</v>
       </c>
       <c r="R10" t="n">
-        <v>49.89</v>
+        <v>148.34</v>
       </c>
       <c r="S10" t="n">
-        <v>63.02</v>
+        <v>189.92</v>
       </c>
       <c r="T10" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="U10" s="3" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="U10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270504</v>
+        <v>270401</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" s="3" t="n">
+      <c r="AD10" s="2" t="n">
         <v>14.8</v>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,32 +1737,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>30.52</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>-17</v>
+        <v>77.39</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-18.39</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-16.63</v>
+        <v>2.93</v>
       </c>
       <c r="H11" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.55</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1770,56 +1770,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K11" s="3" t="n">
-        <v>-13.09</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="K11" s="2" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>16.2</v>
+        <v>27.6</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O11" s="3" t="n">
-        <v>-9.56</v>
+      <c r="O11" s="2" t="n">
+        <v>-11.07</v>
       </c>
       <c r="P11" t="n">
-        <v>11.46</v>
+        <v>14.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>27.02</v>
+        <v>66.2</v>
       </c>
       <c r="R11" t="n">
-        <v>35.12</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>46.74</v>
+        <v>102.82</v>
       </c>
       <c r="T11" t="n">
-        <v>29.37</v>
-      </c>
-      <c r="U11" s="3" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="U11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>270504</v>
+        <v>650201</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1827,8 +1827,8 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="3" t="n">
-        <v>14.8</v>
+      <c r="AD11" s="2" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,30 +1857,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>132.52</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>-5.46</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>-25.28</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>-30.05</v>
+        <v>50</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-22.56</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>-9.34</v>
       </c>
       <c r="H12" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+        <v>0.72</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1890,56 +1890,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>-19.46</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="K12" s="2" t="n">
+        <v>-16.86</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O12" s="3" t="n">
-        <v>-17.84</v>
+      <c r="O12" s="2" t="n">
+        <v>-15.24</v>
       </c>
       <c r="P12" t="n">
-        <v>14.84</v>
+        <v>14.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>112.85</v>
+        <v>42.82</v>
       </c>
       <c r="R12" t="n">
-        <v>164.54</v>
+        <v>60.14</v>
       </c>
       <c r="S12" t="n">
-        <v>203.97</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="U12" s="3" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="U12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>730204</v>
+        <v>270303</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1947,8 +1947,8 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AD12" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD12" s="2" t="n">
+        <v>11.1</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>56.34</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-6.08</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-16.77</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>-34.06</v>
+        <v>111.01</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-11.69</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>-3.49</v>
       </c>
       <c r="H13" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.15</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2010,50 +2010,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K13" s="3" t="n">
-        <v>-13.22</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="K13" s="2" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>-9.33</v>
+        <v>31.7</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>-4.37</v>
       </c>
       <c r="P13" t="n">
-        <v>10.28</v>
+        <v>12.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>50.55</v>
+        <v>97.11</v>
       </c>
       <c r="R13" t="n">
-        <v>64.92</v>
+        <v>118.85</v>
       </c>
       <c r="S13" t="n">
-        <v>89.83</v>
+        <v>131.25</v>
       </c>
       <c r="T13" t="n">
-        <v>54.23</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>0</v>
+        <v>94.73</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270107</v>
+        <v>270202</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2067,7 +2067,7 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" s="3" t="n">
+      <c r="AD13" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE13" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>163.81</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-6.86</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-27.02</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>-6.95</v>
+        <v>64.59999999999999</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>-8.91</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>-29.57</v>
       </c>
       <c r="H14" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.97</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2130,50 +2130,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>-18.28</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="K14" s="2" t="n">
+        <v>-20.14</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>19.9</v>
+        <v>7.5</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O14" s="3" t="n">
-        <v>-19.58</v>
+      <c r="O14" s="2" t="n">
+        <v>-22.68</v>
       </c>
       <c r="P14" t="n">
-        <v>16.31</v>
+        <v>14.37</v>
       </c>
       <c r="Q14" t="n">
-        <v>137.09</v>
+        <v>55.32</v>
       </c>
       <c r="R14" t="n">
-        <v>200.46</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>237.87</v>
+        <v>109.88</v>
       </c>
       <c r="T14" t="n">
-        <v>125.61</v>
-      </c>
-      <c r="U14" s="3" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="U14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>730206</v>
+        <v>640703</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="n">
+      <c r="AD14" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2217,30 +2217,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>48.49</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>-8.609999999999999</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>-25.31</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>-19.25</v>
+        <v>298.17</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>-15.12</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-25.81</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>-41.54</v>
       </c>
       <c r="H15" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+        <v>1.14</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2250,50 +2250,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>-20.33</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="K15" s="2" t="n">
+        <v>-22.22</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>11.4</v>
+        <v>3.4</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O15" s="3" t="n">
-        <v>-17.87</v>
+      <c r="O15" s="2" t="n">
+        <v>-18.49</v>
       </c>
       <c r="P15" t="n">
-        <v>14.59</v>
+        <v>14.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.42</v>
+        <v>253.51</v>
       </c>
       <c r="R15" t="n">
-        <v>60.87</v>
+        <v>383.35</v>
       </c>
       <c r="S15" t="n">
-        <v>72.68000000000001</v>
+        <v>554.4</v>
       </c>
       <c r="T15" t="n">
-        <v>46.88</v>
-      </c>
-      <c r="U15" s="3" t="n">
+        <v>294.66</v>
+      </c>
+      <c r="U15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270303</v>
+        <v>730204</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="n">
+      <c r="AD15" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,28 +2337,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>167.38</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>-9.58</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>-16.67</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>5.88</v>
+        <v>26.27</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>-7.82</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-28.42</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.42</v>
       </c>
       <c r="H16" t="n">
-        <v>0.88</v>
+        <v>0.38</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2370,56 +2370,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
-        <v>-17.81</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="K16" s="2" t="n">
+        <v>-18.21</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>27.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O16" s="3" t="n">
-        <v>-9.23</v>
+      <c r="O16" s="2" t="n">
+        <v>-21.1</v>
       </c>
       <c r="P16" t="n">
-        <v>19.12</v>
+        <v>13.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>135.38</v>
+        <v>22.73</v>
       </c>
       <c r="R16" t="n">
-        <v>203.66</v>
+        <v>32.12</v>
       </c>
       <c r="S16" t="n">
-        <v>242.99</v>
+        <v>39.58</v>
       </c>
       <c r="T16" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="U16" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="U16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>730204</v>
+        <v>640209</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2427,8 +2427,8 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD16" s="2" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>今日上涨且放量</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,30 +2457,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>-31.93</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>-37.98</v>
+        <v>44.84</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-25.28</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>-19.15</v>
       </c>
       <c r="H17" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+        <v>0.65</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2490,56 +2490,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>-23.19</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="K17" s="2" t="n">
+        <v>-16.93</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O17" s="3" t="n">
-        <v>-24.49</v>
+      <c r="O17" s="2" t="n">
+        <v>-17.96</v>
       </c>
       <c r="P17" t="n">
-        <v>14.83</v>
+        <v>11.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>53.83</v>
+        <v>39.62</v>
       </c>
       <c r="R17" t="n">
-        <v>82.28</v>
+        <v>53.98</v>
       </c>
       <c r="S17" t="n">
-        <v>109.88</v>
+        <v>70.62</v>
       </c>
       <c r="T17" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="U17" s="3" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="U17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>640703</v>
+        <v>640209</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2547,8 +2547,8 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD17" s="2" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,32 +2577,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>122.15</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-10.12</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>-37.17</v>
+        <v>162.98</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>-12.43</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-25.54</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-49.51</v>
+        <v>2.87</v>
       </c>
       <c r="H18" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.74</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2610,56 +2610,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n">
-        <v>-25.99</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="K18" s="2" t="n">
+        <v>-17.55</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>10.7</v>
+        <v>20.6</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O18" s="3" t="n">
-        <v>-29.73</v>
+      <c r="O18" s="2" t="n">
+        <v>-18.22</v>
       </c>
       <c r="P18" t="n">
-        <v>16.29</v>
+        <v>15.97</v>
       </c>
       <c r="Q18" t="n">
-        <v>102.26</v>
+        <v>136.95</v>
       </c>
       <c r="R18" t="n">
-        <v>165.04</v>
+        <v>197.67</v>
       </c>
       <c r="S18" t="n">
-        <v>246</v>
+        <v>237.87</v>
       </c>
       <c r="T18" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="U18" s="3" t="n">
+        <v>125.61</v>
+      </c>
+      <c r="U18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270202</v>
+        <v>730206</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2667,8 +2667,8 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD18" s="2" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>203.3</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-11.43</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>-22.24</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>-3.59</v>
+        <v>28.09</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>-14.36</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-14.98</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>-15.67</v>
       </c>
       <c r="H19" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.14</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2730,56 +2730,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>-18.99</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="K19" s="2" t="n">
+        <v>-11.85</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>-14.8</v>
+        <v>33.7</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>-7.66</v>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>12.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>168.53</v>
+        <v>24.6</v>
       </c>
       <c r="R19" t="n">
-        <v>250.95</v>
+        <v>31.87</v>
       </c>
       <c r="S19" t="n">
-        <v>294.5</v>
+        <v>40.38</v>
       </c>
       <c r="T19" t="n">
-        <v>155.05</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>0</v>
+        <v>27.51</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>730204</v>
+        <v>630702</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2787,8 +2787,8 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD19" s="2" t="n">
+        <v>5.6</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,30 +2817,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-19.66</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-13.62</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>-21.42</v>
+        <v>76.04000000000001</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-9.84</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>-24.81</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
+        <v>0.82</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2850,56 +2850,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>-13.09</v>
+      <c r="K20" s="2" t="n">
+        <v>-7.37</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>-6.18</v>
+        <v>23</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>-2.52</v>
       </c>
       <c r="P20" t="n">
-        <v>12.37</v>
+        <v>7.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>24.46</v>
+        <v>70.2</v>
       </c>
       <c r="R20" t="n">
-        <v>32.11</v>
+        <v>82.09</v>
       </c>
       <c r="S20" t="n">
-        <v>40.38</v>
+        <v>121.57</v>
       </c>
       <c r="T20" t="n">
-        <v>27.51</v>
-      </c>
-      <c r="U20" s="3" t="n">
+        <v>75.12</v>
+      </c>
+      <c r="U20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>630702</v>
+        <v>630503</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2907,8 +2907,8 @@
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="AD20" s="2" t="n">
+        <v>3.7</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,32 +2937,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>75.47</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-4.56</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>-21.32</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>-10.64</v>
+        <v>122.15</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>-12.59</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-34.01</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>-43.9</v>
       </c>
       <c r="H21" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.89</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2970,56 +2970,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>-15.12</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="K21" s="2" t="n">
+        <v>-24.55</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>29.1</v>
+        <v>7.6</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>-13.88</v>
+      <c r="O21" s="2" t="n">
+        <v>-26.69</v>
       </c>
       <c r="P21" t="n">
-        <v>14.86</v>
+        <v>15.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>64.25</v>
+        <v>103.29</v>
       </c>
       <c r="R21" t="n">
-        <v>88.91</v>
+        <v>161.9</v>
       </c>
       <c r="S21" t="n">
-        <v>102.82</v>
+        <v>239.77</v>
       </c>
       <c r="T21" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="U21" s="3" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="U21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>650201</v>
+        <v>270202</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3027,8 +3027,8 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" s="3" t="n">
-        <v>5.6</v>
+      <c r="AD21" s="2" t="n">
+        <v>3.7</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,32 +3057,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-6.86</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>-25.64</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>-9.359999999999999</v>
+        <v>173.63</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>-12.88</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-26.77</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>-12.75</v>
       </c>
       <c r="H22" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.93</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3090,56 +3090,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>-20.5</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="K22" s="2" t="n">
+        <v>-21.09</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O22" s="3" t="n">
-        <v>-18.2</v>
+      <c r="O22" s="2" t="n">
+        <v>-19.45</v>
       </c>
       <c r="P22" t="n">
-        <v>13.82</v>
+        <v>13.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>22.36</v>
+        <v>149.84</v>
       </c>
       <c r="R22" t="n">
-        <v>32.64</v>
+        <v>220.03</v>
       </c>
       <c r="S22" t="n">
-        <v>39.58</v>
+        <v>279.78</v>
       </c>
       <c r="T22" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="U22" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="U22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>640209</v>
+        <v>270103</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3147,8 +3147,8 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="n">
-        <v>5.6</v>
+      <c r="AD22" s="2" t="n">
+        <v>3.7</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,30 +3177,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75.22</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>-8.91</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>-27.59</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>-36.05</v>
+        <v>57.25</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>-25.59</v>
       </c>
       <c r="H23" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
+        <v>0.75</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3210,56 +3210,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K23" s="3" t="n">
-        <v>-19.59</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="K23" s="2" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O23" s="3" t="n">
-        <v>-20.15</v>
+      <c r="O23" s="2" t="n">
+        <v>-6.3</v>
       </c>
       <c r="P23" t="n">
-        <v>12.24</v>
+        <v>9.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>66.01000000000001</v>
+        <v>51.57</v>
       </c>
       <c r="R23" t="n">
-        <v>93.55</v>
+        <v>64.47</v>
       </c>
       <c r="S23" t="n">
-        <v>119.51</v>
+        <v>89.83</v>
       </c>
       <c r="T23" t="n">
-        <v>72.13</v>
-      </c>
-      <c r="U23" s="3" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="U23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>640703</v>
+        <v>270107</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3267,8 +3267,8 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" s="3" t="n">
-        <v>5.6</v>
+      <c r="AD23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,30 +3297,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>44.46</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-8.99</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>-26.57</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>-27.79</v>
+        <v>134.06</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>-8.09</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-21.97</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>-21.38</v>
       </c>
       <c r="H24" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
+        <v>0.79</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3330,56 +3330,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>-18.77</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="K24" s="2" t="n">
+        <v>-17.58</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>6.6</v>
+        <v>14.2</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O24" s="3" t="n">
-        <v>-19.13</v>
+      <c r="O24" s="2" t="n">
+        <v>-14.65</v>
       </c>
       <c r="P24" t="n">
-        <v>11.87</v>
+        <v>14.73</v>
       </c>
       <c r="Q24" t="n">
-        <v>39.18</v>
+        <v>114.32</v>
       </c>
       <c r="R24" t="n">
-        <v>54.74</v>
+        <v>162.65</v>
       </c>
       <c r="S24" t="n">
-        <v>70.62</v>
+        <v>203.97</v>
       </c>
       <c r="T24" t="n">
-        <v>43.04</v>
-      </c>
-      <c r="U24" s="3" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="U24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>640209</v>
+        <v>730204</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3387,8 +3387,8 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" s="3" t="n">
-        <v>5.6</v>
+      <c r="AD24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,30 +3417,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>40.54</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-9.73</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>-30.13</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>-44.68</v>
+        <v>76.2</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>-28.02</v>
       </c>
       <c r="H25" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
+        <v>0.59</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3450,56 +3450,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>-22.77</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="K25" s="2" t="n">
+        <v>-17.49</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>7.3</v>
+        <v>9.6</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O25" s="3" t="n">
-        <v>-22.69</v>
+      <c r="O25" s="2" t="n">
+        <v>-16.48</v>
       </c>
       <c r="P25" t="n">
-        <v>15.33</v>
+        <v>11.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>34.32</v>
+        <v>67.28</v>
       </c>
       <c r="R25" t="n">
-        <v>52.49</v>
+        <v>92.36</v>
       </c>
       <c r="S25" t="n">
-        <v>76.43000000000001</v>
+        <v>119.51</v>
       </c>
       <c r="T25" t="n">
-        <v>39.04</v>
-      </c>
-      <c r="U25" s="3" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="U25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>270203</v>
+        <v>640703</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3507,8 +3507,8 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" s="3" t="n">
-        <v>5.6</v>
+      <c r="AD25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,30 +3537,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-10.45</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-17.84</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>-30.3</v>
+        <v>41.29</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-28.97</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>-37.39</v>
       </c>
       <c r="H26" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
+        <v>0.74</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3570,56 +3570,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>-15.96</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="K26" s="2" t="n">
+        <v>-20.05</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>19.7</v>
+        <v>9</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O26" s="3" t="n">
-        <v>-10.4</v>
+      <c r="O26" s="2" t="n">
+        <v>-21.65</v>
       </c>
       <c r="P26" t="n">
-        <v>12.44</v>
+        <v>15.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>41.72</v>
+        <v>35.03</v>
       </c>
       <c r="R26" t="n">
-        <v>56.7</v>
+        <v>51.65</v>
       </c>
       <c r="S26" t="n">
-        <v>76.8</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>46.53</v>
-      </c>
-      <c r="U26" s="3" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="U26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270107</v>
+        <v>270203</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3627,8 +3627,8 @@
       <c r="AC26" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="3" t="n">
-        <v>5.6</v>
+      <c r="AD26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,30 +3657,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>308</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>-11.39</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>-27.19</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>-36.22</v>
+        <v>48.11</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>-10.61</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-15.27</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>-23.63</v>
       </c>
       <c r="H27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
+        <v>0.7</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3690,56 +3690,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K27" s="3" t="n">
-        <v>-20.73</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="K27" s="2" t="n">
+        <v>-14.49</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>12.4</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O27" s="3" t="n">
-        <v>-19.75</v>
+      <c r="O27" s="2" t="n">
+        <v>-7.95</v>
       </c>
       <c r="P27" t="n">
-        <v>14.77</v>
+        <v>11.33</v>
       </c>
       <c r="Q27" t="n">
-        <v>262.51</v>
+        <v>42.66</v>
       </c>
       <c r="R27" t="n">
-        <v>388.54</v>
+        <v>56.27</v>
       </c>
       <c r="S27" t="n">
-        <v>554.4</v>
+        <v>76.8</v>
       </c>
       <c r="T27" t="n">
-        <v>297.49</v>
-      </c>
-      <c r="U27" s="3" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="U27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>730204</v>
+        <v>270107</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3747,8 +3747,8 @@
       <c r="AC27" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="3" t="n">
-        <v>3.7</v>
+      <c r="AD27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>171.37</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>-14.49</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>-25.64</v>
+        <v>170.61</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>-15.22</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-13.96</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-21.4</v>
+        <v>22.47</v>
       </c>
       <c r="H28" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.82</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3810,56 +3810,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K28" s="3" t="n">
-        <v>-23.22</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="K28" s="2" t="n">
+        <v>-15.65</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>2.6</v>
+        <v>26.9</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O28" s="3" t="n">
-        <v>-18.2</v>
+      <c r="O28" s="2" t="n">
+        <v>-6.64</v>
       </c>
       <c r="P28" t="n">
-        <v>14.12</v>
+        <v>18.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>147.17</v>
+        <v>138.36</v>
       </c>
       <c r="R28" t="n">
-        <v>223.21</v>
+        <v>202.27</v>
       </c>
       <c r="S28" t="n">
-        <v>279.78</v>
+        <v>242.99</v>
       </c>
       <c r="T28" t="n">
-        <v>167</v>
-      </c>
-      <c r="U28" s="3" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="U28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>270103</v>
+        <v>730204</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3867,8 +3867,8 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" s="3" t="n">
-        <v>3.7</v>
+      <c r="AD28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>77.68000000000001</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-5.67</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-7.26</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>-23.07</v>
+        <v>204.54</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>-17.09</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-20.24</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>-3.99</v>
       </c>
       <c r="H29" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.82</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3930,12 +3930,12 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>-5.85</v>
+      <c r="K29" s="2" t="n">
+        <v>-17.64</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M29" t="n">
@@ -3947,33 +3947,33 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>0.18</v>
+        <v>-12.92</v>
       </c>
       <c r="P29" t="n">
-        <v>7.55</v>
+        <v>17.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>71.81999999999999</v>
+        <v>169.5</v>
       </c>
       <c r="R29" t="n">
-        <v>82.51000000000001</v>
+        <v>248.35</v>
       </c>
       <c r="S29" t="n">
-        <v>121.57</v>
+        <v>294.5</v>
       </c>
       <c r="T29" t="n">
-        <v>75.12</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2</v>
+        <v>155.05</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>630503</v>
+        <v>730204</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       <c r="AC29" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="n">
+      <c r="AD29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -39,14 +39,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -473,7 +473,7 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="19" customWidth="1" min="31" max="31"/>
+    <col width="57" customWidth="1" min="31" max="31"/>
     <col width="66" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>189.04</v>
+        <v>200</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-3.84</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>-8.59</v>
+        <v>2.3</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-3.31</v>
       </c>
       <c r="H2" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -687,36 +687,36 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-4.09</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+        <v>0.88</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O2" s="3" t="n">
-        <v>13.08</v>
+      <c r="O2" s="2" t="n">
+        <v>20.47</v>
       </c>
       <c r="P2" t="n">
-        <v>12.89</v>
+        <v>12.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>164.68</v>
+        <v>175.43</v>
       </c>
       <c r="R2" t="n">
-        <v>197.11</v>
+        <v>198.25</v>
       </c>
       <c r="S2" t="n">
         <v>232.68</v>
@@ -725,21 +725,21 @@
         <v>159.34</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>270104</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -748,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>33.3</v>
+        <v>48.1</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>20日跑赢沪深300超过10%</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,30 +777,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>-9.81</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>-16.2</v>
+        <v>21.71</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>-20.94</v>
       </c>
       <c r="H3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+        <v>1.16</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -810,50 +810,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="n">
+        <v>-5.51</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>24.3</v>
+        <v>29.4</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>-2.49</v>
+      <c r="O3" s="3" t="n">
+        <v>-1.6</v>
       </c>
       <c r="P3" t="n">
-        <v>8.25</v>
+        <v>11.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>43.67</v>
+        <v>19.19</v>
       </c>
       <c r="R3" t="n">
-        <v>49.64</v>
+        <v>22.98</v>
       </c>
       <c r="S3" t="n">
-        <v>63.02</v>
+        <v>29.4</v>
       </c>
       <c r="T3" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="U3" s="2" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="U3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270504</v>
+        <v>270303</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -867,7 +867,7 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" s="2" t="n">
+      <c r="AD3" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="AE3" t="inlineStr">
@@ -897,30 +897,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.99</v>
+        <v>233.81</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-14.19</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>-15.87</v>
+        <v>3.69</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-35.37</v>
       </c>
       <c r="H4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+        <v>1.91</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -930,56 +930,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>-9.08</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>-6.87</v>
+      <c r="O4" s="3" t="n">
+        <v>-7.26</v>
       </c>
       <c r="P4" t="n">
-        <v>11.65</v>
+        <v>12.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.55</v>
+        <v>204.27</v>
       </c>
       <c r="R4" t="n">
-        <v>23.09</v>
+        <v>253.32</v>
       </c>
       <c r="S4" t="n">
-        <v>29.4</v>
+        <v>346.04</v>
       </c>
       <c r="T4" t="n">
-        <v>19.08</v>
-      </c>
-      <c r="U4" s="2" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="U4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270303</v>
+        <v>270104</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -987,8 +987,8 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="2" t="n">
-        <v>24.1</v>
+      <c r="AD4" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>245</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>-9.66</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-25.98</v>
+        <v>173.61</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-19.77</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-34.93</v>
+        <v>1.55</v>
       </c>
       <c r="H5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.85</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1050,56 +1050,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>-18.31</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" s="3" t="n">
+        <v>-11.21</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>28.8</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>-18.66</v>
+      <c r="O5" s="3" t="n">
+        <v>-12.17</v>
       </c>
       <c r="P5" t="n">
-        <v>11.42</v>
+        <v>15.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>217.02</v>
+        <v>146.32</v>
       </c>
       <c r="R5" t="n">
-        <v>299.9</v>
+        <v>195.53</v>
       </c>
       <c r="S5" t="n">
-        <v>442</v>
+        <v>237.87</v>
       </c>
       <c r="T5" t="n">
-        <v>234.98</v>
-      </c>
-      <c r="U5" s="2" t="n">
+        <v>125.61</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>270104</v>
+        <v>730206</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1107,8 +1107,8 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="2" t="n">
-        <v>24.1</v>
+      <c r="AD5" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,30 +1137,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>219.55</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>-6.09</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-20.45</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>-36.15</v>
+        <v>248.98</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-24.21</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>-40.98</v>
       </c>
       <c r="H6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1170,46 +1170,46 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>-14.02</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="K6" s="3" t="n">
+        <v>-15.86</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>17.3</v>
+        <v>6.6</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>-13.13</v>
+      <c r="O6" s="3" t="n">
+        <v>-16.61</v>
       </c>
       <c r="P6" t="n">
-        <v>12.55</v>
+        <v>11.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>191.99</v>
+        <v>221.13</v>
       </c>
       <c r="R6" t="n">
-        <v>255.36</v>
+        <v>295.92</v>
       </c>
       <c r="S6" t="n">
-        <v>377.5</v>
+        <v>442</v>
       </c>
       <c r="T6" t="n">
-        <v>204.5</v>
-      </c>
-      <c r="U6" s="2" t="n">
+        <v>234.98</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1227,8 +1227,8 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="2" t="n">
-        <v>22.2</v>
+      <c r="AD6" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>74.86</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-8.67</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>-17.77</v>
+        <v>75.98</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-22.37</v>
       </c>
       <c r="H7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+        <v>1.7</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1290,16 +1290,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>-4.05</v>
+      <c r="K7" s="3" t="n">
+        <v>-2.23</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>31.4</v>
+        <v>35.7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-1.35</v>
+        <v>0.19</v>
       </c>
       <c r="P7" t="n">
-        <v>7.54</v>
+        <v>7.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>69.22</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>78.02</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>105.43</v>
@@ -1324,12 +1324,12 @@
       <c r="T7" t="n">
         <v>66.11</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>1</v>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1347,8 +1347,8 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="2" t="n">
-        <v>18.5</v>
+      <c r="AD7" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,32 +1377,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-16.27</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>-8.039999999999999</v>
+        <v>114.97</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>-6.22</v>
       </c>
       <c r="H8" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.21</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1410,50 +1410,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>-9.65</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="3" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>-8.949999999999999</v>
+        <v>33.5</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>11.36</v>
+        <v>12.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.88</v>
+        <v>100.79</v>
       </c>
       <c r="R8" t="n">
-        <v>34.81</v>
+        <v>118.31</v>
       </c>
       <c r="S8" t="n">
-        <v>46.74</v>
+        <v>131.25</v>
       </c>
       <c r="T8" t="n">
-        <v>29.37</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>0</v>
+        <v>94.73</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270504</v>
+        <v>270202</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1467,7 +1467,7 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="2" t="n">
+      <c r="AD8" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="AE8" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-11.91</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>-12.65</v>
+        <v>214.98</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-16.31</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>-6.73</v>
       </c>
       <c r="H9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.86</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1530,50 +1530,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="K9" s="3" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>19.2</v>
+        <v>29.9</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>-4.59</v>
+      <c r="O9" s="3" t="n">
+        <v>-8.710000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>16.6</v>
+        <v>16.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>39.34</v>
+        <v>179.05</v>
       </c>
       <c r="R9" t="n">
-        <v>54.98</v>
+        <v>246.25</v>
       </c>
       <c r="S9" t="n">
-        <v>67.05</v>
+        <v>294.5</v>
       </c>
       <c r="T9" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U9" s="2" t="n">
+        <v>155.05</v>
+      </c>
+      <c r="U9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>640108</v>
+        <v>730204</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="2" t="n">
+      <c r="AD9" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>114.44</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>-11.05</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-29.09</v>
+        <v>176.08</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-8.67</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>-9.42</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-25.53</v>
+        <v>14.94</v>
       </c>
       <c r="H10" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.9</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1650,50 +1650,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K10" s="2" t="n">
-        <v>-22.85</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="3" t="n">
+        <v>-12.55</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>-21.77</v>
+        <v>30.3</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-1.82</v>
       </c>
       <c r="P10" t="n">
-        <v>14.7</v>
+        <v>18.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>97.62</v>
+        <v>142.74</v>
       </c>
       <c r="R10" t="n">
-        <v>148.34</v>
+        <v>201.36</v>
       </c>
       <c r="S10" t="n">
-        <v>189.92</v>
+        <v>242.99</v>
       </c>
       <c r="T10" t="n">
-        <v>107.9</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0</v>
+        <v>102.3</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270401</v>
+        <v>730204</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" s="2" t="n">
+      <c r="AD10" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,32 +1737,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>77.39</v>
+        <v>31.63</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-18.39</v>
+        <v>0.76</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-15.04</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2.93</v>
+        <v>-13.79</v>
       </c>
       <c r="H11" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.79</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1770,56 +1770,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>-12.1</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="3" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>27.6</v>
+        <v>21.7</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O11" s="2" t="n">
-        <v>-11.07</v>
+      <c r="O11" s="3" t="n">
+        <v>-7.44</v>
       </c>
       <c r="P11" t="n">
-        <v>14.45</v>
+        <v>11.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>66.2</v>
+        <v>28.09</v>
       </c>
       <c r="R11" t="n">
-        <v>88.04000000000001</v>
+        <v>34.53</v>
       </c>
       <c r="S11" t="n">
-        <v>102.82</v>
+        <v>46.74</v>
       </c>
       <c r="T11" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="U11" s="2" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>650201</v>
+        <v>270504</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1827,8 +1827,8 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="2" t="n">
-        <v>11.1</v>
+      <c r="AD11" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,30 +1857,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>-8.039999999999999</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-22.56</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>-9.34</v>
+        <v>47.5</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-14.68</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-21.64</v>
       </c>
       <c r="H12" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+        <v>1.44</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -1890,56 +1890,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K12" s="2" t="n">
-        <v>-16.86</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K12" s="3" t="n">
+        <v>-12.95</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>11.8</v>
+        <v>18.1</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>-15.24</v>
+      <c r="O12" s="3" t="n">
+        <v>-7.08</v>
       </c>
       <c r="P12" t="n">
-        <v>14.37</v>
+        <v>16.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>42.82</v>
+        <v>39.73</v>
       </c>
       <c r="R12" t="n">
-        <v>60.14</v>
+        <v>54.57</v>
       </c>
       <c r="S12" t="n">
-        <v>72.68000000000001</v>
+        <v>67.05</v>
       </c>
       <c r="T12" t="n">
-        <v>46.88</v>
-      </c>
-      <c r="U12" s="2" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="U12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>270303</v>
+        <v>640108</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1947,8 +1947,8 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AD12" s="2" t="n">
-        <v>11.1</v>
+      <c r="AD12" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>111.01</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>-4.22</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-11.69</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>-3.49</v>
+        <v>116.78</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-27.77</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-34.02</v>
       </c>
       <c r="H13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.08</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2010,50 +2010,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K13" s="2" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="3" t="n">
+        <v>-20.07</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>-4.37</v>
+        <v>8.5</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>-20.17</v>
       </c>
       <c r="P13" t="n">
-        <v>12.52</v>
+        <v>14.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>97.11</v>
+        <v>100.26</v>
       </c>
       <c r="R13" t="n">
-        <v>118.85</v>
+        <v>146.09</v>
       </c>
       <c r="S13" t="n">
-        <v>131.25</v>
+        <v>189.92</v>
       </c>
       <c r="T13" t="n">
-        <v>94.73</v>
-      </c>
-      <c r="U13" s="2" t="n">
-        <v>1</v>
+        <v>107.9</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270202</v>
+        <v>270401</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2067,7 +2067,7 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" s="2" t="n">
+      <c r="AD13" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE13" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-8.91</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>-29.57</v>
+        <v>64.09999999999999</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-5.68</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-31.52</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-36.47</v>
       </c>
       <c r="H14" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+        <v>1.04</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2130,33 +2130,33 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K14" s="2" t="n">
-        <v>-20.14</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="3" t="n">
+        <v>-19.29</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n">
-        <v>-22.68</v>
+      <c r="O14" s="3" t="n">
+        <v>-23.92</v>
       </c>
       <c r="P14" t="n">
-        <v>14.37</v>
+        <v>14.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>55.32</v>
+        <v>54.87</v>
       </c>
       <c r="R14" t="n">
-        <v>80.90000000000001</v>
+        <v>79.42</v>
       </c>
       <c r="S14" t="n">
         <v>109.88</v>
@@ -2164,12 +2164,12 @@
       <c r="T14" t="n">
         <v>60.4</v>
       </c>
-      <c r="U14" s="2" t="n">
+      <c r="U14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W14" t="n">
@@ -2187,7 +2187,7 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" s="2" t="n">
+      <c r="AD14" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2217,30 +2217,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>298.17</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>-15.12</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-25.81</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>-41.54</v>
+        <v>26.88</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-13.01</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-18.02</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-25.31</v>
       </c>
       <c r="H15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+        <v>1.02</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2250,50 +2250,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K15" s="2" t="n">
-        <v>-22.22</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="K15" s="3" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>-18.49</v>
+        <v>32.2</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>-10.42</v>
       </c>
       <c r="P15" t="n">
-        <v>14.98</v>
+        <v>13.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>253.51</v>
+        <v>23.27</v>
       </c>
       <c r="R15" t="n">
-        <v>383.35</v>
+        <v>31.57</v>
       </c>
       <c r="S15" t="n">
-        <v>554.4</v>
+        <v>40.38</v>
       </c>
       <c r="T15" t="n">
-        <v>294.66</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>0</v>
+        <v>26.72</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>730204</v>
+        <v>630702</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" s="2" t="n">
+      <c r="AD15" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26.27</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>-7.82</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-28.42</v>
+        <v>72.3</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-13.66</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.42</v>
+        <v>-30.1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.97</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2370,56 +2370,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K16" s="2" t="n">
-        <v>-18.21</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+      <c r="K16" s="3" t="n">
+        <v>-11.31</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>8.300000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O16" s="2" t="n">
-        <v>-21.1</v>
+      <c r="O16" s="3" t="n">
+        <v>-6.06</v>
       </c>
       <c r="P16" t="n">
-        <v>13.46</v>
+        <v>8.49</v>
       </c>
       <c r="Q16" t="n">
-        <v>22.73</v>
+        <v>66.16</v>
       </c>
       <c r="R16" t="n">
-        <v>32.12</v>
+        <v>81.52</v>
       </c>
       <c r="S16" t="n">
-        <v>39.58</v>
+        <v>121.57</v>
       </c>
       <c r="T16" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="U16" s="2" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="U16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>640209</v>
+        <v>630503</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2427,8 +2427,8 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" s="2" t="n">
-        <v>5.6</v>
+      <c r="AD16" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>今日上涨且放量</t>
+          <t>量能放大(1.2-1.5倍)</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,30 +2457,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>44.84</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-25.28</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>-19.15</v>
+        <v>294.12</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-11.09</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-25.92</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-46.7</v>
       </c>
       <c r="H17" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+        <v>1.24</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2490,56 +2490,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K17" s="2" t="n">
-        <v>-16.93</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="K17" s="3" t="n">
+        <v>-22.23</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O17" s="2" t="n">
-        <v>-17.96</v>
+      <c r="O17" s="3" t="n">
+        <v>-18.32</v>
       </c>
       <c r="P17" t="n">
-        <v>11.65</v>
+        <v>15.54</v>
       </c>
       <c r="Q17" t="n">
-        <v>39.62</v>
+        <v>248.41</v>
       </c>
       <c r="R17" t="n">
-        <v>53.98</v>
+        <v>378.21</v>
       </c>
       <c r="S17" t="n">
-        <v>70.62</v>
+        <v>551.6</v>
       </c>
       <c r="T17" t="n">
-        <v>43.04</v>
-      </c>
-      <c r="U17" s="2" t="n">
+        <v>289.44</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>640209</v>
+        <v>730204</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2547,8 +2547,8 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" s="2" t="n">
-        <v>5.6</v>
+      <c r="AD17" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,32 +2577,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>162.98</v>
+        <v>78.83</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-12.43</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-25.54</v>
+        <v>0.23</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-18.15</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>2.87</v>
+        <v>-5.85</v>
       </c>
       <c r="H18" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.59</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2610,50 +2610,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K18" s="2" t="n">
-        <v>-17.55</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="K18" s="3" t="n">
+        <v>-9.56</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>20.6</v>
+        <v>27.7</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>-18.22</v>
+      <c r="O18" s="3" t="n">
+        <v>-10.55</v>
       </c>
       <c r="P18" t="n">
-        <v>15.97</v>
+        <v>14.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>136.95</v>
+        <v>67.67</v>
       </c>
       <c r="R18" t="n">
-        <v>197.67</v>
+        <v>87.16</v>
       </c>
       <c r="S18" t="n">
-        <v>237.87</v>
+        <v>102.82</v>
       </c>
       <c r="T18" t="n">
-        <v>125.61</v>
-      </c>
-      <c r="U18" s="2" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>730206</v>
+        <v>650201</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" s="2" t="n">
+      <c r="AD18" s="3" t="n">
         <v>5.6</v>
       </c>
       <c r="AE18" t="inlineStr">
@@ -2697,30 +2697,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>28.09</v>
+        <v>48.09</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-14.36</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-14.98</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>-15.67</v>
+        <v>7.01</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-6.86</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-20.41</v>
       </c>
       <c r="H19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+        <v>1.07</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2730,56 +2730,56 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K19" s="2" t="n">
-        <v>-11.85</v>
+      <c r="K19" s="3" t="n">
+        <v>-2.77</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>空头持续</t>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>27.8</v>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>-7.66</v>
+        <v>0.74</v>
       </c>
       <c r="P19" t="n">
-        <v>12.43</v>
+        <v>8.33</v>
       </c>
       <c r="Q19" t="n">
-        <v>24.6</v>
+        <v>44.09</v>
       </c>
       <c r="R19" t="n">
-        <v>31.87</v>
+        <v>49.46</v>
       </c>
       <c r="S19" t="n">
-        <v>40.38</v>
+        <v>63.02</v>
       </c>
       <c r="T19" t="n">
-        <v>27.51</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>1</v>
+        <v>43.56</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>630702</v>
+        <v>270504</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2787,8 +2787,8 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" s="2" t="n">
-        <v>5.6</v>
+      <c r="AD19" s="3" t="n">
+        <v>3.7</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,30 +2817,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>76.04000000000001</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>-4.84</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-9.84</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>-24.81</v>
+        <v>135.7</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-27.43</v>
       </c>
       <c r="H20" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2850,50 +2850,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K20" s="2" t="n">
-        <v>-7.37</v>
+      <c r="K20" s="3" t="n">
+        <v>-15.72</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>多头持续</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O20" s="2" t="n">
-        <v>-2.52</v>
+      <c r="O20" s="3" t="n">
+        <v>-11.8</v>
       </c>
       <c r="P20" t="n">
-        <v>7.69</v>
+        <v>14.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>70.2</v>
+        <v>115.89</v>
       </c>
       <c r="R20" t="n">
-        <v>82.09</v>
+        <v>161.02</v>
       </c>
       <c r="S20" t="n">
-        <v>121.57</v>
+        <v>203.97</v>
       </c>
       <c r="T20" t="n">
-        <v>75.12</v>
-      </c>
-      <c r="U20" s="2" t="n">
-        <v>1</v>
+        <v>126.7</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>630503</v>
+        <v>730204</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -2907,7 +2907,7 @@
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" s="2" t="n">
+      <c r="AD20" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="AE20" t="inlineStr">
@@ -2946,21 +2946,21 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>122.15</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>-12.59</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-34.01</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>-43.9</v>
+        <v>123.17</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-32.63</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-46.68</v>
       </c>
       <c r="H21" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+        <v>0.87</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -2970,33 +2970,33 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K21" s="2" t="n">
-        <v>-24.55</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="K21" s="3" t="n">
+        <v>-22.49</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>-26.69</v>
+      <c r="O21" s="3" t="n">
+        <v>-25.03</v>
       </c>
       <c r="P21" t="n">
-        <v>15.44</v>
+        <v>15.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>103.29</v>
+        <v>104.42</v>
       </c>
       <c r="R21" t="n">
-        <v>161.9</v>
+        <v>158.91</v>
       </c>
       <c r="S21" t="n">
         <v>239.77</v>
@@ -3004,12 +3004,12 @@
       <c r="T21" t="n">
         <v>117.2</v>
       </c>
-      <c r="U21" s="2" t="n">
+      <c r="U21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W21" t="n">
@@ -3027,7 +3027,7 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" s="2" t="n">
+      <c r="AD21" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="AE21" t="inlineStr">
@@ -3066,21 +3066,21 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>173.63</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>-12.88</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-26.77</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>-12.75</v>
+        <v>171.9</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>-29.75</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-27.39</v>
       </c>
       <c r="H22" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+        <v>0.95</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3090,33 +3090,33 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K22" s="2" t="n">
-        <v>-21.09</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="K22" s="3" t="n">
+        <v>-20.56</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O22" s="2" t="n">
-        <v>-19.45</v>
+      <c r="O22" s="3" t="n">
+        <v>-22.15</v>
       </c>
       <c r="P22" t="n">
-        <v>13.7</v>
+        <v>13.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>149.84</v>
+        <v>147.95</v>
       </c>
       <c r="R22" t="n">
-        <v>220.03</v>
+        <v>216.39</v>
       </c>
       <c r="S22" t="n">
         <v>279.78</v>
@@ -3124,12 +3124,12 @@
       <c r="T22" t="n">
         <v>167</v>
       </c>
-      <c r="U22" s="2" t="n">
+      <c r="U22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -3147,7 +3147,7 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" s="2" t="n">
+      <c r="AD22" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="AE22" t="inlineStr">
@@ -3186,21 +3186,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57.25</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>-4.84</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-13.62</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>-25.59</v>
+        <v>57.23</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-14.34</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-32.38</v>
       </c>
       <c r="H23" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+        <v>0.76</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3210,33 +3210,33 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K23" s="2" t="n">
-        <v>-11.2</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="K23" s="3" t="n">
+        <v>-10.57</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O23" s="2" t="n">
-        <v>-6.3</v>
+      <c r="O23" s="3" t="n">
+        <v>-6.74</v>
       </c>
       <c r="P23" t="n">
-        <v>9.92</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>51.57</v>
+        <v>51.58</v>
       </c>
       <c r="R23" t="n">
-        <v>64.47</v>
+        <v>63.99</v>
       </c>
       <c r="S23" t="n">
         <v>89.83</v>
@@ -3244,12 +3244,12 @@
       <c r="T23" t="n">
         <v>54.23</v>
       </c>
-      <c r="U23" s="2" t="n">
+      <c r="U23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W23" t="n">
@@ -3267,7 +3267,7 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" s="2" t="n">
+      <c r="AD23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3297,30 +3297,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>134.06</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>-8.09</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-21.97</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>-21.38</v>
+        <v>50.63</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-20.22</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-15.02</v>
       </c>
       <c r="H24" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+        <v>0.74</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3330,50 +3330,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K24" s="2" t="n">
-        <v>-17.58</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="K24" s="3" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O24" s="2" t="n">
-        <v>-14.65</v>
+      <c r="O24" s="3" t="n">
+        <v>-12.62</v>
       </c>
       <c r="P24" t="n">
-        <v>14.73</v>
+        <v>13.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>114.32</v>
+        <v>43.63</v>
       </c>
       <c r="R24" t="n">
-        <v>162.65</v>
+        <v>59.5</v>
       </c>
       <c r="S24" t="n">
-        <v>203.97</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="U24" s="2" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="U24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>730204</v>
+        <v>270303</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3387,7 +3387,7 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" s="2" t="n">
+      <c r="AD24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
@@ -3417,32 +3417,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>-8.859999999999999</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-23.8</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>-28.02</v>
+        <v>26.23</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-30.72</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-5.41</v>
       </c>
       <c r="H25" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.43</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3450,50 +3450,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K25" s="2" t="n">
-        <v>-17.49</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="K25" s="3" t="n">
+        <v>-16.83</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O25" s="2" t="n">
-        <v>-16.48</v>
+      <c r="O25" s="3" t="n">
+        <v>-23.12</v>
       </c>
       <c r="P25" t="n">
-        <v>11.7</v>
+        <v>13.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>67.28</v>
+        <v>22.75</v>
       </c>
       <c r="R25" t="n">
-        <v>92.36</v>
+        <v>31.54</v>
       </c>
       <c r="S25" t="n">
-        <v>119.51</v>
+        <v>39.58</v>
       </c>
       <c r="T25" t="n">
-        <v>72.13</v>
-      </c>
-      <c r="U25" s="2" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="U25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>640703</v>
+        <v>640209</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" s="2" t="n">
+      <c r="AD25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
@@ -3537,30 +3537,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>-9.550000000000001</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-28.97</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>-37.39</v>
+        <v>76.66</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-4.35</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-23.49</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-32.25</v>
       </c>
       <c r="H26" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+        <v>0.6</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3570,50 +3570,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K26" s="2" t="n">
-        <v>-20.05</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="K26" s="3" t="n">
+        <v>-15.92</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>9</v>
+        <v>10.9</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O26" s="2" t="n">
-        <v>-21.65</v>
+      <c r="O26" s="3" t="n">
+        <v>-15.89</v>
       </c>
       <c r="P26" t="n">
-        <v>15.16</v>
+        <v>11.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>35.03</v>
+        <v>67.73</v>
       </c>
       <c r="R26" t="n">
-        <v>51.65</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>76.43000000000001</v>
+        <v>119.51</v>
       </c>
       <c r="T26" t="n">
-        <v>39.04</v>
-      </c>
-      <c r="U26" s="2" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="U26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>270203</v>
+        <v>640703</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -3627,7 +3627,7 @@
       <c r="AC26" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="2" t="n">
+      <c r="AD26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
@@ -3657,30 +3657,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>-10.61</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-15.27</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>-23.63</v>
+        <v>45.15</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-24.55</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-24.74</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+        <v>0.71</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>空头排列</t>
         </is>
@@ -3690,50 +3690,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K27" s="2" t="n">
-        <v>-14.49</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="K27" s="3" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>12.4</v>
+        <v>10.1</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O27" s="2" t="n">
-        <v>-7.95</v>
+      <c r="O27" s="3" t="n">
+        <v>-16.95</v>
       </c>
       <c r="P27" t="n">
-        <v>11.33</v>
+        <v>11.61</v>
       </c>
       <c r="Q27" t="n">
-        <v>42.66</v>
+        <v>39.91</v>
       </c>
       <c r="R27" t="n">
-        <v>56.27</v>
+        <v>53.24</v>
       </c>
       <c r="S27" t="n">
-        <v>76.8</v>
+        <v>70.62</v>
       </c>
       <c r="T27" t="n">
-        <v>46.53</v>
-      </c>
-      <c r="U27" s="2" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="U27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>270107</v>
+        <v>640209</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
       <c r="AC27" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="2" t="n">
+      <c r="AD27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>170.61</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>-15.22</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-13.96</v>
+        <v>41.07</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-6.89</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>-30.26</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>22.47</v>
+        <v>-43.39</v>
       </c>
       <c r="H28" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.76</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3810,50 +3810,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K28" s="2" t="n">
-        <v>-15.65</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="K28" s="3" t="n">
+        <v>-19.09</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>26.9</v>
+        <v>9.4</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O28" s="2" t="n">
-        <v>-6.64</v>
+      <c r="O28" s="3" t="n">
+        <v>-22.66</v>
       </c>
       <c r="P28" t="n">
-        <v>18.9</v>
+        <v>15.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>138.36</v>
+        <v>34.84</v>
       </c>
       <c r="R28" t="n">
-        <v>202.27</v>
+        <v>50.76</v>
       </c>
       <c r="S28" t="n">
-        <v>242.99</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="U28" s="2" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="U28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>730204</v>
+        <v>270203</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" s="2" t="n">
+      <c r="AD28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>204.54</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>-17.09</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-20.24</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>-3.99</v>
+        <v>47.67</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-7.85</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-16.82</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-31.21</v>
       </c>
       <c r="H29" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.73</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3930,50 +3930,50 @@
           <t>否</t>
         </is>
       </c>
-      <c r="K29" s="2" t="n">
-        <v>-17.64</v>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="K29" s="3" t="n">
+        <v>-14.54</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>空头持续</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>24.5</v>
+        <v>12.5</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O29" s="2" t="n">
-        <v>-12.92</v>
+      <c r="O29" s="3" t="n">
+        <v>-9.220000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>17.13</v>
+        <v>11.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>169.5</v>
+        <v>42.27</v>
       </c>
       <c r="R29" t="n">
-        <v>248.35</v>
+        <v>55.78</v>
       </c>
       <c r="S29" t="n">
-        <v>294.5</v>
+        <v>76.8</v>
       </c>
       <c r="T29" t="n">
-        <v>155.05</v>
-      </c>
-      <c r="U29" s="2" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="U29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>730204</v>
+        <v>270107</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       <c r="AC29" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" s="2" t="n">
+      <c r="AD29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,7 +473,7 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="57" customWidth="1" min="31" max="31"/>
+    <col width="29" customWidth="1" min="31" max="31"/>
     <col width="66" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
@@ -657,89 +657,89 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>243.17</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>12.87</v>
+        <v>15.22</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>-14.78</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-3.31</v>
+        <v>-25.29</v>
       </c>
       <c r="H2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>2.19</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>38</v>
+        <v>34.8</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>20.47</v>
+      <c r="O2" s="3" t="n">
+        <v>-4.87</v>
       </c>
       <c r="P2" t="n">
-        <v>12.29</v>
+        <v>13.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>175.43</v>
+        <v>211.33</v>
       </c>
       <c r="R2" t="n">
-        <v>198.25</v>
+        <v>251.21</v>
       </c>
       <c r="S2" t="n">
-        <v>232.68</v>
+        <v>333.7</v>
       </c>
       <c r="T2" t="n">
-        <v>159.34</v>
+        <v>204.5</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>270104</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -747,17 +747,17 @@
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" t="n">
-        <v>48.1</v>
+      <c r="AD2" s="3" t="n">
+        <v>25.9</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,28 +777,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.71</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6.11</v>
+        <v>2.61</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-9.199999999999999</v>
+        <v>-15.11</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-20.94</v>
+        <v>-31.18</v>
       </c>
       <c r="H3" t="n">
-        <v>1.16</v>
+        <v>0.85</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-5.51</v>
+        <v>-7.04</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>29.4</v>
+        <v>20</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
@@ -827,33 +827,33 @@
         </is>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-1.6</v>
+        <v>-5.2</v>
       </c>
       <c r="P3" t="n">
-        <v>11.6</v>
+        <v>10.13</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.19</v>
+        <v>53.02</v>
       </c>
       <c r="R3" t="n">
-        <v>22.98</v>
+        <v>63.47</v>
       </c>
       <c r="S3" t="n">
-        <v>29.4</v>
+        <v>87.45</v>
       </c>
       <c r="T3" t="n">
-        <v>19.08</v>
+        <v>54.23</v>
       </c>
       <c r="U3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270303</v>
+        <v>270107</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -897,28 +897,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>233.81</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>3.69</v>
+        <v>47.8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-3.92</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-14.86</v>
+        <v>-19.27</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-35.37</v>
+        <v>-36.18</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91</v>
+        <v>0.84</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>-7.7</v>
+        <v>-13.43</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>26.8</v>
+        <v>14.3</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
@@ -947,39 +947,39 @@
         </is>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-7.26</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>12.63</v>
+        <v>11.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>204.27</v>
+        <v>42.11</v>
       </c>
       <c r="R4" t="n">
-        <v>253.32</v>
+        <v>55.21</v>
       </c>
       <c r="S4" t="n">
-        <v>346.04</v>
+        <v>76.8</v>
       </c>
       <c r="T4" t="n">
-        <v>204.5</v>
+        <v>45.31</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270104</v>
+        <v>270107</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>22.2</v>
+        <v>24.1</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,28 +1017,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>173.61</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-4.45</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-19.77</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1.55</v>
+        <v>196.8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-13.56</v>
       </c>
       <c r="H5" t="n">
-        <v>0.85</v>
+        <v>1.59</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-11.21</v>
+        <v>-1.14</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -1059,47 +1059,47 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-12.17</v>
+        <v>38.3</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>19.04</v>
       </c>
       <c r="P5" t="n">
-        <v>15.72</v>
+        <v>12.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>146.32</v>
+        <v>172.4</v>
       </c>
       <c r="R5" t="n">
-        <v>195.53</v>
+        <v>199.07</v>
       </c>
       <c r="S5" t="n">
-        <v>237.87</v>
+        <v>232.68</v>
       </c>
       <c r="T5" t="n">
-        <v>125.61</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>0</v>
+        <v>159.34</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>730206</v>
+        <v>270104</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>248.98</v>
+        <v>242</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-4.23</v>
+        <v>-0.82</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-24.21</v>
+        <v>-28.61</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-40.98</v>
+        <v>-37.7</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-15.86</v>
+        <v>-16.86</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -1187,16 +1187,16 @@
         </is>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-16.61</v>
+        <v>-18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>11.19</v>
+        <v>11.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>221.13</v>
+        <v>214.53</v>
       </c>
       <c r="R6" t="n">
-        <v>295.92</v>
+        <v>291.07</v>
       </c>
       <c r="S6" t="n">
         <v>442</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,28 +1257,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>75.98</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>10.07</v>
+        <v>106.96</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-7.94</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-7.41</v>
+        <v>-16.31</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-22.37</v>
+        <v>-6.36</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -1291,55 +1291,55 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>金叉(转多)</t>
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>35.7</v>
+        <v>30.4</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.19</v>
+      <c r="O7" s="3" t="n">
+        <v>-6.4</v>
       </c>
       <c r="P7" t="n">
-        <v>7.59</v>
+        <v>13.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>70.20999999999999</v>
+        <v>92.23</v>
       </c>
       <c r="R7" t="n">
-        <v>77.70999999999999</v>
+        <v>117.27</v>
       </c>
       <c r="S7" t="n">
-        <v>105.43</v>
+        <v>131.25</v>
       </c>
       <c r="T7" t="n">
-        <v>66.11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
+        <v>94.73</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>710101</v>
+        <v>270202</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>14.8</v>
+        <v>18.5</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,32 +1377,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>114.97</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-0.03</v>
+        <v>21.52</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>10.25</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-8.619999999999999</v>
+        <v>-12.8</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-6.22</v>
+        <v>-19.85</v>
       </c>
       <c r="H8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.17</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-2.83</v>
+        <v>-5.69</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>33.5</v>
+        <v>31.8</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1427,33 +1427,33 @@
         </is>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-1.02</v>
+        <v>-2.89</v>
       </c>
       <c r="P8" t="n">
-        <v>12.33</v>
+        <v>11.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>100.79</v>
+        <v>19.06</v>
       </c>
       <c r="R8" t="n">
-        <v>118.31</v>
+        <v>22.82</v>
       </c>
       <c r="S8" t="n">
-        <v>131.25</v>
+        <v>29.4</v>
       </c>
       <c r="T8" t="n">
-        <v>94.73</v>
+        <v>19.08</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270202</v>
+        <v>270303</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1497,28 +1497,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>214.98</v>
+        <v>156.25</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-6.12</v>
+        <v>-6.55</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-16.31</v>
+        <v>-30.13</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-6.73</v>
+        <v>-6.42</v>
       </c>
       <c r="H9" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-12.7</v>
+        <v>-18.69</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>29.9</v>
+        <v>26.6</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
@@ -1547,33 +1547,33 @@
         </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-8.710000000000001</v>
+        <v>-20.22</v>
       </c>
       <c r="P9" t="n">
-        <v>16.71</v>
+        <v>18.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>179.05</v>
+        <v>127.78</v>
       </c>
       <c r="R9" t="n">
-        <v>246.25</v>
+        <v>192.16</v>
       </c>
       <c r="S9" t="n">
-        <v>294.5</v>
+        <v>237.87</v>
       </c>
       <c r="T9" t="n">
-        <v>155.05</v>
+        <v>125.61</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>730204</v>
+        <v>730206</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>176.08</v>
+        <v>166.06</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-8.67</v>
+        <v>-7.71</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-9.42</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>14.94</v>
+        <v>-34.32</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-29.36</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.91</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-12.55</v>
+        <v>-21.69</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1659,47 +1659,47 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>2.8</v>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-1.82</v>
+        <v>-24.41</v>
       </c>
       <c r="P10" t="n">
-        <v>18.93</v>
+        <v>14.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>142.74</v>
+        <v>141.41</v>
       </c>
       <c r="R10" t="n">
-        <v>201.36</v>
+        <v>212.06</v>
       </c>
       <c r="S10" t="n">
-        <v>242.99</v>
+        <v>279.78</v>
       </c>
       <c r="T10" t="n">
-        <v>102.3</v>
+        <v>166.06</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>730204</v>
+        <v>270103</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>14.8</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0.76</v>
+        <v>258.01</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-15.69</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-15.04</v>
+        <v>-39.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-13.79</v>
+        <v>-49.29</v>
       </c>
       <c r="H11" t="n">
-        <v>0.79</v>
+        <v>1.29</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-8.4</v>
+        <v>-30.25</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>21.7</v>
+        <v>3</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -1787,39 +1787,39 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-7.44</v>
+        <v>-29.19</v>
       </c>
       <c r="P11" t="n">
-        <v>11.18</v>
+        <v>18.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>28.09</v>
+        <v>209.57</v>
       </c>
       <c r="R11" t="n">
-        <v>34.53</v>
+        <v>369.92</v>
       </c>
       <c r="S11" t="n">
-        <v>46.74</v>
+        <v>523.83</v>
       </c>
       <c r="T11" t="n">
-        <v>29.37</v>
+        <v>258</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>270504</v>
+        <v>730204</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,28 +1857,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>-0.02</v>
+        <v>76.2</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>13.75</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-14.68</v>
+        <v>-8.52</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-21.64</v>
+        <v>-25.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
@@ -1891,49 +1891,49 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>-12.95</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-1.5</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>-7.08</v>
+        <v>38.1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>1.39</v>
       </c>
       <c r="P12" t="n">
-        <v>16.36</v>
+        <v>7.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>39.73</v>
+        <v>70.41</v>
       </c>
       <c r="R12" t="n">
-        <v>54.57</v>
+        <v>77.36</v>
       </c>
       <c r="S12" t="n">
-        <v>67.05</v>
+        <v>104.14</v>
       </c>
       <c r="T12" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>0</v>
+        <v>66.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>640108</v>
+        <v>710101</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,28 +1977,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>116.78</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-4.21</v>
+        <v>47.01</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>5.55</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-27.77</v>
+        <v>-10.93</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-34.02</v>
+        <v>-20.39</v>
       </c>
       <c r="H13" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
@@ -2011,49 +2011,49 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-20.07</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-4.18</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>30.8</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-20.17</v>
+        <v>-1.02</v>
       </c>
       <c r="P13" t="n">
-        <v>14.15</v>
+        <v>8.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>100.26</v>
+        <v>43.17</v>
       </c>
       <c r="R13" t="n">
-        <v>146.09</v>
+        <v>49.06</v>
       </c>
       <c r="S13" t="n">
-        <v>189.92</v>
+        <v>62.91</v>
       </c>
       <c r="T13" t="n">
-        <v>107.9</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>0</v>
+        <v>43.45</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270401</v>
+        <v>270504</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,28 +2097,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-5.68</v>
+        <v>30.46</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2.21</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-31.52</v>
+        <v>-21.39</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-36.47</v>
+        <v>-19.38</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>0.82</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>-19.29</v>
+        <v>-10.72</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>7.7</v>
+        <v>22.3</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
@@ -2147,33 +2147,33 @@
         </is>
       </c>
       <c r="O14" s="3" t="n">
-        <v>-23.92</v>
+        <v>-11.48</v>
       </c>
       <c r="P14" t="n">
-        <v>14.4</v>
+        <v>11.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>54.87</v>
+        <v>26.92</v>
       </c>
       <c r="R14" t="n">
-        <v>79.42</v>
+        <v>34.12</v>
       </c>
       <c r="S14" t="n">
-        <v>109.88</v>
+        <v>46.74</v>
       </c>
       <c r="T14" t="n">
-        <v>60.4</v>
+        <v>29.37</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>640703</v>
+        <v>270504</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26.88</v>
+        <v>111.87</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-13.01</v>
+        <v>-0.65</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-18.02</v>
+        <v>-32.64</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-25.31</v>
+        <v>-32.85</v>
       </c>
       <c r="H15" t="n">
         <v>1.02</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-14.86</v>
+        <v>-21.98</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -2259,41 +2259,41 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>8.6</v>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-10.42</v>
+        <v>-22.73</v>
       </c>
       <c r="P15" t="n">
-        <v>13.43</v>
+        <v>14.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>23.27</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>31.57</v>
+        <v>143.38</v>
       </c>
       <c r="S15" t="n">
-        <v>40.38</v>
+        <v>189.92</v>
       </c>
       <c r="T15" t="n">
-        <v>26.72</v>
+        <v>107.9</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>630702</v>
+        <v>270401</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,28 +2337,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>72.3</v>
+        <v>43.53</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-7.4</v>
+        <v>-2.55</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-13.66</v>
+        <v>-29.82</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-30.1</v>
+        <v>-28.06</v>
       </c>
       <c r="H16" t="n">
-        <v>0.97</v>
+        <v>0.74</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -2371,15 +2371,15 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-11.31</v>
+        <v>-16.8</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>死叉(转空)</t>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>20.8</v>
+        <v>11.5</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
@@ -2387,39 +2387,39 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-6.06</v>
+        <v>-19.91</v>
       </c>
       <c r="P16" t="n">
-        <v>8.49</v>
+        <v>11.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>66.16</v>
+        <v>38.51</v>
       </c>
       <c r="R16" t="n">
-        <v>81.52</v>
+        <v>52.32</v>
       </c>
       <c r="S16" t="n">
-        <v>121.57</v>
+        <v>70.62</v>
       </c>
       <c r="T16" t="n">
-        <v>71.98999999999999</v>
+        <v>43.04</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>630503</v>
+        <v>640209</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>7.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>294.12</v>
+        <v>60.54</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-11.09</v>
+        <v>-4.47</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-25.92</v>
+        <v>-36.63</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-46.7</v>
+        <v>-42.3</v>
       </c>
       <c r="H17" t="n">
-        <v>1.24</v>
+        <v>0.98</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-22.23</v>
+        <v>-22.06</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
@@ -2507,39 +2507,39 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-18.32</v>
+        <v>-26.72</v>
       </c>
       <c r="P17" t="n">
-        <v>15.54</v>
+        <v>15.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>248.41</v>
+        <v>51.33</v>
       </c>
       <c r="R17" t="n">
-        <v>378.21</v>
+        <v>77.67</v>
       </c>
       <c r="S17" t="n">
-        <v>551.6</v>
+        <v>109.38</v>
       </c>
       <c r="T17" t="n">
-        <v>289.44</v>
+        <v>60.4</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>730204</v>
+        <v>640703</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>7.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>78.83</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0.23</v>
+        <v>113.51</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-8.609999999999999</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-18.15</v>
+        <v>-40.88</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-5.85</v>
+        <v>-47.81</v>
       </c>
       <c r="H18" t="n">
-        <v>0.59</v>
+        <v>0.87</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-9.56</v>
+        <v>-26.76</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>27.7</v>
+        <v>8.9</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
@@ -2627,39 +2627,39 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>-10.55</v>
+        <v>-30.97</v>
       </c>
       <c r="P18" t="n">
-        <v>14.15</v>
+        <v>16.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>67.67</v>
+        <v>94.37</v>
       </c>
       <c r="R18" t="n">
-        <v>87.16</v>
+        <v>154.99</v>
       </c>
       <c r="S18" t="n">
-        <v>102.82</v>
+        <v>224.03</v>
       </c>
       <c r="T18" t="n">
-        <v>69.63</v>
+        <v>113</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>650201</v>
+        <v>270202</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48.09</v>
+        <v>74.92</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7.01</v>
+        <v>0.13</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-6.86</v>
+        <v>-23.82</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-20.41</v>
+        <v>-7.97</v>
       </c>
       <c r="H19" t="n">
-        <v>1.07</v>
+        <v>0.61</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -2731,55 +2731,55 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-2.77</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>金叉(转多)</t>
+        <v>-12.88</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>27.8</v>
+        <v>27.1</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
           <t>超卖区间</t>
         </is>
       </c>
-      <c r="O19" s="2" t="n">
-        <v>0.74</v>
+      <c r="O19" s="3" t="n">
+        <v>-13.91</v>
       </c>
       <c r="P19" t="n">
-        <v>8.33</v>
+        <v>14.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.09</v>
+        <v>63.8</v>
       </c>
       <c r="R19" t="n">
-        <v>49.46</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>63.02</v>
+        <v>102.82</v>
       </c>
       <c r="T19" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
+        <v>69.63</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270504</v>
+        <v>650201</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>135.7</v>
+        <v>45.3</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-3.82</v>
+        <v>-4.65</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-19.4</v>
+        <v>-24.1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-27.43</v>
+        <v>-21.03</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-15.72</v>
+        <v>-15.87</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -2867,39 +2867,39 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-11.8</v>
+        <v>-14.19</v>
       </c>
       <c r="P20" t="n">
-        <v>14.6</v>
+        <v>17.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>115.89</v>
+        <v>37.45</v>
       </c>
       <c r="R20" t="n">
-        <v>161.02</v>
+        <v>53.85</v>
       </c>
       <c r="S20" t="n">
-        <v>203.97</v>
+        <v>67.05</v>
       </c>
       <c r="T20" t="n">
-        <v>126.7</v>
+        <v>43.01</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>730204</v>
+        <v>640108</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>123.17</v>
+        <v>39.13</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-6.27</v>
+        <v>-5.19</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-32.63</v>
+        <v>-35.09</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-46.68</v>
+        <v>-44.9</v>
       </c>
       <c r="H21" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-22.49</v>
+        <v>-21.27</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -2987,39 +2987,39 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-25.03</v>
+        <v>-25.18</v>
       </c>
       <c r="P21" t="n">
-        <v>15.22</v>
+        <v>16.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>104.42</v>
+        <v>32.84</v>
       </c>
       <c r="R21" t="n">
-        <v>158.91</v>
+        <v>49.7</v>
       </c>
       <c r="S21" t="n">
-        <v>239.77</v>
+        <v>74.8</v>
       </c>
       <c r="T21" t="n">
-        <v>117.2</v>
+        <v>38.86</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270202</v>
+        <v>270203</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,28 +3057,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>171.9</v>
+        <v>127.6</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-9.630000000000001</v>
+        <v>-4.03</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-29.75</v>
+        <v>-31.11</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-27.39</v>
+        <v>-33.51</v>
       </c>
       <c r="H22" t="n">
-        <v>0.95</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>-20.56</v>
+        <v>-19.31</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2.7</v>
+        <v>16</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
@@ -3107,33 +3107,33 @@
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>-22.15</v>
+        <v>-21.2</v>
       </c>
       <c r="P22" t="n">
-        <v>13.93</v>
+        <v>15.61</v>
       </c>
       <c r="Q22" t="n">
-        <v>147.95</v>
+        <v>107.68</v>
       </c>
       <c r="R22" t="n">
-        <v>216.39</v>
+        <v>158.14</v>
       </c>
       <c r="S22" t="n">
-        <v>279.78</v>
+        <v>202.38</v>
       </c>
       <c r="T22" t="n">
-        <v>167</v>
+        <v>126.7</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>270103</v>
+        <v>730204</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57.23</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-2.42</v>
+        <v>-4.75</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-14.34</v>
+        <v>-31.45</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-32.38</v>
+        <v>-36</v>
       </c>
       <c r="H23" t="n">
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-10.57</v>
+        <v>-18.84</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>8.5</v>
+        <v>10.7</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
@@ -3227,39 +3227,39 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-6.74</v>
+        <v>-21.54</v>
       </c>
       <c r="P23" t="n">
-        <v>9.869999999999999</v>
+        <v>12.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>51.58</v>
+        <v>63.58</v>
       </c>
       <c r="R23" t="n">
-        <v>63.99</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>89.83</v>
+        <v>117</v>
       </c>
       <c r="T23" t="n">
-        <v>54.23</v>
+        <v>72.13</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>270107</v>
+        <v>640703</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>50.63</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-2.99</v>
+        <v>-7.35</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-20.22</v>
+        <v>-16.6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-15.02</v>
+        <v>-35.5</v>
       </c>
       <c r="H24" t="n">
-        <v>0.74</v>
+        <v>0.96</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-14.9</v>
+        <v>-12.75</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>14.3</v>
+        <v>21.6</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
@@ -3347,39 +3347,39 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-12.62</v>
+        <v>-6.69</v>
       </c>
       <c r="P24" t="n">
-        <v>13.82</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>43.63</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="R24" t="n">
-        <v>59.5</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>72.68000000000001</v>
+        <v>121.57</v>
       </c>
       <c r="T24" t="n">
-        <v>46.88</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>270303</v>
+        <v>630503</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.23</v>
+        <v>197</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-4.3</v>
+        <v>-11.79</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-30.72</v>
+        <v>-26.63</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-5.41</v>
+        <v>-9.27</v>
       </c>
       <c r="H25" t="n">
-        <v>0.43</v>
+        <v>0.88</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-16.83</v>
+        <v>-18.82</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>8.5</v>
+        <v>27.9</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
@@ -3467,39 +3467,39 @@
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-23.12</v>
+        <v>-16.72</v>
       </c>
       <c r="P25" t="n">
-        <v>13.25</v>
+        <v>19.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>22.75</v>
+        <v>159.43</v>
       </c>
       <c r="R25" t="n">
-        <v>31.54</v>
+        <v>242.68</v>
       </c>
       <c r="S25" t="n">
-        <v>39.58</v>
+        <v>294.5</v>
       </c>
       <c r="T25" t="n">
-        <v>23.58</v>
+        <v>155.05</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>640209</v>
+        <v>730204</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,32 +3537,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>76.66</v>
+        <v>161.89</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-4.35</v>
+        <v>-14.1</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-23.49</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>-32.25</v>
+        <v>-21.56</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>11.24</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.91</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-15.92</v>
+        <v>-18.7</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>10.9</v>
+        <v>28.7</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
@@ -3587,39 +3587,39 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-15.89</v>
+        <v>-11.65</v>
       </c>
       <c r="P26" t="n">
-        <v>11.65</v>
+        <v>20.87</v>
       </c>
       <c r="Q26" t="n">
-        <v>67.73</v>
+        <v>128.1</v>
       </c>
       <c r="R26" t="n">
-        <v>91.18000000000001</v>
+        <v>199.13</v>
       </c>
       <c r="S26" t="n">
-        <v>119.51</v>
+        <v>242.99</v>
       </c>
       <c r="T26" t="n">
-        <v>72.13</v>
+        <v>102.3</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>640703</v>
+        <v>730204</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,28 +3657,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>45.15</v>
+        <v>48.3</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.46</v>
+        <v>-3.46</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-24.55</v>
+        <v>-29.58</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-24.74</v>
+        <v>-16.03</v>
       </c>
       <c r="H27" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-15.2</v>
+        <v>-17.41</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>10.1</v>
+        <v>14.1</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -3707,33 +3707,33 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-16.95</v>
+        <v>-19.67</v>
       </c>
       <c r="P27" t="n">
-        <v>11.61</v>
+        <v>14.19</v>
       </c>
       <c r="Q27" t="n">
-        <v>39.91</v>
+        <v>41.45</v>
       </c>
       <c r="R27" t="n">
-        <v>53.24</v>
+        <v>58.48</v>
       </c>
       <c r="S27" t="n">
-        <v>70.62</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>43.04</v>
+        <v>46.88</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>640209</v>
+        <v>270303</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>41.07</v>
+        <v>25.05</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-6.89</v>
+        <v>-4.32</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-30.26</v>
+        <v>-34.39</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-43.39</v>
+        <v>-11.08</v>
       </c>
       <c r="H28" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.47</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-19.09</v>
+        <v>-18.88</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -3827,33 +3827,33 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>-22.66</v>
+        <v>-24.48</v>
       </c>
       <c r="P28" t="n">
-        <v>15.18</v>
+        <v>14.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>34.84</v>
+        <v>21.53</v>
       </c>
       <c r="R28" t="n">
-        <v>50.76</v>
+        <v>30.88</v>
       </c>
       <c r="S28" t="n">
-        <v>76.43000000000001</v>
+        <v>39.58</v>
       </c>
       <c r="T28" t="n">
-        <v>39.04</v>
+        <v>23.58</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>270203</v>
+        <v>640209</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3897,28 +3897,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>47.67</v>
+        <v>25.9</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.85</v>
+        <v>-12.08</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-16.82</v>
+        <v>-21.75</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-31.21</v>
+        <v>-26.34</v>
       </c>
       <c r="H29" t="n">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-14.54</v>
+        <v>-17.02</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -3939,41 +3939,41 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>32.4</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-9.220000000000001</v>
+        <v>-11.84</v>
       </c>
       <c r="P29" t="n">
-        <v>11.32</v>
+        <v>13.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>42.27</v>
+        <v>22.29</v>
       </c>
       <c r="R29" t="n">
-        <v>55.78</v>
+        <v>31.21</v>
       </c>
       <c r="S29" t="n">
-        <v>76.8</v>
+        <v>40.38</v>
       </c>
       <c r="T29" t="n">
-        <v>46.53</v>
+        <v>25.9</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>270107</v>
+        <v>630702</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,10 +473,10 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="29" customWidth="1" min="31" max="31"/>
+    <col width="51" customWidth="1" min="31" max="31"/>
     <col width="66" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="25" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,41 +657,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>243.17</v>
+        <v>214.04</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>15.22</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>-14.78</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>-25.29</v>
+        <v>25.16</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.48</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>-3.2</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>6.64</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,47 +699,47 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>34.8</v>
+        <v>51.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O2" s="3" t="n">
-        <v>-4.87</v>
+      <c r="O2" s="2" t="n">
+        <v>26.08</v>
       </c>
       <c r="P2" t="n">
-        <v>13.09</v>
+        <v>12.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>211.33</v>
+        <v>187.68</v>
       </c>
       <c r="R2" t="n">
-        <v>251.21</v>
+        <v>200.71</v>
       </c>
       <c r="S2" t="n">
-        <v>333.7</v>
+        <v>229.8</v>
       </c>
       <c r="T2" t="n">
-        <v>204.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2</v>
+        <v>159.34</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>270104</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -747,17 +747,17 @@
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" s="3" t="n">
-        <v>25.9</v>
+      <c r="AD2" t="n">
+        <v>46.3</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日；OBV创20日新高</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,28 +777,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>22.84</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.61</v>
+        <v>17.73</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-15.11</v>
+        <v>-7.04</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-31.18</v>
+        <v>-15.12</v>
       </c>
       <c r="H3" t="n">
-        <v>0.85</v>
+        <v>1.33</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
@@ -807,59 +807,59 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>-7.04</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>20</v>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-5.2</v>
+        <v>45</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.92</v>
       </c>
       <c r="P3" t="n">
-        <v>10.13</v>
+        <v>11.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>53.02</v>
+        <v>20.25</v>
       </c>
       <c r="R3" t="n">
-        <v>63.47</v>
+        <v>22.73</v>
       </c>
       <c r="S3" t="n">
-        <v>87.45</v>
+        <v>29.4</v>
       </c>
       <c r="T3" t="n">
-        <v>54.23</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>0</v>
+        <v>19.08</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270107</v>
+        <v>270303</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -867,17 +867,17 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" s="3" t="n">
-        <v>24.1</v>
+      <c r="AD3" t="n">
+        <v>40.7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,28 +897,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-3.92</v>
+        <v>78.11</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>10.83</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-19.27</v>
+        <v>-5.53</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-36.18</v>
+        <v>-20.15</v>
       </c>
       <c r="H4" t="n">
-        <v>0.84</v>
+        <v>1.49</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -927,59 +927,59 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>-13.43</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-9.359999999999999</v>
+        <v>46.2</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>2.43</v>
       </c>
       <c r="P4" t="n">
-        <v>11.91</v>
+        <v>7.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>42.11</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>55.21</v>
+        <v>77.13</v>
       </c>
       <c r="S4" t="n">
-        <v>76.8</v>
+        <v>101.5</v>
       </c>
       <c r="T4" t="n">
-        <v>45.31</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>0</v>
+        <v>66.11</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>270107</v>
+        <v>710101</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -987,17 +987,17 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="3" t="n">
-        <v>24.1</v>
+      <c r="AD4" t="n">
+        <v>38.9</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,49 +1017,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>196.8</v>
+        <v>50.42</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>13.15</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-3.08</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-13.56</v>
+        <v>-17.45</v>
       </c>
       <c r="H5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.22</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>38.3</v>
+        <v>52.2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1067,39 +1067,39 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>19.04</v>
+        <v>4.88</v>
       </c>
       <c r="P5" t="n">
-        <v>12.4</v>
+        <v>8.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.4</v>
+        <v>46.31</v>
       </c>
       <c r="R5" t="n">
-        <v>199.07</v>
+        <v>48.98</v>
       </c>
       <c r="S5" t="n">
-        <v>232.68</v>
+        <v>62.91</v>
       </c>
       <c r="T5" t="n">
-        <v>159.34</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
+        <v>43.45</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>270104</v>
+        <v>270504</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1107,17 +1107,17 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="3" t="n">
-        <v>20.4</v>
+      <c r="AD5" t="n">
+        <v>35.2</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>20日均线自身向上；20日跑赢沪深300超过10%</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,28 +1137,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>242</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-0.82</v>
+        <v>251</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>21.84</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-28.61</v>
+        <v>-11.13</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-37.7</v>
+        <v>-18.94</v>
       </c>
       <c r="H6" t="n">
-        <v>1.41</v>
+        <v>2.58</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -1167,59 +1167,59 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>-16.86</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>44.3</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-18.7</v>
+        <v>-3.17</v>
       </c>
       <c r="P6" t="n">
-        <v>11.35</v>
+        <v>12.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>214.53</v>
+        <v>219.16</v>
       </c>
       <c r="R6" t="n">
-        <v>291.07</v>
+        <v>249.64</v>
       </c>
       <c r="S6" t="n">
-        <v>442</v>
+        <v>320.82</v>
       </c>
       <c r="T6" t="n">
-        <v>234.98</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0</v>
+        <v>204.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>270104</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1227,17 +1227,17 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="3" t="n">
-        <v>18.5</v>
+      <c r="AD6" t="n">
+        <v>33.3</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；OBV创20日新高</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,28 +1257,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>106.96</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>-7.94</v>
+        <v>31.26</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5.25</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-16.31</v>
+        <v>-18.7</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-6.36</v>
+        <v>-14.52</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-8.789999999999999</v>
+        <v>-7.39</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>30.4</v>
+        <v>32.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,39 +1307,39 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-6.4</v>
+        <v>-10.74</v>
       </c>
       <c r="P7" t="n">
-        <v>13.77</v>
+        <v>11.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>92.23</v>
+        <v>27.68</v>
       </c>
       <c r="R7" t="n">
-        <v>117.27</v>
+        <v>33.76</v>
       </c>
       <c r="S7" t="n">
-        <v>131.25</v>
+        <v>46.74</v>
       </c>
       <c r="T7" t="n">
-        <v>94.73</v>
+        <v>28.35</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>270202</v>
+        <v>270504</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>18.5</v>
+        <v>24.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1377,28 +1377,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21.52</v>
+        <v>59.78</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10.25</v>
+        <v>4.95</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-12.8</v>
+        <v>-11.7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-19.85</v>
+        <v>-25.98</v>
       </c>
       <c r="H8" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -1411,55 +1411,55 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-5.69</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-5.22</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>金叉(转多)</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>29.4</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-2.89</v>
+        <v>-3.74</v>
       </c>
       <c r="P8" t="n">
-        <v>11.44</v>
+        <v>10.27</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.06</v>
+        <v>53.64</v>
       </c>
       <c r="R8" t="n">
-        <v>22.82</v>
+        <v>63.07</v>
       </c>
       <c r="S8" t="n">
-        <v>29.4</v>
+        <v>87.45</v>
       </c>
       <c r="T8" t="n">
-        <v>19.08</v>
+        <v>54.23</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>270303</v>
+        <v>270107</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>14.8</v>
+        <v>24.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>156.25</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-6.55</v>
+        <v>26.57</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2.55</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-30.13</v>
+        <v>-30.55</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-6.42</v>
+        <v>-4.42</v>
       </c>
       <c r="H9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.62</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-18.69</v>
+        <v>-12.3</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>26.6</v>
+        <v>21.1</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
@@ -1547,39 +1547,39 @@
         </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-20.22</v>
+        <v>-22.59</v>
       </c>
       <c r="P9" t="n">
-        <v>18.22</v>
+        <v>13.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>127.78</v>
+        <v>23.08</v>
       </c>
       <c r="R9" t="n">
-        <v>192.16</v>
+        <v>30.3</v>
       </c>
       <c r="S9" t="n">
-        <v>237.87</v>
+        <v>39.58</v>
       </c>
       <c r="T9" t="n">
-        <v>125.61</v>
+        <v>23.58</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>730206</v>
+        <v>640209</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>14.8</v>
+        <v>24.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,28 +1617,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>166.06</v>
+        <v>44.38</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-7.71</v>
+        <v>-0.72</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-34.32</v>
+        <v>-28.13</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-29.36</v>
+        <v>-27.38</v>
       </c>
       <c r="H10" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-21.69</v>
+        <v>-13.74</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>18.3</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
@@ -1667,39 +1667,39 @@
         </is>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-24.41</v>
+        <v>-20.17</v>
       </c>
       <c r="P10" t="n">
-        <v>14.85</v>
+        <v>11.57</v>
       </c>
       <c r="Q10" t="n">
-        <v>141.41</v>
+        <v>39.25</v>
       </c>
       <c r="R10" t="n">
-        <v>212.06</v>
+        <v>51.45</v>
       </c>
       <c r="S10" t="n">
-        <v>279.78</v>
+        <v>70.62</v>
       </c>
       <c r="T10" t="n">
-        <v>166.06</v>
+        <v>40.56</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>270103</v>
+        <v>640209</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>13</v>
+        <v>24.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>258.01</v>
+        <v>48.32</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-15.69</v>
+        <v>-0.72</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-39.1</v>
+        <v>-17.13</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-49.29</v>
+        <v>-30.79</v>
       </c>
       <c r="H11" t="n">
-        <v>1.29</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-30.25</v>
+        <v>-11.69</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>18.8</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -1787,39 +1787,39 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-29.19</v>
+        <v>-9.17</v>
       </c>
       <c r="P11" t="n">
-        <v>18.78</v>
+        <v>12.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>209.57</v>
+        <v>42.52</v>
       </c>
       <c r="R11" t="n">
-        <v>369.92</v>
+        <v>54.71</v>
       </c>
       <c r="S11" t="n">
-        <v>523.83</v>
+        <v>76.8</v>
       </c>
       <c r="T11" t="n">
-        <v>258</v>
+        <v>44.49</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>730204</v>
+        <v>270107</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>11.1</v>
+        <v>24.1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,28 +1857,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>13.75</v>
+        <v>74.58</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-1.48</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-8.52</v>
+        <v>-29.5</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-25.4</v>
+        <v>-33.36</v>
       </c>
       <c r="H12" t="n">
-        <v>1.62</v>
+        <v>0.74</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
@@ -1891,55 +1891,55 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-15.2</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>1.39</v>
+        <v>20.1</v>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>-21.54</v>
       </c>
       <c r="P12" t="n">
-        <v>7.6</v>
+        <v>11.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>70.41</v>
+        <v>66.02</v>
       </c>
       <c r="R12" t="n">
-        <v>77.36</v>
+        <v>87.95</v>
       </c>
       <c r="S12" t="n">
-        <v>104.14</v>
+        <v>114.58</v>
       </c>
       <c r="T12" t="n">
-        <v>66.11</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
+        <v>68.27</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>710101</v>
+        <v>640703</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>24.1</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,28 +1977,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>47.01</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>5.55</v>
+        <v>128.63</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-3.83</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-10.93</v>
+        <v>-32.73</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-20.39</v>
+        <v>-32.47</v>
       </c>
       <c r="H13" t="n">
-        <v>1.02</v>
+        <v>0.86</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
@@ -2011,55 +2011,55 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-4.18</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-17.02</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>22</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-1.02</v>
+        <v>-24.77</v>
       </c>
       <c r="P13" t="n">
-        <v>8.16</v>
+        <v>14.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>43.17</v>
+        <v>109.49</v>
       </c>
       <c r="R13" t="n">
-        <v>49.06</v>
+        <v>155.01</v>
       </c>
       <c r="S13" t="n">
-        <v>62.91</v>
+        <v>202.38</v>
       </c>
       <c r="T13" t="n">
-        <v>43.45</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
+        <v>116.78</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>270504</v>
+        <v>730204</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>24.1</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2097,28 +2097,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>30.46</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>2.21</v>
+        <v>107.06</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-5.57</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-21.39</v>
+        <v>-13.3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-19.38</v>
+        <v>-7.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>-10.72</v>
+        <v>-8.06</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -2139,47 +2139,47 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>36.3</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O14" s="3" t="n">
-        <v>-11.48</v>
+        <v>-5.34</v>
       </c>
       <c r="P14" t="n">
-        <v>11.63</v>
+        <v>13.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>26.92</v>
+        <v>92.17</v>
       </c>
       <c r="R14" t="n">
-        <v>34.12</v>
+        <v>116.45</v>
       </c>
       <c r="S14" t="n">
-        <v>46.74</v>
+        <v>131.25</v>
       </c>
       <c r="T14" t="n">
-        <v>29.37</v>
+        <v>94.73</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>270504</v>
+        <v>270202</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>24.1</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,28 +2217,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>111.87</v>
+        <v>200.81</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-0.65</v>
+        <v>-5.63</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-32.64</v>
+        <v>-27.68</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-32.85</v>
+        <v>-5.09</v>
       </c>
       <c r="H15" t="n">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-21.98</v>
+        <v>-15.92</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -2259,47 +2259,47 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>34.4</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-22.73</v>
+        <v>-19.72</v>
       </c>
       <c r="P15" t="n">
-        <v>14.59</v>
+        <v>18.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>95.54000000000001</v>
+        <v>163.83</v>
       </c>
       <c r="R15" t="n">
-        <v>143.38</v>
+        <v>238.84</v>
       </c>
       <c r="S15" t="n">
-        <v>189.92</v>
+        <v>294.5</v>
       </c>
       <c r="T15" t="n">
-        <v>107.9</v>
+        <v>155.05</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>270401</v>
+        <v>730204</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>24.1</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,28 +2337,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.53</v>
+        <v>114.22</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-2.55</v>
+        <v>-6.89</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-29.82</v>
+        <v>-40.98</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-28.06</v>
+        <v>-44.73</v>
       </c>
       <c r="H16" t="n">
-        <v>0.74</v>
+        <v>0.99</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-16.8</v>
+        <v>-24.37</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
@@ -2387,39 +2387,39 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-19.91</v>
+        <v>-33.02</v>
       </c>
       <c r="P16" t="n">
-        <v>11.54</v>
+        <v>15.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>38.51</v>
+        <v>96.16</v>
       </c>
       <c r="R16" t="n">
-        <v>52.32</v>
+        <v>151.02</v>
       </c>
       <c r="S16" t="n">
-        <v>70.62</v>
+        <v>219.85</v>
       </c>
       <c r="T16" t="n">
-        <v>43.04</v>
+        <v>105.01</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>640209</v>
+        <v>270202</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>24.1</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>60.54</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-4.47</v>
+        <v>244.68</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1.25</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-36.63</v>
+        <v>-26.98</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-42.3</v>
+        <v>-34.9</v>
       </c>
       <c r="H17" t="n">
-        <v>0.98</v>
+        <v>1.51</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-22.06</v>
+        <v>-14.61</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
@@ -2507,39 +2507,39 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-26.72</v>
+        <v>-19.02</v>
       </c>
       <c r="P17" t="n">
-        <v>15.21</v>
+        <v>10.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>51.33</v>
+        <v>217.9</v>
       </c>
       <c r="R17" t="n">
-        <v>77.67</v>
+        <v>286.55</v>
       </c>
       <c r="S17" t="n">
-        <v>109.38</v>
+        <v>442</v>
       </c>
       <c r="T17" t="n">
-        <v>60.4</v>
+        <v>230.05</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>640703</v>
+        <v>270104</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>22.2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>113.51</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-8.609999999999999</v>
+        <v>114.68</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2.67</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-40.88</v>
+        <v>-30.09</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-47.81</v>
+        <v>-29.65</v>
       </c>
       <c r="H18" t="n">
-        <v>0.87</v>
+        <v>1.07</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-26.76</v>
+        <v>-18.62</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>8.9</v>
+        <v>14.5</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
@@ -2627,39 +2627,39 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>-30.97</v>
+        <v>-22.13</v>
       </c>
       <c r="P18" t="n">
-        <v>16.86</v>
+        <v>13.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>94.37</v>
+        <v>98.95</v>
       </c>
       <c r="R18" t="n">
-        <v>154.99</v>
+        <v>140.92</v>
       </c>
       <c r="S18" t="n">
-        <v>224.03</v>
+        <v>189.92</v>
       </c>
       <c r="T18" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270202</v>
+        <v>270401</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>20.4</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>74.92</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0.13</v>
+        <v>48.92</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-1.25</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-23.82</v>
+        <v>-28.79</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-7.97</v>
+        <v>-14.62</v>
       </c>
       <c r="H19" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-12.88</v>
+        <v>-14.91</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>27.1</v>
+        <v>20.6</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -2747,39 +2747,39 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>-13.91</v>
+        <v>-20.83</v>
       </c>
       <c r="P19" t="n">
-        <v>14.84</v>
+        <v>13.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>63.8</v>
+        <v>42.3</v>
       </c>
       <c r="R19" t="n">
-        <v>85.98999999999999</v>
+        <v>57.49</v>
       </c>
       <c r="S19" t="n">
-        <v>102.82</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>69.63</v>
+        <v>44.32</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>650201</v>
+        <v>270303</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>5.6</v>
+        <v>20.4</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>45.3</v>
+        <v>61.89</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-4.65</v>
+        <v>-3.07</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-24.1</v>
+        <v>-34.72</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-21.03</v>
+        <v>-41.23</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-15.87</v>
+        <v>-18.59</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>14.2</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -2867,39 +2867,39 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-14.19</v>
+        <v>-26.76</v>
       </c>
       <c r="P20" t="n">
-        <v>17.32</v>
+        <v>14.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.45</v>
+        <v>53</v>
       </c>
       <c r="R20" t="n">
-        <v>53.85</v>
+        <v>76.02</v>
       </c>
       <c r="S20" t="n">
-        <v>67.05</v>
+        <v>105.28</v>
       </c>
       <c r="T20" t="n">
-        <v>43.01</v>
+        <v>56.9</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>640108</v>
+        <v>640703</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>5.6</v>
+        <v>18.5</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>39.13</v>
+        <v>167.36</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-5.19</v>
+        <v>-5.12</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-35.09</v>
+        <v>-32.89</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-44.9</v>
+        <v>-26.53</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-21.27</v>
+        <v>-19.52</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -2987,39 +2987,39 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-25.18</v>
+        <v>-24.93</v>
       </c>
       <c r="P21" t="n">
-        <v>16.07</v>
+        <v>14.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>32.84</v>
+        <v>142.72</v>
       </c>
       <c r="R21" t="n">
-        <v>49.7</v>
+        <v>207.95</v>
       </c>
       <c r="S21" t="n">
-        <v>74.8</v>
+        <v>279.78</v>
       </c>
       <c r="T21" t="n">
-        <v>38.86</v>
+        <v>153.89</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270203</v>
+        <v>270103</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>5.6</v>
+        <v>18.5</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3057,32 +3057,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>603083</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>127.6</v>
+        <v>158.38</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-4.03</v>
+        <v>-6.01</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-31.11</v>
+        <v>-27.69</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-33.51</v>
+        <v>-6.25</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>-19.31</v>
+        <v>-16.26</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -3099,47 +3099,47 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>16</v>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>31.2</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>-21.2</v>
+        <v>-19.73</v>
       </c>
       <c r="P22" t="n">
-        <v>15.61</v>
+        <v>17.46</v>
       </c>
       <c r="Q22" t="n">
-        <v>107.68</v>
+        <v>130.72</v>
       </c>
       <c r="R22" t="n">
-        <v>158.14</v>
+        <v>189.13</v>
       </c>
       <c r="S22" t="n">
-        <v>202.38</v>
+        <v>237.87</v>
       </c>
       <c r="T22" t="n">
-        <v>126.7</v>
+        <v>125.61</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>730204</v>
+        <v>730206</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>3.7</v>
+        <v>18.5</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>72.65000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-4.75</v>
+        <v>-6.06</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-31.45</v>
+        <v>-14.08</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-36</v>
+        <v>-38.37</v>
       </c>
       <c r="H23" t="n">
-        <v>0.62</v>
+        <v>1.03</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-18.84</v>
+        <v>-10</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
@@ -3219,47 +3219,47 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>30.4</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-21.54</v>
+        <v>-6.12</v>
       </c>
       <c r="P23" t="n">
-        <v>12.49</v>
+        <v>8.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>63.58</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>89.51000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="S23" t="n">
-        <v>117</v>
+        <v>121.57</v>
       </c>
       <c r="T23" t="n">
-        <v>72.13</v>
+        <v>69.38</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>640703</v>
+        <v>630503</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>3.7</v>
+        <v>18.5</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>70.51000000000001</v>
+        <v>261</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-7.35</v>
+        <v>-14.96</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-16.6</v>
+        <v>-38.49</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-35.5</v>
+        <v>-47.52</v>
       </c>
       <c r="H24" t="n">
-        <v>0.96</v>
+        <v>1.57</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-12.75</v>
+        <v>-27.85</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>21.6</v>
+        <v>5.6</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
@@ -3347,48 +3347,48 @@
         </is>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-6.69</v>
+        <v>-30.53</v>
       </c>
       <c r="P24" t="n">
-        <v>8.539999999999999</v>
+        <v>18.01</v>
       </c>
       <c r="Q24" t="n">
-        <v>64.48999999999999</v>
+        <v>213.99</v>
       </c>
       <c r="R24" t="n">
-        <v>80.81999999999999</v>
+        <v>361.76</v>
       </c>
       <c r="S24" t="n">
-        <v>121.57</v>
+        <v>495.65</v>
       </c>
       <c r="T24" t="n">
-        <v>70.40000000000001</v>
+        <v>236.1</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>630503</v>
+        <v>730204</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>3.7</v>
+        <v>16.7</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>无风险扣分项触发</t>
+          <t>换手率处于近60日95分位以上(极端活跃)</t>
         </is>
       </c>
     </row>
@@ -3417,32 +3417,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>197</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-11.79</v>
+        <v>76.81</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0.71</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-26.63</v>
+        <v>-19.81</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-9.27</v>
+        <v>-4.07</v>
       </c>
       <c r="H25" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.67</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-18.82</v>
+        <v>-9.68</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3459,47 +3459,47 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>35.4</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-16.72</v>
+        <v>-11.85</v>
       </c>
       <c r="P25" t="n">
-        <v>19.07</v>
+        <v>14.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>159.43</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>242.68</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>294.5</v>
+        <v>102.82</v>
       </c>
       <c r="T25" t="n">
-        <v>155.05</v>
+        <v>69.63</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>730204</v>
+        <v>650201</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>3.7</v>
+        <v>14.8</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,32 +3537,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>161.89</v>
+        <v>27.29</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-14.1</v>
+        <v>-5.01</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-21.56</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>11.24</v>
+        <v>-17</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-26.91</v>
       </c>
       <c r="H26" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.85</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-18.7</v>
+        <v>-11.77</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -3579,47 +3579,47 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
+        <v>40.5</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-11.65</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>20.87</v>
+        <v>13.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>128.1</v>
+        <v>23.57</v>
       </c>
       <c r="R26" t="n">
-        <v>199.13</v>
+        <v>30.93</v>
       </c>
       <c r="S26" t="n">
-        <v>242.99</v>
+        <v>40.38</v>
       </c>
       <c r="T26" t="n">
-        <v>102.3</v>
+        <v>25.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>730204</v>
+        <v>630702</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>3.7</v>
+        <v>14.8</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3657,28 +3657,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>48.3</v>
+        <v>45.97</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.46</v>
+        <v>-7.15</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-29.58</v>
+        <v>-23.76</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-16.03</v>
+        <v>-17.5</v>
       </c>
       <c r="H27" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-17.41</v>
+        <v>-13.48</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>14.1</v>
+        <v>22.9</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -3707,39 +3707,39 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-19.67</v>
+        <v>-15.8</v>
       </c>
       <c r="P27" t="n">
-        <v>14.19</v>
+        <v>16.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>41.45</v>
+        <v>38.18</v>
       </c>
       <c r="R27" t="n">
-        <v>58.48</v>
+        <v>53.13</v>
       </c>
       <c r="S27" t="n">
-        <v>72.68000000000001</v>
+        <v>67.05</v>
       </c>
       <c r="T27" t="n">
-        <v>46.88</v>
+        <v>41.8</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>270303</v>
+        <v>640108</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>25.05</v>
+        <v>38.73</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-4.32</v>
+        <v>-5.26</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-34.39</v>
+        <v>-35.51</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-11.08</v>
+        <v>-41.69</v>
       </c>
       <c r="H28" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.85</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-18.88</v>
+        <v>-20.36</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>7.8</v>
+        <v>12.2</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -3827,39 +3827,39 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>-24.48</v>
+        <v>-27.55</v>
       </c>
       <c r="P28" t="n">
-        <v>14.07</v>
+        <v>15.52</v>
       </c>
       <c r="Q28" t="n">
-        <v>21.53</v>
+        <v>32.72</v>
       </c>
       <c r="R28" t="n">
-        <v>30.88</v>
+        <v>48.63</v>
       </c>
       <c r="S28" t="n">
-        <v>39.58</v>
+        <v>72.45</v>
       </c>
       <c r="T28" t="n">
-        <v>23.58</v>
+        <v>35.42</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>640209</v>
+        <v>270203</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>明显放量(1.5-2.5倍)</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25.9</v>
+        <v>160.99</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-12.08</v>
+        <v>-7.47</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-21.75</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>-26.34</v>
+        <v>-25.46</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>14.18</v>
       </c>
       <c r="H29" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.89</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-17.02</v>
+        <v>-18.02</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3947,39 +3947,39 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-11.84</v>
+        <v>-17.5</v>
       </c>
       <c r="P29" t="n">
-        <v>13.95</v>
+        <v>20.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>22.29</v>
+        <v>127.59</v>
       </c>
       <c r="R29" t="n">
-        <v>31.21</v>
+        <v>196.38</v>
       </c>
       <c r="S29" t="n">
-        <v>40.38</v>
+        <v>242.99</v>
       </c>
       <c r="T29" t="n">
-        <v>25.9</v>
+        <v>102.3</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>630702</v>
+        <v>730204</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,10 +473,10 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="51" customWidth="1" min="31" max="31"/>
-    <col width="66" customWidth="1" min="32" max="32"/>
+    <col width="57" customWidth="1" min="31" max="31"/>
+    <col width="58" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
-    <col width="25" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,23 +666,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>214.04</v>
+        <v>210.2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>25.16</v>
+        <v>22.32</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.58</v>
+        <v>10.61</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-4.71</v>
       </c>
       <c r="H2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>1.5</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -691,15 +691,15 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>6.64</v>
+        <v>4.2</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>51.3</v>
+        <v>48.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -707,39 +707,39 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>26.08</v>
+        <v>19.57</v>
       </c>
       <c r="P2" t="n">
-        <v>12.32</v>
+        <v>12.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>187.68</v>
+        <v>183.11</v>
       </c>
       <c r="R2" t="n">
-        <v>200.71</v>
+        <v>201.72</v>
       </c>
       <c r="S2" t="n">
-        <v>229.8</v>
+        <v>228.74</v>
       </c>
       <c r="T2" t="n">
         <v>159.34</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>270104</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -748,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>46.3</v>
+        <v>42.6</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线5-10%</t>
+          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,28 +777,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.84</v>
+        <v>49.81</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17.73</v>
+        <v>8.07</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-7.04</v>
+        <v>-7.74</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-15.12</v>
+        <v>-17.64</v>
       </c>
       <c r="H3" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
@@ -811,15 +811,15 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.48</v>
+        <v>2.13</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>金叉(转多)</t>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>48.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -827,39 +827,39 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.92</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>11.32</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.25</v>
+        <v>45.72</v>
       </c>
       <c r="R3" t="n">
-        <v>22.73</v>
+        <v>48.77</v>
       </c>
       <c r="S3" t="n">
-        <v>29.4</v>
+        <v>62.91</v>
       </c>
       <c r="T3" t="n">
-        <v>19.08</v>
+        <v>43.45</v>
       </c>
       <c r="U3" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270303</v>
+        <v>270504</v>
       </c>
       <c r="Z3" t="n">
         <v>7</v>
       </c>
       <c r="AA3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -867,8 +867,8 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="n">
-        <v>40.7</v>
+      <c r="AD3" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>78.11</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10.83</v>
+        <v>5.26</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-5.53</v>
+        <v>-7.65</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>-20.15</v>
       </c>
       <c r="H4" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>46.2</v>
+        <v>44.9</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,19 +947,19 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>2.43</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>7.91</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>71.93000000000001</v>
+        <v>71.52</v>
       </c>
       <c r="R4" t="n">
-        <v>77.13</v>
+        <v>76.81</v>
       </c>
       <c r="S4" t="n">
-        <v>101.5</v>
+        <v>97.88</v>
       </c>
       <c r="T4" t="n">
         <v>66.11</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -979,7 +979,7 @@
         <v>7</v>
       </c>
       <c r="AA4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -987,8 +987,8 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="n">
-        <v>38.9</v>
+      <c r="AD4" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；OBV创20日新高</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,28 +1017,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>13.15</v>
+        <v>251.69</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-18.28</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-3.08</v>
+        <v>-43.44</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-17.45</v>
+        <v>-47.13</v>
       </c>
       <c r="H5" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -1047,59 +1047,59 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>-28.52</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>4.88</v>
+        <v>5.5</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-34.48</v>
       </c>
       <c r="P5" t="n">
-        <v>8.15</v>
+        <v>19.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>46.31</v>
+        <v>203.01</v>
       </c>
       <c r="R5" t="n">
-        <v>48.98</v>
+        <v>352.09</v>
       </c>
       <c r="S5" t="n">
-        <v>62.91</v>
+        <v>492.41</v>
       </c>
       <c r="T5" t="n">
-        <v>43.45</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>4</v>
+        <v>236.1</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>270504</v>
+        <v>730204</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1107,17 +1107,17 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" t="n">
-        <v>35.2</v>
+      <c r="AD5" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>251</v>
+        <v>242.52</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>21.84</v>
+        <v>10.64</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-11.13</v>
+        <v>-17.51</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-18.94</v>
+        <v>-14.77</v>
       </c>
       <c r="H6" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -1167,11 +1167,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0.54</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-1.84</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>44.3</v>
+        <v>40.9</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1187,16 +1187,16 @@
         </is>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-3.17</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>12.68</v>
+        <v>14.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>219.16</v>
+        <v>208.48</v>
       </c>
       <c r="R6" t="n">
-        <v>249.64</v>
+        <v>247.07</v>
       </c>
       <c r="S6" t="n">
         <v>320.82</v>
@@ -1205,21 +1205,21 @@
         <v>204.5</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>270104</v>
       </c>
       <c r="Z6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1227,17 +1227,17 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" t="n">
-        <v>33.3</v>
+      <c r="AD6" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；OBV创20日新高</t>
+          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,28 +1257,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.26</v>
+        <v>22.13</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5.25</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-18.7</v>
+        <v>-13.11</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-14.52</v>
+        <v>-18.79</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -1291,15 +1291,15 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-7.39</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+        <v>-1.93</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>32.5</v>
+        <v>43.4</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1307,39 +1307,39 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-10.74</v>
+        <v>-4.15</v>
       </c>
       <c r="P7" t="n">
-        <v>11.47</v>
+        <v>11.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.68</v>
+        <v>19.49</v>
       </c>
       <c r="R7" t="n">
-        <v>33.76</v>
+        <v>22.56</v>
       </c>
       <c r="S7" t="n">
-        <v>46.74</v>
+        <v>29.4</v>
       </c>
       <c r="T7" t="n">
-        <v>28.35</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>1</v>
+        <v>19.08</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>270504</v>
+        <v>270303</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1386,19 +1386,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>4.95</v>
+        <v>55.1</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-2.2</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-11.7</v>
+        <v>-24.47</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-25.98</v>
+        <v>-33.49</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -1411,15 +1411,15 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-5.22</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>金叉(转多)</t>
+        <v>-11.39</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>死叉(转空)</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>29.4</v>
+        <v>20.8</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
@@ -1427,16 +1427,16 @@
         </is>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-3.74</v>
+        <v>-15.51</v>
       </c>
       <c r="P8" t="n">
-        <v>10.27</v>
+        <v>11.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>53.64</v>
+        <v>48.51</v>
       </c>
       <c r="R8" t="n">
-        <v>63.07</v>
+        <v>62.18</v>
       </c>
       <c r="S8" t="n">
         <v>87.45</v>
@@ -1445,11 +1445,11 @@
         <v>54.23</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1497,28 +1497,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>2.55</v>
+        <v>196.98</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-3.11</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-30.55</v>
+        <v>-30.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-4.42</v>
+        <v>-2.92</v>
       </c>
       <c r="H9" t="n">
-        <v>0.62</v>
+        <v>1.02</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-12.3</v>
+        <v>-15.98</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>21.1</v>
+        <v>28</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
@@ -1547,39 +1547,39 @@
         </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-22.59</v>
+        <v>-21.84</v>
       </c>
       <c r="P9" t="n">
-        <v>13.15</v>
+        <v>18.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.08</v>
+        <v>159.76</v>
       </c>
       <c r="R9" t="n">
-        <v>30.3</v>
+        <v>234.45</v>
       </c>
       <c r="S9" t="n">
-        <v>39.58</v>
+        <v>294.5</v>
       </c>
       <c r="T9" t="n">
-        <v>23.58</v>
+        <v>155.05</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>640209</v>
+        <v>730204</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1617,28 +1617,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>44.38</v>
+        <v>233</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-0.72</v>
+        <v>-4.04</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-28.13</v>
+        <v>-32.85</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>-27.38</v>
+        <v>-37.03</v>
       </c>
       <c r="H10" t="n">
-        <v>0.86</v>
+        <v>1.47</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-13.74</v>
+        <v>-17.04</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>18.3</v>
+        <v>10.1</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
@@ -1667,39 +1667,39 @@
         </is>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-20.17</v>
+        <v>-23.89</v>
       </c>
       <c r="P10" t="n">
-        <v>11.57</v>
+        <v>11.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.25</v>
+        <v>205.23</v>
       </c>
       <c r="R10" t="n">
-        <v>51.45</v>
+        <v>280.86</v>
       </c>
       <c r="S10" t="n">
-        <v>70.62</v>
+        <v>442</v>
       </c>
       <c r="T10" t="n">
-        <v>40.56</v>
+        <v>230.05</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>640209</v>
+        <v>270104</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>48.32</v>
+        <v>160.16</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.72</v>
+        <v>-6.54</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-17.13</v>
+        <v>-38.5</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-30.79</v>
+        <v>-30.2</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-11.69</v>
+        <v>-21.08</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>18.8</v>
+        <v>4.6</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -1787,39 +1787,39 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-9.17</v>
+        <v>-29.54</v>
       </c>
       <c r="P11" t="n">
-        <v>12.01</v>
+        <v>15.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>42.52</v>
+        <v>135.25</v>
       </c>
       <c r="R11" t="n">
-        <v>54.71</v>
+        <v>202.94</v>
       </c>
       <c r="S11" t="n">
-        <v>76.8</v>
+        <v>279.78</v>
       </c>
       <c r="T11" t="n">
-        <v>44.49</v>
+        <v>153.89</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>270107</v>
+        <v>270103</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1857,28 +1857,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>000988</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>74.58</v>
+        <v>58.44</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-1.48</v>
+        <v>-7.53</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-29.5</v>
+        <v>-41.33</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-33.36</v>
+        <v>-42.57</v>
       </c>
       <c r="H12" t="n">
-        <v>0.74</v>
+        <v>1.05</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>-15.2</v>
+        <v>-20.99</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>20.1</v>
+        <v>12.7</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
@@ -1907,29 +1907,29 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>-21.54</v>
+        <v>-32.37</v>
       </c>
       <c r="P12" t="n">
-        <v>11.48</v>
+        <v>15.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>66.02</v>
+        <v>49.25</v>
       </c>
       <c r="R12" t="n">
-        <v>87.95</v>
+        <v>73.97</v>
       </c>
       <c r="S12" t="n">
-        <v>114.58</v>
+        <v>103.77</v>
       </c>
       <c r="T12" t="n">
-        <v>68.27</v>
+        <v>56.9</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W12" t="n">
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1977,28 +1977,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>128.63</v>
+        <v>70.23</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-3.83</v>
+        <v>-9.59</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-32.73</v>
+        <v>-19.51</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-32.47</v>
+        <v>-37.73</v>
       </c>
       <c r="H13" t="n">
-        <v>0.86</v>
+        <v>1.16</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-17.02</v>
+        <v>-11.52</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
@@ -2027,39 +2027,39 @@
         </is>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-24.77</v>
+        <v>-10.55</v>
       </c>
       <c r="P13" t="n">
-        <v>14.88</v>
+        <v>8.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>109.49</v>
+        <v>64.33</v>
       </c>
       <c r="R13" t="n">
-        <v>155.01</v>
+        <v>79.38</v>
       </c>
       <c r="S13" t="n">
-        <v>202.38</v>
+        <v>121.57</v>
       </c>
       <c r="T13" t="n">
-        <v>116.78</v>
+        <v>69.38</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>730204</v>
+        <v>630503</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2106,19 +2106,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>107.06</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-5.57</v>
+        <v>-11.5</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-13.3</v>
+        <v>-19.92</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-7.5</v>
+        <v>-11.87</v>
       </c>
       <c r="H14" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>-8.06</v>
+        <v>-14.16</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -2139,24 +2139,24 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>26.7</v>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O14" s="3" t="n">
-        <v>-5.34</v>
+        <v>-10.96</v>
       </c>
       <c r="P14" t="n">
-        <v>13.91</v>
+        <v>15.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>92.17</v>
+        <v>83.34</v>
       </c>
       <c r="R14" t="n">
-        <v>116.45</v>
+        <v>115.22</v>
       </c>
       <c r="S14" t="n">
         <v>131.25</v>
@@ -2165,11 +2165,11 @@
         <v>94.73</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W14" t="n">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2217,28 +2217,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>200.81</v>
+        <v>105.43</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-5.63</v>
+        <v>-13.69</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-27.68</v>
+        <v>-46.25</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-5.09</v>
+        <v>-47.07</v>
       </c>
       <c r="H15" t="n">
-        <v>0.97</v>
+        <v>1.12</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-15.92</v>
+        <v>-28.03</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -2259,57 +2259,57 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>7.3</v>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-19.72</v>
+        <v>-37.29</v>
       </c>
       <c r="P15" t="n">
-        <v>18.42</v>
+        <v>18.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>163.83</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>238.84</v>
+        <v>146.49</v>
       </c>
       <c r="S15" t="n">
-        <v>294.5</v>
+        <v>219.85</v>
       </c>
       <c r="T15" t="n">
-        <v>155.05</v>
+        <v>103.05</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>730204</v>
+        <v>270202</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="3" t="n">
-        <v>24.1</v>
-      </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>无明显信号</t>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2337,28 +2337,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>114.22</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>-6.89</v>
+        <v>26.15</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0.77</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-40.98</v>
+        <v>-30.67</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-44.73</v>
+        <v>-3.18</v>
       </c>
       <c r="H16" t="n">
-        <v>0.99</v>
+        <v>0.73</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-24.37</v>
+        <v>-12</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>12</v>
+        <v>20.4</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
@@ -2387,39 +2387,39 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-33.02</v>
+        <v>-21.71</v>
       </c>
       <c r="P16" t="n">
-        <v>15.81</v>
+        <v>13.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>96.16</v>
+        <v>22.62</v>
       </c>
       <c r="R16" t="n">
-        <v>151.02</v>
+        <v>29.72</v>
       </c>
       <c r="S16" t="n">
-        <v>219.85</v>
+        <v>39.58</v>
       </c>
       <c r="T16" t="n">
-        <v>105.01</v>
+        <v>23.58</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>270202</v>
+        <v>640209</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>24.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>244.68</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>1.25</v>
+        <v>29.73</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-2.59</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-26.98</v>
+        <v>-23.93</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-34.9</v>
+        <v>-15.97</v>
       </c>
       <c r="H17" t="n">
-        <v>1.51</v>
+        <v>0.96</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-14.61</v>
+        <v>-10.69</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
@@ -2507,39 +2507,39 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-19.02</v>
+        <v>-14.97</v>
       </c>
       <c r="P17" t="n">
-        <v>10.94</v>
+        <v>12.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>217.9</v>
+        <v>26.11</v>
       </c>
       <c r="R17" t="n">
-        <v>286.55</v>
+        <v>33.29</v>
       </c>
       <c r="S17" t="n">
-        <v>442</v>
+        <v>46.74</v>
       </c>
       <c r="T17" t="n">
-        <v>230.05</v>
+        <v>28.35</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>270104</v>
+        <v>270504</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>22.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>114.68</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>2.67</v>
+        <v>42.97</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-3.35</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-30.09</v>
+        <v>-32.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-29.65</v>
+        <v>-26.8</v>
       </c>
       <c r="H18" t="n">
-        <v>1.07</v>
+        <v>0.9</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-18.62</v>
+        <v>-14.8</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
@@ -2627,39 +2627,39 @@
         </is>
       </c>
       <c r="O18" s="3" t="n">
-        <v>-22.13</v>
+        <v>-23.14</v>
       </c>
       <c r="P18" t="n">
-        <v>13.71</v>
+        <v>11.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>98.95</v>
+        <v>37.9</v>
       </c>
       <c r="R18" t="n">
-        <v>140.92</v>
+        <v>50.43</v>
       </c>
       <c r="S18" t="n">
-        <v>189.92</v>
+        <v>70.62</v>
       </c>
       <c r="T18" t="n">
-        <v>105</v>
+        <v>40.56</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>270401</v>
+        <v>640209</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>20.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2697,28 +2697,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48.92</v>
+        <v>109.06</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-1.25</v>
+        <v>-4.33</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-28.79</v>
+        <v>-37.44</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-14.62</v>
+        <v>-32.51</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-14.91</v>
+        <v>-20.77</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>20.6</v>
+        <v>12.6</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -2747,39 +2747,39 @@
         </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>-20.83</v>
+        <v>-28.48</v>
       </c>
       <c r="P19" t="n">
-        <v>13.53</v>
+        <v>14.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>42.3</v>
+        <v>93.02</v>
       </c>
       <c r="R19" t="n">
-        <v>57.49</v>
+        <v>137.65</v>
       </c>
       <c r="S19" t="n">
-        <v>72.68000000000001</v>
+        <v>189.92</v>
       </c>
       <c r="T19" t="n">
-        <v>44.32</v>
+        <v>105</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>270303</v>
+        <v>270401</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>20.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>61.89</v>
+        <v>44.56</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-3.07</v>
+        <v>-6.48</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-34.72</v>
+        <v>-27.4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-41.23</v>
+        <v>-41.86</v>
       </c>
       <c r="H20" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-18.59</v>
+        <v>-17.29</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>14.2</v>
+        <v>8.9</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -2867,39 +2867,39 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-26.76</v>
+        <v>-18.44</v>
       </c>
       <c r="P20" t="n">
-        <v>14.37</v>
+        <v>13.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>53</v>
+        <v>38.61</v>
       </c>
       <c r="R20" t="n">
-        <v>76.02</v>
+        <v>53.87</v>
       </c>
       <c r="S20" t="n">
-        <v>105.28</v>
+        <v>76.7</v>
       </c>
       <c r="T20" t="n">
-        <v>56.9</v>
+        <v>44.41</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>640703</v>
+        <v>270107</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>18.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>167.36</v>
+        <v>122.53</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-5.12</v>
+        <v>-7.54</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-32.89</v>
+        <v>-37.29</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-26.53</v>
+        <v>-34.41</v>
       </c>
       <c r="H21" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-19.52</v>
+        <v>-19.05</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>4.9</v>
+        <v>16.3</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -2987,39 +2987,39 @@
         </is>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-24.93</v>
+        <v>-28.33</v>
       </c>
       <c r="P21" t="n">
-        <v>14.73</v>
+        <v>15.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>142.72</v>
+        <v>103.11</v>
       </c>
       <c r="R21" t="n">
-        <v>207.95</v>
+        <v>151.36</v>
       </c>
       <c r="S21" t="n">
-        <v>279.78</v>
+        <v>202.38</v>
       </c>
       <c r="T21" t="n">
-        <v>153.89</v>
+        <v>116.78</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>270103</v>
+        <v>730204</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>18.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3066,19 +3066,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>158.38</v>
+        <v>145.89</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-6.01</v>
+        <v>-10.94</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-27.69</v>
+        <v>-36.01</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-6.25</v>
+        <v>-12.49</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>-16.26</v>
+        <v>-21.15</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -3099,24 +3099,24 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>25.5</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O22" s="3" t="n">
-        <v>-19.73</v>
+        <v>-27.05</v>
       </c>
       <c r="P22" t="n">
-        <v>17.46</v>
+        <v>19.22</v>
       </c>
       <c r="Q22" t="n">
-        <v>130.72</v>
+        <v>117.85</v>
       </c>
       <c r="R22" t="n">
-        <v>189.13</v>
+        <v>185.02</v>
       </c>
       <c r="S22" t="n">
         <v>237.87</v>
@@ -3125,11 +3125,11 @@
         <v>125.61</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>18.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300274</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>72.2</v>
+        <v>35.98</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-6.06</v>
+        <v>-11.25</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-14.08</v>
+        <v>-41.48</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-38.37</v>
+        <v>-43.42</v>
       </c>
       <c r="H23" t="n">
-        <v>1.03</v>
+        <v>0.93</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-10</v>
+        <v>-24.03</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
@@ -3219,47 +3219,47 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>7.5</v>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-6.12</v>
+        <v>-32.52</v>
       </c>
       <c r="P23" t="n">
-        <v>8.25</v>
+        <v>16.81</v>
       </c>
       <c r="Q23" t="n">
-        <v>66.23999999999999</v>
+        <v>29.93</v>
       </c>
       <c r="R23" t="n">
-        <v>80.23</v>
+        <v>47.36</v>
       </c>
       <c r="S23" t="n">
-        <v>121.57</v>
+        <v>72.45</v>
       </c>
       <c r="T23" t="n">
-        <v>69.38</v>
+        <v>35.42</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>630503</v>
+        <v>270203</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>18.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>261</v>
+        <v>75.25</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-14.96</v>
+        <v>-0.29</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-38.49</v>
+        <v>-19.27</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-47.52</v>
+        <v>-3.07</v>
       </c>
       <c r="H24" t="n">
-        <v>1.57</v>
+        <v>0.7</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-27.85</v>
+        <v>-10.57</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3339,57 +3339,57 @@
         </is>
       </c>
       <c r="M24" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>-10.31</v>
+      </c>
+      <c r="P24" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="R24" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="S24" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="T24" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>650201</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>-30.53</v>
-      </c>
-      <c r="P24" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>213.99</v>
-      </c>
-      <c r="R24" t="n">
-        <v>361.76</v>
-      </c>
-      <c r="S24" t="n">
-        <v>495.65</v>
-      </c>
-      <c r="T24" t="n">
-        <v>236.1</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="W24" t="n">
-        <v>730204</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD24" s="3" t="n">
-        <v>16.7</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>无明显信号</t>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>换手率处于近60日95分位以上(极端活跃)</t>
+          <t>无风险扣分项触发</t>
         </is>
       </c>
     </row>
@@ -3417,28 +3417,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>76.81</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0.71</v>
+        <v>46.88</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-3.32</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-19.81</v>
+        <v>-32.74</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-4.07</v>
+        <v>-16.27</v>
       </c>
       <c r="H25" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-9.68</v>
+        <v>-16.81</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3459,47 +3459,47 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>17.4</v>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-11.85</v>
+        <v>-23.78</v>
       </c>
       <c r="P25" t="n">
-        <v>14.2</v>
+        <v>14.37</v>
       </c>
       <c r="Q25" t="n">
-        <v>65.90000000000001</v>
+        <v>40.14</v>
       </c>
       <c r="R25" t="n">
-        <v>85.04000000000001</v>
+        <v>56.35</v>
       </c>
       <c r="S25" t="n">
-        <v>102.82</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>69.63</v>
+        <v>44.32</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>650201</v>
+        <v>270303</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3537,28 +3537,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002709</t>
+          <t>000988</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>27.29</v>
+        <v>72.36</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-5.01</v>
+        <v>-3.8</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-17</v>
+        <v>-32.88</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-26.91</v>
+        <v>-33.12</v>
       </c>
       <c r="H26" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-11.77</v>
+        <v>-16.04</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -3579,47 +3579,47 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>14.3</v>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-9.039999999999999</v>
+        <v>-23.92</v>
       </c>
       <c r="P26" t="n">
-        <v>13.63</v>
+        <v>11.87</v>
       </c>
       <c r="Q26" t="n">
-        <v>23.57</v>
+        <v>63.77</v>
       </c>
       <c r="R26" t="n">
-        <v>30.93</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>40.38</v>
+        <v>114.58</v>
       </c>
       <c r="T26" t="n">
-        <v>25.2</v>
+        <v>68.27</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>630702</v>
+        <v>640703</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；今日上涨且放量</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3666,19 +3666,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>45.97</v>
+        <v>43.74</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-7.15</v>
+        <v>-5.22</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-23.76</v>
+        <v>-31.94</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-17.5</v>
+        <v>-22.14</v>
       </c>
       <c r="H27" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-13.48</v>
+        <v>-16.05</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -3707,16 +3707,16 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-15.8</v>
+        <v>-22.98</v>
       </c>
       <c r="P27" t="n">
-        <v>16.96</v>
+        <v>17.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>38.18</v>
+        <v>35.88</v>
       </c>
       <c r="R27" t="n">
-        <v>53.13</v>
+        <v>52.1</v>
       </c>
       <c r="S27" t="n">
         <v>67.05</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W27" t="n">
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>14.8</v>
+        <v>5.6</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,32 +3777,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>38.73</v>
+        <v>152.92</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-5.26</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-35.51</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>-41.69</v>
+        <v>-33.32</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>12.5</v>
       </c>
       <c r="H28" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>0.89</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-20.36</v>
+        <v>-20.59</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>12.2</v>
+        <v>22</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -3827,39 +3827,39 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>-27.55</v>
+        <v>-24.36</v>
       </c>
       <c r="P28" t="n">
-        <v>15.52</v>
+        <v>20.93</v>
       </c>
       <c r="Q28" t="n">
-        <v>32.72</v>
+        <v>120.91</v>
       </c>
       <c r="R28" t="n">
-        <v>48.63</v>
+        <v>192.56</v>
       </c>
       <c r="S28" t="n">
-        <v>72.45</v>
+        <v>242.99</v>
       </c>
       <c r="T28" t="n">
-        <v>35.42</v>
+        <v>102.3</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>270203</v>
+        <v>730204</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>11.1</v>
+        <v>3.7</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)</t>
+          <t>量能温和(0.8-1.2倍)</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3897,32 +3897,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>002709</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>160.99</v>
+        <v>27.43</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.47</v>
+        <v>-1.72</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-25.46</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>14.18</v>
+        <v>-17.78</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-25.32</v>
       </c>
       <c r="H29" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>震荡交织</t>
+        <v>0.82</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-18.02</v>
+        <v>-10.46</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>32.6</v>
+        <v>38.8</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3947,39 +3947,39 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-17.5</v>
+        <v>-8.82</v>
       </c>
       <c r="P29" t="n">
-        <v>20.75</v>
+        <v>13.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>127.59</v>
+        <v>23.7</v>
       </c>
       <c r="R29" t="n">
-        <v>196.38</v>
+        <v>30.63</v>
       </c>
       <c r="S29" t="n">
-        <v>242.99</v>
+        <v>40.38</v>
       </c>
       <c r="T29" t="n">
-        <v>102.3</v>
+        <v>25.2</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>730204</v>
+        <v>630702</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/分析报表.xlsx
+++ b/分析报表.xlsx
@@ -473,7 +473,7 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="57" customWidth="1" min="31" max="31"/>
+    <col width="31" customWidth="1" min="31" max="31"/>
     <col width="58" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
@@ -657,41 +657,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>210.2</v>
+        <v>224</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>22.32</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>10.61</v>
+        <v>2.03</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>-24.16</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-4.71</v>
+        <v>-21.62</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>多头排列</t>
+        <v>2.45</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>空头排列</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>4.2</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>-8.01</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -699,47 +699,47 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>48.7</v>
+        <v>38.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>19.57</v>
+      <c r="O2" s="3" t="n">
+        <v>-13.37</v>
       </c>
       <c r="P2" t="n">
-        <v>12.89</v>
+        <v>15.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.11</v>
+        <v>188.47</v>
       </c>
       <c r="R2" t="n">
-        <v>201.72</v>
+        <v>243.5</v>
       </c>
       <c r="S2" t="n">
-        <v>228.74</v>
+        <v>320.82</v>
       </c>
       <c r="T2" t="n">
-        <v>159.34</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>5</v>
+        <v>204.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>270104</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -747,17 +747,17 @@
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" t="n">
-        <v>42.6</v>
+      <c r="AD2" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>股价站上20日均线；20日均线自身向上；20日跑赢沪深300超过10%；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -777,28 +777,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>49.81</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>8.07</v>
+        <v>48.26</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>-3.48</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-7.74</v>
+        <v>-30.82</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-17.64</v>
+        <v>-15.76</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
@@ -807,59 +807,59 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>-12.69</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>1.22</v>
+        <v>23.4</v>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-20.03</v>
       </c>
       <c r="P3" t="n">
-        <v>8.210000000000001</v>
+        <v>14.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>45.72</v>
+        <v>41.27</v>
       </c>
       <c r="R3" t="n">
-        <v>48.77</v>
+        <v>55.28</v>
       </c>
       <c r="S3" t="n">
-        <v>62.91</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>43.45</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>4</v>
+        <v>44.32</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>270504</v>
+        <v>270303</v>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -868,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>27.8</v>
+        <v>22.2</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>无明显信号</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>明显放量(1.5-2.5倍)；今日上涨且放量；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,41 +897,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>77.84999999999999</v>
+        <v>193</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.26</v>
+        <v>2.09</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-7.65</v>
+        <v>-2.53</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-20.15</v>
+        <v>-10.98</v>
       </c>
       <c r="H4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.35</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>多头排列</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>1.36</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>-4.21</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>44.9</v>
+        <v>40.7</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -947,39 +947,39 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1.31</v>
+        <v>8.26</v>
       </c>
       <c r="P4" t="n">
-        <v>8.130000000000001</v>
+        <v>14.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>71.52</v>
+        <v>164.26</v>
       </c>
       <c r="R4" t="n">
-        <v>76.81</v>
+        <v>201.47</v>
       </c>
       <c r="S4" t="n">
-        <v>97.88</v>
+        <v>228.74</v>
       </c>
       <c r="T4" t="n">
-        <v>66.11</v>
+        <v>159.34</v>
       </c>
       <c r="U4" s="2" t="n">
         <v>4</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>710101</v>
+        <v>270104</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>22.2</v>
+        <v>20.4</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
+          <t>20日均线自身向上</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>量能温和(0.8-1.2倍)；近5日上涨日成交量大于下跌日</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,89 +1017,89 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>251.69</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-18.28</v>
+        <v>48.8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2.76</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-43.44</v>
+        <v>-10.18</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-47.13</v>
+        <v>-22.27</v>
       </c>
       <c r="H5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>空头排列</t>
+        <v>1.12</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>震荡交织</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>-28.52</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>空头持续</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>多头持续</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>超卖区间</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-34.48</v>
+        <v>48.2</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.61</v>
       </c>
       <c r="P5" t="n">
-        <v>19.34</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>203.01</v>
+        <v>44.76</v>
       </c>
       <c r="R5" t="n">
-        <v>352.09</v>
+        <v>48.49</v>
       </c>
       <c r="S5" t="n">
-        <v>492.41</v>
+        <v>62.57</v>
       </c>
       <c r="T5" t="n">
-        <v>236.1</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>0</v>
+        <v>43.45</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>730204</v>
+        <v>270504</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>无明显信号</t>
+          <t>股价站上20日均线；距20日均线0-5%(不过度偏离)</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>量能放大(1.2-1.5倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
+          <t>近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1137,28 +1137,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>242.52</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>10.64</v>
+        <v>228.09</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-6.9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-17.51</v>
+        <v>-34.42</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-14.77</v>
+        <v>-39</v>
       </c>
       <c r="H6" t="n">
-        <v>2.54</v>
+        <v>1.43</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -1171,45 +1171,45 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-17.02</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>10.7</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-8.550000000000001</v>
+        <v>-23.63</v>
       </c>
       <c r="P6" t="n">
-        <v>14.03</v>
+        <v>12.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>208.48</v>
+        <v>200.41</v>
       </c>
       <c r="R6" t="n">
-        <v>247.07</v>
+        <v>274.87</v>
       </c>
       <c r="S6" t="n">
-        <v>320.82</v>
+        <v>442</v>
       </c>
       <c r="T6" t="n">
-        <v>204.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
+        <v>228.09</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>16.7</v>
+        <v>14.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>明显放量(1.5-2.5倍)；换手率处于近20日60-90分位(活跃但不过热)</t>
+          <t>量能温和(0.8-1.2倍)；换手率处于近20日60-90分位(活跃但不过热)；近5日上涨日成交量大于下跌日</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1257,28 +1257,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.13</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>9.449999999999999</v>
+        <v>53.29</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-6.92</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-13.11</v>
+        <v>-26.16</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-18.79</v>
+        <v>-35.25</v>
       </c>
       <c r="H7" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -1291,49 +1291,49 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-1.93</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>多头持续</t>
+        <v>-12.98</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>空头持续</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>中性</t>
+        <v>20.3</v>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>超卖区间</t>
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-4.15</v>
+        <v>-15.37</v>
       </c>
       <c r="P7" t="n">
-        <v>11.94</v>
+        <v>12.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>19.49</v>
+        <v>46.56</v>
       </c>
       <c r="R7" t="n">
-        <v>22.56</v>
+        <v>61.24</v>
       </c>
       <c r="S7" t="n">
-        <v>29.4</v>
+        <v>87.45</v>
       </c>
       <c r="T7" t="n">
-        <v>19.08</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
+        <v>53.25</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>270303</v>
+        <v>270107</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1377,28 +1377,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55.1</v>
+        <v>41.39</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-2.2</v>
+        <v>-7.69</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-24.47</v>
+        <v>-33.49</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-33.49</v>
+        <v>-32.44</v>
       </c>
       <c r="H8" t="n">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -1411,15 +1411,15 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-11.39</v>
+        <v>-16.2</v>
       </c>
       <c r=